--- a/finance/麦安研营业统计_格式化模板.xlsx
+++ b/finance/麦安研营业统计_格式化模板.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wadec\Documents\projects\mainyan-auto\finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C84442FE-F465-4039-B81D-7ECD85DD8B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80FE23C8-5F18-4824-AC5E-B4154F7746DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026年6月东方宝泰店营业额明细统计表" sheetId="1" r:id="rId1"/>
@@ -670,7 +670,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -740,59 +740,17 @@
     <xf numFmtId="177" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="11" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="177" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -827,30 +785,6 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="17" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="17" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="17" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -860,20 +794,8 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -882,6 +804,75 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="11" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="17" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="17" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="17" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1152,19 +1143,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BE199"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.88671875" style="17" customWidth="1"/>
     <col min="2" max="2" width="11.88671875" style="17" customWidth="1"/>
-    <col min="3" max="4" width="9" style="17"/>
+    <col min="3" max="4" width="10.33203125" style="17"/>
     <col min="5" max="5" width="9" style="17" customWidth="1"/>
-    <col min="6" max="6" width="9" style="17"/>
+    <col min="6" max="6" width="10.33203125" style="17"/>
     <col min="7" max="7" width="9.88671875" style="17" customWidth="1"/>
     <col min="8" max="8" width="12.5546875" style="17" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="10.33203125" style="17"/>
+    <col min="9" max="9" width="12.44140625" style="17" customWidth="1"/>
     <col min="10" max="10" width="9.88671875" style="17" customWidth="1"/>
     <col min="11" max="11" width="11.77734375" style="17" customWidth="1"/>
-    <col min="12" max="12" width="9.21875" style="17"/>
+    <col min="12" max="12" width="10.33203125" style="17"/>
     <col min="13" max="13" width="14" style="17" customWidth="1"/>
     <col min="14" max="14" width="14.5546875" style="17" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="9.88671875" style="17" hidden="1" customWidth="1"/>
@@ -1172,24 +1163,22 @@
     <col min="17" max="19" width="11.109375" style="17" hidden="1" customWidth="1"/>
     <col min="20" max="20" width="15.33203125" style="17" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="13.33203125" style="17" hidden="1" customWidth="1"/>
-    <col min="22" max="23" width="9" style="17"/>
+    <col min="22" max="23" width="10.33203125" style="17"/>
     <col min="24" max="24" width="17.6640625" style="17" hidden="1" customWidth="1"/>
-    <col min="25" max="26" width="9" style="17"/>
+    <col min="25" max="26" width="10.33203125" style="17"/>
     <col min="27" max="27" width="12.21875" style="17" hidden="1" customWidth="1"/>
     <col min="28" max="28" width="9" style="17" hidden="1" customWidth="1"/>
-    <col min="29" max="32" width="9" style="17"/>
+    <col min="29" max="32" width="10.33203125" style="17"/>
     <col min="33" max="33" width="13.6640625" style="17" customWidth="1"/>
-    <col min="34" max="35" width="9" style="17"/>
+    <col min="34" max="35" width="10.33203125" style="17"/>
     <col min="36" max="36" width="17.109375" style="17" customWidth="1"/>
     <col min="37" max="37" width="14" style="17" customWidth="1"/>
     <col min="38" max="38" width="16.33203125" style="17" hidden="1" customWidth="1"/>
-    <col min="39" max="39" width="9" style="17"/>
-    <col min="40" max="40" width="11.109375" style="17"/>
-    <col min="41" max="41" width="9" style="17"/>
+    <col min="39" max="41" width="10.33203125" style="17"/>
     <col min="42" max="42" width="11.21875" style="17" customWidth="1"/>
     <col min="43" max="43" width="17.21875" style="17" customWidth="1"/>
     <col min="44" max="44" width="15.109375" style="17" hidden="1" customWidth="1"/>
-    <col min="45" max="45" width="9" style="17"/>
+    <col min="45" max="45" width="10.33203125" style="17"/>
     <col min="46" max="46" width="15.5546875" style="17" customWidth="1"/>
     <col min="47" max="47" width="10" style="17" customWidth="1"/>
     <col min="48" max="48" width="11.5546875" style="17" hidden="1" customWidth="1"/>
@@ -1201,381 +1190,381 @@
     <col min="54" max="54" width="13.33203125" style="17" hidden="1" customWidth="1"/>
     <col min="55" max="55" width="12.21875" style="17" customWidth="1"/>
     <col min="56" max="56" width="9.88671875" style="17" customWidth="1"/>
-    <col min="57" max="16384" width="9" style="17"/>
+    <col min="57" max="16384" width="10.33203125" style="17"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:57" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="50" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
-      <c r="M1" s="23"/>
-      <c r="N1" s="23"/>
-      <c r="O1" s="23"/>
-      <c r="P1" s="23"/>
-      <c r="Q1" s="23"/>
-      <c r="R1" s="23"/>
-      <c r="S1" s="23"/>
-      <c r="T1" s="23"/>
-      <c r="U1" s="23"/>
-      <c r="V1" s="23"/>
-      <c r="W1" s="23"/>
-      <c r="X1" s="23"/>
-      <c r="Y1" s="23"/>
-      <c r="Z1" s="23"/>
-      <c r="AA1" s="23"/>
-      <c r="AB1" s="23"/>
-      <c r="AC1" s="23"/>
-      <c r="AD1" s="23"/>
-      <c r="AE1" s="23"/>
-      <c r="AF1" s="23"/>
-      <c r="AG1" s="23"/>
-      <c r="AH1" s="23"/>
-      <c r="AI1" s="23"/>
-      <c r="AJ1" s="23"/>
-      <c r="AK1" s="23"/>
-      <c r="AL1" s="23"/>
-      <c r="AM1" s="23"/>
-      <c r="AN1" s="23"/>
-      <c r="AO1" s="23"/>
-      <c r="AP1" s="23"/>
-      <c r="AQ1" s="23"/>
-      <c r="AR1" s="23"/>
-      <c r="AS1" s="23"/>
-      <c r="AT1" s="23"/>
-      <c r="AU1" s="23"/>
-      <c r="AV1" s="23"/>
-      <c r="AW1" s="23"/>
-      <c r="AX1" s="23"/>
-      <c r="AY1" s="23"/>
-      <c r="AZ1" s="23"/>
-      <c r="BA1" s="23"/>
-      <c r="BB1" s="23"/>
-      <c r="BC1" s="23"/>
-      <c r="BD1" s="23"/>
-      <c r="BE1" s="23"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
+      <c r="N1" s="50"/>
+      <c r="O1" s="50"/>
+      <c r="P1" s="50"/>
+      <c r="Q1" s="50"/>
+      <c r="R1" s="50"/>
+      <c r="S1" s="50"/>
+      <c r="T1" s="50"/>
+      <c r="U1" s="50"/>
+      <c r="V1" s="50"/>
+      <c r="W1" s="50"/>
+      <c r="X1" s="50"/>
+      <c r="Y1" s="50"/>
+      <c r="Z1" s="50"/>
+      <c r="AA1" s="50"/>
+      <c r="AB1" s="50"/>
+      <c r="AC1" s="50"/>
+      <c r="AD1" s="50"/>
+      <c r="AE1" s="50"/>
+      <c r="AF1" s="50"/>
+      <c r="AG1" s="50"/>
+      <c r="AH1" s="50"/>
+      <c r="AI1" s="50"/>
+      <c r="AJ1" s="50"/>
+      <c r="AK1" s="50"/>
+      <c r="AL1" s="50"/>
+      <c r="AM1" s="50"/>
+      <c r="AN1" s="50"/>
+      <c r="AO1" s="50"/>
+      <c r="AP1" s="50"/>
+      <c r="AQ1" s="50"/>
+      <c r="AR1" s="50"/>
+      <c r="AS1" s="50"/>
+      <c r="AT1" s="50"/>
+      <c r="AU1" s="50"/>
+      <c r="AV1" s="50"/>
+      <c r="AW1" s="50"/>
+      <c r="AX1" s="50"/>
+      <c r="AY1" s="50"/>
+      <c r="AZ1" s="50"/>
+      <c r="BA1" s="50"/>
+      <c r="BB1" s="50"/>
+      <c r="BC1" s="50"/>
+      <c r="BD1" s="50"/>
+      <c r="BE1" s="50"/>
     </row>
     <row r="2" spans="1:57" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="27" t="s">
+      <c r="A2" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27" t="s">
+      <c r="C2" s="45"/>
+      <c r="D2" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="27" t="s">
+      <c r="E2" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="27" t="s">
+      <c r="F2" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="28" t="s">
+      <c r="G2" s="48" t="s">
         <v>107</v>
       </c>
-      <c r="H2" s="29" t="s">
+      <c r="H2" s="55" t="s">
         <v>88</v>
       </c>
-      <c r="I2" s="30" t="s">
+      <c r="I2" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="30"/>
-      <c r="O2" s="30"/>
-      <c r="P2" s="30"/>
-      <c r="Q2" s="30"/>
-      <c r="R2" s="30"/>
-      <c r="S2" s="30"/>
-      <c r="T2" s="30"/>
-      <c r="U2" s="30"/>
-      <c r="V2" s="30"/>
-      <c r="W2" s="30"/>
-      <c r="X2" s="30"/>
-      <c r="Y2" s="30"/>
-      <c r="Z2" s="30"/>
-      <c r="AA2" s="30"/>
-      <c r="AB2" s="31"/>
-      <c r="AC2" s="31"/>
-      <c r="AD2" s="32" t="s">
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="51"/>
+      <c r="N2" s="51"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="51"/>
+      <c r="Q2" s="51"/>
+      <c r="R2" s="51"/>
+      <c r="S2" s="51"/>
+      <c r="T2" s="51"/>
+      <c r="U2" s="51"/>
+      <c r="V2" s="51"/>
+      <c r="W2" s="51"/>
+      <c r="X2" s="51"/>
+      <c r="Y2" s="51"/>
+      <c r="Z2" s="51"/>
+      <c r="AA2" s="51"/>
+      <c r="AB2" s="25"/>
+      <c r="AC2" s="25"/>
+      <c r="AD2" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="AE2" s="32"/>
-      <c r="AF2" s="32"/>
-      <c r="AG2" s="32"/>
-      <c r="AH2" s="32"/>
-      <c r="AI2" s="32"/>
-      <c r="AJ2" s="32"/>
-      <c r="AK2" s="32"/>
-      <c r="AL2" s="32"/>
-      <c r="AM2" s="32"/>
-      <c r="AN2" s="32"/>
-      <c r="AO2" s="32"/>
-      <c r="AP2" s="32"/>
-      <c r="AQ2" s="32"/>
-      <c r="AR2" s="32"/>
-      <c r="AS2" s="32"/>
-      <c r="AT2" s="32"/>
-      <c r="AU2" s="32"/>
-      <c r="AV2" s="32"/>
-      <c r="AW2" s="32"/>
-      <c r="AX2" s="32"/>
-      <c r="AY2" s="32"/>
-      <c r="AZ2" s="32"/>
-      <c r="BA2" s="32"/>
-      <c r="BB2" s="32"/>
-      <c r="BC2" s="33" t="s">
+      <c r="AE2" s="52"/>
+      <c r="AF2" s="52"/>
+      <c r="AG2" s="52"/>
+      <c r="AH2" s="52"/>
+      <c r="AI2" s="52"/>
+      <c r="AJ2" s="52"/>
+      <c r="AK2" s="52"/>
+      <c r="AL2" s="52"/>
+      <c r="AM2" s="52"/>
+      <c r="AN2" s="52"/>
+      <c r="AO2" s="52"/>
+      <c r="AP2" s="52"/>
+      <c r="AQ2" s="52"/>
+      <c r="AR2" s="52"/>
+      <c r="AS2" s="52"/>
+      <c r="AT2" s="52"/>
+      <c r="AU2" s="52"/>
+      <c r="AV2" s="52"/>
+      <c r="AW2" s="52"/>
+      <c r="AX2" s="52"/>
+      <c r="AY2" s="52"/>
+      <c r="AZ2" s="52"/>
+      <c r="BA2" s="52"/>
+      <c r="BB2" s="52"/>
+      <c r="BC2" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="BD2" s="34" t="s">
+      <c r="BD2" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="BE2" s="27" t="s">
+      <c r="BE2" s="45" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:57" s="18" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="27"/>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="27" t="s">
+      <c r="A3" s="45"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="27"/>
-      <c r="K3" s="27"/>
-      <c r="L3" s="27"/>
-      <c r="M3" s="27"/>
-      <c r="N3" s="27"/>
-      <c r="O3" s="35"/>
-      <c r="P3" s="35"/>
-      <c r="Q3" s="27" t="s">
+      <c r="J3" s="45"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="45"/>
+      <c r="M3" s="45"/>
+      <c r="N3" s="45"/>
+      <c r="O3" s="23"/>
+      <c r="P3" s="23"/>
+      <c r="Q3" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="R3" s="27"/>
-      <c r="S3" s="27"/>
-      <c r="T3" s="27"/>
-      <c r="U3" s="27"/>
-      <c r="V3" s="28" t="s">
+      <c r="R3" s="45"/>
+      <c r="S3" s="45"/>
+      <c r="T3" s="45"/>
+      <c r="U3" s="45"/>
+      <c r="V3" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="W3" s="28" t="s">
+      <c r="W3" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="X3" s="35" t="s">
+      <c r="X3" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="Y3" s="36" t="s">
+      <c r="Y3" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="Z3" s="36" t="s">
+      <c r="Z3" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="AA3" s="27" t="s">
+      <c r="AA3" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="AB3" s="27" t="s">
+      <c r="AB3" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="AC3" s="27" t="s">
+      <c r="AC3" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="AD3" s="37" t="s">
+      <c r="AD3" s="53" t="s">
         <v>19</v>
       </c>
-      <c r="AE3" s="37"/>
-      <c r="AF3" s="37"/>
-      <c r="AG3" s="37"/>
-      <c r="AH3" s="37"/>
-      <c r="AI3" s="37"/>
-      <c r="AJ3" s="37"/>
-      <c r="AK3" s="37"/>
-      <c r="AL3" s="37"/>
-      <c r="AM3" s="37" t="s">
+      <c r="AE3" s="53"/>
+      <c r="AF3" s="53"/>
+      <c r="AG3" s="53"/>
+      <c r="AH3" s="53"/>
+      <c r="AI3" s="53"/>
+      <c r="AJ3" s="53"/>
+      <c r="AK3" s="53"/>
+      <c r="AL3" s="53"/>
+      <c r="AM3" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="AN3" s="37"/>
-      <c r="AO3" s="37"/>
-      <c r="AP3" s="37"/>
-      <c r="AQ3" s="37"/>
-      <c r="AR3" s="37"/>
-      <c r="AS3" s="37" t="s">
+      <c r="AN3" s="53"/>
+      <c r="AO3" s="53"/>
+      <c r="AP3" s="53"/>
+      <c r="AQ3" s="53"/>
+      <c r="AR3" s="53"/>
+      <c r="AS3" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="AT3" s="37"/>
-      <c r="AU3" s="37"/>
-      <c r="AV3" s="38"/>
-      <c r="AW3" s="39" t="s">
+      <c r="AT3" s="53"/>
+      <c r="AU3" s="53"/>
+      <c r="AV3" s="26"/>
+      <c r="AW3" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="AX3" s="39"/>
-      <c r="AY3" s="37" t="s">
+      <c r="AX3" s="54"/>
+      <c r="AY3" s="53" t="s">
         <v>90</v>
       </c>
-      <c r="AZ3" s="37"/>
-      <c r="BA3" s="37"/>
-      <c r="BB3" s="37"/>
-      <c r="BC3" s="33"/>
-      <c r="BD3" s="34"/>
-      <c r="BE3" s="27"/>
+      <c r="AZ3" s="53"/>
+      <c r="BA3" s="53"/>
+      <c r="BB3" s="53"/>
+      <c r="BC3" s="46"/>
+      <c r="BD3" s="47"/>
+      <c r="BE3" s="45"/>
     </row>
     <row r="4" spans="1:57" s="18" customFormat="1" ht="87" x14ac:dyDescent="0.25">
-      <c r="A4" s="27"/>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="35" t="s">
+      <c r="A4" s="45"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="35" t="s">
+      <c r="J4" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="K4" s="40" t="s">
+      <c r="K4" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="L4" s="41" t="s">
+      <c r="L4" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="M4" s="41" t="s">
+      <c r="M4" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="N4" s="42" t="s">
+      <c r="N4" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="O4" s="43" t="s">
+      <c r="O4" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="P4" s="43" t="s">
+      <c r="P4" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="Q4" s="43" t="s">
+      <c r="Q4" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="R4" s="43" t="s">
+      <c r="R4" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="S4" s="44" t="s">
+      <c r="S4" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="T4" s="44" t="s">
+      <c r="T4" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="U4" s="45" t="s">
+      <c r="U4" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="V4" s="28"/>
-      <c r="W4" s="28"/>
-      <c r="X4" s="46" t="s">
+      <c r="V4" s="48"/>
+      <c r="W4" s="48"/>
+      <c r="X4" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="Y4" s="36"/>
-      <c r="Z4" s="36"/>
-      <c r="AA4" s="27"/>
-      <c r="AB4" s="27"/>
-      <c r="AC4" s="27"/>
-      <c r="AD4" s="40" t="s">
+      <c r="Y4" s="49"/>
+      <c r="Z4" s="49"/>
+      <c r="AA4" s="45"/>
+      <c r="AB4" s="45"/>
+      <c r="AC4" s="45"/>
+      <c r="AD4" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="AE4" s="40" t="s">
+      <c r="AE4" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="AF4" s="40" t="s">
+      <c r="AF4" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="AG4" s="40" t="s">
+      <c r="AG4" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="AH4" s="40" t="s">
+      <c r="AH4" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="AI4" s="40" t="s">
+      <c r="AI4" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="AJ4" s="40" t="s">
+      <c r="AJ4" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="AK4" s="47" t="s">
+      <c r="AK4" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="AL4" s="48" t="s">
+      <c r="AL4" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="AM4" s="40" t="s">
+      <c r="AM4" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="AN4" s="40" t="s">
+      <c r="AN4" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="AO4" s="40" t="s">
+      <c r="AO4" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="AP4" s="40" t="s">
+      <c r="AP4" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="AQ4" s="49" t="s">
+      <c r="AQ4" s="35" t="s">
         <v>100</v>
       </c>
-      <c r="AR4" s="48" t="s">
+      <c r="AR4" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="AS4" s="41" t="s">
+      <c r="AS4" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="AT4" s="41" t="s">
+      <c r="AT4" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="AU4" s="41" t="s">
+      <c r="AU4" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="AV4" s="42" t="s">
+      <c r="AV4" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="AW4" s="40" t="s">
+      <c r="AW4" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="AX4" s="48" t="s">
+      <c r="AX4" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="AY4" s="40" t="s">
+      <c r="AY4" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="AZ4" s="40" t="s">
+      <c r="AZ4" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="BA4" s="49" t="s">
+      <c r="BA4" s="35" t="s">
         <v>105</v>
       </c>
-      <c r="BB4" s="48" t="s">
+      <c r="BB4" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="BC4" s="33"/>
-      <c r="BD4" s="34"/>
-      <c r="BE4" s="27"/>
+      <c r="BC4" s="46"/>
+      <c r="BD4" s="47"/>
+      <c r="BE4" s="45"/>
     </row>
     <row r="5" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="35">
+      <c r="A5" s="23">
         <f t="shared" ref="A5:A36" si="0">ROW()-4</f>
         <v>1</v>
       </c>
@@ -1585,96 +1574,96 @@
       <c r="C5" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="D5" s="50">
+      <c r="D5" s="36">
         <f>F5-E5</f>
         <v>0</v>
       </c>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51"/>
-      <c r="J5" s="51"/>
-      <c r="K5" s="50">
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="37"/>
+      <c r="I5" s="37"/>
+      <c r="J5" s="37"/>
+      <c r="K5" s="59">
         <f>I5-J5</f>
         <v>0</v>
       </c>
-      <c r="L5" s="52"/>
-      <c r="M5" s="53">
+      <c r="L5" s="41"/>
+      <c r="M5" s="59">
         <f t="shared" ref="M5:M35" si="1">K5-L5</f>
         <v>0</v>
       </c>
-      <c r="N5" s="51"/>
-      <c r="O5" s="51"/>
-      <c r="P5" s="51"/>
-      <c r="Q5" s="51"/>
-      <c r="R5" s="50">
+      <c r="N5" s="41"/>
+      <c r="O5" s="41"/>
+      <c r="P5" s="41"/>
+      <c r="Q5" s="41"/>
+      <c r="R5" s="59">
         <f t="shared" ref="R5:R35" si="2">P5-Q5</f>
         <v>0</v>
       </c>
-      <c r="S5" s="52"/>
-      <c r="T5" s="53">
+      <c r="S5" s="41"/>
+      <c r="T5" s="59">
         <f t="shared" ref="T5:T35" si="3">R5-S5</f>
         <v>0</v>
       </c>
-      <c r="U5" s="52"/>
-      <c r="V5" s="51"/>
-      <c r="W5" s="51"/>
-      <c r="X5" s="51"/>
-      <c r="Y5" s="51"/>
-      <c r="Z5" s="51"/>
-      <c r="AA5" s="51"/>
-      <c r="AB5" s="51"/>
-      <c r="AC5" s="51"/>
-      <c r="AD5" s="54"/>
-      <c r="AE5" s="54"/>
-      <c r="AF5" s="51"/>
-      <c r="AG5" s="51"/>
-      <c r="AH5" s="51"/>
-      <c r="AI5" s="51"/>
-      <c r="AJ5" s="51"/>
-      <c r="AK5" s="50">
+      <c r="U5" s="41"/>
+      <c r="V5" s="41"/>
+      <c r="W5" s="41"/>
+      <c r="X5" s="41"/>
+      <c r="Y5" s="41"/>
+      <c r="Z5" s="41"/>
+      <c r="AA5" s="41"/>
+      <c r="AB5" s="41"/>
+      <c r="AC5" s="41"/>
+      <c r="AD5" s="60"/>
+      <c r="AE5" s="60"/>
+      <c r="AF5" s="41"/>
+      <c r="AG5" s="41"/>
+      <c r="AH5" s="41"/>
+      <c r="AI5" s="41"/>
+      <c r="AJ5" s="41"/>
+      <c r="AK5" s="59">
         <f>AE5+AF5-AG5-AH5-AI5-AJ5</f>
         <v>0</v>
       </c>
-      <c r="AL5" s="51"/>
-      <c r="AM5" s="55"/>
-      <c r="AN5" s="51"/>
-      <c r="AO5" s="51"/>
-      <c r="AP5" s="56"/>
-      <c r="AQ5" s="50">
+      <c r="AL5" s="41"/>
+      <c r="AM5" s="41"/>
+      <c r="AN5" s="41"/>
+      <c r="AO5" s="41"/>
+      <c r="AP5" s="61"/>
+      <c r="AQ5" s="59">
         <f t="shared" ref="AQ5:AQ26" si="4">AM5-AN5-AO5-AP5</f>
         <v>0</v>
       </c>
-      <c r="AR5" s="51"/>
-      <c r="AS5" s="51"/>
-      <c r="AT5" s="51"/>
-      <c r="AU5" s="50">
+      <c r="AR5" s="41"/>
+      <c r="AS5" s="41"/>
+      <c r="AT5" s="41"/>
+      <c r="AU5" s="59">
         <f t="shared" ref="AU5:AU35" si="5">AS5-AT5</f>
         <v>0</v>
       </c>
-      <c r="AV5" s="51"/>
-      <c r="AW5" s="51"/>
-      <c r="AX5" s="51"/>
-      <c r="AY5" s="57"/>
-      <c r="AZ5" s="51"/>
-      <c r="BA5" s="50">
+      <c r="AV5" s="41"/>
+      <c r="AW5" s="41"/>
+      <c r="AX5" s="41"/>
+      <c r="AY5" s="61"/>
+      <c r="AZ5" s="41"/>
+      <c r="BA5" s="59">
         <f t="shared" ref="BA5:BA35" si="6">AY5-AZ5</f>
         <v>0</v>
       </c>
-      <c r="BB5" s="51"/>
-      <c r="BC5" s="58">
+      <c r="BB5" s="41"/>
+      <c r="BC5" s="62">
         <f t="shared" ref="BC5:BC35" si="7">F5+M5+T5+AK5+AQ5+AU5+AW5+BA5</f>
         <v>0</v>
       </c>
-      <c r="BD5" s="59">
+      <c r="BD5" s="63">
         <f t="shared" ref="BD5:BD35" si="8">F5+K5+R5+AD5+AM5+AS5+AW5+AY5</f>
         <v>0</v>
       </c>
-      <c r="BE5" s="51"/>
+      <c r="BE5" s="37"/>
     </row>
     <row r="6" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="35">
+      <c r="A6" s="23">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -1684,96 +1673,96 @@
       <c r="C6" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="D6" s="50">
+      <c r="D6" s="36">
         <f t="shared" ref="D6:D35" si="9">F6-E6</f>
         <v>0</v>
       </c>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51"/>
-      <c r="K6" s="50">
+      <c r="E6" s="37"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="37"/>
+      <c r="H6" s="37"/>
+      <c r="I6" s="37"/>
+      <c r="J6" s="37"/>
+      <c r="K6" s="59">
         <f t="shared" ref="K6:K35" si="10">I6-J6</f>
         <v>0</v>
       </c>
-      <c r="L6" s="52"/>
-      <c r="M6" s="53">
+      <c r="L6" s="41"/>
+      <c r="M6" s="59">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N6" s="51"/>
-      <c r="O6" s="51"/>
-      <c r="P6" s="51"/>
-      <c r="Q6" s="51"/>
-      <c r="R6" s="50">
+      <c r="N6" s="41"/>
+      <c r="O6" s="41"/>
+      <c r="P6" s="41"/>
+      <c r="Q6" s="41"/>
+      <c r="R6" s="59">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S6" s="52"/>
-      <c r="T6" s="53">
+      <c r="S6" s="41"/>
+      <c r="T6" s="59">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U6" s="52"/>
-      <c r="V6" s="51"/>
-      <c r="W6" s="51"/>
-      <c r="X6" s="51"/>
-      <c r="Y6" s="51"/>
-      <c r="Z6" s="51"/>
-      <c r="AA6" s="51"/>
-      <c r="AB6" s="51"/>
-      <c r="AC6" s="51"/>
-      <c r="AD6" s="51"/>
-      <c r="AE6" s="51"/>
-      <c r="AF6" s="51"/>
-      <c r="AG6" s="51"/>
-      <c r="AH6" s="51"/>
-      <c r="AI6" s="51"/>
-      <c r="AJ6" s="51"/>
-      <c r="AK6" s="50">
+      <c r="U6" s="41"/>
+      <c r="V6" s="41"/>
+      <c r="W6" s="41"/>
+      <c r="X6" s="41"/>
+      <c r="Y6" s="41"/>
+      <c r="Z6" s="41"/>
+      <c r="AA6" s="41"/>
+      <c r="AB6" s="41"/>
+      <c r="AC6" s="41"/>
+      <c r="AD6" s="41"/>
+      <c r="AE6" s="41"/>
+      <c r="AF6" s="41"/>
+      <c r="AG6" s="41"/>
+      <c r="AH6" s="41"/>
+      <c r="AI6" s="41"/>
+      <c r="AJ6" s="41"/>
+      <c r="AK6" s="59">
         <f t="shared" ref="AK6:AK35" si="11">AE6+AF6-AG6-AH6-AI6-AJ6</f>
         <v>0</v>
       </c>
-      <c r="AL6" s="51"/>
-      <c r="AM6" s="55"/>
-      <c r="AN6" s="51"/>
-      <c r="AO6" s="51"/>
-      <c r="AP6" s="56"/>
-      <c r="AQ6" s="50">
+      <c r="AL6" s="41"/>
+      <c r="AM6" s="41"/>
+      <c r="AN6" s="41"/>
+      <c r="AO6" s="41"/>
+      <c r="AP6" s="61"/>
+      <c r="AQ6" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AR6" s="51"/>
-      <c r="AS6" s="51"/>
-      <c r="AT6" s="51"/>
-      <c r="AU6" s="50">
+      <c r="AR6" s="41"/>
+      <c r="AS6" s="41"/>
+      <c r="AT6" s="41"/>
+      <c r="AU6" s="59">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV6" s="51"/>
-      <c r="AW6" s="51"/>
-      <c r="AX6" s="51"/>
-      <c r="AY6" s="57"/>
-      <c r="AZ6" s="51"/>
-      <c r="BA6" s="50">
+      <c r="AV6" s="41"/>
+      <c r="AW6" s="41"/>
+      <c r="AX6" s="41"/>
+      <c r="AY6" s="61"/>
+      <c r="AZ6" s="41"/>
+      <c r="BA6" s="59">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB6" s="51"/>
-      <c r="BC6" s="58">
+      <c r="BB6" s="41"/>
+      <c r="BC6" s="62">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD6" s="59">
+      <c r="BD6" s="63">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BE6" s="51"/>
+      <c r="BE6" s="37"/>
     </row>
     <row r="7" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="35">
+      <c r="A7" s="23">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -1783,96 +1772,96 @@
       <c r="C7" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="50">
+      <c r="D7" s="36">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="E7" s="51"/>
-      <c r="F7" s="51"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="51"/>
-      <c r="I7" s="51"/>
-      <c r="J7" s="51"/>
-      <c r="K7" s="50">
+      <c r="E7" s="37"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="37"/>
+      <c r="I7" s="37"/>
+      <c r="J7" s="37"/>
+      <c r="K7" s="59">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="L7" s="52"/>
-      <c r="M7" s="53">
+      <c r="L7" s="41"/>
+      <c r="M7" s="59">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N7" s="51"/>
-      <c r="O7" s="51"/>
-      <c r="P7" s="51"/>
-      <c r="Q7" s="51"/>
-      <c r="R7" s="50">
+      <c r="N7" s="41"/>
+      <c r="O7" s="41"/>
+      <c r="P7" s="41"/>
+      <c r="Q7" s="41"/>
+      <c r="R7" s="59">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S7" s="52"/>
-      <c r="T7" s="53">
+      <c r="S7" s="41"/>
+      <c r="T7" s="59">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U7" s="52"/>
-      <c r="V7" s="51"/>
-      <c r="W7" s="51"/>
-      <c r="X7" s="51"/>
-      <c r="Y7" s="51"/>
-      <c r="Z7" s="51"/>
-      <c r="AA7" s="51"/>
-      <c r="AB7" s="51"/>
-      <c r="AC7" s="51"/>
-      <c r="AD7" s="51"/>
-      <c r="AE7" s="51"/>
-      <c r="AF7" s="51"/>
-      <c r="AG7" s="51"/>
-      <c r="AH7" s="51"/>
-      <c r="AI7" s="51"/>
-      <c r="AJ7" s="51"/>
-      <c r="AK7" s="50">
+      <c r="U7" s="41"/>
+      <c r="V7" s="41"/>
+      <c r="W7" s="41"/>
+      <c r="X7" s="41"/>
+      <c r="Y7" s="41"/>
+      <c r="Z7" s="41"/>
+      <c r="AA7" s="41"/>
+      <c r="AB7" s="41"/>
+      <c r="AC7" s="41"/>
+      <c r="AD7" s="41"/>
+      <c r="AE7" s="41"/>
+      <c r="AF7" s="41"/>
+      <c r="AG7" s="41"/>
+      <c r="AH7" s="41"/>
+      <c r="AI7" s="41"/>
+      <c r="AJ7" s="41"/>
+      <c r="AK7" s="59">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AL7" s="51"/>
-      <c r="AM7" s="55"/>
-      <c r="AN7" s="56"/>
-      <c r="AO7" s="56"/>
-      <c r="AP7" s="56"/>
-      <c r="AQ7" s="50">
+      <c r="AL7" s="41"/>
+      <c r="AM7" s="41"/>
+      <c r="AN7" s="61"/>
+      <c r="AO7" s="61"/>
+      <c r="AP7" s="61"/>
+      <c r="AQ7" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AR7" s="51"/>
-      <c r="AS7" s="51"/>
-      <c r="AT7" s="51"/>
-      <c r="AU7" s="50">
+      <c r="AR7" s="41"/>
+      <c r="AS7" s="41"/>
+      <c r="AT7" s="41"/>
+      <c r="AU7" s="59">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV7" s="51"/>
-      <c r="AW7" s="51"/>
-      <c r="AX7" s="51"/>
-      <c r="AY7" s="57"/>
-      <c r="AZ7" s="51"/>
-      <c r="BA7" s="50">
+      <c r="AV7" s="41"/>
+      <c r="AW7" s="41"/>
+      <c r="AX7" s="41"/>
+      <c r="AY7" s="61"/>
+      <c r="AZ7" s="41"/>
+      <c r="BA7" s="59">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB7" s="51"/>
-      <c r="BC7" s="58">
+      <c r="BB7" s="41"/>
+      <c r="BC7" s="62">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD7" s="59">
+      <c r="BD7" s="63">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BE7" s="60"/>
+      <c r="BE7" s="38"/>
     </row>
     <row r="8" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="35">
+      <c r="A8" s="23">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -1882,96 +1871,96 @@
       <c r="C8" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="D8" s="50">
+      <c r="D8" s="36">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="E8" s="51"/>
-      <c r="F8" s="51"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="51"/>
-      <c r="J8" s="51"/>
-      <c r="K8" s="50">
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="37"/>
+      <c r="I8" s="37"/>
+      <c r="J8" s="37"/>
+      <c r="K8" s="59">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="L8" s="52"/>
-      <c r="M8" s="53">
+      <c r="L8" s="41"/>
+      <c r="M8" s="59">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N8" s="51"/>
-      <c r="O8" s="51"/>
-      <c r="P8" s="51"/>
-      <c r="Q8" s="51"/>
-      <c r="R8" s="50">
+      <c r="N8" s="41"/>
+      <c r="O8" s="41"/>
+      <c r="P8" s="41"/>
+      <c r="Q8" s="41"/>
+      <c r="R8" s="59">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S8" s="52"/>
-      <c r="T8" s="53">
+      <c r="S8" s="41"/>
+      <c r="T8" s="59">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U8" s="52"/>
-      <c r="V8" s="51"/>
-      <c r="W8" s="51"/>
-      <c r="X8" s="51"/>
-      <c r="Y8" s="51"/>
-      <c r="Z8" s="51"/>
-      <c r="AA8" s="51"/>
-      <c r="AB8" s="51"/>
-      <c r="AC8" s="51"/>
-      <c r="AD8" s="51"/>
-      <c r="AE8" s="51"/>
-      <c r="AF8" s="51"/>
-      <c r="AG8" s="51"/>
-      <c r="AH8" s="51"/>
-      <c r="AI8" s="51"/>
-      <c r="AJ8" s="51"/>
-      <c r="AK8" s="50">
+      <c r="U8" s="41"/>
+      <c r="V8" s="41"/>
+      <c r="W8" s="41"/>
+      <c r="X8" s="41"/>
+      <c r="Y8" s="41"/>
+      <c r="Z8" s="41"/>
+      <c r="AA8" s="41"/>
+      <c r="AB8" s="41"/>
+      <c r="AC8" s="41"/>
+      <c r="AD8" s="41"/>
+      <c r="AE8" s="41"/>
+      <c r="AF8" s="41"/>
+      <c r="AG8" s="41"/>
+      <c r="AH8" s="41"/>
+      <c r="AI8" s="41"/>
+      <c r="AJ8" s="41"/>
+      <c r="AK8" s="59">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AL8" s="51"/>
-      <c r="AM8" s="51"/>
-      <c r="AN8" s="51"/>
-      <c r="AO8" s="51"/>
-      <c r="AP8" s="56"/>
-      <c r="AQ8" s="50">
+      <c r="AL8" s="41"/>
+      <c r="AM8" s="41"/>
+      <c r="AN8" s="41"/>
+      <c r="AO8" s="41"/>
+      <c r="AP8" s="61"/>
+      <c r="AQ8" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AR8" s="51"/>
-      <c r="AS8" s="51"/>
-      <c r="AT8" s="51"/>
-      <c r="AU8" s="50">
+      <c r="AR8" s="41"/>
+      <c r="AS8" s="41"/>
+      <c r="AT8" s="41"/>
+      <c r="AU8" s="59">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV8" s="51"/>
-      <c r="AW8" s="51"/>
-      <c r="AX8" s="51"/>
-      <c r="AY8" s="57"/>
-      <c r="AZ8" s="56"/>
-      <c r="BA8" s="50">
+      <c r="AV8" s="41"/>
+      <c r="AW8" s="41"/>
+      <c r="AX8" s="41"/>
+      <c r="AY8" s="61"/>
+      <c r="AZ8" s="61"/>
+      <c r="BA8" s="59">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB8" s="51"/>
-      <c r="BC8" s="58">
+      <c r="BB8" s="41"/>
+      <c r="BC8" s="62">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD8" s="59">
+      <c r="BD8" s="63">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BE8" s="61"/>
+      <c r="BE8" s="39"/>
     </row>
     <row r="9" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="35">
+      <c r="A9" s="23">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -1981,96 +1970,96 @@
       <c r="C9" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="D9" s="50">
+      <c r="D9" s="36">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="E9" s="51"/>
-      <c r="F9" s="51"/>
-      <c r="G9" s="51"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="51"/>
-      <c r="J9" s="51"/>
-      <c r="K9" s="50">
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="37"/>
+      <c r="H9" s="37"/>
+      <c r="I9" s="37"/>
+      <c r="J9" s="37"/>
+      <c r="K9" s="59">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="L9" s="52"/>
-      <c r="M9" s="53">
+      <c r="L9" s="41"/>
+      <c r="M9" s="59">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N9" s="51"/>
-      <c r="O9" s="51"/>
-      <c r="P9" s="51"/>
-      <c r="Q9" s="51"/>
-      <c r="R9" s="50">
+      <c r="N9" s="41"/>
+      <c r="O9" s="41"/>
+      <c r="P9" s="41"/>
+      <c r="Q9" s="41"/>
+      <c r="R9" s="59">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S9" s="52"/>
-      <c r="T9" s="53">
+      <c r="S9" s="41"/>
+      <c r="T9" s="59">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U9" s="52"/>
-      <c r="V9" s="51"/>
-      <c r="W9" s="51"/>
-      <c r="X9" s="51"/>
-      <c r="Y9" s="51"/>
-      <c r="Z9" s="51"/>
-      <c r="AA9" s="51"/>
-      <c r="AB9" s="51"/>
-      <c r="AC9" s="51"/>
-      <c r="AD9" s="51"/>
-      <c r="AE9" s="51"/>
-      <c r="AF9" s="51"/>
-      <c r="AG9" s="51"/>
-      <c r="AH9" s="51"/>
-      <c r="AI9" s="51"/>
-      <c r="AJ9" s="51"/>
-      <c r="AK9" s="50">
+      <c r="U9" s="41"/>
+      <c r="V9" s="41"/>
+      <c r="W9" s="41"/>
+      <c r="X9" s="41"/>
+      <c r="Y9" s="41"/>
+      <c r="Z9" s="41"/>
+      <c r="AA9" s="41"/>
+      <c r="AB9" s="41"/>
+      <c r="AC9" s="41"/>
+      <c r="AD9" s="41"/>
+      <c r="AE9" s="41"/>
+      <c r="AF9" s="41"/>
+      <c r="AG9" s="41"/>
+      <c r="AH9" s="41"/>
+      <c r="AI9" s="41"/>
+      <c r="AJ9" s="41"/>
+      <c r="AK9" s="59">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AL9" s="51"/>
-      <c r="AM9" s="51"/>
-      <c r="AN9" s="51"/>
-      <c r="AO9" s="51"/>
-      <c r="AP9" s="51"/>
-      <c r="AQ9" s="50">
+      <c r="AL9" s="41"/>
+      <c r="AM9" s="41"/>
+      <c r="AN9" s="41"/>
+      <c r="AO9" s="41"/>
+      <c r="AP9" s="41"/>
+      <c r="AQ9" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AR9" s="51"/>
-      <c r="AS9" s="51"/>
-      <c r="AT9" s="51"/>
-      <c r="AU9" s="50">
+      <c r="AR9" s="41"/>
+      <c r="AS9" s="41"/>
+      <c r="AT9" s="41"/>
+      <c r="AU9" s="59">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV9" s="51"/>
-      <c r="AW9" s="51"/>
-      <c r="AX9" s="51"/>
-      <c r="AY9" s="57"/>
-      <c r="AZ9" s="56"/>
-      <c r="BA9" s="50">
+      <c r="AV9" s="41"/>
+      <c r="AW9" s="41"/>
+      <c r="AX9" s="41"/>
+      <c r="AY9" s="61"/>
+      <c r="AZ9" s="61"/>
+      <c r="BA9" s="59">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB9" s="51"/>
-      <c r="BC9" s="58">
+      <c r="BB9" s="41"/>
+      <c r="BC9" s="62">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD9" s="59">
+      <c r="BD9" s="63">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BE9" s="51"/>
+      <c r="BE9" s="37"/>
     </row>
     <row r="10" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="35">
+      <c r="A10" s="23">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
@@ -2080,96 +2069,96 @@
       <c r="C10" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="50">
+      <c r="D10" s="36">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="E10" s="51"/>
-      <c r="F10" s="51"/>
-      <c r="G10" s="51"/>
-      <c r="H10" s="51"/>
-      <c r="I10" s="62"/>
-      <c r="J10" s="51"/>
-      <c r="K10" s="50">
+      <c r="E10" s="37"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="37"/>
+      <c r="H10" s="37"/>
+      <c r="I10" s="40"/>
+      <c r="J10" s="37"/>
+      <c r="K10" s="59">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="L10" s="52"/>
-      <c r="M10" s="53">
+      <c r="L10" s="41"/>
+      <c r="M10" s="59">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N10" s="51"/>
-      <c r="O10" s="51"/>
-      <c r="P10" s="51"/>
-      <c r="Q10" s="51"/>
-      <c r="R10" s="50">
+      <c r="N10" s="41"/>
+      <c r="O10" s="41"/>
+      <c r="P10" s="41"/>
+      <c r="Q10" s="41"/>
+      <c r="R10" s="59">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S10" s="52"/>
-      <c r="T10" s="53">
+      <c r="S10" s="41"/>
+      <c r="T10" s="59">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U10" s="63"/>
-      <c r="V10" s="51"/>
-      <c r="W10" s="51"/>
-      <c r="X10" s="51"/>
-      <c r="Y10" s="51"/>
-      <c r="Z10" s="51"/>
-      <c r="AA10" s="51"/>
-      <c r="AB10" s="51"/>
-      <c r="AC10" s="51"/>
-      <c r="AD10" s="51"/>
-      <c r="AE10" s="51"/>
-      <c r="AF10" s="51"/>
-      <c r="AG10" s="51"/>
-      <c r="AH10" s="51"/>
-      <c r="AI10" s="51"/>
-      <c r="AJ10" s="51"/>
-      <c r="AK10" s="50">
+      <c r="U10" s="64"/>
+      <c r="V10" s="41"/>
+      <c r="W10" s="41"/>
+      <c r="X10" s="41"/>
+      <c r="Y10" s="41"/>
+      <c r="Z10" s="41"/>
+      <c r="AA10" s="41"/>
+      <c r="AB10" s="41"/>
+      <c r="AC10" s="41"/>
+      <c r="AD10" s="41"/>
+      <c r="AE10" s="41"/>
+      <c r="AF10" s="41"/>
+      <c r="AG10" s="41"/>
+      <c r="AH10" s="41"/>
+      <c r="AI10" s="41"/>
+      <c r="AJ10" s="41"/>
+      <c r="AK10" s="59">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AL10" s="51"/>
-      <c r="AM10" s="51"/>
-      <c r="AN10" s="51"/>
-      <c r="AO10" s="51"/>
-      <c r="AP10" s="51"/>
-      <c r="AQ10" s="50">
+      <c r="AL10" s="41"/>
+      <c r="AM10" s="41"/>
+      <c r="AN10" s="41"/>
+      <c r="AO10" s="41"/>
+      <c r="AP10" s="41"/>
+      <c r="AQ10" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AR10" s="51"/>
-      <c r="AS10" s="51"/>
-      <c r="AT10" s="51"/>
-      <c r="AU10" s="50">
+      <c r="AR10" s="41"/>
+      <c r="AS10" s="41"/>
+      <c r="AT10" s="41"/>
+      <c r="AU10" s="59">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV10" s="51"/>
-      <c r="AW10" s="51"/>
-      <c r="AX10" s="51"/>
-      <c r="AY10" s="57"/>
-      <c r="AZ10" s="51"/>
-      <c r="BA10" s="50">
+      <c r="AV10" s="41"/>
+      <c r="AW10" s="41"/>
+      <c r="AX10" s="41"/>
+      <c r="AY10" s="61"/>
+      <c r="AZ10" s="41"/>
+      <c r="BA10" s="59">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB10" s="51"/>
-      <c r="BC10" s="58">
+      <c r="BB10" s="41"/>
+      <c r="BC10" s="62">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD10" s="59">
+      <c r="BD10" s="63">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BE10" s="51"/>
+      <c r="BE10" s="37"/>
     </row>
     <row r="11" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="35">
+      <c r="A11" s="23">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
@@ -2179,96 +2168,96 @@
       <c r="C11" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="D11" s="50">
+      <c r="D11" s="36">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="E11" s="51"/>
-      <c r="F11" s="51"/>
-      <c r="G11" s="51"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="51"/>
-      <c r="J11" s="51"/>
-      <c r="K11" s="50">
+      <c r="E11" s="37"/>
+      <c r="F11" s="37"/>
+      <c r="G11" s="37"/>
+      <c r="H11" s="37"/>
+      <c r="I11" s="37"/>
+      <c r="J11" s="37"/>
+      <c r="K11" s="59">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="L11" s="52"/>
-      <c r="M11" s="53">
+      <c r="L11" s="41"/>
+      <c r="M11" s="59">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N11" s="51"/>
-      <c r="O11" s="51"/>
-      <c r="P11" s="51"/>
-      <c r="Q11" s="51"/>
-      <c r="R11" s="50">
+      <c r="N11" s="41"/>
+      <c r="O11" s="41"/>
+      <c r="P11" s="41"/>
+      <c r="Q11" s="41"/>
+      <c r="R11" s="59">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S11" s="52"/>
-      <c r="T11" s="53">
+      <c r="S11" s="41"/>
+      <c r="T11" s="59">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U11" s="63"/>
-      <c r="V11" s="51"/>
-      <c r="W11" s="51"/>
-      <c r="X11" s="51"/>
-      <c r="Y11" s="51"/>
-      <c r="Z11" s="51"/>
-      <c r="AA11" s="51"/>
-      <c r="AB11" s="51"/>
-      <c r="AC11" s="51"/>
-      <c r="AD11" s="51"/>
-      <c r="AE11" s="51"/>
-      <c r="AF11" s="51"/>
-      <c r="AG11" s="51"/>
-      <c r="AH11" s="51"/>
-      <c r="AI11" s="51"/>
-      <c r="AJ11" s="51"/>
-      <c r="AK11" s="50">
+      <c r="U11" s="64"/>
+      <c r="V11" s="41"/>
+      <c r="W11" s="41"/>
+      <c r="X11" s="41"/>
+      <c r="Y11" s="41"/>
+      <c r="Z11" s="41"/>
+      <c r="AA11" s="41"/>
+      <c r="AB11" s="41"/>
+      <c r="AC11" s="41"/>
+      <c r="AD11" s="41"/>
+      <c r="AE11" s="41"/>
+      <c r="AF11" s="41"/>
+      <c r="AG11" s="41"/>
+      <c r="AH11" s="41"/>
+      <c r="AI11" s="41"/>
+      <c r="AJ11" s="41"/>
+      <c r="AK11" s="59">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AL11" s="51"/>
-      <c r="AM11" s="55"/>
-      <c r="AN11" s="51"/>
-      <c r="AO11" s="51"/>
-      <c r="AP11" s="56"/>
-      <c r="AQ11" s="50">
+      <c r="AL11" s="41"/>
+      <c r="AM11" s="41"/>
+      <c r="AN11" s="41"/>
+      <c r="AO11" s="41"/>
+      <c r="AP11" s="61"/>
+      <c r="AQ11" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AR11" s="51"/>
-      <c r="AS11" s="51"/>
-      <c r="AT11" s="51"/>
-      <c r="AU11" s="50">
+      <c r="AR11" s="41"/>
+      <c r="AS11" s="41"/>
+      <c r="AT11" s="41"/>
+      <c r="AU11" s="59">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV11" s="51"/>
-      <c r="AW11" s="51"/>
-      <c r="AX11" s="51"/>
-      <c r="AY11" s="57"/>
-      <c r="AZ11" s="51"/>
-      <c r="BA11" s="50">
+      <c r="AV11" s="41"/>
+      <c r="AW11" s="41"/>
+      <c r="AX11" s="41"/>
+      <c r="AY11" s="61"/>
+      <c r="AZ11" s="41"/>
+      <c r="BA11" s="59">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB11" s="51"/>
-      <c r="BC11" s="58">
+      <c r="BB11" s="41"/>
+      <c r="BC11" s="62">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD11" s="59">
+      <c r="BD11" s="63">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BE11" s="51"/>
+      <c r="BE11" s="37"/>
     </row>
     <row r="12" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="35">
+      <c r="A12" s="23">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -2278,96 +2267,96 @@
       <c r="C12" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="50">
+      <c r="D12" s="36">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="E12" s="51"/>
-      <c r="F12" s="51"/>
-      <c r="G12" s="51"/>
-      <c r="H12" s="51"/>
-      <c r="I12" s="51"/>
-      <c r="J12" s="51"/>
-      <c r="K12" s="50">
+      <c r="E12" s="37"/>
+      <c r="F12" s="37"/>
+      <c r="G12" s="37"/>
+      <c r="H12" s="37"/>
+      <c r="I12" s="37"/>
+      <c r="J12" s="37"/>
+      <c r="K12" s="59">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="L12" s="52"/>
-      <c r="M12" s="53">
+      <c r="L12" s="41"/>
+      <c r="M12" s="59">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N12" s="51"/>
-      <c r="O12" s="51"/>
-      <c r="P12" s="51"/>
-      <c r="Q12" s="51"/>
-      <c r="R12" s="50">
+      <c r="N12" s="41"/>
+      <c r="O12" s="41"/>
+      <c r="P12" s="41"/>
+      <c r="Q12" s="41"/>
+      <c r="R12" s="59">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S12" s="52"/>
-      <c r="T12" s="53">
+      <c r="S12" s="41"/>
+      <c r="T12" s="59">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U12" s="63"/>
-      <c r="V12" s="51"/>
-      <c r="W12" s="51"/>
-      <c r="X12" s="51"/>
-      <c r="Y12" s="51"/>
-      <c r="Z12" s="51"/>
-      <c r="AA12" s="51"/>
-      <c r="AB12" s="51"/>
-      <c r="AC12" s="51"/>
-      <c r="AD12" s="51"/>
-      <c r="AE12" s="51"/>
-      <c r="AF12" s="51"/>
-      <c r="AG12" s="51"/>
-      <c r="AH12" s="51"/>
-      <c r="AI12" s="51"/>
-      <c r="AJ12" s="51"/>
-      <c r="AK12" s="50">
+      <c r="U12" s="64"/>
+      <c r="V12" s="41"/>
+      <c r="W12" s="41"/>
+      <c r="X12" s="41"/>
+      <c r="Y12" s="41"/>
+      <c r="Z12" s="41"/>
+      <c r="AA12" s="41"/>
+      <c r="AB12" s="41"/>
+      <c r="AC12" s="41"/>
+      <c r="AD12" s="41"/>
+      <c r="AE12" s="41"/>
+      <c r="AF12" s="41"/>
+      <c r="AG12" s="41"/>
+      <c r="AH12" s="41"/>
+      <c r="AI12" s="41"/>
+      <c r="AJ12" s="41"/>
+      <c r="AK12" s="59">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AL12" s="51"/>
-      <c r="AM12" s="55"/>
-      <c r="AN12" s="51"/>
-      <c r="AO12" s="51"/>
-      <c r="AP12" s="51"/>
-      <c r="AQ12" s="50">
+      <c r="AL12" s="41"/>
+      <c r="AM12" s="41"/>
+      <c r="AN12" s="41"/>
+      <c r="AO12" s="41"/>
+      <c r="AP12" s="41"/>
+      <c r="AQ12" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AR12" s="51"/>
-      <c r="AS12" s="51"/>
-      <c r="AT12" s="51"/>
-      <c r="AU12" s="50">
+      <c r="AR12" s="41"/>
+      <c r="AS12" s="41"/>
+      <c r="AT12" s="41"/>
+      <c r="AU12" s="59">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV12" s="51"/>
-      <c r="AW12" s="51"/>
-      <c r="AX12" s="51"/>
-      <c r="AY12" s="57"/>
-      <c r="AZ12" s="51"/>
-      <c r="BA12" s="50">
+      <c r="AV12" s="41"/>
+      <c r="AW12" s="41"/>
+      <c r="AX12" s="41"/>
+      <c r="AY12" s="61"/>
+      <c r="AZ12" s="41"/>
+      <c r="BA12" s="59">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB12" s="51"/>
-      <c r="BC12" s="58">
+      <c r="BB12" s="41"/>
+      <c r="BC12" s="62">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD12" s="59">
+      <c r="BD12" s="63">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BE12" s="51"/>
+      <c r="BE12" s="37"/>
     </row>
     <row r="13" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="35">
+      <c r="A13" s="23">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -2377,96 +2366,96 @@
       <c r="C13" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="D13" s="50">
+      <c r="D13" s="36">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="E13" s="51"/>
-      <c r="F13" s="51"/>
-      <c r="G13" s="51"/>
-      <c r="H13" s="51"/>
-      <c r="I13" s="51"/>
-      <c r="J13" s="51"/>
-      <c r="K13" s="50">
+      <c r="E13" s="37"/>
+      <c r="F13" s="37"/>
+      <c r="G13" s="37"/>
+      <c r="H13" s="37"/>
+      <c r="I13" s="37"/>
+      <c r="J13" s="37"/>
+      <c r="K13" s="59">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="L13" s="52"/>
-      <c r="M13" s="53">
+      <c r="L13" s="41"/>
+      <c r="M13" s="59">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N13" s="51"/>
-      <c r="O13" s="51"/>
-      <c r="P13" s="51"/>
-      <c r="Q13" s="51"/>
-      <c r="R13" s="50">
+      <c r="N13" s="41"/>
+      <c r="O13" s="41"/>
+      <c r="P13" s="41"/>
+      <c r="Q13" s="41"/>
+      <c r="R13" s="59">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S13" s="52"/>
-      <c r="T13" s="53">
+      <c r="S13" s="41"/>
+      <c r="T13" s="59">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U13" s="63"/>
-      <c r="V13" s="51"/>
-      <c r="W13" s="51"/>
-      <c r="X13" s="51"/>
-      <c r="Y13" s="51"/>
-      <c r="Z13" s="51"/>
-      <c r="AA13" s="51"/>
-      <c r="AB13" s="51"/>
-      <c r="AC13" s="51"/>
-      <c r="AD13" s="51"/>
-      <c r="AE13" s="51"/>
-      <c r="AF13" s="51"/>
-      <c r="AG13" s="51"/>
-      <c r="AH13" s="51"/>
-      <c r="AI13" s="51"/>
-      <c r="AJ13" s="51"/>
-      <c r="AK13" s="50">
+      <c r="U13" s="64"/>
+      <c r="V13" s="41"/>
+      <c r="W13" s="41"/>
+      <c r="X13" s="41"/>
+      <c r="Y13" s="41"/>
+      <c r="Z13" s="41"/>
+      <c r="AA13" s="41"/>
+      <c r="AB13" s="41"/>
+      <c r="AC13" s="41"/>
+      <c r="AD13" s="41"/>
+      <c r="AE13" s="41"/>
+      <c r="AF13" s="41"/>
+      <c r="AG13" s="41"/>
+      <c r="AH13" s="41"/>
+      <c r="AI13" s="41"/>
+      <c r="AJ13" s="41"/>
+      <c r="AK13" s="59">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AL13" s="51"/>
-      <c r="AM13" s="51"/>
-      <c r="AN13" s="51"/>
-      <c r="AO13" s="51"/>
-      <c r="AP13" s="51"/>
-      <c r="AQ13" s="50">
+      <c r="AL13" s="41"/>
+      <c r="AM13" s="41"/>
+      <c r="AN13" s="41"/>
+      <c r="AO13" s="41"/>
+      <c r="AP13" s="41"/>
+      <c r="AQ13" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AR13" s="51"/>
-      <c r="AS13" s="51"/>
-      <c r="AT13" s="51"/>
-      <c r="AU13" s="50">
+      <c r="AR13" s="41"/>
+      <c r="AS13" s="41"/>
+      <c r="AT13" s="41"/>
+      <c r="AU13" s="59">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV13" s="51"/>
-      <c r="AW13" s="51"/>
-      <c r="AX13" s="51"/>
-      <c r="AY13" s="57"/>
-      <c r="AZ13" s="51"/>
-      <c r="BA13" s="50">
+      <c r="AV13" s="41"/>
+      <c r="AW13" s="41"/>
+      <c r="AX13" s="41"/>
+      <c r="AY13" s="61"/>
+      <c r="AZ13" s="41"/>
+      <c r="BA13" s="59">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB13" s="51"/>
-      <c r="BC13" s="58">
+      <c r="BB13" s="41"/>
+      <c r="BC13" s="62">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD13" s="59">
+      <c r="BD13" s="63">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BE13" s="51"/>
+      <c r="BE13" s="37"/>
     </row>
     <row r="14" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="35">
+      <c r="A14" s="23">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -2476,96 +2465,96 @@
       <c r="C14" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="50">
+      <c r="D14" s="36">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="E14" s="51"/>
-      <c r="F14" s="51"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="51"/>
-      <c r="I14" s="51"/>
-      <c r="J14" s="51"/>
-      <c r="K14" s="50">
+      <c r="E14" s="37"/>
+      <c r="F14" s="37"/>
+      <c r="G14" s="37"/>
+      <c r="H14" s="37"/>
+      <c r="I14" s="37"/>
+      <c r="J14" s="37"/>
+      <c r="K14" s="59">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="L14" s="52"/>
-      <c r="M14" s="53">
+      <c r="L14" s="41"/>
+      <c r="M14" s="59">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N14" s="51"/>
-      <c r="O14" s="51"/>
-      <c r="P14" s="51"/>
-      <c r="Q14" s="51"/>
-      <c r="R14" s="50">
+      <c r="N14" s="41"/>
+      <c r="O14" s="41"/>
+      <c r="P14" s="41"/>
+      <c r="Q14" s="41"/>
+      <c r="R14" s="59">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S14" s="52"/>
-      <c r="T14" s="53">
+      <c r="S14" s="41"/>
+      <c r="T14" s="59">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U14" s="63"/>
-      <c r="V14" s="51"/>
-      <c r="W14" s="51"/>
-      <c r="X14" s="51"/>
-      <c r="Y14" s="51"/>
-      <c r="Z14" s="51"/>
-      <c r="AA14" s="51"/>
-      <c r="AB14" s="51"/>
-      <c r="AC14" s="51"/>
-      <c r="AD14" s="51"/>
-      <c r="AE14" s="51"/>
-      <c r="AF14" s="51"/>
-      <c r="AG14" s="51"/>
-      <c r="AH14" s="51"/>
-      <c r="AI14" s="51"/>
-      <c r="AJ14" s="51"/>
-      <c r="AK14" s="50">
+      <c r="U14" s="64"/>
+      <c r="V14" s="41"/>
+      <c r="W14" s="41"/>
+      <c r="X14" s="41"/>
+      <c r="Y14" s="41"/>
+      <c r="Z14" s="41"/>
+      <c r="AA14" s="41"/>
+      <c r="AB14" s="41"/>
+      <c r="AC14" s="41"/>
+      <c r="AD14" s="41"/>
+      <c r="AE14" s="41"/>
+      <c r="AF14" s="41"/>
+      <c r="AG14" s="41"/>
+      <c r="AH14" s="41"/>
+      <c r="AI14" s="41"/>
+      <c r="AJ14" s="41"/>
+      <c r="AK14" s="59">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AL14" s="51"/>
-      <c r="AM14" s="55"/>
-      <c r="AN14" s="51"/>
-      <c r="AO14" s="51"/>
-      <c r="AP14" s="51"/>
-      <c r="AQ14" s="50">
+      <c r="AL14" s="41"/>
+      <c r="AM14" s="41"/>
+      <c r="AN14" s="41"/>
+      <c r="AO14" s="41"/>
+      <c r="AP14" s="41"/>
+      <c r="AQ14" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AR14" s="51"/>
-      <c r="AS14" s="51"/>
-      <c r="AT14" s="51"/>
-      <c r="AU14" s="50">
+      <c r="AR14" s="41"/>
+      <c r="AS14" s="41"/>
+      <c r="AT14" s="41"/>
+      <c r="AU14" s="59">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV14" s="51"/>
-      <c r="AW14" s="51"/>
-      <c r="AX14" s="51"/>
-      <c r="AY14" s="57"/>
-      <c r="AZ14" s="51"/>
-      <c r="BA14" s="50">
+      <c r="AV14" s="41"/>
+      <c r="AW14" s="41"/>
+      <c r="AX14" s="41"/>
+      <c r="AY14" s="61"/>
+      <c r="AZ14" s="41"/>
+      <c r="BA14" s="59">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB14" s="51"/>
-      <c r="BC14" s="58">
+      <c r="BB14" s="41"/>
+      <c r="BC14" s="62">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD14" s="59">
+      <c r="BD14" s="63">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BE14" s="51"/>
+      <c r="BE14" s="37"/>
     </row>
     <row r="15" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="35">
+      <c r="A15" s="23">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
@@ -2575,96 +2564,96 @@
       <c r="C15" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="D15" s="50">
+      <c r="D15" s="36">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="E15" s="51"/>
-      <c r="F15" s="51"/>
-      <c r="G15" s="51"/>
-      <c r="H15" s="51"/>
-      <c r="I15" s="51"/>
-      <c r="J15" s="51"/>
-      <c r="K15" s="50">
+      <c r="E15" s="37"/>
+      <c r="F15" s="37"/>
+      <c r="G15" s="37"/>
+      <c r="H15" s="37"/>
+      <c r="I15" s="37"/>
+      <c r="J15" s="37"/>
+      <c r="K15" s="59">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="L15" s="52"/>
-      <c r="M15" s="53">
+      <c r="L15" s="41"/>
+      <c r="M15" s="59">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N15" s="51"/>
-      <c r="O15" s="51"/>
-      <c r="P15" s="51"/>
-      <c r="Q15" s="51"/>
-      <c r="R15" s="50">
+      <c r="N15" s="41"/>
+      <c r="O15" s="41"/>
+      <c r="P15" s="41"/>
+      <c r="Q15" s="41"/>
+      <c r="R15" s="59">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S15" s="52"/>
-      <c r="T15" s="53">
+      <c r="S15" s="41"/>
+      <c r="T15" s="59">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U15" s="63"/>
-      <c r="V15" s="51"/>
-      <c r="W15" s="51"/>
-      <c r="X15" s="51"/>
-      <c r="Y15" s="51"/>
-      <c r="Z15" s="51"/>
-      <c r="AA15" s="51"/>
-      <c r="AB15" s="51"/>
-      <c r="AC15" s="51"/>
-      <c r="AD15" s="51"/>
-      <c r="AE15" s="51"/>
-      <c r="AF15" s="51"/>
-      <c r="AG15" s="51"/>
-      <c r="AH15" s="51"/>
-      <c r="AI15" s="51"/>
-      <c r="AJ15" s="51"/>
-      <c r="AK15" s="50">
+      <c r="U15" s="64"/>
+      <c r="V15" s="41"/>
+      <c r="W15" s="41"/>
+      <c r="X15" s="41"/>
+      <c r="Y15" s="41"/>
+      <c r="Z15" s="41"/>
+      <c r="AA15" s="41"/>
+      <c r="AB15" s="41"/>
+      <c r="AC15" s="41"/>
+      <c r="AD15" s="41"/>
+      <c r="AE15" s="41"/>
+      <c r="AF15" s="41"/>
+      <c r="AG15" s="41"/>
+      <c r="AH15" s="41"/>
+      <c r="AI15" s="41"/>
+      <c r="AJ15" s="41"/>
+      <c r="AK15" s="59">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AL15" s="51"/>
-      <c r="AM15" s="51"/>
-      <c r="AN15" s="51"/>
-      <c r="AO15" s="51"/>
-      <c r="AP15" s="51"/>
-      <c r="AQ15" s="50">
+      <c r="AL15" s="41"/>
+      <c r="AM15" s="41"/>
+      <c r="AN15" s="41"/>
+      <c r="AO15" s="41"/>
+      <c r="AP15" s="41"/>
+      <c r="AQ15" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AR15" s="51"/>
-      <c r="AS15" s="51"/>
-      <c r="AT15" s="51"/>
-      <c r="AU15" s="50">
+      <c r="AR15" s="41"/>
+      <c r="AS15" s="41"/>
+      <c r="AT15" s="41"/>
+      <c r="AU15" s="59">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV15" s="51"/>
-      <c r="AW15" s="51"/>
-      <c r="AX15" s="51"/>
-      <c r="AY15" s="57"/>
-      <c r="AZ15" s="51"/>
-      <c r="BA15" s="50">
+      <c r="AV15" s="41"/>
+      <c r="AW15" s="41"/>
+      <c r="AX15" s="41"/>
+      <c r="AY15" s="61"/>
+      <c r="AZ15" s="41"/>
+      <c r="BA15" s="59">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB15" s="51"/>
-      <c r="BC15" s="58">
+      <c r="BB15" s="41"/>
+      <c r="BC15" s="62">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD15" s="59">
+      <c r="BD15" s="63">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BE15" s="51"/>
+      <c r="BE15" s="37"/>
     </row>
     <row r="16" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="35">
+      <c r="A16" s="23">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -2674,96 +2663,96 @@
       <c r="C16" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="50">
+      <c r="D16" s="36">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="E16" s="51"/>
-      <c r="F16" s="51"/>
-      <c r="G16" s="51"/>
-      <c r="H16" s="51"/>
-      <c r="I16" s="51"/>
-      <c r="J16" s="51"/>
-      <c r="K16" s="50">
+      <c r="E16" s="37"/>
+      <c r="F16" s="37"/>
+      <c r="G16" s="37"/>
+      <c r="H16" s="37"/>
+      <c r="I16" s="37"/>
+      <c r="J16" s="37"/>
+      <c r="K16" s="59">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="L16" s="52"/>
-      <c r="M16" s="53">
+      <c r="L16" s="41"/>
+      <c r="M16" s="59">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N16" s="51"/>
-      <c r="O16" s="51"/>
-      <c r="P16" s="51"/>
-      <c r="Q16" s="51"/>
-      <c r="R16" s="50">
+      <c r="N16" s="41"/>
+      <c r="O16" s="41"/>
+      <c r="P16" s="41"/>
+      <c r="Q16" s="41"/>
+      <c r="R16" s="59">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S16" s="52"/>
-      <c r="T16" s="53">
+      <c r="S16" s="41"/>
+      <c r="T16" s="59">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U16" s="63"/>
-      <c r="V16" s="51"/>
-      <c r="W16" s="51"/>
-      <c r="X16" s="51"/>
-      <c r="Y16" s="51"/>
-      <c r="Z16" s="51"/>
-      <c r="AA16" s="51"/>
-      <c r="AB16" s="51"/>
-      <c r="AC16" s="51"/>
-      <c r="AD16" s="51"/>
-      <c r="AE16" s="51"/>
-      <c r="AF16" s="51"/>
-      <c r="AG16" s="51"/>
-      <c r="AH16" s="51"/>
-      <c r="AI16" s="51"/>
-      <c r="AJ16" s="51"/>
-      <c r="AK16" s="50">
+      <c r="U16" s="64"/>
+      <c r="V16" s="41"/>
+      <c r="W16" s="41"/>
+      <c r="X16" s="41"/>
+      <c r="Y16" s="41"/>
+      <c r="Z16" s="41"/>
+      <c r="AA16" s="41"/>
+      <c r="AB16" s="41"/>
+      <c r="AC16" s="41"/>
+      <c r="AD16" s="41"/>
+      <c r="AE16" s="41"/>
+      <c r="AF16" s="41"/>
+      <c r="AG16" s="41"/>
+      <c r="AH16" s="41"/>
+      <c r="AI16" s="41"/>
+      <c r="AJ16" s="41"/>
+      <c r="AK16" s="59">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AL16" s="51"/>
-      <c r="AM16" s="51"/>
-      <c r="AN16" s="51"/>
-      <c r="AO16" s="51"/>
-      <c r="AP16" s="51"/>
-      <c r="AQ16" s="50">
+      <c r="AL16" s="41"/>
+      <c r="AM16" s="41"/>
+      <c r="AN16" s="41"/>
+      <c r="AO16" s="41"/>
+      <c r="AP16" s="41"/>
+      <c r="AQ16" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AR16" s="51"/>
-      <c r="AS16" s="51"/>
-      <c r="AT16" s="51"/>
-      <c r="AU16" s="50">
+      <c r="AR16" s="41"/>
+      <c r="AS16" s="41"/>
+      <c r="AT16" s="41"/>
+      <c r="AU16" s="59">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV16" s="51"/>
-      <c r="AW16" s="51"/>
-      <c r="AX16" s="51"/>
-      <c r="AY16" s="57"/>
-      <c r="AZ16" s="51"/>
-      <c r="BA16" s="50">
+      <c r="AV16" s="41"/>
+      <c r="AW16" s="41"/>
+      <c r="AX16" s="41"/>
+      <c r="AY16" s="61"/>
+      <c r="AZ16" s="41"/>
+      <c r="BA16" s="59">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB16" s="51"/>
-      <c r="BC16" s="58">
+      <c r="BB16" s="41"/>
+      <c r="BC16" s="62">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD16" s="59">
+      <c r="BD16" s="63">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BE16" s="51"/>
+      <c r="BE16" s="37"/>
     </row>
     <row r="17" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="35">
+      <c r="A17" s="23">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
@@ -2773,96 +2762,96 @@
       <c r="C17" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="D17" s="50">
+      <c r="D17" s="36">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="E17" s="51"/>
-      <c r="F17" s="51"/>
-      <c r="G17" s="51"/>
-      <c r="H17" s="51"/>
-      <c r="I17" s="51"/>
-      <c r="J17" s="51"/>
-      <c r="K17" s="50">
+      <c r="E17" s="37"/>
+      <c r="F17" s="37"/>
+      <c r="G17" s="37"/>
+      <c r="H17" s="37"/>
+      <c r="I17" s="37"/>
+      <c r="J17" s="37"/>
+      <c r="K17" s="59">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="L17" s="52"/>
-      <c r="M17" s="53">
+      <c r="L17" s="41"/>
+      <c r="M17" s="59">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N17" s="51"/>
-      <c r="O17" s="51"/>
-      <c r="P17" s="51"/>
-      <c r="Q17" s="51"/>
-      <c r="R17" s="50">
+      <c r="N17" s="41"/>
+      <c r="O17" s="41"/>
+      <c r="P17" s="41"/>
+      <c r="Q17" s="41"/>
+      <c r="R17" s="59">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S17" s="52"/>
-      <c r="T17" s="53">
+      <c r="S17" s="41"/>
+      <c r="T17" s="59">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U17" s="63"/>
-      <c r="V17" s="51"/>
-      <c r="W17" s="51"/>
-      <c r="X17" s="51"/>
-      <c r="Y17" s="51"/>
-      <c r="Z17" s="51"/>
-      <c r="AA17" s="51"/>
-      <c r="AB17" s="51"/>
-      <c r="AC17" s="51"/>
-      <c r="AD17" s="51"/>
-      <c r="AE17" s="51"/>
-      <c r="AF17" s="51"/>
-      <c r="AG17" s="51"/>
-      <c r="AH17" s="51"/>
-      <c r="AI17" s="51"/>
-      <c r="AJ17" s="51"/>
-      <c r="AK17" s="50">
+      <c r="U17" s="64"/>
+      <c r="V17" s="41"/>
+      <c r="W17" s="41"/>
+      <c r="X17" s="41"/>
+      <c r="Y17" s="41"/>
+      <c r="Z17" s="41"/>
+      <c r="AA17" s="41"/>
+      <c r="AB17" s="41"/>
+      <c r="AC17" s="41"/>
+      <c r="AD17" s="41"/>
+      <c r="AE17" s="41"/>
+      <c r="AF17" s="41"/>
+      <c r="AG17" s="41"/>
+      <c r="AH17" s="41"/>
+      <c r="AI17" s="41"/>
+      <c r="AJ17" s="41"/>
+      <c r="AK17" s="59">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AL17" s="51"/>
-      <c r="AM17" s="55"/>
-      <c r="AN17" s="51"/>
-      <c r="AO17" s="51"/>
-      <c r="AP17" s="51"/>
-      <c r="AQ17" s="50">
+      <c r="AL17" s="41"/>
+      <c r="AM17" s="41"/>
+      <c r="AN17" s="41"/>
+      <c r="AO17" s="41"/>
+      <c r="AP17" s="41"/>
+      <c r="AQ17" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AR17" s="51"/>
-      <c r="AS17" s="51"/>
-      <c r="AT17" s="51"/>
-      <c r="AU17" s="50">
+      <c r="AR17" s="41"/>
+      <c r="AS17" s="41"/>
+      <c r="AT17" s="41"/>
+      <c r="AU17" s="59">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV17" s="51"/>
-      <c r="AW17" s="51"/>
-      <c r="AX17" s="51"/>
-      <c r="AY17" s="57"/>
-      <c r="AZ17" s="51"/>
-      <c r="BA17" s="50">
+      <c r="AV17" s="41"/>
+      <c r="AW17" s="41"/>
+      <c r="AX17" s="41"/>
+      <c r="AY17" s="61"/>
+      <c r="AZ17" s="41"/>
+      <c r="BA17" s="59">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BB17" s="64"/>
-      <c r="BC17" s="58">
+      <c r="BC17" s="62">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD17" s="59">
+      <c r="BD17" s="63">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BE17" s="51"/>
+      <c r="BE17" s="37"/>
     </row>
     <row r="18" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="35">
+      <c r="A18" s="23">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
@@ -2872,96 +2861,96 @@
       <c r="C18" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="D18" s="50">
+      <c r="D18" s="36">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="E18" s="51"/>
-      <c r="F18" s="51"/>
-      <c r="G18" s="51"/>
-      <c r="H18" s="51"/>
-      <c r="I18" s="51"/>
-      <c r="J18" s="51"/>
-      <c r="K18" s="50">
+      <c r="E18" s="37"/>
+      <c r="F18" s="37"/>
+      <c r="G18" s="37"/>
+      <c r="H18" s="37"/>
+      <c r="I18" s="37"/>
+      <c r="J18" s="37"/>
+      <c r="K18" s="59">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="L18" s="52"/>
-      <c r="M18" s="53">
+      <c r="L18" s="41"/>
+      <c r="M18" s="59">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N18" s="65"/>
       <c r="O18" s="65"/>
-      <c r="P18" s="51"/>
-      <c r="Q18" s="51"/>
-      <c r="R18" s="50">
+      <c r="P18" s="41"/>
+      <c r="Q18" s="41"/>
+      <c r="R18" s="59">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S18" s="52"/>
-      <c r="T18" s="53">
+      <c r="S18" s="41"/>
+      <c r="T18" s="59">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U18" s="63"/>
-      <c r="V18" s="51"/>
-      <c r="W18" s="51"/>
-      <c r="X18" s="51"/>
-      <c r="Y18" s="51"/>
-      <c r="Z18" s="51"/>
-      <c r="AA18" s="51"/>
-      <c r="AB18" s="51"/>
-      <c r="AC18" s="51"/>
-      <c r="AD18" s="51"/>
-      <c r="AE18" s="51"/>
-      <c r="AF18" s="51"/>
-      <c r="AG18" s="51"/>
-      <c r="AH18" s="51"/>
-      <c r="AI18" s="51"/>
-      <c r="AJ18" s="51"/>
-      <c r="AK18" s="50">
+      <c r="U18" s="64"/>
+      <c r="V18" s="41"/>
+      <c r="W18" s="41"/>
+      <c r="X18" s="41"/>
+      <c r="Y18" s="41"/>
+      <c r="Z18" s="41"/>
+      <c r="AA18" s="41"/>
+      <c r="AB18" s="41"/>
+      <c r="AC18" s="41"/>
+      <c r="AD18" s="41"/>
+      <c r="AE18" s="41"/>
+      <c r="AF18" s="41"/>
+      <c r="AG18" s="41"/>
+      <c r="AH18" s="41"/>
+      <c r="AI18" s="41"/>
+      <c r="AJ18" s="41"/>
+      <c r="AK18" s="59">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AL18" s="51"/>
-      <c r="AM18" s="56"/>
-      <c r="AN18" s="51"/>
-      <c r="AO18" s="51"/>
-      <c r="AP18" s="51"/>
-      <c r="AQ18" s="50">
+      <c r="AL18" s="41"/>
+      <c r="AM18" s="61"/>
+      <c r="AN18" s="41"/>
+      <c r="AO18" s="41"/>
+      <c r="AP18" s="41"/>
+      <c r="AQ18" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AR18" s="51"/>
-      <c r="AS18" s="51"/>
-      <c r="AT18" s="51"/>
-      <c r="AU18" s="50">
+      <c r="AR18" s="41"/>
+      <c r="AS18" s="41"/>
+      <c r="AT18" s="41"/>
+      <c r="AU18" s="59">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV18" s="51"/>
-      <c r="AW18" s="51"/>
-      <c r="AX18" s="51"/>
-      <c r="AY18" s="57"/>
-      <c r="AZ18" s="51"/>
-      <c r="BA18" s="50">
+      <c r="AV18" s="41"/>
+      <c r="AW18" s="41"/>
+      <c r="AX18" s="41"/>
+      <c r="AY18" s="61"/>
+      <c r="AZ18" s="41"/>
+      <c r="BA18" s="59">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BB18" s="64"/>
-      <c r="BC18" s="58">
+      <c r="BC18" s="62">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD18" s="59">
+      <c r="BD18" s="63">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BE18" s="51"/>
+      <c r="BE18" s="37"/>
     </row>
     <row r="19" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="35">
+      <c r="A19" s="23">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
@@ -2971,96 +2960,96 @@
       <c r="C19" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="D19" s="50">
+      <c r="D19" s="36">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="E19" s="51"/>
-      <c r="F19" s="51"/>
-      <c r="G19" s="51"/>
-      <c r="H19" s="51"/>
-      <c r="I19" s="66"/>
-      <c r="J19" s="51"/>
-      <c r="K19" s="50">
+      <c r="E19" s="37"/>
+      <c r="F19" s="37"/>
+      <c r="G19" s="37"/>
+      <c r="H19" s="37"/>
+      <c r="I19" s="41"/>
+      <c r="J19" s="37"/>
+      <c r="K19" s="59">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="L19" s="52"/>
-      <c r="M19" s="53">
+      <c r="L19" s="41"/>
+      <c r="M19" s="59">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N19" s="51"/>
-      <c r="O19" s="51"/>
-      <c r="P19" s="51"/>
-      <c r="Q19" s="51"/>
-      <c r="R19" s="50">
+      <c r="N19" s="41"/>
+      <c r="O19" s="41"/>
+      <c r="P19" s="41"/>
+      <c r="Q19" s="41"/>
+      <c r="R19" s="59">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S19" s="52"/>
-      <c r="T19" s="53">
+      <c r="S19" s="41"/>
+      <c r="T19" s="59">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U19" s="63"/>
-      <c r="V19" s="51"/>
-      <c r="W19" s="51"/>
-      <c r="X19" s="51"/>
-      <c r="Y19" s="51"/>
-      <c r="Z19" s="51"/>
-      <c r="AA19" s="51"/>
-      <c r="AB19" s="51"/>
-      <c r="AC19" s="51"/>
-      <c r="AD19" s="51"/>
-      <c r="AE19" s="51"/>
-      <c r="AF19" s="51"/>
-      <c r="AG19" s="51"/>
-      <c r="AH19" s="51"/>
-      <c r="AI19" s="51"/>
-      <c r="AJ19" s="51"/>
-      <c r="AK19" s="50">
+      <c r="U19" s="64"/>
+      <c r="V19" s="41"/>
+      <c r="W19" s="41"/>
+      <c r="X19" s="41"/>
+      <c r="Y19" s="41"/>
+      <c r="Z19" s="41"/>
+      <c r="AA19" s="41"/>
+      <c r="AB19" s="41"/>
+      <c r="AC19" s="41"/>
+      <c r="AD19" s="41"/>
+      <c r="AE19" s="41"/>
+      <c r="AF19" s="41"/>
+      <c r="AG19" s="41"/>
+      <c r="AH19" s="41"/>
+      <c r="AI19" s="41"/>
+      <c r="AJ19" s="41"/>
+      <c r="AK19" s="59">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AL19" s="51"/>
-      <c r="AM19" s="55"/>
-      <c r="AN19" s="51"/>
-      <c r="AO19" s="51"/>
-      <c r="AP19" s="51"/>
-      <c r="AQ19" s="50">
+      <c r="AL19" s="41"/>
+      <c r="AM19" s="41"/>
+      <c r="AN19" s="41"/>
+      <c r="AO19" s="41"/>
+      <c r="AP19" s="41"/>
+      <c r="AQ19" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AR19" s="51"/>
-      <c r="AS19" s="51"/>
-      <c r="AT19" s="51"/>
-      <c r="AU19" s="50">
+      <c r="AR19" s="41"/>
+      <c r="AS19" s="41"/>
+      <c r="AT19" s="41"/>
+      <c r="AU19" s="59">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV19" s="51"/>
-      <c r="AW19" s="51"/>
-      <c r="AX19" s="51"/>
-      <c r="AY19" s="55"/>
-      <c r="AZ19" s="51"/>
-      <c r="BA19" s="50">
+      <c r="AV19" s="41"/>
+      <c r="AW19" s="41"/>
+      <c r="AX19" s="41"/>
+      <c r="AY19" s="41"/>
+      <c r="AZ19" s="41"/>
+      <c r="BA19" s="59">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BB19" s="64"/>
-      <c r="BC19" s="58">
+      <c r="BC19" s="62">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD19" s="59">
+      <c r="BD19" s="63">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BE19" s="51"/>
+      <c r="BE19" s="37"/>
     </row>
     <row r="20" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="35">
+      <c r="A20" s="23">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
@@ -3070,96 +3059,96 @@
       <c r="C20" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="50">
+      <c r="D20" s="36">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="E20" s="51"/>
-      <c r="F20" s="51"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="51"/>
-      <c r="I20" s="51"/>
-      <c r="J20" s="51"/>
-      <c r="K20" s="50">
+      <c r="E20" s="37"/>
+      <c r="F20" s="37"/>
+      <c r="G20" s="37"/>
+      <c r="H20" s="37"/>
+      <c r="I20" s="37"/>
+      <c r="J20" s="37"/>
+      <c r="K20" s="59">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="L20" s="52"/>
-      <c r="M20" s="53">
+      <c r="L20" s="41"/>
+      <c r="M20" s="59">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N20" s="51"/>
-      <c r="O20" s="51"/>
-      <c r="P20" s="51"/>
-      <c r="Q20" s="51"/>
-      <c r="R20" s="50">
+      <c r="N20" s="41"/>
+      <c r="O20" s="41"/>
+      <c r="P20" s="41"/>
+      <c r="Q20" s="41"/>
+      <c r="R20" s="59">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S20" s="52"/>
-      <c r="T20" s="53">
+      <c r="S20" s="41"/>
+      <c r="T20" s="59">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U20" s="63"/>
-      <c r="V20" s="51"/>
-      <c r="W20" s="51"/>
-      <c r="X20" s="51"/>
-      <c r="Y20" s="51"/>
-      <c r="Z20" s="51"/>
-      <c r="AA20" s="51"/>
-      <c r="AB20" s="51"/>
-      <c r="AC20" s="51"/>
-      <c r="AD20" s="51"/>
-      <c r="AE20" s="51"/>
-      <c r="AF20" s="51"/>
-      <c r="AG20" s="51"/>
-      <c r="AH20" s="51"/>
-      <c r="AI20" s="51"/>
-      <c r="AJ20" s="51"/>
-      <c r="AK20" s="50">
+      <c r="U20" s="64"/>
+      <c r="V20" s="41"/>
+      <c r="W20" s="41"/>
+      <c r="X20" s="41"/>
+      <c r="Y20" s="41"/>
+      <c r="Z20" s="41"/>
+      <c r="AA20" s="41"/>
+      <c r="AB20" s="41"/>
+      <c r="AC20" s="41"/>
+      <c r="AD20" s="41"/>
+      <c r="AE20" s="41"/>
+      <c r="AF20" s="41"/>
+      <c r="AG20" s="41"/>
+      <c r="AH20" s="41"/>
+      <c r="AI20" s="41"/>
+      <c r="AJ20" s="41"/>
+      <c r="AK20" s="59">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AL20" s="51"/>
-      <c r="AM20" s="55"/>
-      <c r="AN20" s="51"/>
-      <c r="AO20" s="51"/>
-      <c r="AP20" s="56"/>
-      <c r="AQ20" s="50">
+      <c r="AL20" s="41"/>
+      <c r="AM20" s="41"/>
+      <c r="AN20" s="41"/>
+      <c r="AO20" s="41"/>
+      <c r="AP20" s="61"/>
+      <c r="AQ20" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AR20" s="51"/>
-      <c r="AS20" s="51"/>
-      <c r="AT20" s="51"/>
-      <c r="AU20" s="50">
+      <c r="AR20" s="41"/>
+      <c r="AS20" s="41"/>
+      <c r="AT20" s="41"/>
+      <c r="AU20" s="59">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV20" s="51"/>
-      <c r="AW20" s="51"/>
-      <c r="AX20" s="51"/>
-      <c r="AY20" s="55"/>
-      <c r="AZ20" s="51"/>
-      <c r="BA20" s="50">
+      <c r="AV20" s="41"/>
+      <c r="AW20" s="41"/>
+      <c r="AX20" s="41"/>
+      <c r="AY20" s="41"/>
+      <c r="AZ20" s="41"/>
+      <c r="BA20" s="59">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BB20" s="64"/>
-      <c r="BC20" s="58">
+      <c r="BC20" s="62">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD20" s="59">
+      <c r="BD20" s="63">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BE20" s="51"/>
+      <c r="BE20" s="37"/>
     </row>
     <row r="21" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="35">
+      <c r="A21" s="23">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
@@ -3169,96 +3158,96 @@
       <c r="C21" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="D21" s="50">
+      <c r="D21" s="36">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="E21" s="51"/>
-      <c r="F21" s="51"/>
-      <c r="G21" s="51"/>
-      <c r="H21" s="51"/>
-      <c r="I21" s="51"/>
-      <c r="J21" s="51"/>
-      <c r="K21" s="50">
+      <c r="E21" s="37"/>
+      <c r="F21" s="37"/>
+      <c r="G21" s="37"/>
+      <c r="H21" s="37"/>
+      <c r="I21" s="37"/>
+      <c r="J21" s="37"/>
+      <c r="K21" s="59">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="L21" s="52"/>
-      <c r="M21" s="53">
+      <c r="L21" s="41"/>
+      <c r="M21" s="59">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N21" s="51"/>
-      <c r="O21" s="51"/>
-      <c r="P21" s="51"/>
-      <c r="Q21" s="51"/>
-      <c r="R21" s="50">
+      <c r="N21" s="41"/>
+      <c r="O21" s="41"/>
+      <c r="P21" s="41"/>
+      <c r="Q21" s="41"/>
+      <c r="R21" s="59">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S21" s="52"/>
-      <c r="T21" s="53">
+      <c r="S21" s="41"/>
+      <c r="T21" s="59">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U21" s="63"/>
-      <c r="V21" s="51"/>
-      <c r="W21" s="51"/>
-      <c r="X21" s="51"/>
-      <c r="Y21" s="51"/>
-      <c r="Z21" s="51"/>
-      <c r="AA21" s="51"/>
-      <c r="AB21" s="51"/>
-      <c r="AC21" s="51"/>
-      <c r="AD21" s="51"/>
-      <c r="AE21" s="51"/>
-      <c r="AF21" s="51"/>
-      <c r="AG21" s="51"/>
-      <c r="AH21" s="51"/>
-      <c r="AI21" s="51"/>
-      <c r="AJ21" s="51"/>
-      <c r="AK21" s="50">
+      <c r="U21" s="64"/>
+      <c r="V21" s="41"/>
+      <c r="W21" s="41"/>
+      <c r="X21" s="41"/>
+      <c r="Y21" s="41"/>
+      <c r="Z21" s="41"/>
+      <c r="AA21" s="41"/>
+      <c r="AB21" s="41"/>
+      <c r="AC21" s="41"/>
+      <c r="AD21" s="41"/>
+      <c r="AE21" s="41"/>
+      <c r="AF21" s="41"/>
+      <c r="AG21" s="41"/>
+      <c r="AH21" s="41"/>
+      <c r="AI21" s="41"/>
+      <c r="AJ21" s="41"/>
+      <c r="AK21" s="59">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AL21" s="51"/>
-      <c r="AM21" s="57"/>
-      <c r="AN21" s="51"/>
-      <c r="AO21" s="51"/>
-      <c r="AP21" s="56"/>
-      <c r="AQ21" s="50">
+      <c r="AL21" s="41"/>
+      <c r="AM21" s="61"/>
+      <c r="AN21" s="41"/>
+      <c r="AO21" s="41"/>
+      <c r="AP21" s="61"/>
+      <c r="AQ21" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AR21" s="51"/>
-      <c r="AS21" s="51"/>
-      <c r="AT21" s="51"/>
-      <c r="AU21" s="50">
+      <c r="AR21" s="41"/>
+      <c r="AS21" s="41"/>
+      <c r="AT21" s="41"/>
+      <c r="AU21" s="59">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV21" s="51"/>
-      <c r="AW21" s="51"/>
-      <c r="AX21" s="51"/>
-      <c r="AY21" s="57"/>
-      <c r="AZ21" s="51"/>
-      <c r="BA21" s="50">
+      <c r="AV21" s="41"/>
+      <c r="AW21" s="41"/>
+      <c r="AX21" s="41"/>
+      <c r="AY21" s="61"/>
+      <c r="AZ21" s="41"/>
+      <c r="BA21" s="59">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BB21" s="64"/>
-      <c r="BC21" s="58">
+      <c r="BC21" s="62">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD21" s="59">
+      <c r="BD21" s="63">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BE21" s="51"/>
+      <c r="BE21" s="37"/>
     </row>
     <row r="22" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="35">
+      <c r="A22" s="23">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
@@ -3268,96 +3257,96 @@
       <c r="C22" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="D22" s="50">
+      <c r="D22" s="36">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="E22" s="51"/>
-      <c r="F22" s="51"/>
-      <c r="G22" s="51"/>
-      <c r="H22" s="51"/>
-      <c r="I22" s="51"/>
-      <c r="J22" s="51"/>
-      <c r="K22" s="50">
+      <c r="E22" s="37"/>
+      <c r="F22" s="37"/>
+      <c r="G22" s="37"/>
+      <c r="H22" s="37"/>
+      <c r="I22" s="37"/>
+      <c r="J22" s="37"/>
+      <c r="K22" s="59">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="L22" s="52"/>
-      <c r="M22" s="53">
+      <c r="L22" s="41"/>
+      <c r="M22" s="59">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N22" s="51"/>
-      <c r="O22" s="51"/>
-      <c r="P22" s="51"/>
-      <c r="Q22" s="51"/>
-      <c r="R22" s="50">
+      <c r="N22" s="41"/>
+      <c r="O22" s="41"/>
+      <c r="P22" s="41"/>
+      <c r="Q22" s="41"/>
+      <c r="R22" s="59">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S22" s="52"/>
-      <c r="T22" s="53">
+      <c r="S22" s="41"/>
+      <c r="T22" s="59">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U22" s="63"/>
-      <c r="V22" s="51"/>
-      <c r="W22" s="51"/>
-      <c r="X22" s="51"/>
-      <c r="Y22" s="51"/>
-      <c r="Z22" s="51"/>
-      <c r="AA22" s="51"/>
-      <c r="AB22" s="51"/>
-      <c r="AC22" s="51"/>
-      <c r="AD22" s="51"/>
-      <c r="AE22" s="51"/>
-      <c r="AF22" s="51"/>
-      <c r="AG22" s="51"/>
-      <c r="AH22" s="51"/>
-      <c r="AI22" s="51"/>
-      <c r="AJ22" s="51"/>
-      <c r="AK22" s="50">
+      <c r="U22" s="64"/>
+      <c r="V22" s="41"/>
+      <c r="W22" s="41"/>
+      <c r="X22" s="41"/>
+      <c r="Y22" s="41"/>
+      <c r="Z22" s="41"/>
+      <c r="AA22" s="41"/>
+      <c r="AB22" s="41"/>
+      <c r="AC22" s="41"/>
+      <c r="AD22" s="41"/>
+      <c r="AE22" s="41"/>
+      <c r="AF22" s="41"/>
+      <c r="AG22" s="41"/>
+      <c r="AH22" s="41"/>
+      <c r="AI22" s="41"/>
+      <c r="AJ22" s="41"/>
+      <c r="AK22" s="59">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AL22" s="51"/>
-      <c r="AM22" s="55"/>
-      <c r="AN22" s="56"/>
-      <c r="AO22" s="51"/>
-      <c r="AP22" s="56"/>
-      <c r="AQ22" s="50">
+      <c r="AL22" s="41"/>
+      <c r="AM22" s="41"/>
+      <c r="AN22" s="61"/>
+      <c r="AO22" s="41"/>
+      <c r="AP22" s="61"/>
+      <c r="AQ22" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AR22" s="51"/>
-      <c r="AS22" s="51"/>
-      <c r="AT22" s="51"/>
-      <c r="AU22" s="50">
+      <c r="AR22" s="41"/>
+      <c r="AS22" s="41"/>
+      <c r="AT22" s="41"/>
+      <c r="AU22" s="59">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV22" s="51"/>
-      <c r="AW22" s="51"/>
-      <c r="AX22" s="51"/>
-      <c r="AY22" s="57"/>
-      <c r="AZ22" s="67"/>
-      <c r="BA22" s="50">
+      <c r="AV22" s="41"/>
+      <c r="AW22" s="41"/>
+      <c r="AX22" s="41"/>
+      <c r="AY22" s="61"/>
+      <c r="AZ22" s="66"/>
+      <c r="BA22" s="59">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB22" s="56"/>
-      <c r="BC22" s="58">
+      <c r="BB22" s="61"/>
+      <c r="BC22" s="62">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD22" s="59">
+      <c r="BD22" s="63">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BE22" s="68"/>
+      <c r="BE22" s="42"/>
     </row>
     <row r="23" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="35">
+      <c r="A23" s="23">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
@@ -3367,96 +3356,96 @@
       <c r="C23" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="D23" s="50">
+      <c r="D23" s="36">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="E23" s="51"/>
-      <c r="F23" s="51"/>
-      <c r="G23" s="51"/>
-      <c r="H23" s="51"/>
-      <c r="I23" s="51"/>
-      <c r="J23" s="51"/>
-      <c r="K23" s="50">
+      <c r="E23" s="37"/>
+      <c r="F23" s="37"/>
+      <c r="G23" s="37"/>
+      <c r="H23" s="37"/>
+      <c r="I23" s="37"/>
+      <c r="J23" s="37"/>
+      <c r="K23" s="59">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="L23" s="52"/>
-      <c r="M23" s="53">
+      <c r="L23" s="41"/>
+      <c r="M23" s="59">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N23" s="51"/>
-      <c r="O23" s="51"/>
-      <c r="P23" s="51"/>
-      <c r="Q23" s="51"/>
-      <c r="R23" s="50">
+      <c r="N23" s="41"/>
+      <c r="O23" s="41"/>
+      <c r="P23" s="41"/>
+      <c r="Q23" s="41"/>
+      <c r="R23" s="59">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S23" s="52"/>
-      <c r="T23" s="53">
+      <c r="S23" s="41"/>
+      <c r="T23" s="59">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U23" s="63"/>
-      <c r="V23" s="51"/>
-      <c r="W23" s="51"/>
-      <c r="X23" s="51"/>
-      <c r="Y23" s="51"/>
-      <c r="Z23" s="51"/>
-      <c r="AA23" s="51"/>
-      <c r="AB23" s="51"/>
-      <c r="AC23" s="51"/>
-      <c r="AD23" s="51"/>
-      <c r="AE23" s="51"/>
-      <c r="AF23" s="51"/>
-      <c r="AG23" s="51"/>
-      <c r="AH23" s="51"/>
-      <c r="AI23" s="51"/>
-      <c r="AJ23" s="51"/>
-      <c r="AK23" s="50">
+      <c r="U23" s="64"/>
+      <c r="V23" s="41"/>
+      <c r="W23" s="41"/>
+      <c r="X23" s="41"/>
+      <c r="Y23" s="41"/>
+      <c r="Z23" s="41"/>
+      <c r="AA23" s="41"/>
+      <c r="AB23" s="41"/>
+      <c r="AC23" s="41"/>
+      <c r="AD23" s="41"/>
+      <c r="AE23" s="41"/>
+      <c r="AF23" s="41"/>
+      <c r="AG23" s="41"/>
+      <c r="AH23" s="41"/>
+      <c r="AI23" s="41"/>
+      <c r="AJ23" s="41"/>
+      <c r="AK23" s="59">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AL23" s="51"/>
-      <c r="AM23" s="55"/>
-      <c r="AN23" s="51"/>
-      <c r="AO23" s="56"/>
-      <c r="AP23" s="51"/>
-      <c r="AQ23" s="50">
+      <c r="AL23" s="41"/>
+      <c r="AM23" s="41"/>
+      <c r="AN23" s="41"/>
+      <c r="AO23" s="61"/>
+      <c r="AP23" s="41"/>
+      <c r="AQ23" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AR23" s="51"/>
-      <c r="AS23" s="51"/>
-      <c r="AT23" s="51"/>
-      <c r="AU23" s="50">
+      <c r="AR23" s="41"/>
+      <c r="AS23" s="41"/>
+      <c r="AT23" s="41"/>
+      <c r="AU23" s="59">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV23" s="51"/>
-      <c r="AW23" s="51"/>
-      <c r="AX23" s="51"/>
-      <c r="AY23" s="57"/>
-      <c r="AZ23" s="56"/>
-      <c r="BA23" s="50">
+      <c r="AV23" s="41"/>
+      <c r="AW23" s="41"/>
+      <c r="AX23" s="41"/>
+      <c r="AY23" s="61"/>
+      <c r="AZ23" s="61"/>
+      <c r="BA23" s="59">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB23" s="51"/>
-      <c r="BC23" s="58">
+      <c r="BB23" s="41"/>
+      <c r="BC23" s="62">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD23" s="59">
+      <c r="BD23" s="63">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BE23" s="69"/>
+      <c r="BE23" s="43"/>
     </row>
     <row r="24" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="35">
+      <c r="A24" s="23">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
@@ -3466,96 +3455,96 @@
       <c r="C24" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="D24" s="50">
+      <c r="D24" s="36">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="E24" s="51"/>
-      <c r="F24" s="51"/>
-      <c r="G24" s="51"/>
-      <c r="H24" s="51"/>
-      <c r="I24" s="51"/>
-      <c r="J24" s="51"/>
-      <c r="K24" s="50">
+      <c r="E24" s="37"/>
+      <c r="F24" s="37"/>
+      <c r="G24" s="37"/>
+      <c r="H24" s="37"/>
+      <c r="I24" s="37"/>
+      <c r="J24" s="37"/>
+      <c r="K24" s="59">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="L24" s="52"/>
-      <c r="M24" s="53">
+      <c r="L24" s="41"/>
+      <c r="M24" s="59">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N24" s="51"/>
-      <c r="O24" s="51"/>
-      <c r="P24" s="51"/>
-      <c r="Q24" s="66"/>
-      <c r="R24" s="50">
+      <c r="N24" s="41"/>
+      <c r="O24" s="41"/>
+      <c r="P24" s="41"/>
+      <c r="Q24" s="41"/>
+      <c r="R24" s="59">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S24" s="52"/>
-      <c r="T24" s="53">
+      <c r="S24" s="41"/>
+      <c r="T24" s="59">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U24" s="63"/>
-      <c r="V24" s="51"/>
-      <c r="W24" s="51"/>
-      <c r="X24" s="51"/>
-      <c r="Y24" s="51"/>
-      <c r="Z24" s="51"/>
-      <c r="AA24" s="51"/>
-      <c r="AB24" s="51"/>
-      <c r="AC24" s="51"/>
-      <c r="AD24" s="51"/>
-      <c r="AE24" s="51"/>
-      <c r="AF24" s="51"/>
-      <c r="AG24" s="51"/>
-      <c r="AH24" s="51"/>
-      <c r="AI24" s="51"/>
-      <c r="AJ24" s="51"/>
-      <c r="AK24" s="50">
+      <c r="U24" s="64"/>
+      <c r="V24" s="41"/>
+      <c r="W24" s="41"/>
+      <c r="X24" s="41"/>
+      <c r="Y24" s="41"/>
+      <c r="Z24" s="41"/>
+      <c r="AA24" s="41"/>
+      <c r="AB24" s="41"/>
+      <c r="AC24" s="41"/>
+      <c r="AD24" s="41"/>
+      <c r="AE24" s="41"/>
+      <c r="AF24" s="41"/>
+      <c r="AG24" s="41"/>
+      <c r="AH24" s="41"/>
+      <c r="AI24" s="41"/>
+      <c r="AJ24" s="41"/>
+      <c r="AK24" s="59">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AL24" s="51"/>
-      <c r="AM24" s="55"/>
-      <c r="AN24" s="51"/>
-      <c r="AO24" s="66"/>
-      <c r="AP24" s="56"/>
-      <c r="AQ24" s="50">
+      <c r="AL24" s="41"/>
+      <c r="AM24" s="41"/>
+      <c r="AN24" s="41"/>
+      <c r="AO24" s="41"/>
+      <c r="AP24" s="61"/>
+      <c r="AQ24" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AR24" s="51"/>
-      <c r="AS24" s="51"/>
-      <c r="AT24" s="51"/>
-      <c r="AU24" s="50">
+      <c r="AR24" s="41"/>
+      <c r="AS24" s="41"/>
+      <c r="AT24" s="41"/>
+      <c r="AU24" s="59">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV24" s="51"/>
-      <c r="AW24" s="51"/>
-      <c r="AX24" s="51"/>
-      <c r="AY24" s="57"/>
-      <c r="AZ24" s="66"/>
-      <c r="BA24" s="50">
+      <c r="AV24" s="41"/>
+      <c r="AW24" s="41"/>
+      <c r="AX24" s="41"/>
+      <c r="AY24" s="61"/>
+      <c r="AZ24" s="41"/>
+      <c r="BA24" s="59">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB24" s="51"/>
-      <c r="BC24" s="58">
+      <c r="BB24" s="41"/>
+      <c r="BC24" s="62">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD24" s="59">
+      <c r="BD24" s="63">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BE24" s="69"/>
+      <c r="BE24" s="43"/>
     </row>
     <row r="25" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="35">
+      <c r="A25" s="23">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
@@ -3565,96 +3554,96 @@
       <c r="C25" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="D25" s="50">
+      <c r="D25" s="36">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="E25" s="70"/>
-      <c r="F25" s="51"/>
-      <c r="G25" s="51"/>
-      <c r="H25" s="70"/>
-      <c r="I25" s="51"/>
-      <c r="J25" s="66"/>
-      <c r="K25" s="50">
+      <c r="E25" s="44"/>
+      <c r="F25" s="37"/>
+      <c r="G25" s="37"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="37"/>
+      <c r="J25" s="41"/>
+      <c r="K25" s="59">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="L25" s="52"/>
-      <c r="M25" s="53">
+      <c r="L25" s="41"/>
+      <c r="M25" s="59">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N25" s="70"/>
-      <c r="O25" s="70"/>
-      <c r="P25" s="51"/>
-      <c r="Q25" s="66"/>
-      <c r="R25" s="50">
+      <c r="N25" s="41"/>
+      <c r="O25" s="41"/>
+      <c r="P25" s="41"/>
+      <c r="Q25" s="41"/>
+      <c r="R25" s="59">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S25" s="52"/>
-      <c r="T25" s="53">
+      <c r="S25" s="41"/>
+      <c r="T25" s="59">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U25" s="63"/>
-      <c r="V25" s="51"/>
-      <c r="W25" s="51"/>
-      <c r="X25" s="51"/>
-      <c r="Y25" s="51"/>
-      <c r="Z25" s="51"/>
-      <c r="AA25" s="51"/>
-      <c r="AB25" s="51"/>
-      <c r="AC25" s="51"/>
-      <c r="AD25" s="51"/>
-      <c r="AE25" s="51"/>
-      <c r="AF25" s="51"/>
-      <c r="AG25" s="51"/>
-      <c r="AH25" s="51"/>
-      <c r="AI25" s="51"/>
-      <c r="AJ25" s="51"/>
-      <c r="AK25" s="50">
+      <c r="U25" s="64"/>
+      <c r="V25" s="41"/>
+      <c r="W25" s="41"/>
+      <c r="X25" s="41"/>
+      <c r="Y25" s="41"/>
+      <c r="Z25" s="41"/>
+      <c r="AA25" s="41"/>
+      <c r="AB25" s="41"/>
+      <c r="AC25" s="41"/>
+      <c r="AD25" s="41"/>
+      <c r="AE25" s="41"/>
+      <c r="AF25" s="41"/>
+      <c r="AG25" s="41"/>
+      <c r="AH25" s="41"/>
+      <c r="AI25" s="41"/>
+      <c r="AJ25" s="41"/>
+      <c r="AK25" s="59">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AL25" s="51"/>
-      <c r="AM25" s="55"/>
-      <c r="AN25" s="51"/>
-      <c r="AO25" s="51"/>
-      <c r="AP25" s="51"/>
-      <c r="AQ25" s="50">
+      <c r="AL25" s="41"/>
+      <c r="AM25" s="41"/>
+      <c r="AN25" s="41"/>
+      <c r="AO25" s="41"/>
+      <c r="AP25" s="41"/>
+      <c r="AQ25" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AR25" s="51"/>
-      <c r="AS25" s="51"/>
-      <c r="AT25" s="51"/>
-      <c r="AU25" s="50">
+      <c r="AR25" s="41"/>
+      <c r="AS25" s="41"/>
+      <c r="AT25" s="41"/>
+      <c r="AU25" s="59">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV25" s="51"/>
-      <c r="AW25" s="51"/>
-      <c r="AX25" s="51"/>
-      <c r="AY25" s="57"/>
-      <c r="AZ25" s="51"/>
-      <c r="BA25" s="50">
+      <c r="AV25" s="41"/>
+      <c r="AW25" s="41"/>
+      <c r="AX25" s="41"/>
+      <c r="AY25" s="61"/>
+      <c r="AZ25" s="41"/>
+      <c r="BA25" s="59">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB25" s="51"/>
-      <c r="BC25" s="58">
+      <c r="BB25" s="41"/>
+      <c r="BC25" s="62">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD25" s="59">
+      <c r="BD25" s="63">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BE25" s="69"/>
+      <c r="BE25" s="43"/>
     </row>
     <row r="26" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="35">
+      <c r="A26" s="23">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
@@ -3664,96 +3653,96 @@
       <c r="C26" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="D26" s="50">
+      <c r="D26" s="36">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="E26" s="51"/>
-      <c r="F26" s="51"/>
-      <c r="G26" s="51"/>
-      <c r="H26" s="51"/>
-      <c r="I26" s="51"/>
-      <c r="J26" s="51"/>
-      <c r="K26" s="50">
+      <c r="E26" s="37"/>
+      <c r="F26" s="37"/>
+      <c r="G26" s="37"/>
+      <c r="H26" s="37"/>
+      <c r="I26" s="37"/>
+      <c r="J26" s="37"/>
+      <c r="K26" s="59">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="L26" s="52"/>
-      <c r="M26" s="53">
+      <c r="L26" s="41"/>
+      <c r="M26" s="59">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N26" s="51"/>
-      <c r="O26" s="51"/>
-      <c r="P26" s="51"/>
-      <c r="Q26" s="66"/>
-      <c r="R26" s="50">
+      <c r="N26" s="41"/>
+      <c r="O26" s="41"/>
+      <c r="P26" s="41"/>
+      <c r="Q26" s="41"/>
+      <c r="R26" s="59">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S26" s="52"/>
-      <c r="T26" s="53">
+      <c r="S26" s="41"/>
+      <c r="T26" s="59">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U26" s="63"/>
-      <c r="V26" s="51"/>
-      <c r="W26" s="51"/>
-      <c r="X26" s="51"/>
-      <c r="Y26" s="51"/>
-      <c r="Z26" s="51"/>
-      <c r="AA26" s="51"/>
-      <c r="AB26" s="51"/>
-      <c r="AC26" s="51"/>
-      <c r="AD26" s="51"/>
-      <c r="AE26" s="51"/>
-      <c r="AF26" s="51"/>
-      <c r="AG26" s="51"/>
-      <c r="AH26" s="51"/>
-      <c r="AI26" s="51"/>
-      <c r="AJ26" s="51"/>
-      <c r="AK26" s="50">
+      <c r="U26" s="64"/>
+      <c r="V26" s="41"/>
+      <c r="W26" s="41"/>
+      <c r="X26" s="41"/>
+      <c r="Y26" s="41"/>
+      <c r="Z26" s="41"/>
+      <c r="AA26" s="41"/>
+      <c r="AB26" s="41"/>
+      <c r="AC26" s="41"/>
+      <c r="AD26" s="41"/>
+      <c r="AE26" s="41"/>
+      <c r="AF26" s="41"/>
+      <c r="AG26" s="41"/>
+      <c r="AH26" s="41"/>
+      <c r="AI26" s="41"/>
+      <c r="AJ26" s="41"/>
+      <c r="AK26" s="59">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AL26" s="51"/>
-      <c r="AM26" s="55"/>
-      <c r="AN26" s="51"/>
-      <c r="AO26" s="51"/>
-      <c r="AP26" s="51"/>
-      <c r="AQ26" s="50">
+      <c r="AL26" s="41"/>
+      <c r="AM26" s="41"/>
+      <c r="AN26" s="41"/>
+      <c r="AO26" s="41"/>
+      <c r="AP26" s="41"/>
+      <c r="AQ26" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AR26" s="51"/>
-      <c r="AS26" s="51"/>
-      <c r="AT26" s="51"/>
-      <c r="AU26" s="50">
+      <c r="AR26" s="41"/>
+      <c r="AS26" s="41"/>
+      <c r="AT26" s="41"/>
+      <c r="AU26" s="59">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV26" s="51"/>
-      <c r="AW26" s="51"/>
-      <c r="AX26" s="51"/>
-      <c r="AY26" s="57"/>
-      <c r="AZ26" s="51"/>
-      <c r="BA26" s="50">
+      <c r="AV26" s="41"/>
+      <c r="AW26" s="41"/>
+      <c r="AX26" s="41"/>
+      <c r="AY26" s="61"/>
+      <c r="AZ26" s="41"/>
+      <c r="BA26" s="59">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BB26" s="64"/>
-      <c r="BC26" s="58">
+      <c r="BC26" s="62">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD26" s="59">
+      <c r="BD26" s="63">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BE26" s="69"/>
+      <c r="BE26" s="43"/>
     </row>
     <row r="27" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="35">
+      <c r="A27" s="23">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
@@ -3763,96 +3752,96 @@
       <c r="C27" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="D27" s="50">
+      <c r="D27" s="36">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="E27" s="51"/>
-      <c r="F27" s="51"/>
-      <c r="G27" s="51"/>
-      <c r="H27" s="51"/>
-      <c r="I27" s="51"/>
-      <c r="J27" s="51"/>
-      <c r="K27" s="50">
+      <c r="E27" s="37"/>
+      <c r="F27" s="37"/>
+      <c r="G27" s="37"/>
+      <c r="H27" s="37"/>
+      <c r="I27" s="37"/>
+      <c r="J27" s="37"/>
+      <c r="K27" s="59">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="L27" s="52"/>
-      <c r="M27" s="53">
+      <c r="L27" s="41"/>
+      <c r="M27" s="59">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N27" s="51"/>
-      <c r="O27" s="51"/>
-      <c r="P27" s="51"/>
-      <c r="Q27" s="66"/>
-      <c r="R27" s="50">
+      <c r="N27" s="41"/>
+      <c r="O27" s="41"/>
+      <c r="P27" s="41"/>
+      <c r="Q27" s="41"/>
+      <c r="R27" s="59">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S27" s="52"/>
-      <c r="T27" s="53">
+      <c r="S27" s="41"/>
+      <c r="T27" s="59">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U27" s="63"/>
-      <c r="V27" s="51"/>
-      <c r="W27" s="51"/>
-      <c r="X27" s="51"/>
-      <c r="Y27" s="51"/>
-      <c r="Z27" s="51"/>
-      <c r="AA27" s="51"/>
-      <c r="AB27" s="51"/>
-      <c r="AC27" s="51"/>
-      <c r="AD27" s="51"/>
-      <c r="AE27" s="51"/>
-      <c r="AF27" s="51"/>
-      <c r="AG27" s="51"/>
-      <c r="AH27" s="51"/>
-      <c r="AI27" s="51"/>
-      <c r="AJ27" s="51"/>
-      <c r="AK27" s="50">
+      <c r="U27" s="64"/>
+      <c r="V27" s="41"/>
+      <c r="W27" s="41"/>
+      <c r="X27" s="41"/>
+      <c r="Y27" s="41"/>
+      <c r="Z27" s="41"/>
+      <c r="AA27" s="41"/>
+      <c r="AB27" s="41"/>
+      <c r="AC27" s="41"/>
+      <c r="AD27" s="41"/>
+      <c r="AE27" s="41"/>
+      <c r="AF27" s="41"/>
+      <c r="AG27" s="41"/>
+      <c r="AH27" s="41"/>
+      <c r="AI27" s="41"/>
+      <c r="AJ27" s="41"/>
+      <c r="AK27" s="59">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AL27" s="51"/>
-      <c r="AM27" s="55"/>
-      <c r="AN27" s="51"/>
-      <c r="AO27" s="51"/>
-      <c r="AP27" s="56"/>
-      <c r="AQ27" s="50">
+      <c r="AL27" s="41"/>
+      <c r="AM27" s="41"/>
+      <c r="AN27" s="41"/>
+      <c r="AO27" s="41"/>
+      <c r="AP27" s="61"/>
+      <c r="AQ27" s="59">
         <f t="shared" ref="AQ27:AQ35" si="12">AM27-AN27-AO27-AP27</f>
         <v>0</v>
       </c>
-      <c r="AR27" s="51"/>
-      <c r="AS27" s="51"/>
-      <c r="AT27" s="51"/>
-      <c r="AU27" s="50">
+      <c r="AR27" s="41"/>
+      <c r="AS27" s="41"/>
+      <c r="AT27" s="41"/>
+      <c r="AU27" s="59">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV27" s="51"/>
-      <c r="AW27" s="51"/>
-      <c r="AX27" s="51"/>
-      <c r="AY27" s="57"/>
-      <c r="AZ27" s="51"/>
-      <c r="BA27" s="50">
+      <c r="AV27" s="41"/>
+      <c r="AW27" s="41"/>
+      <c r="AX27" s="41"/>
+      <c r="AY27" s="61"/>
+      <c r="AZ27" s="41"/>
+      <c r="BA27" s="59">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB27" s="51"/>
-      <c r="BC27" s="58">
+      <c r="BB27" s="41"/>
+      <c r="BC27" s="62">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD27" s="59">
+      <c r="BD27" s="63">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BE27" s="69"/>
+      <c r="BE27" s="43"/>
     </row>
     <row r="28" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="35">
+      <c r="A28" s="23">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
@@ -3862,96 +3851,96 @@
       <c r="C28" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="D28" s="50">
+      <c r="D28" s="36">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="E28" s="51"/>
-      <c r="F28" s="51"/>
-      <c r="G28" s="51"/>
-      <c r="H28" s="51"/>
-      <c r="I28" s="51"/>
-      <c r="J28" s="51"/>
-      <c r="K28" s="50">
+      <c r="E28" s="37"/>
+      <c r="F28" s="37"/>
+      <c r="G28" s="37"/>
+      <c r="H28" s="37"/>
+      <c r="I28" s="37"/>
+      <c r="J28" s="37"/>
+      <c r="K28" s="59">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="L28" s="52"/>
-      <c r="M28" s="53">
+      <c r="L28" s="41"/>
+      <c r="M28" s="59">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N28" s="51"/>
-      <c r="O28" s="51"/>
-      <c r="P28" s="51"/>
-      <c r="Q28" s="66"/>
-      <c r="R28" s="50">
+      <c r="N28" s="41"/>
+      <c r="O28" s="41"/>
+      <c r="P28" s="41"/>
+      <c r="Q28" s="41"/>
+      <c r="R28" s="59">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S28" s="52"/>
-      <c r="T28" s="53">
+      <c r="S28" s="41"/>
+      <c r="T28" s="59">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U28" s="63"/>
-      <c r="V28" s="51"/>
-      <c r="W28" s="51"/>
-      <c r="X28" s="51"/>
-      <c r="Y28" s="51"/>
-      <c r="Z28" s="51"/>
-      <c r="AA28" s="51"/>
-      <c r="AB28" s="51"/>
-      <c r="AC28" s="51"/>
-      <c r="AD28" s="51"/>
-      <c r="AE28" s="51"/>
-      <c r="AF28" s="51"/>
-      <c r="AG28" s="51"/>
-      <c r="AH28" s="51"/>
-      <c r="AI28" s="51"/>
-      <c r="AJ28" s="51"/>
-      <c r="AK28" s="50">
+      <c r="U28" s="64"/>
+      <c r="V28" s="41"/>
+      <c r="W28" s="41"/>
+      <c r="X28" s="41"/>
+      <c r="Y28" s="41"/>
+      <c r="Z28" s="41"/>
+      <c r="AA28" s="41"/>
+      <c r="AB28" s="41"/>
+      <c r="AC28" s="41"/>
+      <c r="AD28" s="41"/>
+      <c r="AE28" s="41"/>
+      <c r="AF28" s="41"/>
+      <c r="AG28" s="41"/>
+      <c r="AH28" s="41"/>
+      <c r="AI28" s="41"/>
+      <c r="AJ28" s="41"/>
+      <c r="AK28" s="59">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AL28" s="51"/>
-      <c r="AM28" s="57"/>
-      <c r="AN28" s="51"/>
-      <c r="AO28" s="51"/>
-      <c r="AP28" s="56"/>
-      <c r="AQ28" s="50">
+      <c r="AL28" s="41"/>
+      <c r="AM28" s="61"/>
+      <c r="AN28" s="41"/>
+      <c r="AO28" s="41"/>
+      <c r="AP28" s="61"/>
+      <c r="AQ28" s="59">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AR28" s="51"/>
-      <c r="AS28" s="51"/>
-      <c r="AT28" s="51"/>
-      <c r="AU28" s="50">
+      <c r="AR28" s="41"/>
+      <c r="AS28" s="41"/>
+      <c r="AT28" s="41"/>
+      <c r="AU28" s="59">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV28" s="51"/>
-      <c r="AW28" s="51"/>
-      <c r="AX28" s="51"/>
-      <c r="AY28" s="57"/>
-      <c r="AZ28" s="56"/>
-      <c r="BA28" s="50">
+      <c r="AV28" s="41"/>
+      <c r="AW28" s="41"/>
+      <c r="AX28" s="41"/>
+      <c r="AY28" s="61"/>
+      <c r="AZ28" s="61"/>
+      <c r="BA28" s="59">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BB28" s="64"/>
-      <c r="BC28" s="58">
+      <c r="BC28" s="62">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD28" s="59">
+      <c r="BD28" s="63">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BE28" s="69"/>
+      <c r="BE28" s="43"/>
     </row>
     <row r="29" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="35">
+      <c r="A29" s="23">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
@@ -3961,96 +3950,96 @@
       <c r="C29" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="D29" s="50">
+      <c r="D29" s="36">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="E29" s="51"/>
-      <c r="F29" s="51"/>
-      <c r="G29" s="51"/>
-      <c r="H29" s="51"/>
-      <c r="I29" s="51"/>
-      <c r="J29" s="51"/>
-      <c r="K29" s="50">
+      <c r="E29" s="37"/>
+      <c r="F29" s="37"/>
+      <c r="G29" s="37"/>
+      <c r="H29" s="37"/>
+      <c r="I29" s="37"/>
+      <c r="J29" s="37"/>
+      <c r="K29" s="59">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="L29" s="52"/>
-      <c r="M29" s="53">
+      <c r="L29" s="41"/>
+      <c r="M29" s="59">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N29" s="51"/>
-      <c r="O29" s="51"/>
-      <c r="P29" s="51"/>
-      <c r="Q29" s="66"/>
-      <c r="R29" s="50">
+      <c r="N29" s="41"/>
+      <c r="O29" s="41"/>
+      <c r="P29" s="41"/>
+      <c r="Q29" s="41"/>
+      <c r="R29" s="59">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S29" s="52"/>
-      <c r="T29" s="53">
+      <c r="S29" s="41"/>
+      <c r="T29" s="59">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U29" s="63"/>
-      <c r="V29" s="51"/>
-      <c r="W29" s="51"/>
-      <c r="X29" s="51"/>
-      <c r="Y29" s="51"/>
-      <c r="Z29" s="51"/>
-      <c r="AA29" s="51"/>
-      <c r="AB29" s="51"/>
-      <c r="AC29" s="51"/>
-      <c r="AD29" s="51"/>
-      <c r="AE29" s="51"/>
-      <c r="AF29" s="51"/>
-      <c r="AG29" s="51"/>
-      <c r="AH29" s="51"/>
-      <c r="AI29" s="51"/>
-      <c r="AJ29" s="51"/>
-      <c r="AK29" s="50">
+      <c r="U29" s="64"/>
+      <c r="V29" s="41"/>
+      <c r="W29" s="41"/>
+      <c r="X29" s="41"/>
+      <c r="Y29" s="41"/>
+      <c r="Z29" s="41"/>
+      <c r="AA29" s="41"/>
+      <c r="AB29" s="41"/>
+      <c r="AC29" s="41"/>
+      <c r="AD29" s="41"/>
+      <c r="AE29" s="41"/>
+      <c r="AF29" s="41"/>
+      <c r="AG29" s="41"/>
+      <c r="AH29" s="41"/>
+      <c r="AI29" s="41"/>
+      <c r="AJ29" s="41"/>
+      <c r="AK29" s="59">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AL29" s="51"/>
-      <c r="AM29" s="57"/>
-      <c r="AN29" s="56"/>
-      <c r="AO29" s="51"/>
-      <c r="AP29" s="51"/>
-      <c r="AQ29" s="50">
+      <c r="AL29" s="41"/>
+      <c r="AM29" s="61"/>
+      <c r="AN29" s="61"/>
+      <c r="AO29" s="41"/>
+      <c r="AP29" s="41"/>
+      <c r="AQ29" s="59">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AR29" s="51"/>
-      <c r="AS29" s="51"/>
-      <c r="AT29" s="51"/>
-      <c r="AU29" s="50">
+      <c r="AR29" s="41"/>
+      <c r="AS29" s="41"/>
+      <c r="AT29" s="41"/>
+      <c r="AU29" s="59">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV29" s="51"/>
-      <c r="AW29" s="51"/>
-      <c r="AX29" s="51"/>
-      <c r="AY29" s="57"/>
-      <c r="AZ29" s="66"/>
-      <c r="BA29" s="50">
+      <c r="AV29" s="41"/>
+      <c r="AW29" s="41"/>
+      <c r="AX29" s="41"/>
+      <c r="AY29" s="61"/>
+      <c r="AZ29" s="41"/>
+      <c r="BA29" s="59">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB29" s="51"/>
-      <c r="BC29" s="58">
+      <c r="BB29" s="41"/>
+      <c r="BC29" s="62">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD29" s="59">
+      <c r="BD29" s="63">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BE29" s="69"/>
+      <c r="BE29" s="43"/>
     </row>
     <row r="30" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="35">
+      <c r="A30" s="23">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
@@ -4060,96 +4049,96 @@
       <c r="C30" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="D30" s="50">
+      <c r="D30" s="36">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="E30" s="51"/>
-      <c r="F30" s="51"/>
-      <c r="G30" s="51"/>
-      <c r="H30" s="51"/>
-      <c r="I30" s="51"/>
-      <c r="J30" s="51"/>
-      <c r="K30" s="50">
+      <c r="E30" s="37"/>
+      <c r="F30" s="37"/>
+      <c r="G30" s="37"/>
+      <c r="H30" s="37"/>
+      <c r="I30" s="37"/>
+      <c r="J30" s="37"/>
+      <c r="K30" s="59">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="L30" s="52"/>
-      <c r="M30" s="53">
+      <c r="L30" s="41"/>
+      <c r="M30" s="59">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N30" s="51"/>
-      <c r="O30" s="51"/>
-      <c r="P30" s="51"/>
-      <c r="Q30" s="66"/>
-      <c r="R30" s="50">
+      <c r="N30" s="41"/>
+      <c r="O30" s="41"/>
+      <c r="P30" s="41"/>
+      <c r="Q30" s="41"/>
+      <c r="R30" s="59">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S30" s="52"/>
-      <c r="T30" s="53">
+      <c r="S30" s="41"/>
+      <c r="T30" s="59">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U30" s="63"/>
-      <c r="V30" s="51"/>
-      <c r="W30" s="51"/>
-      <c r="X30" s="51"/>
-      <c r="Y30" s="51"/>
-      <c r="Z30" s="51"/>
-      <c r="AA30" s="51"/>
-      <c r="AB30" s="51"/>
-      <c r="AC30" s="51"/>
-      <c r="AD30" s="51"/>
-      <c r="AE30" s="51"/>
-      <c r="AF30" s="51"/>
-      <c r="AG30" s="51"/>
-      <c r="AH30" s="51"/>
-      <c r="AI30" s="51"/>
-      <c r="AJ30" s="51"/>
-      <c r="AK30" s="50">
+      <c r="U30" s="64"/>
+      <c r="V30" s="41"/>
+      <c r="W30" s="41"/>
+      <c r="X30" s="41"/>
+      <c r="Y30" s="41"/>
+      <c r="Z30" s="41"/>
+      <c r="AA30" s="41"/>
+      <c r="AB30" s="41"/>
+      <c r="AC30" s="41"/>
+      <c r="AD30" s="41"/>
+      <c r="AE30" s="41"/>
+      <c r="AF30" s="41"/>
+      <c r="AG30" s="41"/>
+      <c r="AH30" s="41"/>
+      <c r="AI30" s="41"/>
+      <c r="AJ30" s="41"/>
+      <c r="AK30" s="59">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AL30" s="51"/>
-      <c r="AM30" s="55"/>
-      <c r="AN30" s="66"/>
-      <c r="AO30" s="51"/>
-      <c r="AP30" s="51"/>
-      <c r="AQ30" s="50">
+      <c r="AL30" s="41"/>
+      <c r="AM30" s="41"/>
+      <c r="AN30" s="41"/>
+      <c r="AO30" s="41"/>
+      <c r="AP30" s="41"/>
+      <c r="AQ30" s="59">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AR30" s="51"/>
-      <c r="AS30" s="51"/>
-      <c r="AT30" s="51"/>
-      <c r="AU30" s="50">
+      <c r="AR30" s="41"/>
+      <c r="AS30" s="41"/>
+      <c r="AT30" s="41"/>
+      <c r="AU30" s="59">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV30" s="51"/>
-      <c r="AW30" s="51"/>
-      <c r="AX30" s="51"/>
-      <c r="AY30" s="57"/>
-      <c r="AZ30" s="51"/>
-      <c r="BA30" s="50">
+      <c r="AV30" s="41"/>
+      <c r="AW30" s="41"/>
+      <c r="AX30" s="41"/>
+      <c r="AY30" s="61"/>
+      <c r="AZ30" s="41"/>
+      <c r="BA30" s="59">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB30" s="51"/>
-      <c r="BC30" s="58">
+      <c r="BB30" s="41"/>
+      <c r="BC30" s="62">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD30" s="59">
+      <c r="BD30" s="63">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BE30" s="69"/>
+      <c r="BE30" s="43"/>
     </row>
     <row r="31" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="35">
+      <c r="A31" s="23">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
@@ -4159,96 +4148,96 @@
       <c r="C31" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="D31" s="50">
+      <c r="D31" s="36">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="E31" s="51"/>
-      <c r="F31" s="51"/>
-      <c r="G31" s="51"/>
-      <c r="H31" s="51"/>
-      <c r="I31" s="51"/>
-      <c r="J31" s="51"/>
-      <c r="K31" s="50">
+      <c r="E31" s="37"/>
+      <c r="F31" s="37"/>
+      <c r="G31" s="37"/>
+      <c r="H31" s="37"/>
+      <c r="I31" s="37"/>
+      <c r="J31" s="37"/>
+      <c r="K31" s="59">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="L31" s="52"/>
-      <c r="M31" s="53">
+      <c r="L31" s="41"/>
+      <c r="M31" s="59">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N31" s="51"/>
-      <c r="O31" s="51"/>
-      <c r="P31" s="51"/>
-      <c r="Q31" s="66"/>
-      <c r="R31" s="50">
+      <c r="N31" s="41"/>
+      <c r="O31" s="41"/>
+      <c r="P31" s="41"/>
+      <c r="Q31" s="41"/>
+      <c r="R31" s="59">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S31" s="52"/>
-      <c r="T31" s="53">
+      <c r="S31" s="41"/>
+      <c r="T31" s="59">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U31" s="63"/>
-      <c r="V31" s="51"/>
-      <c r="W31" s="51"/>
-      <c r="X31" s="51"/>
-      <c r="Y31" s="51"/>
-      <c r="Z31" s="51"/>
-      <c r="AA31" s="51"/>
-      <c r="AB31" s="51"/>
-      <c r="AC31" s="51"/>
-      <c r="AD31" s="51"/>
-      <c r="AE31" s="51"/>
-      <c r="AF31" s="51"/>
-      <c r="AG31" s="51"/>
-      <c r="AH31" s="51"/>
-      <c r="AI31" s="51"/>
-      <c r="AJ31" s="51"/>
-      <c r="AK31" s="50">
+      <c r="U31" s="64"/>
+      <c r="V31" s="41"/>
+      <c r="W31" s="41"/>
+      <c r="X31" s="41"/>
+      <c r="Y31" s="41"/>
+      <c r="Z31" s="41"/>
+      <c r="AA31" s="41"/>
+      <c r="AB31" s="41"/>
+      <c r="AC31" s="41"/>
+      <c r="AD31" s="41"/>
+      <c r="AE31" s="41"/>
+      <c r="AF31" s="41"/>
+      <c r="AG31" s="41"/>
+      <c r="AH31" s="41"/>
+      <c r="AI31" s="41"/>
+      <c r="AJ31" s="41"/>
+      <c r="AK31" s="59">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AL31" s="64"/>
-      <c r="AM31" s="55"/>
-      <c r="AN31" s="66"/>
-      <c r="AO31" s="51"/>
-      <c r="AP31" s="66"/>
-      <c r="AQ31" s="50">
+      <c r="AM31" s="41"/>
+      <c r="AN31" s="41"/>
+      <c r="AO31" s="41"/>
+      <c r="AP31" s="41"/>
+      <c r="AQ31" s="59">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AR31" s="51"/>
-      <c r="AS31" s="51"/>
-      <c r="AT31" s="51"/>
-      <c r="AU31" s="50">
+      <c r="AR31" s="41"/>
+      <c r="AS31" s="41"/>
+      <c r="AT31" s="41"/>
+      <c r="AU31" s="59">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV31" s="51"/>
-      <c r="AW31" s="51"/>
-      <c r="AX31" s="51"/>
-      <c r="AY31" s="57"/>
-      <c r="AZ31" s="56"/>
-      <c r="BA31" s="50">
+      <c r="AV31" s="41"/>
+      <c r="AW31" s="41"/>
+      <c r="AX31" s="41"/>
+      <c r="AY31" s="61"/>
+      <c r="AZ31" s="61"/>
+      <c r="BA31" s="59">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB31" s="51"/>
-      <c r="BC31" s="58">
+      <c r="BB31" s="41"/>
+      <c r="BC31" s="62">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD31" s="59">
+      <c r="BD31" s="63">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BE31" s="69"/>
+      <c r="BE31" s="43"/>
     </row>
     <row r="32" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="35">
+      <c r="A32" s="23">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
@@ -4258,96 +4247,96 @@
       <c r="C32" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="D32" s="50">
+      <c r="D32" s="36">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="E32" s="51"/>
-      <c r="F32" s="51"/>
-      <c r="G32" s="51"/>
-      <c r="H32" s="51"/>
-      <c r="I32" s="51"/>
-      <c r="J32" s="51"/>
-      <c r="K32" s="50">
+      <c r="E32" s="37"/>
+      <c r="F32" s="37"/>
+      <c r="G32" s="37"/>
+      <c r="H32" s="37"/>
+      <c r="I32" s="37"/>
+      <c r="J32" s="37"/>
+      <c r="K32" s="59">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="L32" s="52"/>
-      <c r="M32" s="53">
+      <c r="L32" s="41"/>
+      <c r="M32" s="59">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N32" s="51"/>
-      <c r="O32" s="51"/>
-      <c r="P32" s="51"/>
-      <c r="Q32" s="66"/>
-      <c r="R32" s="50">
+      <c r="N32" s="41"/>
+      <c r="O32" s="41"/>
+      <c r="P32" s="41"/>
+      <c r="Q32" s="41"/>
+      <c r="R32" s="59">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S32" s="52"/>
-      <c r="T32" s="53">
+      <c r="S32" s="41"/>
+      <c r="T32" s="59">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U32" s="63"/>
-      <c r="V32" s="51"/>
-      <c r="W32" s="51"/>
-      <c r="X32" s="51"/>
-      <c r="Y32" s="51"/>
-      <c r="Z32" s="51"/>
-      <c r="AA32" s="51"/>
-      <c r="AB32" s="51"/>
-      <c r="AC32" s="51"/>
-      <c r="AD32" s="51"/>
-      <c r="AE32" s="51"/>
-      <c r="AF32" s="51"/>
-      <c r="AG32" s="51"/>
-      <c r="AH32" s="51"/>
-      <c r="AI32" s="66"/>
-      <c r="AJ32" s="51"/>
-      <c r="AK32" s="50">
+      <c r="U32" s="64"/>
+      <c r="V32" s="41"/>
+      <c r="W32" s="41"/>
+      <c r="X32" s="41"/>
+      <c r="Y32" s="41"/>
+      <c r="Z32" s="41"/>
+      <c r="AA32" s="41"/>
+      <c r="AB32" s="41"/>
+      <c r="AC32" s="41"/>
+      <c r="AD32" s="41"/>
+      <c r="AE32" s="41"/>
+      <c r="AF32" s="41"/>
+      <c r="AG32" s="41"/>
+      <c r="AH32" s="41"/>
+      <c r="AI32" s="41"/>
+      <c r="AJ32" s="41"/>
+      <c r="AK32" s="59">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AL32" s="64"/>
-      <c r="AM32" s="57"/>
-      <c r="AN32" s="51"/>
-      <c r="AO32" s="51"/>
-      <c r="AP32" s="51"/>
-      <c r="AQ32" s="50">
+      <c r="AM32" s="61"/>
+      <c r="AN32" s="41"/>
+      <c r="AO32" s="41"/>
+      <c r="AP32" s="41"/>
+      <c r="AQ32" s="59">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AR32" s="51"/>
-      <c r="AS32" s="51"/>
-      <c r="AT32" s="51"/>
-      <c r="AU32" s="50">
+      <c r="AR32" s="41"/>
+      <c r="AS32" s="41"/>
+      <c r="AT32" s="41"/>
+      <c r="AU32" s="59">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV32" s="51"/>
-      <c r="AW32" s="51"/>
-      <c r="AX32" s="51"/>
-      <c r="AY32" s="57"/>
-      <c r="AZ32" s="51"/>
-      <c r="BA32" s="50">
+      <c r="AV32" s="41"/>
+      <c r="AW32" s="41"/>
+      <c r="AX32" s="41"/>
+      <c r="AY32" s="61"/>
+      <c r="AZ32" s="41"/>
+      <c r="BA32" s="59">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB32" s="51"/>
-      <c r="BC32" s="58">
+      <c r="BB32" s="41"/>
+      <c r="BC32" s="62">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD32" s="59">
+      <c r="BD32" s="63">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BE32" s="51"/>
+      <c r="BE32" s="37"/>
     </row>
     <row r="33" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="35">
+      <c r="A33" s="23">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
@@ -4357,96 +4346,96 @@
       <c r="C33" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="D33" s="50">
+      <c r="D33" s="36">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="E33" s="51"/>
-      <c r="F33" s="51"/>
-      <c r="G33" s="51"/>
-      <c r="H33" s="51"/>
-      <c r="I33" s="51"/>
-      <c r="J33" s="51"/>
-      <c r="K33" s="50">
+      <c r="E33" s="37"/>
+      <c r="F33" s="37"/>
+      <c r="G33" s="37"/>
+      <c r="H33" s="37"/>
+      <c r="I33" s="37"/>
+      <c r="J33" s="37"/>
+      <c r="K33" s="59">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="L33" s="52"/>
-      <c r="M33" s="53">
+      <c r="L33" s="41"/>
+      <c r="M33" s="59">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N33" s="51"/>
-      <c r="O33" s="51"/>
-      <c r="P33" s="51"/>
-      <c r="Q33" s="66"/>
-      <c r="R33" s="50">
+      <c r="N33" s="41"/>
+      <c r="O33" s="41"/>
+      <c r="P33" s="41"/>
+      <c r="Q33" s="41"/>
+      <c r="R33" s="59">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S33" s="52"/>
-      <c r="T33" s="53">
+      <c r="S33" s="41"/>
+      <c r="T33" s="59">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U33" s="63"/>
-      <c r="V33" s="51"/>
-      <c r="W33" s="51"/>
-      <c r="X33" s="51"/>
-      <c r="Y33" s="51"/>
-      <c r="Z33" s="51"/>
-      <c r="AA33" s="51"/>
-      <c r="AB33" s="51"/>
-      <c r="AC33" s="51"/>
-      <c r="AD33" s="51"/>
-      <c r="AE33" s="51"/>
-      <c r="AF33" s="51"/>
-      <c r="AG33" s="51"/>
-      <c r="AH33" s="51"/>
-      <c r="AI33" s="66"/>
-      <c r="AJ33" s="51"/>
-      <c r="AK33" s="50">
+      <c r="U33" s="64"/>
+      <c r="V33" s="41"/>
+      <c r="W33" s="41"/>
+      <c r="X33" s="41"/>
+      <c r="Y33" s="41"/>
+      <c r="Z33" s="41"/>
+      <c r="AA33" s="41"/>
+      <c r="AB33" s="41"/>
+      <c r="AC33" s="41"/>
+      <c r="AD33" s="41"/>
+      <c r="AE33" s="41"/>
+      <c r="AF33" s="41"/>
+      <c r="AG33" s="41"/>
+      <c r="AH33" s="41"/>
+      <c r="AI33" s="41"/>
+      <c r="AJ33" s="41"/>
+      <c r="AK33" s="59">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AL33" s="64"/>
-      <c r="AM33" s="57"/>
-      <c r="AN33" s="51"/>
-      <c r="AO33" s="51"/>
-      <c r="AP33" s="51"/>
-      <c r="AQ33" s="50">
+      <c r="AM33" s="61"/>
+      <c r="AN33" s="41"/>
+      <c r="AO33" s="41"/>
+      <c r="AP33" s="41"/>
+      <c r="AQ33" s="59">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AR33" s="51"/>
-      <c r="AS33" s="51"/>
-      <c r="AT33" s="51"/>
-      <c r="AU33" s="50">
+      <c r="AR33" s="41"/>
+      <c r="AS33" s="41"/>
+      <c r="AT33" s="41"/>
+      <c r="AU33" s="59">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV33" s="51"/>
-      <c r="AW33" s="51"/>
-      <c r="AX33" s="51"/>
-      <c r="AY33" s="57"/>
-      <c r="AZ33" s="51"/>
-      <c r="BA33" s="50">
+      <c r="AV33" s="41"/>
+      <c r="AW33" s="41"/>
+      <c r="AX33" s="41"/>
+      <c r="AY33" s="61"/>
+      <c r="AZ33" s="41"/>
+      <c r="BA33" s="59">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB33" s="51"/>
-      <c r="BC33" s="58">
+      <c r="BB33" s="41"/>
+      <c r="BC33" s="62">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD33" s="59">
+      <c r="BD33" s="63">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BE33" s="51"/>
+      <c r="BE33" s="37"/>
     </row>
     <row r="34" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="35">
+      <c r="A34" s="23">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
@@ -4456,405 +4445,405 @@
       <c r="C34" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="D34" s="50">
+      <c r="D34" s="36">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="E34" s="51"/>
-      <c r="F34" s="51"/>
-      <c r="G34" s="51"/>
-      <c r="H34" s="51"/>
-      <c r="I34" s="51"/>
-      <c r="J34" s="51"/>
-      <c r="K34" s="50">
+      <c r="E34" s="37"/>
+      <c r="F34" s="37"/>
+      <c r="G34" s="37"/>
+      <c r="H34" s="37"/>
+      <c r="I34" s="37"/>
+      <c r="J34" s="37"/>
+      <c r="K34" s="59">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="L34" s="52"/>
-      <c r="M34" s="53">
+      <c r="L34" s="41"/>
+      <c r="M34" s="59">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N34" s="51"/>
-      <c r="O34" s="51"/>
-      <c r="P34" s="51"/>
-      <c r="Q34" s="66"/>
-      <c r="R34" s="50">
+      <c r="N34" s="41"/>
+      <c r="O34" s="41"/>
+      <c r="P34" s="41"/>
+      <c r="Q34" s="41"/>
+      <c r="R34" s="59">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S34" s="52"/>
-      <c r="T34" s="53">
+      <c r="S34" s="41"/>
+      <c r="T34" s="59">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U34" s="63"/>
-      <c r="V34" s="51"/>
-      <c r="W34" s="51"/>
-      <c r="X34" s="51"/>
-      <c r="Y34" s="51"/>
-      <c r="Z34" s="51"/>
-      <c r="AA34" s="51"/>
-      <c r="AB34" s="51"/>
-      <c r="AC34" s="51"/>
-      <c r="AD34" s="51"/>
-      <c r="AE34" s="51"/>
-      <c r="AF34" s="51"/>
-      <c r="AG34" s="51"/>
-      <c r="AH34" s="51"/>
-      <c r="AI34" s="66"/>
-      <c r="AJ34" s="51"/>
-      <c r="AK34" s="50">
+      <c r="U34" s="64"/>
+      <c r="V34" s="41"/>
+      <c r="W34" s="41"/>
+      <c r="X34" s="41"/>
+      <c r="Y34" s="41"/>
+      <c r="Z34" s="41"/>
+      <c r="AA34" s="41"/>
+      <c r="AB34" s="41"/>
+      <c r="AC34" s="41"/>
+      <c r="AD34" s="41"/>
+      <c r="AE34" s="41"/>
+      <c r="AF34" s="41"/>
+      <c r="AG34" s="41"/>
+      <c r="AH34" s="41"/>
+      <c r="AI34" s="41"/>
+      <c r="AJ34" s="41"/>
+      <c r="AK34" s="59">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AL34" s="64"/>
-      <c r="AM34" s="57"/>
-      <c r="AN34" s="51"/>
-      <c r="AO34" s="51"/>
-      <c r="AP34" s="51"/>
-      <c r="AQ34" s="50">
+      <c r="AM34" s="61"/>
+      <c r="AN34" s="41"/>
+      <c r="AO34" s="41"/>
+      <c r="AP34" s="41"/>
+      <c r="AQ34" s="59">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AR34" s="51"/>
-      <c r="AS34" s="51"/>
-      <c r="AT34" s="51"/>
-      <c r="AU34" s="50">
+      <c r="AR34" s="41"/>
+      <c r="AS34" s="41"/>
+      <c r="AT34" s="41"/>
+      <c r="AU34" s="59">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV34" s="51"/>
-      <c r="AW34" s="51"/>
-      <c r="AX34" s="51"/>
-      <c r="AY34" s="57"/>
-      <c r="AZ34" s="51"/>
-      <c r="BA34" s="50">
+      <c r="AV34" s="41"/>
+      <c r="AW34" s="41"/>
+      <c r="AX34" s="41"/>
+      <c r="AY34" s="61"/>
+      <c r="AZ34" s="41"/>
+      <c r="BA34" s="59">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB34" s="51"/>
-      <c r="BC34" s="58">
+      <c r="BB34" s="41"/>
+      <c r="BC34" s="62">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD34" s="59">
+      <c r="BD34" s="63">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BE34" s="51"/>
+      <c r="BE34" s="37"/>
     </row>
     <row r="35" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="35">
+      <c r="A35" s="23">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="B35" s="19"/>
       <c r="C35" s="19"/>
-      <c r="D35" s="50">
+      <c r="D35" s="36">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="E35" s="51"/>
-      <c r="F35" s="51"/>
-      <c r="G35" s="51"/>
-      <c r="H35" s="51"/>
-      <c r="I35" s="51"/>
-      <c r="J35" s="51"/>
-      <c r="K35" s="50">
+      <c r="E35" s="37"/>
+      <c r="F35" s="37"/>
+      <c r="G35" s="37"/>
+      <c r="H35" s="37"/>
+      <c r="I35" s="37"/>
+      <c r="J35" s="37"/>
+      <c r="K35" s="59">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="L35" s="52"/>
-      <c r="M35" s="53">
+      <c r="L35" s="41"/>
+      <c r="M35" s="59">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N35" s="51"/>
-      <c r="O35" s="51"/>
-      <c r="P35" s="51"/>
-      <c r="Q35" s="66"/>
-      <c r="R35" s="50">
+      <c r="N35" s="41"/>
+      <c r="O35" s="41"/>
+      <c r="P35" s="41"/>
+      <c r="Q35" s="41"/>
+      <c r="R35" s="59">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S35" s="52"/>
-      <c r="T35" s="53">
+      <c r="S35" s="41"/>
+      <c r="T35" s="59">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U35" s="63"/>
-      <c r="V35" s="51"/>
-      <c r="W35" s="51"/>
-      <c r="X35" s="51"/>
-      <c r="Y35" s="51"/>
-      <c r="Z35" s="51"/>
-      <c r="AA35" s="51"/>
-      <c r="AB35" s="51"/>
-      <c r="AC35" s="51"/>
-      <c r="AD35" s="51"/>
-      <c r="AE35" s="51"/>
-      <c r="AF35" s="51"/>
-      <c r="AG35" s="51"/>
-      <c r="AH35" s="51"/>
-      <c r="AI35" s="66"/>
-      <c r="AJ35" s="51"/>
-      <c r="AK35" s="50">
+      <c r="U35" s="64"/>
+      <c r="V35" s="41"/>
+      <c r="W35" s="41"/>
+      <c r="X35" s="41"/>
+      <c r="Y35" s="41"/>
+      <c r="Z35" s="41"/>
+      <c r="AA35" s="41"/>
+      <c r="AB35" s="41"/>
+      <c r="AC35" s="41"/>
+      <c r="AD35" s="41"/>
+      <c r="AE35" s="41"/>
+      <c r="AF35" s="41"/>
+      <c r="AG35" s="41"/>
+      <c r="AH35" s="41"/>
+      <c r="AI35" s="41"/>
+      <c r="AJ35" s="41"/>
+      <c r="AK35" s="59">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AL35" s="64"/>
-      <c r="AM35" s="57"/>
-      <c r="AN35" s="51"/>
-      <c r="AO35" s="51"/>
-      <c r="AP35" s="51"/>
-      <c r="AQ35" s="50">
+      <c r="AM35" s="61"/>
+      <c r="AN35" s="41"/>
+      <c r="AO35" s="41"/>
+      <c r="AP35" s="41"/>
+      <c r="AQ35" s="59">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AR35" s="51"/>
-      <c r="AS35" s="51"/>
-      <c r="AT35" s="51"/>
-      <c r="AU35" s="50">
+      <c r="AR35" s="41"/>
+      <c r="AS35" s="41"/>
+      <c r="AT35" s="41"/>
+      <c r="AU35" s="59">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV35" s="51"/>
-      <c r="AW35" s="51"/>
-      <c r="AX35" s="51"/>
-      <c r="AY35" s="57"/>
-      <c r="AZ35" s="51"/>
-      <c r="BA35" s="50">
+      <c r="AV35" s="41"/>
+      <c r="AW35" s="41"/>
+      <c r="AX35" s="41"/>
+      <c r="AY35" s="61"/>
+      <c r="AZ35" s="41"/>
+      <c r="BA35" s="59">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB35" s="51"/>
-      <c r="BC35" s="58">
+      <c r="BB35" s="41"/>
+      <c r="BC35" s="62">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD35" s="59">
+      <c r="BD35" s="63">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BE35" s="51"/>
+      <c r="BE35" s="37"/>
     </row>
     <row r="36" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="35">
+      <c r="A36" s="23">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="B36" s="35" t="s">
+      <c r="B36" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="C36" s="51"/>
-      <c r="D36" s="35">
+      <c r="C36" s="37"/>
+      <c r="D36" s="23">
         <f t="shared" ref="D36:BD36" si="13">SUM(D5:D35)</f>
         <v>0</v>
       </c>
-      <c r="E36" s="35">
+      <c r="E36" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F36" s="35">
+      <c r="F36" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="G36" s="35"/>
-      <c r="H36" s="35">
+      <c r="G36" s="23"/>
+      <c r="H36" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I36" s="35">
+      <c r="I36" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="J36" s="35">
+      <c r="J36" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="K36" s="35">
+      <c r="K36" s="67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="L36" s="35">
+      <c r="L36" s="67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="M36" s="35">
+      <c r="M36" s="67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="N36" s="35">
+      <c r="N36" s="67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="O36" s="35">
+      <c r="O36" s="67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="P36" s="35">
+      <c r="P36" s="67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="Q36" s="35">
+      <c r="Q36" s="67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="R36" s="35">
+      <c r="R36" s="67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="S36" s="35">
+      <c r="S36" s="67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="T36" s="35">
+      <c r="T36" s="67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="U36" s="35">
+      <c r="U36" s="67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V36" s="35">
+      <c r="V36" s="67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="W36" s="35">
+      <c r="W36" s="67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="X36" s="35">
+      <c r="X36" s="67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="Y36" s="35">
+      <c r="Y36" s="67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="Z36" s="35">
+      <c r="Z36" s="67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AA36" s="35">
+      <c r="AA36" s="67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AB36" s="35">
+      <c r="AB36" s="67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AC36" s="35">
+      <c r="AC36" s="67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AD36" s="35">
+      <c r="AD36" s="67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AE36" s="35"/>
-      <c r="AF36" s="35">
+      <c r="AE36" s="67"/>
+      <c r="AF36" s="67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AG36" s="35">
+      <c r="AG36" s="67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AH36" s="35">
+      <c r="AH36" s="67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AI36" s="35">
+      <c r="AI36" s="67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AJ36" s="35">
+      <c r="AJ36" s="67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AK36" s="35">
+      <c r="AK36" s="67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AL36" s="35">
+      <c r="AL36" s="67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AM36" s="35">
+      <c r="AM36" s="67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AN36" s="35">
+      <c r="AN36" s="67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AO36" s="35">
+      <c r="AO36" s="67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP36" s="35">
+      <c r="AP36" s="67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AQ36" s="35">
+      <c r="AQ36" s="67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AR36" s="35">
+      <c r="AR36" s="67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AS36" s="35">
+      <c r="AS36" s="67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AT36" s="35">
+      <c r="AT36" s="67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AU36" s="35">
+      <c r="AU36" s="67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AV36" s="35">
+      <c r="AV36" s="67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AW36" s="35">
+      <c r="AW36" s="67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AX36" s="35">
+      <c r="AX36" s="67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AY36" s="35">
+      <c r="AY36" s="67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ36" s="35">
+      <c r="AZ36" s="67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA36" s="35">
+      <c r="BA36" s="67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BB36" s="35">
+      <c r="BB36" s="67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BC36" s="35">
+      <c r="BC36" s="67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BD36" s="35">
+      <c r="BD36" s="67">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BE36" s="51"/>
+      <c r="BE36" s="37"/>
     </row>
     <row r="37" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A37" s="20"/>
@@ -14470,17 +14459,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="AC3:AC4"/>
-    <mergeCell ref="BC2:BC4"/>
-    <mergeCell ref="BD2:BD4"/>
-    <mergeCell ref="BE2:BE4"/>
-    <mergeCell ref="B2:C4"/>
-    <mergeCell ref="G2:G4"/>
-    <mergeCell ref="W3:W4"/>
-    <mergeCell ref="Y3:Y4"/>
-    <mergeCell ref="Z3:Z4"/>
-    <mergeCell ref="AA3:AA4"/>
-    <mergeCell ref="AB3:AB4"/>
     <mergeCell ref="A1:BE1"/>
     <mergeCell ref="I2:AA2"/>
     <mergeCell ref="AD2:BB2"/>
@@ -14497,6 +14475,17 @@
     <mergeCell ref="F2:F4"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="V3:V4"/>
+    <mergeCell ref="AC3:AC4"/>
+    <mergeCell ref="BC2:BC4"/>
+    <mergeCell ref="BD2:BD4"/>
+    <mergeCell ref="BE2:BE4"/>
+    <mergeCell ref="B2:C4"/>
+    <mergeCell ref="G2:G4"/>
+    <mergeCell ref="W3:W4"/>
+    <mergeCell ref="Y3:Y4"/>
+    <mergeCell ref="Z3:Z4"/>
+    <mergeCell ref="AA3:AA4"/>
+    <mergeCell ref="AB3:AB4"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14523,23 +14512,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="56" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
     </row>
     <row r="2" spans="1:9" s="2" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="25"/>
+      <c r="B2" s="57"/>
       <c r="C2" s="3" t="s">
         <v>82</v>
       </c>
@@ -15230,10 +15219,10 @@
       <c r="I33" s="11"/>
     </row>
     <row r="34" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="26" t="s">
+      <c r="A34" s="58" t="s">
         <v>86</v>
       </c>
-      <c r="B34" s="26"/>
+      <c r="B34" s="58"/>
       <c r="C34" s="9"/>
       <c r="D34" s="9">
         <f>SUM(D3:D33)</f>

--- a/finance/麦安研营业统计_格式化模板.xlsx
+++ b/finance/麦安研营业统计_格式化模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wadec\Documents\projects\mainyan-auto\finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80FE23C8-5F18-4824-AC5E-B4154F7746DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E4C38AF-EB87-4DD7-B4EB-A6D80080FCA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -806,48 +806,6 @@
     <xf numFmtId="178" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="11" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="17" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -873,6 +831,48 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="11" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1189,252 +1189,252 @@
     <col min="53" max="53" width="14.5546875" style="17" customWidth="1"/>
     <col min="54" max="54" width="13.33203125" style="17" hidden="1" customWidth="1"/>
     <col min="55" max="55" width="12.21875" style="17" customWidth="1"/>
-    <col min="56" max="56" width="9.88671875" style="17" customWidth="1"/>
+    <col min="56" max="56" width="12.44140625" style="17" customWidth="1"/>
     <col min="57" max="16384" width="10.33203125" style="17"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:57" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
-      <c r="M1" s="50"/>
-      <c r="N1" s="50"/>
-      <c r="O1" s="50"/>
-      <c r="P1" s="50"/>
-      <c r="Q1" s="50"/>
-      <c r="R1" s="50"/>
-      <c r="S1" s="50"/>
-      <c r="T1" s="50"/>
-      <c r="U1" s="50"/>
-      <c r="V1" s="50"/>
-      <c r="W1" s="50"/>
-      <c r="X1" s="50"/>
-      <c r="Y1" s="50"/>
-      <c r="Z1" s="50"/>
-      <c r="AA1" s="50"/>
-      <c r="AB1" s="50"/>
-      <c r="AC1" s="50"/>
-      <c r="AD1" s="50"/>
-      <c r="AE1" s="50"/>
-      <c r="AF1" s="50"/>
-      <c r="AG1" s="50"/>
-      <c r="AH1" s="50"/>
-      <c r="AI1" s="50"/>
-      <c r="AJ1" s="50"/>
-      <c r="AK1" s="50"/>
-      <c r="AL1" s="50"/>
-      <c r="AM1" s="50"/>
-      <c r="AN1" s="50"/>
-      <c r="AO1" s="50"/>
-      <c r="AP1" s="50"/>
-      <c r="AQ1" s="50"/>
-      <c r="AR1" s="50"/>
-      <c r="AS1" s="50"/>
-      <c r="AT1" s="50"/>
-      <c r="AU1" s="50"/>
-      <c r="AV1" s="50"/>
-      <c r="AW1" s="50"/>
-      <c r="AX1" s="50"/>
-      <c r="AY1" s="50"/>
-      <c r="AZ1" s="50"/>
-      <c r="BA1" s="50"/>
-      <c r="BB1" s="50"/>
-      <c r="BC1" s="50"/>
-      <c r="BD1" s="50"/>
-      <c r="BE1" s="50"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="54"/>
+      <c r="O1" s="54"/>
+      <c r="P1" s="54"/>
+      <c r="Q1" s="54"/>
+      <c r="R1" s="54"/>
+      <c r="S1" s="54"/>
+      <c r="T1" s="54"/>
+      <c r="U1" s="54"/>
+      <c r="V1" s="54"/>
+      <c r="W1" s="54"/>
+      <c r="X1" s="54"/>
+      <c r="Y1" s="54"/>
+      <c r="Z1" s="54"/>
+      <c r="AA1" s="54"/>
+      <c r="AB1" s="54"/>
+      <c r="AC1" s="54"/>
+      <c r="AD1" s="54"/>
+      <c r="AE1" s="54"/>
+      <c r="AF1" s="54"/>
+      <c r="AG1" s="54"/>
+      <c r="AH1" s="54"/>
+      <c r="AI1" s="54"/>
+      <c r="AJ1" s="54"/>
+      <c r="AK1" s="54"/>
+      <c r="AL1" s="54"/>
+      <c r="AM1" s="54"/>
+      <c r="AN1" s="54"/>
+      <c r="AO1" s="54"/>
+      <c r="AP1" s="54"/>
+      <c r="AQ1" s="54"/>
+      <c r="AR1" s="54"/>
+      <c r="AS1" s="54"/>
+      <c r="AT1" s="54"/>
+      <c r="AU1" s="54"/>
+      <c r="AV1" s="54"/>
+      <c r="AW1" s="54"/>
+      <c r="AX1" s="54"/>
+      <c r="AY1" s="54"/>
+      <c r="AZ1" s="54"/>
+      <c r="BA1" s="54"/>
+      <c r="BB1" s="54"/>
+      <c r="BC1" s="54"/>
+      <c r="BD1" s="54"/>
+      <c r="BE1" s="54"/>
     </row>
     <row r="2" spans="1:57" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="45" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="45" t="s">
+      <c r="A2" s="57" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45" t="s">
+      <c r="C2" s="57"/>
+      <c r="D2" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="45" t="s">
+      <c r="E2" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="45" t="s">
+      <c r="F2" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="48" t="s">
+      <c r="G2" s="61" t="s">
         <v>107</v>
       </c>
-      <c r="H2" s="55" t="s">
+      <c r="H2" s="60" t="s">
         <v>88</v>
       </c>
-      <c r="I2" s="51" t="s">
+      <c r="I2" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="51"/>
-      <c r="M2" s="51"/>
-      <c r="N2" s="51"/>
-      <c r="O2" s="51"/>
-      <c r="P2" s="51"/>
-      <c r="Q2" s="51"/>
-      <c r="R2" s="51"/>
-      <c r="S2" s="51"/>
-      <c r="T2" s="51"/>
-      <c r="U2" s="51"/>
-      <c r="V2" s="51"/>
-      <c r="W2" s="51"/>
-      <c r="X2" s="51"/>
-      <c r="Y2" s="51"/>
-      <c r="Z2" s="51"/>
-      <c r="AA2" s="51"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
+      <c r="P2" s="55"/>
+      <c r="Q2" s="55"/>
+      <c r="R2" s="55"/>
+      <c r="S2" s="55"/>
+      <c r="T2" s="55"/>
+      <c r="U2" s="55"/>
+      <c r="V2" s="55"/>
+      <c r="W2" s="55"/>
+      <c r="X2" s="55"/>
+      <c r="Y2" s="55"/>
+      <c r="Z2" s="55"/>
+      <c r="AA2" s="55"/>
       <c r="AB2" s="25"/>
       <c r="AC2" s="25"/>
-      <c r="AD2" s="52" t="s">
+      <c r="AD2" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="AE2" s="52"/>
-      <c r="AF2" s="52"/>
-      <c r="AG2" s="52"/>
-      <c r="AH2" s="52"/>
-      <c r="AI2" s="52"/>
-      <c r="AJ2" s="52"/>
-      <c r="AK2" s="52"/>
-      <c r="AL2" s="52"/>
-      <c r="AM2" s="52"/>
-      <c r="AN2" s="52"/>
-      <c r="AO2" s="52"/>
-      <c r="AP2" s="52"/>
-      <c r="AQ2" s="52"/>
-      <c r="AR2" s="52"/>
-      <c r="AS2" s="52"/>
-      <c r="AT2" s="52"/>
-      <c r="AU2" s="52"/>
-      <c r="AV2" s="52"/>
-      <c r="AW2" s="52"/>
-      <c r="AX2" s="52"/>
-      <c r="AY2" s="52"/>
-      <c r="AZ2" s="52"/>
-      <c r="BA2" s="52"/>
-      <c r="BB2" s="52"/>
-      <c r="BC2" s="46" t="s">
+      <c r="AE2" s="56"/>
+      <c r="AF2" s="56"/>
+      <c r="AG2" s="56"/>
+      <c r="AH2" s="56"/>
+      <c r="AI2" s="56"/>
+      <c r="AJ2" s="56"/>
+      <c r="AK2" s="56"/>
+      <c r="AL2" s="56"/>
+      <c r="AM2" s="56"/>
+      <c r="AN2" s="56"/>
+      <c r="AO2" s="56"/>
+      <c r="AP2" s="56"/>
+      <c r="AQ2" s="56"/>
+      <c r="AR2" s="56"/>
+      <c r="AS2" s="56"/>
+      <c r="AT2" s="56"/>
+      <c r="AU2" s="56"/>
+      <c r="AV2" s="56"/>
+      <c r="AW2" s="56"/>
+      <c r="AX2" s="56"/>
+      <c r="AY2" s="56"/>
+      <c r="AZ2" s="56"/>
+      <c r="BA2" s="56"/>
+      <c r="BB2" s="56"/>
+      <c r="BC2" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="BD2" s="47" t="s">
+      <c r="BD2" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="BE2" s="45" t="s">
+      <c r="BE2" s="57" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:57" s="18" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="45"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="45" t="s">
+      <c r="A3" s="57"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="45"/>
-      <c r="K3" s="45"/>
-      <c r="L3" s="45"/>
-      <c r="M3" s="45"/>
-      <c r="N3" s="45"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="57"/>
+      <c r="N3" s="57"/>
       <c r="O3" s="23"/>
       <c r="P3" s="23"/>
-      <c r="Q3" s="45" t="s">
+      <c r="Q3" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="R3" s="45"/>
-      <c r="S3" s="45"/>
-      <c r="T3" s="45"/>
-      <c r="U3" s="45"/>
-      <c r="V3" s="48" t="s">
+      <c r="R3" s="57"/>
+      <c r="S3" s="57"/>
+      <c r="T3" s="57"/>
+      <c r="U3" s="57"/>
+      <c r="V3" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="W3" s="48" t="s">
+      <c r="W3" s="61" t="s">
         <v>13</v>
       </c>
       <c r="X3" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="Y3" s="49" t="s">
+      <c r="Y3" s="64" t="s">
         <v>14</v>
       </c>
-      <c r="Z3" s="49" t="s">
+      <c r="Z3" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="AA3" s="45" t="s">
+      <c r="AA3" s="57" t="s">
         <v>16</v>
       </c>
-      <c r="AB3" s="45" t="s">
+      <c r="AB3" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="AC3" s="45" t="s">
+      <c r="AC3" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="AD3" s="53" t="s">
+      <c r="AD3" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="AE3" s="53"/>
-      <c r="AF3" s="53"/>
-      <c r="AG3" s="53"/>
-      <c r="AH3" s="53"/>
-      <c r="AI3" s="53"/>
-      <c r="AJ3" s="53"/>
-      <c r="AK3" s="53"/>
-      <c r="AL3" s="53"/>
-      <c r="AM3" s="53" t="s">
+      <c r="AE3" s="58"/>
+      <c r="AF3" s="58"/>
+      <c r="AG3" s="58"/>
+      <c r="AH3" s="58"/>
+      <c r="AI3" s="58"/>
+      <c r="AJ3" s="58"/>
+      <c r="AK3" s="58"/>
+      <c r="AL3" s="58"/>
+      <c r="AM3" s="58" t="s">
         <v>20</v>
       </c>
-      <c r="AN3" s="53"/>
-      <c r="AO3" s="53"/>
-      <c r="AP3" s="53"/>
-      <c r="AQ3" s="53"/>
-      <c r="AR3" s="53"/>
-      <c r="AS3" s="53" t="s">
+      <c r="AN3" s="58"/>
+      <c r="AO3" s="58"/>
+      <c r="AP3" s="58"/>
+      <c r="AQ3" s="58"/>
+      <c r="AR3" s="58"/>
+      <c r="AS3" s="58" t="s">
         <v>21</v>
       </c>
-      <c r="AT3" s="53"/>
-      <c r="AU3" s="53"/>
+      <c r="AT3" s="58"/>
+      <c r="AU3" s="58"/>
       <c r="AV3" s="26"/>
-      <c r="AW3" s="54" t="s">
+      <c r="AW3" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="AX3" s="54"/>
-      <c r="AY3" s="53" t="s">
+      <c r="AX3" s="59"/>
+      <c r="AY3" s="58" t="s">
         <v>90</v>
       </c>
-      <c r="AZ3" s="53"/>
-      <c r="BA3" s="53"/>
-      <c r="BB3" s="53"/>
-      <c r="BC3" s="46"/>
-      <c r="BD3" s="47"/>
-      <c r="BE3" s="45"/>
+      <c r="AZ3" s="58"/>
+      <c r="BA3" s="58"/>
+      <c r="BB3" s="58"/>
+      <c r="BC3" s="62"/>
+      <c r="BD3" s="63"/>
+      <c r="BE3" s="57"/>
     </row>
     <row r="4" spans="1:57" s="18" customFormat="1" ht="87" x14ac:dyDescent="0.25">
-      <c r="A4" s="45"/>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="55"/>
+      <c r="A4" s="57"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="60"/>
       <c r="I4" s="23" t="s">
         <v>23</v>
       </c>
@@ -1474,16 +1474,16 @@
       <c r="U4" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="V4" s="48"/>
-      <c r="W4" s="48"/>
+      <c r="V4" s="61"/>
+      <c r="W4" s="61"/>
       <c r="X4" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="Y4" s="49"/>
-      <c r="Z4" s="49"/>
-      <c r="AA4" s="45"/>
-      <c r="AB4" s="45"/>
-      <c r="AC4" s="45"/>
+      <c r="Y4" s="64"/>
+      <c r="Z4" s="64"/>
+      <c r="AA4" s="57"/>
+      <c r="AB4" s="57"/>
+      <c r="AC4" s="57"/>
       <c r="AD4" s="24" t="s">
         <v>108</v>
       </c>
@@ -1559,9 +1559,9 @@
       <c r="BB4" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="BC4" s="46"/>
-      <c r="BD4" s="47"/>
-      <c r="BE4" s="45"/>
+      <c r="BC4" s="62"/>
+      <c r="BD4" s="63"/>
+      <c r="BE4" s="57"/>
     </row>
     <row r="5" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="23">
@@ -1584,12 +1584,12 @@
       <c r="H5" s="37"/>
       <c r="I5" s="37"/>
       <c r="J5" s="37"/>
-      <c r="K5" s="59">
+      <c r="K5" s="45">
         <f>I5-J5</f>
         <v>0</v>
       </c>
       <c r="L5" s="41"/>
-      <c r="M5" s="59">
+      <c r="M5" s="45">
         <f t="shared" ref="M5:M35" si="1">K5-L5</f>
         <v>0</v>
       </c>
@@ -1597,12 +1597,12 @@
       <c r="O5" s="41"/>
       <c r="P5" s="41"/>
       <c r="Q5" s="41"/>
-      <c r="R5" s="59">
+      <c r="R5" s="45">
         <f t="shared" ref="R5:R35" si="2">P5-Q5</f>
         <v>0</v>
       </c>
       <c r="S5" s="41"/>
-      <c r="T5" s="59">
+      <c r="T5" s="45">
         <f t="shared" ref="T5:T35" si="3">R5-S5</f>
         <v>0</v>
       </c>
@@ -1615,14 +1615,14 @@
       <c r="AA5" s="41"/>
       <c r="AB5" s="41"/>
       <c r="AC5" s="41"/>
-      <c r="AD5" s="60"/>
-      <c r="AE5" s="60"/>
+      <c r="AD5" s="46"/>
+      <c r="AE5" s="46"/>
       <c r="AF5" s="41"/>
       <c r="AG5" s="41"/>
       <c r="AH5" s="41"/>
       <c r="AI5" s="41"/>
       <c r="AJ5" s="41"/>
-      <c r="AK5" s="59">
+      <c r="AK5" s="45">
         <f>AE5+AF5-AG5-AH5-AI5-AJ5</f>
         <v>0</v>
       </c>
@@ -1630,33 +1630,33 @@
       <c r="AM5" s="41"/>
       <c r="AN5" s="41"/>
       <c r="AO5" s="41"/>
-      <c r="AP5" s="61"/>
-      <c r="AQ5" s="59">
+      <c r="AP5" s="47"/>
+      <c r="AQ5" s="45">
         <f t="shared" ref="AQ5:AQ26" si="4">AM5-AN5-AO5-AP5</f>
         <v>0</v>
       </c>
       <c r="AR5" s="41"/>
       <c r="AS5" s="41"/>
       <c r="AT5" s="41"/>
-      <c r="AU5" s="59">
+      <c r="AU5" s="45">
         <f t="shared" ref="AU5:AU35" si="5">AS5-AT5</f>
         <v>0</v>
       </c>
       <c r="AV5" s="41"/>
       <c r="AW5" s="41"/>
       <c r="AX5" s="41"/>
-      <c r="AY5" s="61"/>
+      <c r="AY5" s="47"/>
       <c r="AZ5" s="41"/>
-      <c r="BA5" s="59">
+      <c r="BA5" s="45">
         <f t="shared" ref="BA5:BA35" si="6">AY5-AZ5</f>
         <v>0</v>
       </c>
       <c r="BB5" s="41"/>
-      <c r="BC5" s="62">
+      <c r="BC5" s="48">
         <f t="shared" ref="BC5:BC35" si="7">F5+M5+T5+AK5+AQ5+AU5+AW5+BA5</f>
         <v>0</v>
       </c>
-      <c r="BD5" s="63">
+      <c r="BD5" s="49">
         <f t="shared" ref="BD5:BD35" si="8">F5+K5+R5+AD5+AM5+AS5+AW5+AY5</f>
         <v>0</v>
       </c>
@@ -1683,12 +1683,12 @@
       <c r="H6" s="37"/>
       <c r="I6" s="37"/>
       <c r="J6" s="37"/>
-      <c r="K6" s="59">
+      <c r="K6" s="45">
         <f t="shared" ref="K6:K35" si="10">I6-J6</f>
         <v>0</v>
       </c>
       <c r="L6" s="41"/>
-      <c r="M6" s="59">
+      <c r="M6" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1696,12 +1696,12 @@
       <c r="O6" s="41"/>
       <c r="P6" s="41"/>
       <c r="Q6" s="41"/>
-      <c r="R6" s="59">
+      <c r="R6" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S6" s="41"/>
-      <c r="T6" s="59">
+      <c r="T6" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -1721,7 +1721,7 @@
       <c r="AH6" s="41"/>
       <c r="AI6" s="41"/>
       <c r="AJ6" s="41"/>
-      <c r="AK6" s="59">
+      <c r="AK6" s="45">
         <f t="shared" ref="AK6:AK35" si="11">AE6+AF6-AG6-AH6-AI6-AJ6</f>
         <v>0</v>
       </c>
@@ -1729,33 +1729,33 @@
       <c r="AM6" s="41"/>
       <c r="AN6" s="41"/>
       <c r="AO6" s="41"/>
-      <c r="AP6" s="61"/>
-      <c r="AQ6" s="59">
+      <c r="AP6" s="47"/>
+      <c r="AQ6" s="45">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AR6" s="41"/>
       <c r="AS6" s="41"/>
       <c r="AT6" s="41"/>
-      <c r="AU6" s="59">
+      <c r="AU6" s="45">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV6" s="41"/>
       <c r="AW6" s="41"/>
       <c r="AX6" s="41"/>
-      <c r="AY6" s="61"/>
+      <c r="AY6" s="47"/>
       <c r="AZ6" s="41"/>
-      <c r="BA6" s="59">
+      <c r="BA6" s="45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BB6" s="41"/>
-      <c r="BC6" s="62">
+      <c r="BC6" s="48">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD6" s="63">
+      <c r="BD6" s="49">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -1782,12 +1782,12 @@
       <c r="H7" s="37"/>
       <c r="I7" s="37"/>
       <c r="J7" s="37"/>
-      <c r="K7" s="59">
+      <c r="K7" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L7" s="41"/>
-      <c r="M7" s="59">
+      <c r="M7" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1795,12 +1795,12 @@
       <c r="O7" s="41"/>
       <c r="P7" s="41"/>
       <c r="Q7" s="41"/>
-      <c r="R7" s="59">
+      <c r="R7" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S7" s="41"/>
-      <c r="T7" s="59">
+      <c r="T7" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -1820,41 +1820,41 @@
       <c r="AH7" s="41"/>
       <c r="AI7" s="41"/>
       <c r="AJ7" s="41"/>
-      <c r="AK7" s="59">
+      <c r="AK7" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AL7" s="41"/>
       <c r="AM7" s="41"/>
-      <c r="AN7" s="61"/>
-      <c r="AO7" s="61"/>
-      <c r="AP7" s="61"/>
-      <c r="AQ7" s="59">
+      <c r="AN7" s="47"/>
+      <c r="AO7" s="47"/>
+      <c r="AP7" s="47"/>
+      <c r="AQ7" s="45">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AR7" s="41"/>
       <c r="AS7" s="41"/>
       <c r="AT7" s="41"/>
-      <c r="AU7" s="59">
+      <c r="AU7" s="45">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV7" s="41"/>
       <c r="AW7" s="41"/>
       <c r="AX7" s="41"/>
-      <c r="AY7" s="61"/>
+      <c r="AY7" s="47"/>
       <c r="AZ7" s="41"/>
-      <c r="BA7" s="59">
+      <c r="BA7" s="45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BB7" s="41"/>
-      <c r="BC7" s="62">
+      <c r="BC7" s="48">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD7" s="63">
+      <c r="BD7" s="49">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -1881,12 +1881,12 @@
       <c r="H8" s="37"/>
       <c r="I8" s="37"/>
       <c r="J8" s="37"/>
-      <c r="K8" s="59">
+      <c r="K8" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L8" s="41"/>
-      <c r="M8" s="59">
+      <c r="M8" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1894,12 +1894,12 @@
       <c r="O8" s="41"/>
       <c r="P8" s="41"/>
       <c r="Q8" s="41"/>
-      <c r="R8" s="59">
+      <c r="R8" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S8" s="41"/>
-      <c r="T8" s="59">
+      <c r="T8" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -1919,7 +1919,7 @@
       <c r="AH8" s="41"/>
       <c r="AI8" s="41"/>
       <c r="AJ8" s="41"/>
-      <c r="AK8" s="59">
+      <c r="AK8" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -1927,33 +1927,33 @@
       <c r="AM8" s="41"/>
       <c r="AN8" s="41"/>
       <c r="AO8" s="41"/>
-      <c r="AP8" s="61"/>
-      <c r="AQ8" s="59">
+      <c r="AP8" s="47"/>
+      <c r="AQ8" s="45">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AR8" s="41"/>
       <c r="AS8" s="41"/>
       <c r="AT8" s="41"/>
-      <c r="AU8" s="59">
+      <c r="AU8" s="45">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV8" s="41"/>
       <c r="AW8" s="41"/>
       <c r="AX8" s="41"/>
-      <c r="AY8" s="61"/>
-      <c r="AZ8" s="61"/>
-      <c r="BA8" s="59">
+      <c r="AY8" s="47"/>
+      <c r="AZ8" s="47"/>
+      <c r="BA8" s="45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BB8" s="41"/>
-      <c r="BC8" s="62">
+      <c r="BC8" s="48">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD8" s="63">
+      <c r="BD8" s="49">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -1980,12 +1980,12 @@
       <c r="H9" s="37"/>
       <c r="I9" s="37"/>
       <c r="J9" s="37"/>
-      <c r="K9" s="59">
+      <c r="K9" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L9" s="41"/>
-      <c r="M9" s="59">
+      <c r="M9" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1993,12 +1993,12 @@
       <c r="O9" s="41"/>
       <c r="P9" s="41"/>
       <c r="Q9" s="41"/>
-      <c r="R9" s="59">
+      <c r="R9" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S9" s="41"/>
-      <c r="T9" s="59">
+      <c r="T9" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -2018,7 +2018,7 @@
       <c r="AH9" s="41"/>
       <c r="AI9" s="41"/>
       <c r="AJ9" s="41"/>
-      <c r="AK9" s="59">
+      <c r="AK9" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -2027,32 +2027,32 @@
       <c r="AN9" s="41"/>
       <c r="AO9" s="41"/>
       <c r="AP9" s="41"/>
-      <c r="AQ9" s="59">
+      <c r="AQ9" s="45">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AR9" s="41"/>
       <c r="AS9" s="41"/>
       <c r="AT9" s="41"/>
-      <c r="AU9" s="59">
+      <c r="AU9" s="45">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV9" s="41"/>
       <c r="AW9" s="41"/>
       <c r="AX9" s="41"/>
-      <c r="AY9" s="61"/>
-      <c r="AZ9" s="61"/>
-      <c r="BA9" s="59">
+      <c r="AY9" s="47"/>
+      <c r="AZ9" s="47"/>
+      <c r="BA9" s="45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BB9" s="41"/>
-      <c r="BC9" s="62">
+      <c r="BC9" s="48">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD9" s="63">
+      <c r="BD9" s="49">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -2079,12 +2079,12 @@
       <c r="H10" s="37"/>
       <c r="I10" s="40"/>
       <c r="J10" s="37"/>
-      <c r="K10" s="59">
+      <c r="K10" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L10" s="41"/>
-      <c r="M10" s="59">
+      <c r="M10" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2092,16 +2092,16 @@
       <c r="O10" s="41"/>
       <c r="P10" s="41"/>
       <c r="Q10" s="41"/>
-      <c r="R10" s="59">
+      <c r="R10" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S10" s="41"/>
-      <c r="T10" s="59">
+      <c r="T10" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U10" s="64"/>
+      <c r="U10" s="50"/>
       <c r="V10" s="41"/>
       <c r="W10" s="41"/>
       <c r="X10" s="41"/>
@@ -2117,7 +2117,7 @@
       <c r="AH10" s="41"/>
       <c r="AI10" s="41"/>
       <c r="AJ10" s="41"/>
-      <c r="AK10" s="59">
+      <c r="AK10" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -2126,32 +2126,32 @@
       <c r="AN10" s="41"/>
       <c r="AO10" s="41"/>
       <c r="AP10" s="41"/>
-      <c r="AQ10" s="59">
+      <c r="AQ10" s="45">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AR10" s="41"/>
       <c r="AS10" s="41"/>
       <c r="AT10" s="41"/>
-      <c r="AU10" s="59">
+      <c r="AU10" s="45">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV10" s="41"/>
       <c r="AW10" s="41"/>
       <c r="AX10" s="41"/>
-      <c r="AY10" s="61"/>
+      <c r="AY10" s="47"/>
       <c r="AZ10" s="41"/>
-      <c r="BA10" s="59">
+      <c r="BA10" s="45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BB10" s="41"/>
-      <c r="BC10" s="62">
+      <c r="BC10" s="48">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD10" s="63">
+      <c r="BD10" s="49">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -2178,12 +2178,12 @@
       <c r="H11" s="37"/>
       <c r="I11" s="37"/>
       <c r="J11" s="37"/>
-      <c r="K11" s="59">
+      <c r="K11" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L11" s="41"/>
-      <c r="M11" s="59">
+      <c r="M11" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2191,16 +2191,16 @@
       <c r="O11" s="41"/>
       <c r="P11" s="41"/>
       <c r="Q11" s="41"/>
-      <c r="R11" s="59">
+      <c r="R11" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S11" s="41"/>
-      <c r="T11" s="59">
+      <c r="T11" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U11" s="64"/>
+      <c r="U11" s="50"/>
       <c r="V11" s="41"/>
       <c r="W11" s="41"/>
       <c r="X11" s="41"/>
@@ -2216,7 +2216,7 @@
       <c r="AH11" s="41"/>
       <c r="AI11" s="41"/>
       <c r="AJ11" s="41"/>
-      <c r="AK11" s="59">
+      <c r="AK11" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -2224,33 +2224,33 @@
       <c r="AM11" s="41"/>
       <c r="AN11" s="41"/>
       <c r="AO11" s="41"/>
-      <c r="AP11" s="61"/>
-      <c r="AQ11" s="59">
+      <c r="AP11" s="47"/>
+      <c r="AQ11" s="45">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AR11" s="41"/>
       <c r="AS11" s="41"/>
       <c r="AT11" s="41"/>
-      <c r="AU11" s="59">
+      <c r="AU11" s="45">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV11" s="41"/>
       <c r="AW11" s="41"/>
       <c r="AX11" s="41"/>
-      <c r="AY11" s="61"/>
+      <c r="AY11" s="47"/>
       <c r="AZ11" s="41"/>
-      <c r="BA11" s="59">
+      <c r="BA11" s="45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BB11" s="41"/>
-      <c r="BC11" s="62">
+      <c r="BC11" s="48">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD11" s="63">
+      <c r="BD11" s="49">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -2277,12 +2277,12 @@
       <c r="H12" s="37"/>
       <c r="I12" s="37"/>
       <c r="J12" s="37"/>
-      <c r="K12" s="59">
+      <c r="K12" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L12" s="41"/>
-      <c r="M12" s="59">
+      <c r="M12" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2290,16 +2290,16 @@
       <c r="O12" s="41"/>
       <c r="P12" s="41"/>
       <c r="Q12" s="41"/>
-      <c r="R12" s="59">
+      <c r="R12" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S12" s="41"/>
-      <c r="T12" s="59">
+      <c r="T12" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U12" s="64"/>
+      <c r="U12" s="50"/>
       <c r="V12" s="41"/>
       <c r="W12" s="41"/>
       <c r="X12" s="41"/>
@@ -2315,7 +2315,7 @@
       <c r="AH12" s="41"/>
       <c r="AI12" s="41"/>
       <c r="AJ12" s="41"/>
-      <c r="AK12" s="59">
+      <c r="AK12" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -2324,32 +2324,32 @@
       <c r="AN12" s="41"/>
       <c r="AO12" s="41"/>
       <c r="AP12" s="41"/>
-      <c r="AQ12" s="59">
+      <c r="AQ12" s="45">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AR12" s="41"/>
       <c r="AS12" s="41"/>
       <c r="AT12" s="41"/>
-      <c r="AU12" s="59">
+      <c r="AU12" s="45">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV12" s="41"/>
       <c r="AW12" s="41"/>
       <c r="AX12" s="41"/>
-      <c r="AY12" s="61"/>
+      <c r="AY12" s="47"/>
       <c r="AZ12" s="41"/>
-      <c r="BA12" s="59">
+      <c r="BA12" s="45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BB12" s="41"/>
-      <c r="BC12" s="62">
+      <c r="BC12" s="48">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD12" s="63">
+      <c r="BD12" s="49">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -2376,12 +2376,12 @@
       <c r="H13" s="37"/>
       <c r="I13" s="37"/>
       <c r="J13" s="37"/>
-      <c r="K13" s="59">
+      <c r="K13" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L13" s="41"/>
-      <c r="M13" s="59">
+      <c r="M13" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2389,16 +2389,16 @@
       <c r="O13" s="41"/>
       <c r="P13" s="41"/>
       <c r="Q13" s="41"/>
-      <c r="R13" s="59">
+      <c r="R13" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S13" s="41"/>
-      <c r="T13" s="59">
+      <c r="T13" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U13" s="64"/>
+      <c r="U13" s="50"/>
       <c r="V13" s="41"/>
       <c r="W13" s="41"/>
       <c r="X13" s="41"/>
@@ -2414,7 +2414,7 @@
       <c r="AH13" s="41"/>
       <c r="AI13" s="41"/>
       <c r="AJ13" s="41"/>
-      <c r="AK13" s="59">
+      <c r="AK13" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -2423,32 +2423,32 @@
       <c r="AN13" s="41"/>
       <c r="AO13" s="41"/>
       <c r="AP13" s="41"/>
-      <c r="AQ13" s="59">
+      <c r="AQ13" s="45">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AR13" s="41"/>
       <c r="AS13" s="41"/>
       <c r="AT13" s="41"/>
-      <c r="AU13" s="59">
+      <c r="AU13" s="45">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV13" s="41"/>
       <c r="AW13" s="41"/>
       <c r="AX13" s="41"/>
-      <c r="AY13" s="61"/>
+      <c r="AY13" s="47"/>
       <c r="AZ13" s="41"/>
-      <c r="BA13" s="59">
+      <c r="BA13" s="45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BB13" s="41"/>
-      <c r="BC13" s="62">
+      <c r="BC13" s="48">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD13" s="63">
+      <c r="BD13" s="49">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -2475,12 +2475,12 @@
       <c r="H14" s="37"/>
       <c r="I14" s="37"/>
       <c r="J14" s="37"/>
-      <c r="K14" s="59">
+      <c r="K14" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L14" s="41"/>
-      <c r="M14" s="59">
+      <c r="M14" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2488,16 +2488,16 @@
       <c r="O14" s="41"/>
       <c r="P14" s="41"/>
       <c r="Q14" s="41"/>
-      <c r="R14" s="59">
+      <c r="R14" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S14" s="41"/>
-      <c r="T14" s="59">
+      <c r="T14" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U14" s="64"/>
+      <c r="U14" s="50"/>
       <c r="V14" s="41"/>
       <c r="W14" s="41"/>
       <c r="X14" s="41"/>
@@ -2513,7 +2513,7 @@
       <c r="AH14" s="41"/>
       <c r="AI14" s="41"/>
       <c r="AJ14" s="41"/>
-      <c r="AK14" s="59">
+      <c r="AK14" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -2522,32 +2522,32 @@
       <c r="AN14" s="41"/>
       <c r="AO14" s="41"/>
       <c r="AP14" s="41"/>
-      <c r="AQ14" s="59">
+      <c r="AQ14" s="45">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AR14" s="41"/>
       <c r="AS14" s="41"/>
       <c r="AT14" s="41"/>
-      <c r="AU14" s="59">
+      <c r="AU14" s="45">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV14" s="41"/>
       <c r="AW14" s="41"/>
       <c r="AX14" s="41"/>
-      <c r="AY14" s="61"/>
+      <c r="AY14" s="47"/>
       <c r="AZ14" s="41"/>
-      <c r="BA14" s="59">
+      <c r="BA14" s="45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BB14" s="41"/>
-      <c r="BC14" s="62">
+      <c r="BC14" s="48">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD14" s="63">
+      <c r="BD14" s="49">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -2574,12 +2574,12 @@
       <c r="H15" s="37"/>
       <c r="I15" s="37"/>
       <c r="J15" s="37"/>
-      <c r="K15" s="59">
+      <c r="K15" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L15" s="41"/>
-      <c r="M15" s="59">
+      <c r="M15" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2587,16 +2587,16 @@
       <c r="O15" s="41"/>
       <c r="P15" s="41"/>
       <c r="Q15" s="41"/>
-      <c r="R15" s="59">
+      <c r="R15" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S15" s="41"/>
-      <c r="T15" s="59">
+      <c r="T15" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U15" s="64"/>
+      <c r="U15" s="50"/>
       <c r="V15" s="41"/>
       <c r="W15" s="41"/>
       <c r="X15" s="41"/>
@@ -2612,7 +2612,7 @@
       <c r="AH15" s="41"/>
       <c r="AI15" s="41"/>
       <c r="AJ15" s="41"/>
-      <c r="AK15" s="59">
+      <c r="AK15" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -2621,32 +2621,32 @@
       <c r="AN15" s="41"/>
       <c r="AO15" s="41"/>
       <c r="AP15" s="41"/>
-      <c r="AQ15" s="59">
+      <c r="AQ15" s="45">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AR15" s="41"/>
       <c r="AS15" s="41"/>
       <c r="AT15" s="41"/>
-      <c r="AU15" s="59">
+      <c r="AU15" s="45">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV15" s="41"/>
       <c r="AW15" s="41"/>
       <c r="AX15" s="41"/>
-      <c r="AY15" s="61"/>
+      <c r="AY15" s="47"/>
       <c r="AZ15" s="41"/>
-      <c r="BA15" s="59">
+      <c r="BA15" s="45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BB15" s="41"/>
-      <c r="BC15" s="62">
+      <c r="BC15" s="48">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD15" s="63">
+      <c r="BD15" s="49">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -2673,12 +2673,12 @@
       <c r="H16" s="37"/>
       <c r="I16" s="37"/>
       <c r="J16" s="37"/>
-      <c r="K16" s="59">
+      <c r="K16" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L16" s="41"/>
-      <c r="M16" s="59">
+      <c r="M16" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2686,16 +2686,16 @@
       <c r="O16" s="41"/>
       <c r="P16" s="41"/>
       <c r="Q16" s="41"/>
-      <c r="R16" s="59">
+      <c r="R16" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S16" s="41"/>
-      <c r="T16" s="59">
+      <c r="T16" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U16" s="64"/>
+      <c r="U16" s="50"/>
       <c r="V16" s="41"/>
       <c r="W16" s="41"/>
       <c r="X16" s="41"/>
@@ -2711,7 +2711,7 @@
       <c r="AH16" s="41"/>
       <c r="AI16" s="41"/>
       <c r="AJ16" s="41"/>
-      <c r="AK16" s="59">
+      <c r="AK16" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -2720,32 +2720,32 @@
       <c r="AN16" s="41"/>
       <c r="AO16" s="41"/>
       <c r="AP16" s="41"/>
-      <c r="AQ16" s="59">
+      <c r="AQ16" s="45">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AR16" s="41"/>
       <c r="AS16" s="41"/>
       <c r="AT16" s="41"/>
-      <c r="AU16" s="59">
+      <c r="AU16" s="45">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV16" s="41"/>
       <c r="AW16" s="41"/>
       <c r="AX16" s="41"/>
-      <c r="AY16" s="61"/>
+      <c r="AY16" s="47"/>
       <c r="AZ16" s="41"/>
-      <c r="BA16" s="59">
+      <c r="BA16" s="45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BB16" s="41"/>
-      <c r="BC16" s="62">
+      <c r="BC16" s="48">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD16" s="63">
+      <c r="BD16" s="49">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -2772,12 +2772,12 @@
       <c r="H17" s="37"/>
       <c r="I17" s="37"/>
       <c r="J17" s="37"/>
-      <c r="K17" s="59">
+      <c r="K17" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L17" s="41"/>
-      <c r="M17" s="59">
+      <c r="M17" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2785,16 +2785,16 @@
       <c r="O17" s="41"/>
       <c r="P17" s="41"/>
       <c r="Q17" s="41"/>
-      <c r="R17" s="59">
+      <c r="R17" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S17" s="41"/>
-      <c r="T17" s="59">
+      <c r="T17" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U17" s="64"/>
+      <c r="U17" s="50"/>
       <c r="V17" s="41"/>
       <c r="W17" s="41"/>
       <c r="X17" s="41"/>
@@ -2810,7 +2810,7 @@
       <c r="AH17" s="41"/>
       <c r="AI17" s="41"/>
       <c r="AJ17" s="41"/>
-      <c r="AK17" s="59">
+      <c r="AK17" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -2819,32 +2819,32 @@
       <c r="AN17" s="41"/>
       <c r="AO17" s="41"/>
       <c r="AP17" s="41"/>
-      <c r="AQ17" s="59">
+      <c r="AQ17" s="45">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AR17" s="41"/>
       <c r="AS17" s="41"/>
       <c r="AT17" s="41"/>
-      <c r="AU17" s="59">
+      <c r="AU17" s="45">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV17" s="41"/>
       <c r="AW17" s="41"/>
       <c r="AX17" s="41"/>
-      <c r="AY17" s="61"/>
+      <c r="AY17" s="47"/>
       <c r="AZ17" s="41"/>
-      <c r="BA17" s="59">
+      <c r="BA17" s="45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB17" s="64"/>
-      <c r="BC17" s="62">
+      <c r="BB17" s="50"/>
+      <c r="BC17" s="48">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD17" s="63">
+      <c r="BD17" s="49">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -2871,29 +2871,29 @@
       <c r="H18" s="37"/>
       <c r="I18" s="37"/>
       <c r="J18" s="37"/>
-      <c r="K18" s="59">
+      <c r="K18" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L18" s="41"/>
-      <c r="M18" s="59">
+      <c r="M18" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N18" s="65"/>
-      <c r="O18" s="65"/>
+      <c r="N18" s="51"/>
+      <c r="O18" s="51"/>
       <c r="P18" s="41"/>
       <c r="Q18" s="41"/>
-      <c r="R18" s="59">
+      <c r="R18" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S18" s="41"/>
-      <c r="T18" s="59">
+      <c r="T18" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U18" s="64"/>
+      <c r="U18" s="50"/>
       <c r="V18" s="41"/>
       <c r="W18" s="41"/>
       <c r="X18" s="41"/>
@@ -2909,41 +2909,41 @@
       <c r="AH18" s="41"/>
       <c r="AI18" s="41"/>
       <c r="AJ18" s="41"/>
-      <c r="AK18" s="59">
+      <c r="AK18" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AL18" s="41"/>
-      <c r="AM18" s="61"/>
+      <c r="AM18" s="47"/>
       <c r="AN18" s="41"/>
       <c r="AO18" s="41"/>
       <c r="AP18" s="41"/>
-      <c r="AQ18" s="59">
+      <c r="AQ18" s="45">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AR18" s="41"/>
       <c r="AS18" s="41"/>
       <c r="AT18" s="41"/>
-      <c r="AU18" s="59">
+      <c r="AU18" s="45">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV18" s="41"/>
       <c r="AW18" s="41"/>
       <c r="AX18" s="41"/>
-      <c r="AY18" s="61"/>
+      <c r="AY18" s="47"/>
       <c r="AZ18" s="41"/>
-      <c r="BA18" s="59">
+      <c r="BA18" s="45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB18" s="64"/>
-      <c r="BC18" s="62">
+      <c r="BB18" s="50"/>
+      <c r="BC18" s="48">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD18" s="63">
+      <c r="BD18" s="49">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -2970,12 +2970,12 @@
       <c r="H19" s="37"/>
       <c r="I19" s="41"/>
       <c r="J19" s="37"/>
-      <c r="K19" s="59">
+      <c r="K19" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L19" s="41"/>
-      <c r="M19" s="59">
+      <c r="M19" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2983,16 +2983,16 @@
       <c r="O19" s="41"/>
       <c r="P19" s="41"/>
       <c r="Q19" s="41"/>
-      <c r="R19" s="59">
+      <c r="R19" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S19" s="41"/>
-      <c r="T19" s="59">
+      <c r="T19" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U19" s="64"/>
+      <c r="U19" s="50"/>
       <c r="V19" s="41"/>
       <c r="W19" s="41"/>
       <c r="X19" s="41"/>
@@ -3008,7 +3008,7 @@
       <c r="AH19" s="41"/>
       <c r="AI19" s="41"/>
       <c r="AJ19" s="41"/>
-      <c r="AK19" s="59">
+      <c r="AK19" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -3017,14 +3017,14 @@
       <c r="AN19" s="41"/>
       <c r="AO19" s="41"/>
       <c r="AP19" s="41"/>
-      <c r="AQ19" s="59">
+      <c r="AQ19" s="45">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AR19" s="41"/>
       <c r="AS19" s="41"/>
       <c r="AT19" s="41"/>
-      <c r="AU19" s="59">
+      <c r="AU19" s="45">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -3033,16 +3033,16 @@
       <c r="AX19" s="41"/>
       <c r="AY19" s="41"/>
       <c r="AZ19" s="41"/>
-      <c r="BA19" s="59">
+      <c r="BA19" s="45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB19" s="64"/>
-      <c r="BC19" s="62">
+      <c r="BB19" s="50"/>
+      <c r="BC19" s="48">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD19" s="63">
+      <c r="BD19" s="49">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -3069,12 +3069,12 @@
       <c r="H20" s="37"/>
       <c r="I20" s="37"/>
       <c r="J20" s="37"/>
-      <c r="K20" s="59">
+      <c r="K20" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L20" s="41"/>
-      <c r="M20" s="59">
+      <c r="M20" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3082,16 +3082,16 @@
       <c r="O20" s="41"/>
       <c r="P20" s="41"/>
       <c r="Q20" s="41"/>
-      <c r="R20" s="59">
+      <c r="R20" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S20" s="41"/>
-      <c r="T20" s="59">
+      <c r="T20" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U20" s="64"/>
+      <c r="U20" s="50"/>
       <c r="V20" s="41"/>
       <c r="W20" s="41"/>
       <c r="X20" s="41"/>
@@ -3107,7 +3107,7 @@
       <c r="AH20" s="41"/>
       <c r="AI20" s="41"/>
       <c r="AJ20" s="41"/>
-      <c r="AK20" s="59">
+      <c r="AK20" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -3115,15 +3115,15 @@
       <c r="AM20" s="41"/>
       <c r="AN20" s="41"/>
       <c r="AO20" s="41"/>
-      <c r="AP20" s="61"/>
-      <c r="AQ20" s="59">
+      <c r="AP20" s="47"/>
+      <c r="AQ20" s="45">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AR20" s="41"/>
       <c r="AS20" s="41"/>
       <c r="AT20" s="41"/>
-      <c r="AU20" s="59">
+      <c r="AU20" s="45">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -3132,16 +3132,16 @@
       <c r="AX20" s="41"/>
       <c r="AY20" s="41"/>
       <c r="AZ20" s="41"/>
-      <c r="BA20" s="59">
+      <c r="BA20" s="45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB20" s="64"/>
-      <c r="BC20" s="62">
+      <c r="BB20" s="50"/>
+      <c r="BC20" s="48">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD20" s="63">
+      <c r="BD20" s="49">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -3168,12 +3168,12 @@
       <c r="H21" s="37"/>
       <c r="I21" s="37"/>
       <c r="J21" s="37"/>
-      <c r="K21" s="59">
+      <c r="K21" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L21" s="41"/>
-      <c r="M21" s="59">
+      <c r="M21" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3181,16 +3181,16 @@
       <c r="O21" s="41"/>
       <c r="P21" s="41"/>
       <c r="Q21" s="41"/>
-      <c r="R21" s="59">
+      <c r="R21" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S21" s="41"/>
-      <c r="T21" s="59">
+      <c r="T21" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U21" s="64"/>
+      <c r="U21" s="50"/>
       <c r="V21" s="41"/>
       <c r="W21" s="41"/>
       <c r="X21" s="41"/>
@@ -3206,41 +3206,41 @@
       <c r="AH21" s="41"/>
       <c r="AI21" s="41"/>
       <c r="AJ21" s="41"/>
-      <c r="AK21" s="59">
+      <c r="AK21" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AL21" s="41"/>
-      <c r="AM21" s="61"/>
+      <c r="AM21" s="47"/>
       <c r="AN21" s="41"/>
       <c r="AO21" s="41"/>
-      <c r="AP21" s="61"/>
-      <c r="AQ21" s="59">
+      <c r="AP21" s="47"/>
+      <c r="AQ21" s="45">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AR21" s="41"/>
       <c r="AS21" s="41"/>
       <c r="AT21" s="41"/>
-      <c r="AU21" s="59">
+      <c r="AU21" s="45">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV21" s="41"/>
       <c r="AW21" s="41"/>
       <c r="AX21" s="41"/>
-      <c r="AY21" s="61"/>
+      <c r="AY21" s="47"/>
       <c r="AZ21" s="41"/>
-      <c r="BA21" s="59">
+      <c r="BA21" s="45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB21" s="64"/>
-      <c r="BC21" s="62">
+      <c r="BB21" s="50"/>
+      <c r="BC21" s="48">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD21" s="63">
+      <c r="BD21" s="49">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -3267,12 +3267,12 @@
       <c r="H22" s="37"/>
       <c r="I22" s="37"/>
       <c r="J22" s="37"/>
-      <c r="K22" s="59">
+      <c r="K22" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L22" s="41"/>
-      <c r="M22" s="59">
+      <c r="M22" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3280,16 +3280,16 @@
       <c r="O22" s="41"/>
       <c r="P22" s="41"/>
       <c r="Q22" s="41"/>
-      <c r="R22" s="59">
+      <c r="R22" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S22" s="41"/>
-      <c r="T22" s="59">
+      <c r="T22" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U22" s="64"/>
+      <c r="U22" s="50"/>
       <c r="V22" s="41"/>
       <c r="W22" s="41"/>
       <c r="X22" s="41"/>
@@ -3305,41 +3305,41 @@
       <c r="AH22" s="41"/>
       <c r="AI22" s="41"/>
       <c r="AJ22" s="41"/>
-      <c r="AK22" s="59">
+      <c r="AK22" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AL22" s="41"/>
       <c r="AM22" s="41"/>
-      <c r="AN22" s="61"/>
+      <c r="AN22" s="47"/>
       <c r="AO22" s="41"/>
-      <c r="AP22" s="61"/>
-      <c r="AQ22" s="59">
+      <c r="AP22" s="47"/>
+      <c r="AQ22" s="45">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AR22" s="41"/>
       <c r="AS22" s="41"/>
       <c r="AT22" s="41"/>
-      <c r="AU22" s="59">
+      <c r="AU22" s="45">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV22" s="41"/>
       <c r="AW22" s="41"/>
       <c r="AX22" s="41"/>
-      <c r="AY22" s="61"/>
-      <c r="AZ22" s="66"/>
-      <c r="BA22" s="59">
+      <c r="AY22" s="47"/>
+      <c r="AZ22" s="52"/>
+      <c r="BA22" s="45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB22" s="61"/>
-      <c r="BC22" s="62">
+      <c r="BB22" s="47"/>
+      <c r="BC22" s="48">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD22" s="63">
+      <c r="BD22" s="49">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -3366,12 +3366,12 @@
       <c r="H23" s="37"/>
       <c r="I23" s="37"/>
       <c r="J23" s="37"/>
-      <c r="K23" s="59">
+      <c r="K23" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L23" s="41"/>
-      <c r="M23" s="59">
+      <c r="M23" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3379,16 +3379,16 @@
       <c r="O23" s="41"/>
       <c r="P23" s="41"/>
       <c r="Q23" s="41"/>
-      <c r="R23" s="59">
+      <c r="R23" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S23" s="41"/>
-      <c r="T23" s="59">
+      <c r="T23" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U23" s="64"/>
+      <c r="U23" s="50"/>
       <c r="V23" s="41"/>
       <c r="W23" s="41"/>
       <c r="X23" s="41"/>
@@ -3404,41 +3404,41 @@
       <c r="AH23" s="41"/>
       <c r="AI23" s="41"/>
       <c r="AJ23" s="41"/>
-      <c r="AK23" s="59">
+      <c r="AK23" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AL23" s="41"/>
       <c r="AM23" s="41"/>
       <c r="AN23" s="41"/>
-      <c r="AO23" s="61"/>
+      <c r="AO23" s="47"/>
       <c r="AP23" s="41"/>
-      <c r="AQ23" s="59">
+      <c r="AQ23" s="45">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AR23" s="41"/>
       <c r="AS23" s="41"/>
       <c r="AT23" s="41"/>
-      <c r="AU23" s="59">
+      <c r="AU23" s="45">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV23" s="41"/>
       <c r="AW23" s="41"/>
       <c r="AX23" s="41"/>
-      <c r="AY23" s="61"/>
-      <c r="AZ23" s="61"/>
-      <c r="BA23" s="59">
+      <c r="AY23" s="47"/>
+      <c r="AZ23" s="47"/>
+      <c r="BA23" s="45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BB23" s="41"/>
-      <c r="BC23" s="62">
+      <c r="BC23" s="48">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD23" s="63">
+      <c r="BD23" s="49">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -3465,12 +3465,12 @@
       <c r="H24" s="37"/>
       <c r="I24" s="37"/>
       <c r="J24" s="37"/>
-      <c r="K24" s="59">
+      <c r="K24" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L24" s="41"/>
-      <c r="M24" s="59">
+      <c r="M24" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3478,16 +3478,16 @@
       <c r="O24" s="41"/>
       <c r="P24" s="41"/>
       <c r="Q24" s="41"/>
-      <c r="R24" s="59">
+      <c r="R24" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S24" s="41"/>
-      <c r="T24" s="59">
+      <c r="T24" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U24" s="64"/>
+      <c r="U24" s="50"/>
       <c r="V24" s="41"/>
       <c r="W24" s="41"/>
       <c r="X24" s="41"/>
@@ -3503,7 +3503,7 @@
       <c r="AH24" s="41"/>
       <c r="AI24" s="41"/>
       <c r="AJ24" s="41"/>
-      <c r="AK24" s="59">
+      <c r="AK24" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -3511,33 +3511,33 @@
       <c r="AM24" s="41"/>
       <c r="AN24" s="41"/>
       <c r="AO24" s="41"/>
-      <c r="AP24" s="61"/>
-      <c r="AQ24" s="59">
+      <c r="AP24" s="47"/>
+      <c r="AQ24" s="45">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AR24" s="41"/>
       <c r="AS24" s="41"/>
       <c r="AT24" s="41"/>
-      <c r="AU24" s="59">
+      <c r="AU24" s="45">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV24" s="41"/>
       <c r="AW24" s="41"/>
       <c r="AX24" s="41"/>
-      <c r="AY24" s="61"/>
+      <c r="AY24" s="47"/>
       <c r="AZ24" s="41"/>
-      <c r="BA24" s="59">
+      <c r="BA24" s="45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BB24" s="41"/>
-      <c r="BC24" s="62">
+      <c r="BC24" s="48">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD24" s="63">
+      <c r="BD24" s="49">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -3564,12 +3564,12 @@
       <c r="H25" s="44"/>
       <c r="I25" s="37"/>
       <c r="J25" s="41"/>
-      <c r="K25" s="59">
+      <c r="K25" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L25" s="41"/>
-      <c r="M25" s="59">
+      <c r="M25" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3577,16 +3577,16 @@
       <c r="O25" s="41"/>
       <c r="P25" s="41"/>
       <c r="Q25" s="41"/>
-      <c r="R25" s="59">
+      <c r="R25" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S25" s="41"/>
-      <c r="T25" s="59">
+      <c r="T25" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U25" s="64"/>
+      <c r="U25" s="50"/>
       <c r="V25" s="41"/>
       <c r="W25" s="41"/>
       <c r="X25" s="41"/>
@@ -3602,7 +3602,7 @@
       <c r="AH25" s="41"/>
       <c r="AI25" s="41"/>
       <c r="AJ25" s="41"/>
-      <c r="AK25" s="59">
+      <c r="AK25" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -3611,32 +3611,32 @@
       <c r="AN25" s="41"/>
       <c r="AO25" s="41"/>
       <c r="AP25" s="41"/>
-      <c r="AQ25" s="59">
+      <c r="AQ25" s="45">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AR25" s="41"/>
       <c r="AS25" s="41"/>
       <c r="AT25" s="41"/>
-      <c r="AU25" s="59">
+      <c r="AU25" s="45">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV25" s="41"/>
       <c r="AW25" s="41"/>
       <c r="AX25" s="41"/>
-      <c r="AY25" s="61"/>
+      <c r="AY25" s="47"/>
       <c r="AZ25" s="41"/>
-      <c r="BA25" s="59">
+      <c r="BA25" s="45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BB25" s="41"/>
-      <c r="BC25" s="62">
+      <c r="BC25" s="48">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD25" s="63">
+      <c r="BD25" s="49">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -3663,12 +3663,12 @@
       <c r="H26" s="37"/>
       <c r="I26" s="37"/>
       <c r="J26" s="37"/>
-      <c r="K26" s="59">
+      <c r="K26" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L26" s="41"/>
-      <c r="M26" s="59">
+      <c r="M26" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3676,16 +3676,16 @@
       <c r="O26" s="41"/>
       <c r="P26" s="41"/>
       <c r="Q26" s="41"/>
-      <c r="R26" s="59">
+      <c r="R26" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S26" s="41"/>
-      <c r="T26" s="59">
+      <c r="T26" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U26" s="64"/>
+      <c r="U26" s="50"/>
       <c r="V26" s="41"/>
       <c r="W26" s="41"/>
       <c r="X26" s="41"/>
@@ -3701,7 +3701,7 @@
       <c r="AH26" s="41"/>
       <c r="AI26" s="41"/>
       <c r="AJ26" s="41"/>
-      <c r="AK26" s="59">
+      <c r="AK26" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -3710,32 +3710,32 @@
       <c r="AN26" s="41"/>
       <c r="AO26" s="41"/>
       <c r="AP26" s="41"/>
-      <c r="AQ26" s="59">
+      <c r="AQ26" s="45">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AR26" s="41"/>
       <c r="AS26" s="41"/>
       <c r="AT26" s="41"/>
-      <c r="AU26" s="59">
+      <c r="AU26" s="45">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV26" s="41"/>
       <c r="AW26" s="41"/>
       <c r="AX26" s="41"/>
-      <c r="AY26" s="61"/>
+      <c r="AY26" s="47"/>
       <c r="AZ26" s="41"/>
-      <c r="BA26" s="59">
+      <c r="BA26" s="45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB26" s="64"/>
-      <c r="BC26" s="62">
+      <c r="BB26" s="50"/>
+      <c r="BC26" s="48">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD26" s="63">
+      <c r="BD26" s="49">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -3762,12 +3762,12 @@
       <c r="H27" s="37"/>
       <c r="I27" s="37"/>
       <c r="J27" s="37"/>
-      <c r="K27" s="59">
+      <c r="K27" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L27" s="41"/>
-      <c r="M27" s="59">
+      <c r="M27" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3775,16 +3775,16 @@
       <c r="O27" s="41"/>
       <c r="P27" s="41"/>
       <c r="Q27" s="41"/>
-      <c r="R27" s="59">
+      <c r="R27" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S27" s="41"/>
-      <c r="T27" s="59">
+      <c r="T27" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U27" s="64"/>
+      <c r="U27" s="50"/>
       <c r="V27" s="41"/>
       <c r="W27" s="41"/>
       <c r="X27" s="41"/>
@@ -3800,7 +3800,7 @@
       <c r="AH27" s="41"/>
       <c r="AI27" s="41"/>
       <c r="AJ27" s="41"/>
-      <c r="AK27" s="59">
+      <c r="AK27" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -3808,33 +3808,33 @@
       <c r="AM27" s="41"/>
       <c r="AN27" s="41"/>
       <c r="AO27" s="41"/>
-      <c r="AP27" s="61"/>
-      <c r="AQ27" s="59">
+      <c r="AP27" s="47"/>
+      <c r="AQ27" s="45">
         <f t="shared" ref="AQ27:AQ35" si="12">AM27-AN27-AO27-AP27</f>
         <v>0</v>
       </c>
       <c r="AR27" s="41"/>
       <c r="AS27" s="41"/>
       <c r="AT27" s="41"/>
-      <c r="AU27" s="59">
+      <c r="AU27" s="45">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV27" s="41"/>
       <c r="AW27" s="41"/>
       <c r="AX27" s="41"/>
-      <c r="AY27" s="61"/>
+      <c r="AY27" s="47"/>
       <c r="AZ27" s="41"/>
-      <c r="BA27" s="59">
+      <c r="BA27" s="45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BB27" s="41"/>
-      <c r="BC27" s="62">
+      <c r="BC27" s="48">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD27" s="63">
+      <c r="BD27" s="49">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -3861,12 +3861,12 @@
       <c r="H28" s="37"/>
       <c r="I28" s="37"/>
       <c r="J28" s="37"/>
-      <c r="K28" s="59">
+      <c r="K28" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L28" s="41"/>
-      <c r="M28" s="59">
+      <c r="M28" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3874,16 +3874,16 @@
       <c r="O28" s="41"/>
       <c r="P28" s="41"/>
       <c r="Q28" s="41"/>
-      <c r="R28" s="59">
+      <c r="R28" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S28" s="41"/>
-      <c r="T28" s="59">
+      <c r="T28" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U28" s="64"/>
+      <c r="U28" s="50"/>
       <c r="V28" s="41"/>
       <c r="W28" s="41"/>
       <c r="X28" s="41"/>
@@ -3899,41 +3899,41 @@
       <c r="AH28" s="41"/>
       <c r="AI28" s="41"/>
       <c r="AJ28" s="41"/>
-      <c r="AK28" s="59">
+      <c r="AK28" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AL28" s="41"/>
-      <c r="AM28" s="61"/>
+      <c r="AM28" s="47"/>
       <c r="AN28" s="41"/>
       <c r="AO28" s="41"/>
-      <c r="AP28" s="61"/>
-      <c r="AQ28" s="59">
+      <c r="AP28" s="47"/>
+      <c r="AQ28" s="45">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AR28" s="41"/>
       <c r="AS28" s="41"/>
       <c r="AT28" s="41"/>
-      <c r="AU28" s="59">
+      <c r="AU28" s="45">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV28" s="41"/>
       <c r="AW28" s="41"/>
       <c r="AX28" s="41"/>
-      <c r="AY28" s="61"/>
-      <c r="AZ28" s="61"/>
-      <c r="BA28" s="59">
+      <c r="AY28" s="47"/>
+      <c r="AZ28" s="47"/>
+      <c r="BA28" s="45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB28" s="64"/>
-      <c r="BC28" s="62">
+      <c r="BB28" s="50"/>
+      <c r="BC28" s="48">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD28" s="63">
+      <c r="BD28" s="49">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -3960,12 +3960,12 @@
       <c r="H29" s="37"/>
       <c r="I29" s="37"/>
       <c r="J29" s="37"/>
-      <c r="K29" s="59">
+      <c r="K29" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L29" s="41"/>
-      <c r="M29" s="59">
+      <c r="M29" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3973,16 +3973,16 @@
       <c r="O29" s="41"/>
       <c r="P29" s="41"/>
       <c r="Q29" s="41"/>
-      <c r="R29" s="59">
+      <c r="R29" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S29" s="41"/>
-      <c r="T29" s="59">
+      <c r="T29" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U29" s="64"/>
+      <c r="U29" s="50"/>
       <c r="V29" s="41"/>
       <c r="W29" s="41"/>
       <c r="X29" s="41"/>
@@ -3998,41 +3998,41 @@
       <c r="AH29" s="41"/>
       <c r="AI29" s="41"/>
       <c r="AJ29" s="41"/>
-      <c r="AK29" s="59">
+      <c r="AK29" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AL29" s="41"/>
-      <c r="AM29" s="61"/>
-      <c r="AN29" s="61"/>
+      <c r="AM29" s="47"/>
+      <c r="AN29" s="47"/>
       <c r="AO29" s="41"/>
       <c r="AP29" s="41"/>
-      <c r="AQ29" s="59">
+      <c r="AQ29" s="45">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AR29" s="41"/>
       <c r="AS29" s="41"/>
       <c r="AT29" s="41"/>
-      <c r="AU29" s="59">
+      <c r="AU29" s="45">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV29" s="41"/>
       <c r="AW29" s="41"/>
       <c r="AX29" s="41"/>
-      <c r="AY29" s="61"/>
+      <c r="AY29" s="47"/>
       <c r="AZ29" s="41"/>
-      <c r="BA29" s="59">
+      <c r="BA29" s="45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BB29" s="41"/>
-      <c r="BC29" s="62">
+      <c r="BC29" s="48">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD29" s="63">
+      <c r="BD29" s="49">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -4059,12 +4059,12 @@
       <c r="H30" s="37"/>
       <c r="I30" s="37"/>
       <c r="J30" s="37"/>
-      <c r="K30" s="59">
+      <c r="K30" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L30" s="41"/>
-      <c r="M30" s="59">
+      <c r="M30" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4072,16 +4072,16 @@
       <c r="O30" s="41"/>
       <c r="P30" s="41"/>
       <c r="Q30" s="41"/>
-      <c r="R30" s="59">
+      <c r="R30" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S30" s="41"/>
-      <c r="T30" s="59">
+      <c r="T30" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U30" s="64"/>
+      <c r="U30" s="50"/>
       <c r="V30" s="41"/>
       <c r="W30" s="41"/>
       <c r="X30" s="41"/>
@@ -4097,7 +4097,7 @@
       <c r="AH30" s="41"/>
       <c r="AI30" s="41"/>
       <c r="AJ30" s="41"/>
-      <c r="AK30" s="59">
+      <c r="AK30" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -4106,32 +4106,32 @@
       <c r="AN30" s="41"/>
       <c r="AO30" s="41"/>
       <c r="AP30" s="41"/>
-      <c r="AQ30" s="59">
+      <c r="AQ30" s="45">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AR30" s="41"/>
       <c r="AS30" s="41"/>
       <c r="AT30" s="41"/>
-      <c r="AU30" s="59">
+      <c r="AU30" s="45">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV30" s="41"/>
       <c r="AW30" s="41"/>
       <c r="AX30" s="41"/>
-      <c r="AY30" s="61"/>
+      <c r="AY30" s="47"/>
       <c r="AZ30" s="41"/>
-      <c r="BA30" s="59">
+      <c r="BA30" s="45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BB30" s="41"/>
-      <c r="BC30" s="62">
+      <c r="BC30" s="48">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD30" s="63">
+      <c r="BD30" s="49">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -4158,12 +4158,12 @@
       <c r="H31" s="37"/>
       <c r="I31" s="37"/>
       <c r="J31" s="37"/>
-      <c r="K31" s="59">
+      <c r="K31" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L31" s="41"/>
-      <c r="M31" s="59">
+      <c r="M31" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4171,16 +4171,16 @@
       <c r="O31" s="41"/>
       <c r="P31" s="41"/>
       <c r="Q31" s="41"/>
-      <c r="R31" s="59">
+      <c r="R31" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S31" s="41"/>
-      <c r="T31" s="59">
+      <c r="T31" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U31" s="64"/>
+      <c r="U31" s="50"/>
       <c r="V31" s="41"/>
       <c r="W31" s="41"/>
       <c r="X31" s="41"/>
@@ -4196,41 +4196,41 @@
       <c r="AH31" s="41"/>
       <c r="AI31" s="41"/>
       <c r="AJ31" s="41"/>
-      <c r="AK31" s="59">
+      <c r="AK31" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AL31" s="64"/>
+      <c r="AL31" s="50"/>
       <c r="AM31" s="41"/>
       <c r="AN31" s="41"/>
       <c r="AO31" s="41"/>
       <c r="AP31" s="41"/>
-      <c r="AQ31" s="59">
+      <c r="AQ31" s="45">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AR31" s="41"/>
       <c r="AS31" s="41"/>
       <c r="AT31" s="41"/>
-      <c r="AU31" s="59">
+      <c r="AU31" s="45">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV31" s="41"/>
       <c r="AW31" s="41"/>
       <c r="AX31" s="41"/>
-      <c r="AY31" s="61"/>
-      <c r="AZ31" s="61"/>
-      <c r="BA31" s="59">
+      <c r="AY31" s="47"/>
+      <c r="AZ31" s="47"/>
+      <c r="BA31" s="45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BB31" s="41"/>
-      <c r="BC31" s="62">
+      <c r="BC31" s="48">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD31" s="63">
+      <c r="BD31" s="49">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -4257,12 +4257,12 @@
       <c r="H32" s="37"/>
       <c r="I32" s="37"/>
       <c r="J32" s="37"/>
-      <c r="K32" s="59">
+      <c r="K32" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L32" s="41"/>
-      <c r="M32" s="59">
+      <c r="M32" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4270,16 +4270,16 @@
       <c r="O32" s="41"/>
       <c r="P32" s="41"/>
       <c r="Q32" s="41"/>
-      <c r="R32" s="59">
+      <c r="R32" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S32" s="41"/>
-      <c r="T32" s="59">
+      <c r="T32" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U32" s="64"/>
+      <c r="U32" s="50"/>
       <c r="V32" s="41"/>
       <c r="W32" s="41"/>
       <c r="X32" s="41"/>
@@ -4295,41 +4295,41 @@
       <c r="AH32" s="41"/>
       <c r="AI32" s="41"/>
       <c r="AJ32" s="41"/>
-      <c r="AK32" s="59">
+      <c r="AK32" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AL32" s="64"/>
-      <c r="AM32" s="61"/>
+      <c r="AL32" s="50"/>
+      <c r="AM32" s="47"/>
       <c r="AN32" s="41"/>
       <c r="AO32" s="41"/>
       <c r="AP32" s="41"/>
-      <c r="AQ32" s="59">
+      <c r="AQ32" s="45">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AR32" s="41"/>
       <c r="AS32" s="41"/>
       <c r="AT32" s="41"/>
-      <c r="AU32" s="59">
+      <c r="AU32" s="45">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV32" s="41"/>
       <c r="AW32" s="41"/>
       <c r="AX32" s="41"/>
-      <c r="AY32" s="61"/>
+      <c r="AY32" s="47"/>
       <c r="AZ32" s="41"/>
-      <c r="BA32" s="59">
+      <c r="BA32" s="45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BB32" s="41"/>
-      <c r="BC32" s="62">
+      <c r="BC32" s="48">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD32" s="63">
+      <c r="BD32" s="49">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -4356,12 +4356,12 @@
       <c r="H33" s="37"/>
       <c r="I33" s="37"/>
       <c r="J33" s="37"/>
-      <c r="K33" s="59">
+      <c r="K33" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L33" s="41"/>
-      <c r="M33" s="59">
+      <c r="M33" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4369,16 +4369,16 @@
       <c r="O33" s="41"/>
       <c r="P33" s="41"/>
       <c r="Q33" s="41"/>
-      <c r="R33" s="59">
+      <c r="R33" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S33" s="41"/>
-      <c r="T33" s="59">
+      <c r="T33" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U33" s="64"/>
+      <c r="U33" s="50"/>
       <c r="V33" s="41"/>
       <c r="W33" s="41"/>
       <c r="X33" s="41"/>
@@ -4394,41 +4394,41 @@
       <c r="AH33" s="41"/>
       <c r="AI33" s="41"/>
       <c r="AJ33" s="41"/>
-      <c r="AK33" s="59">
+      <c r="AK33" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AL33" s="64"/>
-      <c r="AM33" s="61"/>
+      <c r="AL33" s="50"/>
+      <c r="AM33" s="47"/>
       <c r="AN33" s="41"/>
       <c r="AO33" s="41"/>
       <c r="AP33" s="41"/>
-      <c r="AQ33" s="59">
+      <c r="AQ33" s="45">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AR33" s="41"/>
       <c r="AS33" s="41"/>
       <c r="AT33" s="41"/>
-      <c r="AU33" s="59">
+      <c r="AU33" s="45">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV33" s="41"/>
       <c r="AW33" s="41"/>
       <c r="AX33" s="41"/>
-      <c r="AY33" s="61"/>
+      <c r="AY33" s="47"/>
       <c r="AZ33" s="41"/>
-      <c r="BA33" s="59">
+      <c r="BA33" s="45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BB33" s="41"/>
-      <c r="BC33" s="62">
+      <c r="BC33" s="48">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD33" s="63">
+      <c r="BD33" s="49">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -4455,12 +4455,12 @@
       <c r="H34" s="37"/>
       <c r="I34" s="37"/>
       <c r="J34" s="37"/>
-      <c r="K34" s="59">
+      <c r="K34" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L34" s="41"/>
-      <c r="M34" s="59">
+      <c r="M34" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4468,16 +4468,16 @@
       <c r="O34" s="41"/>
       <c r="P34" s="41"/>
       <c r="Q34" s="41"/>
-      <c r="R34" s="59">
+      <c r="R34" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S34" s="41"/>
-      <c r="T34" s="59">
+      <c r="T34" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U34" s="64"/>
+      <c r="U34" s="50"/>
       <c r="V34" s="41"/>
       <c r="W34" s="41"/>
       <c r="X34" s="41"/>
@@ -4493,41 +4493,41 @@
       <c r="AH34" s="41"/>
       <c r="AI34" s="41"/>
       <c r="AJ34" s="41"/>
-      <c r="AK34" s="59">
+      <c r="AK34" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AL34" s="64"/>
-      <c r="AM34" s="61"/>
+      <c r="AL34" s="50"/>
+      <c r="AM34" s="47"/>
       <c r="AN34" s="41"/>
       <c r="AO34" s="41"/>
       <c r="AP34" s="41"/>
-      <c r="AQ34" s="59">
+      <c r="AQ34" s="45">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AR34" s="41"/>
       <c r="AS34" s="41"/>
       <c r="AT34" s="41"/>
-      <c r="AU34" s="59">
+      <c r="AU34" s="45">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV34" s="41"/>
       <c r="AW34" s="41"/>
       <c r="AX34" s="41"/>
-      <c r="AY34" s="61"/>
+      <c r="AY34" s="47"/>
       <c r="AZ34" s="41"/>
-      <c r="BA34" s="59">
+      <c r="BA34" s="45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BB34" s="41"/>
-      <c r="BC34" s="62">
+      <c r="BC34" s="48">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD34" s="63">
+      <c r="BD34" s="49">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -4550,12 +4550,12 @@
       <c r="H35" s="37"/>
       <c r="I35" s="37"/>
       <c r="J35" s="37"/>
-      <c r="K35" s="59">
+      <c r="K35" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L35" s="41"/>
-      <c r="M35" s="59">
+      <c r="M35" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4563,16 +4563,16 @@
       <c r="O35" s="41"/>
       <c r="P35" s="41"/>
       <c r="Q35" s="41"/>
-      <c r="R35" s="59">
+      <c r="R35" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S35" s="41"/>
-      <c r="T35" s="59">
+      <c r="T35" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U35" s="64"/>
+      <c r="U35" s="50"/>
       <c r="V35" s="41"/>
       <c r="W35" s="41"/>
       <c r="X35" s="41"/>
@@ -4588,41 +4588,41 @@
       <c r="AH35" s="41"/>
       <c r="AI35" s="41"/>
       <c r="AJ35" s="41"/>
-      <c r="AK35" s="59">
+      <c r="AK35" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AL35" s="64"/>
-      <c r="AM35" s="61"/>
+      <c r="AL35" s="50"/>
+      <c r="AM35" s="47"/>
       <c r="AN35" s="41"/>
       <c r="AO35" s="41"/>
       <c r="AP35" s="41"/>
-      <c r="AQ35" s="59">
+      <c r="AQ35" s="45">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AR35" s="41"/>
       <c r="AS35" s="41"/>
       <c r="AT35" s="41"/>
-      <c r="AU35" s="59">
+      <c r="AU35" s="45">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV35" s="41"/>
       <c r="AW35" s="41"/>
       <c r="AX35" s="41"/>
-      <c r="AY35" s="61"/>
+      <c r="AY35" s="47"/>
       <c r="AZ35" s="41"/>
-      <c r="BA35" s="59">
+      <c r="BA35" s="45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BB35" s="41"/>
-      <c r="BC35" s="62">
+      <c r="BC35" s="48">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD35" s="63">
+      <c r="BD35" s="49">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -4662,184 +4662,184 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="K36" s="67">
+      <c r="K36" s="53">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="L36" s="67">
+      <c r="L36" s="53">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="M36" s="67">
+      <c r="M36" s="53">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="N36" s="67">
+      <c r="N36" s="53">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="O36" s="67">
+      <c r="O36" s="53">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="P36" s="67">
+      <c r="P36" s="53">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="Q36" s="67">
+      <c r="Q36" s="53">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="R36" s="67">
+      <c r="R36" s="53">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="S36" s="67">
+      <c r="S36" s="53">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="T36" s="67">
+      <c r="T36" s="53">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="U36" s="67">
+      <c r="U36" s="53">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V36" s="67">
+      <c r="V36" s="53">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="W36" s="67">
+      <c r="W36" s="53">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="X36" s="67">
+      <c r="X36" s="53">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="Y36" s="67">
+      <c r="Y36" s="53">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="Z36" s="67">
+      <c r="Z36" s="53">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AA36" s="67">
+      <c r="AA36" s="53">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AB36" s="67">
+      <c r="AB36" s="53">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AC36" s="67">
+      <c r="AC36" s="53">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AD36" s="67">
+      <c r="AD36" s="53">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AE36" s="67"/>
-      <c r="AF36" s="67">
+      <c r="AE36" s="53"/>
+      <c r="AF36" s="53">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AG36" s="67">
+      <c r="AG36" s="53">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AH36" s="67">
+      <c r="AH36" s="53">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AI36" s="67">
+      <c r="AI36" s="53">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AJ36" s="67">
+      <c r="AJ36" s="53">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AK36" s="67">
+      <c r="AK36" s="53">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AL36" s="67">
+      <c r="AL36" s="53">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AM36" s="67">
+      <c r="AM36" s="53">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AN36" s="67">
+      <c r="AN36" s="53">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AO36" s="67">
+      <c r="AO36" s="53">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP36" s="67">
+      <c r="AP36" s="53">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AQ36" s="67">
+      <c r="AQ36" s="53">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AR36" s="67">
+      <c r="AR36" s="53">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AS36" s="67">
+      <c r="AS36" s="53">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AT36" s="67">
+      <c r="AT36" s="53">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AU36" s="67">
+      <c r="AU36" s="53">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AV36" s="67">
+      <c r="AV36" s="53">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AW36" s="67">
+      <c r="AW36" s="53">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AX36" s="67">
+      <c r="AX36" s="53">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AY36" s="67">
+      <c r="AY36" s="53">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AZ36" s="67">
+      <c r="AZ36" s="53">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BA36" s="67">
+      <c r="BA36" s="53">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BB36" s="67">
+      <c r="BB36" s="53">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BC36" s="67">
+      <c r="BC36" s="53">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BD36" s="67">
+      <c r="BD36" s="53">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
@@ -14459,6 +14459,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="AC3:AC4"/>
+    <mergeCell ref="BC2:BC4"/>
+    <mergeCell ref="BD2:BD4"/>
+    <mergeCell ref="BE2:BE4"/>
+    <mergeCell ref="B2:C4"/>
+    <mergeCell ref="G2:G4"/>
+    <mergeCell ref="W3:W4"/>
+    <mergeCell ref="Y3:Y4"/>
+    <mergeCell ref="Z3:Z4"/>
+    <mergeCell ref="AA3:AA4"/>
+    <mergeCell ref="AB3:AB4"/>
     <mergeCell ref="A1:BE1"/>
     <mergeCell ref="I2:AA2"/>
     <mergeCell ref="AD2:BB2"/>
@@ -14475,17 +14486,6 @@
     <mergeCell ref="F2:F4"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="V3:V4"/>
-    <mergeCell ref="AC3:AC4"/>
-    <mergeCell ref="BC2:BC4"/>
-    <mergeCell ref="BD2:BD4"/>
-    <mergeCell ref="BE2:BE4"/>
-    <mergeCell ref="B2:C4"/>
-    <mergeCell ref="G2:G4"/>
-    <mergeCell ref="W3:W4"/>
-    <mergeCell ref="Y3:Y4"/>
-    <mergeCell ref="Z3:Z4"/>
-    <mergeCell ref="AA3:AA4"/>
-    <mergeCell ref="AB3:AB4"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14512,23 +14512,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="65" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
     </row>
     <row r="2" spans="1:9" s="2" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="57"/>
+      <c r="B2" s="66"/>
       <c r="C2" s="3" t="s">
         <v>82</v>
       </c>
@@ -15219,10 +15219,10 @@
       <c r="I33" s="11"/>
     </row>
     <row r="34" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="58" t="s">
+      <c r="A34" s="67" t="s">
         <v>86</v>
       </c>
-      <c r="B34" s="58"/>
+      <c r="B34" s="67"/>
       <c r="C34" s="9"/>
       <c r="D34" s="9">
         <f>SUM(D3:D33)</f>

--- a/finance/麦安研营业统计_格式化模板.xlsx
+++ b/finance/麦安研营业统计_格式化模板.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wadec\Documents\projects\mainyan-auto\finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E4C38AF-EB87-4DD7-B4EB-A6D80080FCA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B14CB826-A4EF-4E43-9ECC-7F017ED2A121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="120" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026年6月东方宝泰店营业额明细统计表" sheetId="1" r:id="rId1"/>
@@ -833,6 +833,21 @@
     <xf numFmtId="176" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="11" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -842,9 +857,6 @@
     <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -852,18 +864,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="11" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1194,247 +1194,247 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:57" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="59" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
-      <c r="M1" s="54"/>
-      <c r="N1" s="54"/>
-      <c r="O1" s="54"/>
-      <c r="P1" s="54"/>
-      <c r="Q1" s="54"/>
-      <c r="R1" s="54"/>
-      <c r="S1" s="54"/>
-      <c r="T1" s="54"/>
-      <c r="U1" s="54"/>
-      <c r="V1" s="54"/>
-      <c r="W1" s="54"/>
-      <c r="X1" s="54"/>
-      <c r="Y1" s="54"/>
-      <c r="Z1" s="54"/>
-      <c r="AA1" s="54"/>
-      <c r="AB1" s="54"/>
-      <c r="AC1" s="54"/>
-      <c r="AD1" s="54"/>
-      <c r="AE1" s="54"/>
-      <c r="AF1" s="54"/>
-      <c r="AG1" s="54"/>
-      <c r="AH1" s="54"/>
-      <c r="AI1" s="54"/>
-      <c r="AJ1" s="54"/>
-      <c r="AK1" s="54"/>
-      <c r="AL1" s="54"/>
-      <c r="AM1" s="54"/>
-      <c r="AN1" s="54"/>
-      <c r="AO1" s="54"/>
-      <c r="AP1" s="54"/>
-      <c r="AQ1" s="54"/>
-      <c r="AR1" s="54"/>
-      <c r="AS1" s="54"/>
-      <c r="AT1" s="54"/>
-      <c r="AU1" s="54"/>
-      <c r="AV1" s="54"/>
-      <c r="AW1" s="54"/>
-      <c r="AX1" s="54"/>
-      <c r="AY1" s="54"/>
-      <c r="AZ1" s="54"/>
-      <c r="BA1" s="54"/>
-      <c r="BB1" s="54"/>
-      <c r="BC1" s="54"/>
-      <c r="BD1" s="54"/>
-      <c r="BE1" s="54"/>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
+      <c r="K1" s="59"/>
+      <c r="L1" s="59"/>
+      <c r="M1" s="59"/>
+      <c r="N1" s="59"/>
+      <c r="O1" s="59"/>
+      <c r="P1" s="59"/>
+      <c r="Q1" s="59"/>
+      <c r="R1" s="59"/>
+      <c r="S1" s="59"/>
+      <c r="T1" s="59"/>
+      <c r="U1" s="59"/>
+      <c r="V1" s="59"/>
+      <c r="W1" s="59"/>
+      <c r="X1" s="59"/>
+      <c r="Y1" s="59"/>
+      <c r="Z1" s="59"/>
+      <c r="AA1" s="59"/>
+      <c r="AB1" s="59"/>
+      <c r="AC1" s="59"/>
+      <c r="AD1" s="59"/>
+      <c r="AE1" s="59"/>
+      <c r="AF1" s="59"/>
+      <c r="AG1" s="59"/>
+      <c r="AH1" s="59"/>
+      <c r="AI1" s="59"/>
+      <c r="AJ1" s="59"/>
+      <c r="AK1" s="59"/>
+      <c r="AL1" s="59"/>
+      <c r="AM1" s="59"/>
+      <c r="AN1" s="59"/>
+      <c r="AO1" s="59"/>
+      <c r="AP1" s="59"/>
+      <c r="AQ1" s="59"/>
+      <c r="AR1" s="59"/>
+      <c r="AS1" s="59"/>
+      <c r="AT1" s="59"/>
+      <c r="AU1" s="59"/>
+      <c r="AV1" s="59"/>
+      <c r="AW1" s="59"/>
+      <c r="AX1" s="59"/>
+      <c r="AY1" s="59"/>
+      <c r="AZ1" s="59"/>
+      <c r="BA1" s="59"/>
+      <c r="BB1" s="59"/>
+      <c r="BC1" s="59"/>
+      <c r="BD1" s="59"/>
+      <c r="BE1" s="59"/>
     </row>
     <row r="2" spans="1:57" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="57" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="57" t="s">
+      <c r="A2" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57" t="s">
+      <c r="C2" s="54"/>
+      <c r="D2" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="57" t="s">
+      <c r="E2" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="57" t="s">
+      <c r="F2" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="61" t="s">
+      <c r="G2" s="57" t="s">
         <v>107</v>
       </c>
-      <c r="H2" s="60" t="s">
+      <c r="H2" s="64" t="s">
         <v>88</v>
       </c>
-      <c r="I2" s="55" t="s">
+      <c r="I2" s="60" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
-      <c r="P2" s="55"/>
-      <c r="Q2" s="55"/>
-      <c r="R2" s="55"/>
-      <c r="S2" s="55"/>
-      <c r="T2" s="55"/>
-      <c r="U2" s="55"/>
-      <c r="V2" s="55"/>
-      <c r="W2" s="55"/>
-      <c r="X2" s="55"/>
-      <c r="Y2" s="55"/>
-      <c r="Z2" s="55"/>
-      <c r="AA2" s="55"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="60"/>
+      <c r="Q2" s="60"/>
+      <c r="R2" s="60"/>
+      <c r="S2" s="60"/>
+      <c r="T2" s="60"/>
+      <c r="U2" s="60"/>
+      <c r="V2" s="60"/>
+      <c r="W2" s="60"/>
+      <c r="X2" s="60"/>
+      <c r="Y2" s="60"/>
+      <c r="Z2" s="60"/>
+      <c r="AA2" s="60"/>
       <c r="AB2" s="25"/>
       <c r="AC2" s="25"/>
-      <c r="AD2" s="56" t="s">
+      <c r="AD2" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="AE2" s="56"/>
-      <c r="AF2" s="56"/>
-      <c r="AG2" s="56"/>
-      <c r="AH2" s="56"/>
-      <c r="AI2" s="56"/>
-      <c r="AJ2" s="56"/>
-      <c r="AK2" s="56"/>
-      <c r="AL2" s="56"/>
-      <c r="AM2" s="56"/>
-      <c r="AN2" s="56"/>
-      <c r="AO2" s="56"/>
-      <c r="AP2" s="56"/>
-      <c r="AQ2" s="56"/>
-      <c r="AR2" s="56"/>
-      <c r="AS2" s="56"/>
-      <c r="AT2" s="56"/>
-      <c r="AU2" s="56"/>
-      <c r="AV2" s="56"/>
-      <c r="AW2" s="56"/>
-      <c r="AX2" s="56"/>
-      <c r="AY2" s="56"/>
-      <c r="AZ2" s="56"/>
-      <c r="BA2" s="56"/>
-      <c r="BB2" s="56"/>
-      <c r="BC2" s="62" t="s">
+      <c r="AE2" s="61"/>
+      <c r="AF2" s="61"/>
+      <c r="AG2" s="61"/>
+      <c r="AH2" s="61"/>
+      <c r="AI2" s="61"/>
+      <c r="AJ2" s="61"/>
+      <c r="AK2" s="61"/>
+      <c r="AL2" s="61"/>
+      <c r="AM2" s="61"/>
+      <c r="AN2" s="61"/>
+      <c r="AO2" s="61"/>
+      <c r="AP2" s="61"/>
+      <c r="AQ2" s="61"/>
+      <c r="AR2" s="61"/>
+      <c r="AS2" s="61"/>
+      <c r="AT2" s="61"/>
+      <c r="AU2" s="61"/>
+      <c r="AV2" s="61"/>
+      <c r="AW2" s="61"/>
+      <c r="AX2" s="61"/>
+      <c r="AY2" s="61"/>
+      <c r="AZ2" s="61"/>
+      <c r="BA2" s="61"/>
+      <c r="BB2" s="61"/>
+      <c r="BC2" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="BD2" s="63" t="s">
+      <c r="BD2" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="BE2" s="57" t="s">
+      <c r="BE2" s="54" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:57" s="18" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="57"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="57" t="s">
+      <c r="A3" s="54"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="57"/>
-      <c r="K3" s="57"/>
-      <c r="L3" s="57"/>
-      <c r="M3" s="57"/>
-      <c r="N3" s="57"/>
+      <c r="J3" s="54"/>
+      <c r="K3" s="54"/>
+      <c r="L3" s="54"/>
+      <c r="M3" s="54"/>
+      <c r="N3" s="54"/>
       <c r="O3" s="23"/>
       <c r="P3" s="23"/>
-      <c r="Q3" s="57" t="s">
+      <c r="Q3" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="R3" s="57"/>
-      <c r="S3" s="57"/>
-      <c r="T3" s="57"/>
-      <c r="U3" s="57"/>
-      <c r="V3" s="61" t="s">
+      <c r="R3" s="54"/>
+      <c r="S3" s="54"/>
+      <c r="T3" s="54"/>
+      <c r="U3" s="54"/>
+      <c r="V3" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="W3" s="61" t="s">
+      <c r="W3" s="57" t="s">
         <v>13</v>
       </c>
       <c r="X3" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="Y3" s="64" t="s">
+      <c r="Y3" s="58" t="s">
         <v>14</v>
       </c>
-      <c r="Z3" s="64" t="s">
+      <c r="Z3" s="58" t="s">
         <v>15</v>
       </c>
-      <c r="AA3" s="57" t="s">
+      <c r="AA3" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="AB3" s="57" t="s">
+      <c r="AB3" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="AC3" s="57" t="s">
+      <c r="AC3" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="AD3" s="58" t="s">
+      <c r="AD3" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="AE3" s="58"/>
-      <c r="AF3" s="58"/>
-      <c r="AG3" s="58"/>
-      <c r="AH3" s="58"/>
-      <c r="AI3" s="58"/>
-      <c r="AJ3" s="58"/>
-      <c r="AK3" s="58"/>
-      <c r="AL3" s="58"/>
-      <c r="AM3" s="58" t="s">
+      <c r="AE3" s="62"/>
+      <c r="AF3" s="62"/>
+      <c r="AG3" s="62"/>
+      <c r="AH3" s="62"/>
+      <c r="AI3" s="62"/>
+      <c r="AJ3" s="62"/>
+      <c r="AK3" s="62"/>
+      <c r="AL3" s="62"/>
+      <c r="AM3" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="AN3" s="58"/>
-      <c r="AO3" s="58"/>
-      <c r="AP3" s="58"/>
-      <c r="AQ3" s="58"/>
-      <c r="AR3" s="58"/>
-      <c r="AS3" s="58" t="s">
+      <c r="AN3" s="62"/>
+      <c r="AO3" s="62"/>
+      <c r="AP3" s="62"/>
+      <c r="AQ3" s="62"/>
+      <c r="AR3" s="62"/>
+      <c r="AS3" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="AT3" s="58"/>
-      <c r="AU3" s="58"/>
+      <c r="AT3" s="62"/>
+      <c r="AU3" s="62"/>
       <c r="AV3" s="26"/>
-      <c r="AW3" s="59" t="s">
+      <c r="AW3" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="AX3" s="59"/>
-      <c r="AY3" s="58" t="s">
+      <c r="AX3" s="63"/>
+      <c r="AY3" s="62" t="s">
         <v>90</v>
       </c>
-      <c r="AZ3" s="58"/>
-      <c r="BA3" s="58"/>
-      <c r="BB3" s="58"/>
-      <c r="BC3" s="62"/>
-      <c r="BD3" s="63"/>
-      <c r="BE3" s="57"/>
+      <c r="AZ3" s="62"/>
+      <c r="BA3" s="62"/>
+      <c r="BB3" s="62"/>
+      <c r="BC3" s="55"/>
+      <c r="BD3" s="56"/>
+      <c r="BE3" s="54"/>
     </row>
     <row r="4" spans="1:57" s="18" customFormat="1" ht="87" x14ac:dyDescent="0.25">
-      <c r="A4" s="57"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="60"/>
+      <c r="A4" s="54"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="64"/>
       <c r="I4" s="23" t="s">
         <v>23</v>
       </c>
@@ -1474,16 +1474,16 @@
       <c r="U4" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="V4" s="61"/>
-      <c r="W4" s="61"/>
+      <c r="V4" s="57"/>
+      <c r="W4" s="57"/>
       <c r="X4" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="Y4" s="64"/>
-      <c r="Z4" s="64"/>
-      <c r="AA4" s="57"/>
-      <c r="AB4" s="57"/>
-      <c r="AC4" s="57"/>
+      <c r="Y4" s="58"/>
+      <c r="Z4" s="58"/>
+      <c r="AA4" s="54"/>
+      <c r="AB4" s="54"/>
+      <c r="AC4" s="54"/>
       <c r="AD4" s="24" t="s">
         <v>108</v>
       </c>
@@ -1559,9 +1559,9 @@
       <c r="BB4" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="BC4" s="62"/>
-      <c r="BD4" s="63"/>
-      <c r="BE4" s="57"/>
+      <c r="BC4" s="55"/>
+      <c r="BD4" s="56"/>
+      <c r="BE4" s="54"/>
     </row>
     <row r="5" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="23">
@@ -1653,11 +1653,11 @@
       </c>
       <c r="BB5" s="41"/>
       <c r="BC5" s="48">
-        <f t="shared" ref="BC5:BC35" si="7">F5+M5+T5+AK5+AQ5+AU5+AW5+BA5</f>
+        <f>G5+M5+T5+AK5+AQ5+AU5+AW5+BA5</f>
         <v>0</v>
       </c>
       <c r="BD5" s="49">
-        <f t="shared" ref="BD5:BD35" si="8">F5+K5+R5+AD5+AM5+AS5+AW5+AY5</f>
+        <f>G5+K5+R5+AE5+AM5+AS5+AW5+AY5</f>
         <v>0</v>
       </c>
       <c r="BE5" s="37"/>
@@ -1674,7 +1674,7 @@
         <v>46</v>
       </c>
       <c r="D6" s="36">
-        <f t="shared" ref="D6:D35" si="9">F6-E6</f>
+        <f t="shared" ref="D6:D35" si="7">F6-E6</f>
         <v>0</v>
       </c>
       <c r="E6" s="37"/>
@@ -1684,7 +1684,7 @@
       <c r="I6" s="37"/>
       <c r="J6" s="37"/>
       <c r="K6" s="45">
-        <f t="shared" ref="K6:K35" si="10">I6-J6</f>
+        <f t="shared" ref="K6:K35" si="8">I6-J6</f>
         <v>0</v>
       </c>
       <c r="L6" s="41"/>
@@ -1722,7 +1722,7 @@
       <c r="AI6" s="41"/>
       <c r="AJ6" s="41"/>
       <c r="AK6" s="45">
-        <f t="shared" ref="AK6:AK35" si="11">AE6+AF6-AG6-AH6-AI6-AJ6</f>
+        <f t="shared" ref="AK6:AK35" si="9">AE6+AF6-AG6-AH6-AI6-AJ6</f>
         <v>0</v>
       </c>
       <c r="AL6" s="41"/>
@@ -1752,11 +1752,11 @@
       </c>
       <c r="BB6" s="41"/>
       <c r="BC6" s="48">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="BC6:BC35" si="10">G6+M6+T6+AK6+AQ6+AU6+AW6+BA6</f>
         <v>0</v>
       </c>
       <c r="BD6" s="49">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="BD6:BD35" si="11">G6+K6+R6+AE6+AM6+AS6+AW6+AY6</f>
         <v>0</v>
       </c>
       <c r="BE6" s="37"/>
@@ -1773,7 +1773,7 @@
         <v>48</v>
       </c>
       <c r="D7" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E7" s="37"/>
@@ -1783,7 +1783,7 @@
       <c r="I7" s="37"/>
       <c r="J7" s="37"/>
       <c r="K7" s="45">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L7" s="41"/>
@@ -1821,7 +1821,7 @@
       <c r="AI7" s="41"/>
       <c r="AJ7" s="41"/>
       <c r="AK7" s="45">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AL7" s="41"/>
@@ -1851,11 +1851,11 @@
       </c>
       <c r="BB7" s="41"/>
       <c r="BC7" s="48">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BD7" s="49">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BE7" s="38"/>
@@ -1872,7 +1872,7 @@
         <v>50</v>
       </c>
       <c r="D8" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E8" s="37"/>
@@ -1882,7 +1882,7 @@
       <c r="I8" s="37"/>
       <c r="J8" s="37"/>
       <c r="K8" s="45">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L8" s="41"/>
@@ -1920,7 +1920,7 @@
       <c r="AI8" s="41"/>
       <c r="AJ8" s="41"/>
       <c r="AK8" s="45">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AL8" s="41"/>
@@ -1950,11 +1950,11 @@
       </c>
       <c r="BB8" s="41"/>
       <c r="BC8" s="48">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BD8" s="49">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BE8" s="39"/>
@@ -1971,7 +1971,7 @@
         <v>52</v>
       </c>
       <c r="D9" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E9" s="37"/>
@@ -1981,7 +1981,7 @@
       <c r="I9" s="37"/>
       <c r="J9" s="37"/>
       <c r="K9" s="45">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L9" s="41"/>
@@ -2019,7 +2019,7 @@
       <c r="AI9" s="41"/>
       <c r="AJ9" s="41"/>
       <c r="AK9" s="45">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AL9" s="41"/>
@@ -2049,11 +2049,11 @@
       </c>
       <c r="BB9" s="41"/>
       <c r="BC9" s="48">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BD9" s="49">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BE9" s="37"/>
@@ -2070,7 +2070,7 @@
         <v>54</v>
       </c>
       <c r="D10" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E10" s="37"/>
@@ -2080,7 +2080,7 @@
       <c r="I10" s="40"/>
       <c r="J10" s="37"/>
       <c r="K10" s="45">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L10" s="41"/>
@@ -2118,7 +2118,7 @@
       <c r="AI10" s="41"/>
       <c r="AJ10" s="41"/>
       <c r="AK10" s="45">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AL10" s="41"/>
@@ -2148,11 +2148,11 @@
       </c>
       <c r="BB10" s="41"/>
       <c r="BC10" s="48">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BD10" s="49">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BE10" s="37"/>
@@ -2169,7 +2169,7 @@
         <v>56</v>
       </c>
       <c r="D11" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E11" s="37"/>
@@ -2179,7 +2179,7 @@
       <c r="I11" s="37"/>
       <c r="J11" s="37"/>
       <c r="K11" s="45">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L11" s="41"/>
@@ -2217,7 +2217,7 @@
       <c r="AI11" s="41"/>
       <c r="AJ11" s="41"/>
       <c r="AK11" s="45">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AL11" s="41"/>
@@ -2247,11 +2247,11 @@
       </c>
       <c r="BB11" s="41"/>
       <c r="BC11" s="48">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BD11" s="49">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BE11" s="37"/>
@@ -2268,7 +2268,7 @@
         <v>44</v>
       </c>
       <c r="D12" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E12" s="37"/>
@@ -2278,7 +2278,7 @@
       <c r="I12" s="37"/>
       <c r="J12" s="37"/>
       <c r="K12" s="45">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L12" s="41"/>
@@ -2316,7 +2316,7 @@
       <c r="AI12" s="41"/>
       <c r="AJ12" s="41"/>
       <c r="AK12" s="45">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AL12" s="41"/>
@@ -2346,11 +2346,11 @@
       </c>
       <c r="BB12" s="41"/>
       <c r="BC12" s="48">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BD12" s="49">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BE12" s="37"/>
@@ -2367,7 +2367,7 @@
         <v>46</v>
       </c>
       <c r="D13" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E13" s="37"/>
@@ -2377,7 +2377,7 @@
       <c r="I13" s="37"/>
       <c r="J13" s="37"/>
       <c r="K13" s="45">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L13" s="41"/>
@@ -2415,7 +2415,7 @@
       <c r="AI13" s="41"/>
       <c r="AJ13" s="41"/>
       <c r="AK13" s="45">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AL13" s="41"/>
@@ -2445,11 +2445,11 @@
       </c>
       <c r="BB13" s="41"/>
       <c r="BC13" s="48">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BD13" s="49">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BE13" s="37"/>
@@ -2466,7 +2466,7 @@
         <v>48</v>
       </c>
       <c r="D14" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E14" s="37"/>
@@ -2476,7 +2476,7 @@
       <c r="I14" s="37"/>
       <c r="J14" s="37"/>
       <c r="K14" s="45">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L14" s="41"/>
@@ -2514,7 +2514,7 @@
       <c r="AI14" s="41"/>
       <c r="AJ14" s="41"/>
       <c r="AK14" s="45">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AL14" s="41"/>
@@ -2544,11 +2544,11 @@
       </c>
       <c r="BB14" s="41"/>
       <c r="BC14" s="48">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BD14" s="49">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BE14" s="37"/>
@@ -2565,7 +2565,7 @@
         <v>50</v>
       </c>
       <c r="D15" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E15" s="37"/>
@@ -2575,7 +2575,7 @@
       <c r="I15" s="37"/>
       <c r="J15" s="37"/>
       <c r="K15" s="45">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L15" s="41"/>
@@ -2613,7 +2613,7 @@
       <c r="AI15" s="41"/>
       <c r="AJ15" s="41"/>
       <c r="AK15" s="45">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AL15" s="41"/>
@@ -2643,11 +2643,11 @@
       </c>
       <c r="BB15" s="41"/>
       <c r="BC15" s="48">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BD15" s="49">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BE15" s="37"/>
@@ -2664,7 +2664,7 @@
         <v>52</v>
       </c>
       <c r="D16" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E16" s="37"/>
@@ -2674,7 +2674,7 @@
       <c r="I16" s="37"/>
       <c r="J16" s="37"/>
       <c r="K16" s="45">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L16" s="41"/>
@@ -2712,7 +2712,7 @@
       <c r="AI16" s="41"/>
       <c r="AJ16" s="41"/>
       <c r="AK16" s="45">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AL16" s="41"/>
@@ -2742,11 +2742,11 @@
       </c>
       <c r="BB16" s="41"/>
       <c r="BC16" s="48">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BD16" s="49">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BE16" s="37"/>
@@ -2763,7 +2763,7 @@
         <v>54</v>
       </c>
       <c r="D17" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E17" s="37"/>
@@ -2773,7 +2773,7 @@
       <c r="I17" s="37"/>
       <c r="J17" s="37"/>
       <c r="K17" s="45">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L17" s="41"/>
@@ -2811,7 +2811,7 @@
       <c r="AI17" s="41"/>
       <c r="AJ17" s="41"/>
       <c r="AK17" s="45">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AL17" s="41"/>
@@ -2841,11 +2841,11 @@
       </c>
       <c r="BB17" s="50"/>
       <c r="BC17" s="48">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BD17" s="49">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BE17" s="37"/>
@@ -2862,7 +2862,7 @@
         <v>56</v>
       </c>
       <c r="D18" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E18" s="37"/>
@@ -2872,7 +2872,7 @@
       <c r="I18" s="37"/>
       <c r="J18" s="37"/>
       <c r="K18" s="45">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L18" s="41"/>
@@ -2910,7 +2910,7 @@
       <c r="AI18" s="41"/>
       <c r="AJ18" s="41"/>
       <c r="AK18" s="45">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AL18" s="41"/>
@@ -2940,11 +2940,11 @@
       </c>
       <c r="BB18" s="50"/>
       <c r="BC18" s="48">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BD18" s="49">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BE18" s="37"/>
@@ -2961,7 +2961,7 @@
         <v>44</v>
       </c>
       <c r="D19" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E19" s="37"/>
@@ -2971,7 +2971,7 @@
       <c r="I19" s="41"/>
       <c r="J19" s="37"/>
       <c r="K19" s="45">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L19" s="41"/>
@@ -3009,7 +3009,7 @@
       <c r="AI19" s="41"/>
       <c r="AJ19" s="41"/>
       <c r="AK19" s="45">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AL19" s="41"/>
@@ -3039,11 +3039,11 @@
       </c>
       <c r="BB19" s="50"/>
       <c r="BC19" s="48">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BD19" s="49">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BE19" s="37"/>
@@ -3060,7 +3060,7 @@
         <v>46</v>
       </c>
       <c r="D20" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E20" s="37"/>
@@ -3070,7 +3070,7 @@
       <c r="I20" s="37"/>
       <c r="J20" s="37"/>
       <c r="K20" s="45">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L20" s="41"/>
@@ -3108,7 +3108,7 @@
       <c r="AI20" s="41"/>
       <c r="AJ20" s="41"/>
       <c r="AK20" s="45">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AL20" s="41"/>
@@ -3138,11 +3138,11 @@
       </c>
       <c r="BB20" s="50"/>
       <c r="BC20" s="48">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BD20" s="49">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BE20" s="37"/>
@@ -3159,7 +3159,7 @@
         <v>48</v>
       </c>
       <c r="D21" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E21" s="37"/>
@@ -3169,7 +3169,7 @@
       <c r="I21" s="37"/>
       <c r="J21" s="37"/>
       <c r="K21" s="45">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L21" s="41"/>
@@ -3207,7 +3207,7 @@
       <c r="AI21" s="41"/>
       <c r="AJ21" s="41"/>
       <c r="AK21" s="45">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AL21" s="41"/>
@@ -3237,11 +3237,11 @@
       </c>
       <c r="BB21" s="50"/>
       <c r="BC21" s="48">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BD21" s="49">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BE21" s="37"/>
@@ -3258,7 +3258,7 @@
         <v>50</v>
       </c>
       <c r="D22" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E22" s="37"/>
@@ -3268,7 +3268,7 @@
       <c r="I22" s="37"/>
       <c r="J22" s="37"/>
       <c r="K22" s="45">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L22" s="41"/>
@@ -3306,7 +3306,7 @@
       <c r="AI22" s="41"/>
       <c r="AJ22" s="41"/>
       <c r="AK22" s="45">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AL22" s="41"/>
@@ -3336,11 +3336,11 @@
       </c>
       <c r="BB22" s="47"/>
       <c r="BC22" s="48">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BD22" s="49">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BE22" s="42"/>
@@ -3357,7 +3357,7 @@
         <v>52</v>
       </c>
       <c r="D23" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E23" s="37"/>
@@ -3367,7 +3367,7 @@
       <c r="I23" s="37"/>
       <c r="J23" s="37"/>
       <c r="K23" s="45">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L23" s="41"/>
@@ -3405,7 +3405,7 @@
       <c r="AI23" s="41"/>
       <c r="AJ23" s="41"/>
       <c r="AK23" s="45">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AL23" s="41"/>
@@ -3435,11 +3435,11 @@
       </c>
       <c r="BB23" s="41"/>
       <c r="BC23" s="48">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BD23" s="49">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BE23" s="43"/>
@@ -3456,7 +3456,7 @@
         <v>54</v>
       </c>
       <c r="D24" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E24" s="37"/>
@@ -3466,7 +3466,7 @@
       <c r="I24" s="37"/>
       <c r="J24" s="37"/>
       <c r="K24" s="45">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L24" s="41"/>
@@ -3504,7 +3504,7 @@
       <c r="AI24" s="41"/>
       <c r="AJ24" s="41"/>
       <c r="AK24" s="45">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AL24" s="41"/>
@@ -3534,11 +3534,11 @@
       </c>
       <c r="BB24" s="41"/>
       <c r="BC24" s="48">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BD24" s="49">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BE24" s="43"/>
@@ -3555,7 +3555,7 @@
         <v>56</v>
       </c>
       <c r="D25" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E25" s="44"/>
@@ -3565,7 +3565,7 @@
       <c r="I25" s="37"/>
       <c r="J25" s="41"/>
       <c r="K25" s="45">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L25" s="41"/>
@@ -3603,7 +3603,7 @@
       <c r="AI25" s="41"/>
       <c r="AJ25" s="41"/>
       <c r="AK25" s="45">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AL25" s="41"/>
@@ -3633,11 +3633,11 @@
       </c>
       <c r="BB25" s="41"/>
       <c r="BC25" s="48">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BD25" s="49">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BE25" s="43"/>
@@ -3654,7 +3654,7 @@
         <v>44</v>
       </c>
       <c r="D26" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E26" s="37"/>
@@ -3664,7 +3664,7 @@
       <c r="I26" s="37"/>
       <c r="J26" s="37"/>
       <c r="K26" s="45">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L26" s="41"/>
@@ -3702,7 +3702,7 @@
       <c r="AI26" s="41"/>
       <c r="AJ26" s="41"/>
       <c r="AK26" s="45">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AL26" s="41"/>
@@ -3732,11 +3732,11 @@
       </c>
       <c r="BB26" s="50"/>
       <c r="BC26" s="48">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BD26" s="49">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BE26" s="43"/>
@@ -3753,7 +3753,7 @@
         <v>46</v>
       </c>
       <c r="D27" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E27" s="37"/>
@@ -3763,7 +3763,7 @@
       <c r="I27" s="37"/>
       <c r="J27" s="37"/>
       <c r="K27" s="45">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L27" s="41"/>
@@ -3801,7 +3801,7 @@
       <c r="AI27" s="41"/>
       <c r="AJ27" s="41"/>
       <c r="AK27" s="45">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AL27" s="41"/>
@@ -3831,11 +3831,11 @@
       </c>
       <c r="BB27" s="41"/>
       <c r="BC27" s="48">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BD27" s="49">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BE27" s="43"/>
@@ -3852,7 +3852,7 @@
         <v>48</v>
       </c>
       <c r="D28" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E28" s="37"/>
@@ -3862,7 +3862,7 @@
       <c r="I28" s="37"/>
       <c r="J28" s="37"/>
       <c r="K28" s="45">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L28" s="41"/>
@@ -3900,7 +3900,7 @@
       <c r="AI28" s="41"/>
       <c r="AJ28" s="41"/>
       <c r="AK28" s="45">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AL28" s="41"/>
@@ -3930,11 +3930,11 @@
       </c>
       <c r="BB28" s="50"/>
       <c r="BC28" s="48">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BD28" s="49">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BE28" s="43"/>
@@ -3951,7 +3951,7 @@
         <v>50</v>
       </c>
       <c r="D29" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E29" s="37"/>
@@ -3961,7 +3961,7 @@
       <c r="I29" s="37"/>
       <c r="J29" s="37"/>
       <c r="K29" s="45">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L29" s="41"/>
@@ -3999,7 +3999,7 @@
       <c r="AI29" s="41"/>
       <c r="AJ29" s="41"/>
       <c r="AK29" s="45">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AL29" s="41"/>
@@ -4029,11 +4029,11 @@
       </c>
       <c r="BB29" s="41"/>
       <c r="BC29" s="48">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BD29" s="49">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BE29" s="43"/>
@@ -4050,7 +4050,7 @@
         <v>52</v>
       </c>
       <c r="D30" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E30" s="37"/>
@@ -4060,7 +4060,7 @@
       <c r="I30" s="37"/>
       <c r="J30" s="37"/>
       <c r="K30" s="45">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L30" s="41"/>
@@ -4098,7 +4098,7 @@
       <c r="AI30" s="41"/>
       <c r="AJ30" s="41"/>
       <c r="AK30" s="45">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AL30" s="41"/>
@@ -4128,11 +4128,11 @@
       </c>
       <c r="BB30" s="41"/>
       <c r="BC30" s="48">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BD30" s="49">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BE30" s="43"/>
@@ -4149,7 +4149,7 @@
         <v>54</v>
       </c>
       <c r="D31" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E31" s="37"/>
@@ -4159,7 +4159,7 @@
       <c r="I31" s="37"/>
       <c r="J31" s="37"/>
       <c r="K31" s="45">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L31" s="41"/>
@@ -4197,7 +4197,7 @@
       <c r="AI31" s="41"/>
       <c r="AJ31" s="41"/>
       <c r="AK31" s="45">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AL31" s="50"/>
@@ -4227,11 +4227,11 @@
       </c>
       <c r="BB31" s="41"/>
       <c r="BC31" s="48">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BD31" s="49">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BE31" s="43"/>
@@ -4248,7 +4248,7 @@
         <v>56</v>
       </c>
       <c r="D32" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E32" s="37"/>
@@ -4258,7 +4258,7 @@
       <c r="I32" s="37"/>
       <c r="J32" s="37"/>
       <c r="K32" s="45">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L32" s="41"/>
@@ -4296,7 +4296,7 @@
       <c r="AI32" s="41"/>
       <c r="AJ32" s="41"/>
       <c r="AK32" s="45">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AL32" s="50"/>
@@ -4326,11 +4326,11 @@
       </c>
       <c r="BB32" s="41"/>
       <c r="BC32" s="48">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BD32" s="49">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BE32" s="37"/>
@@ -4347,7 +4347,7 @@
         <v>44</v>
       </c>
       <c r="D33" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E33" s="37"/>
@@ -4357,7 +4357,7 @@
       <c r="I33" s="37"/>
       <c r="J33" s="37"/>
       <c r="K33" s="45">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L33" s="41"/>
@@ -4395,7 +4395,7 @@
       <c r="AI33" s="41"/>
       <c r="AJ33" s="41"/>
       <c r="AK33" s="45">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AL33" s="50"/>
@@ -4425,11 +4425,11 @@
       </c>
       <c r="BB33" s="41"/>
       <c r="BC33" s="48">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BD33" s="49">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BE33" s="37"/>
@@ -4446,7 +4446,7 @@
         <v>46</v>
       </c>
       <c r="D34" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E34" s="37"/>
@@ -4456,7 +4456,7 @@
       <c r="I34" s="37"/>
       <c r="J34" s="37"/>
       <c r="K34" s="45">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L34" s="41"/>
@@ -4494,7 +4494,7 @@
       <c r="AI34" s="41"/>
       <c r="AJ34" s="41"/>
       <c r="AK34" s="45">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AL34" s="50"/>
@@ -4524,11 +4524,11 @@
       </c>
       <c r="BB34" s="41"/>
       <c r="BC34" s="48">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BD34" s="49">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BE34" s="37"/>
@@ -4541,7 +4541,7 @@
       <c r="B35" s="19"/>
       <c r="C35" s="19"/>
       <c r="D35" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E35" s="37"/>
@@ -4551,7 +4551,7 @@
       <c r="I35" s="37"/>
       <c r="J35" s="37"/>
       <c r="K35" s="45">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L35" s="41"/>
@@ -4589,7 +4589,7 @@
       <c r="AI35" s="41"/>
       <c r="AJ35" s="41"/>
       <c r="AK35" s="45">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AL35" s="50"/>
@@ -4619,11 +4619,11 @@
       </c>
       <c r="BB35" s="41"/>
       <c r="BC35" s="48">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BD35" s="49">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BE35" s="37"/>
@@ -14459,17 +14459,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="AC3:AC4"/>
-    <mergeCell ref="BC2:BC4"/>
-    <mergeCell ref="BD2:BD4"/>
-    <mergeCell ref="BE2:BE4"/>
-    <mergeCell ref="B2:C4"/>
-    <mergeCell ref="G2:G4"/>
-    <mergeCell ref="W3:W4"/>
-    <mergeCell ref="Y3:Y4"/>
-    <mergeCell ref="Z3:Z4"/>
-    <mergeCell ref="AA3:AA4"/>
-    <mergeCell ref="AB3:AB4"/>
     <mergeCell ref="A1:BE1"/>
     <mergeCell ref="I2:AA2"/>
     <mergeCell ref="AD2:BB2"/>
@@ -14486,6 +14475,17 @@
     <mergeCell ref="F2:F4"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="V3:V4"/>
+    <mergeCell ref="AC3:AC4"/>
+    <mergeCell ref="BC2:BC4"/>
+    <mergeCell ref="BD2:BD4"/>
+    <mergeCell ref="BE2:BE4"/>
+    <mergeCell ref="B2:C4"/>
+    <mergeCell ref="G2:G4"/>
+    <mergeCell ref="W3:W4"/>
+    <mergeCell ref="Y3:Y4"/>
+    <mergeCell ref="Z3:Z4"/>
+    <mergeCell ref="AA3:AA4"/>
+    <mergeCell ref="AB3:AB4"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/finance/麦安研营业统计_格式化模板.xlsx
+++ b/finance/麦安研营业统计_格式化模板.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wadec\Documents\projects\mainyan-auto\finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B14CB826-A4EF-4E43-9ECC-7F017ED2A121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD1B87E2-8E11-422C-9050-E5CF39032FCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="120" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026年6月东方宝泰店营业额明细统计表" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="114">
   <si>
     <t>序号</t>
   </si>
@@ -353,6 +353,24 @@
     <t>美团推广费</t>
     <phoneticPr fontId="23" type="noConversion"/>
   </si>
+  <si>
+    <t>高德口碑外卖后台</t>
+    <phoneticPr fontId="23" type="noConversion"/>
+  </si>
+  <si>
+    <t>订单金额</t>
+  </si>
+  <si>
+    <t>银行卡实收金额</t>
+  </si>
+  <si>
+    <t>商家优惠</t>
+    <phoneticPr fontId="23" type="noConversion"/>
+  </si>
+  <si>
+    <t>服务费</t>
+    <phoneticPr fontId="23" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -363,7 +381,7 @@
     <numFmt numFmtId="177" formatCode="0.00_);\(0.00\)"/>
     <numFmt numFmtId="178" formatCode="0.0_ "/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -548,6 +566,13 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -617,7 +642,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -664,13 +689,50 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -833,20 +895,8 @@
     <xf numFmtId="176" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="11" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -855,6 +905,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -866,6 +919,18 @@
     <xf numFmtId="176" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="11" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -874,6 +939,18 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1142,7 +1219,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BE199"/>
+  <dimension ref="A1:BJ199"/>
   <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.88671875" style="17" customWidth="1"/>
@@ -1187,254 +1264,271 @@
     <col min="51" max="51" width="10.88671875" style="17" customWidth="1"/>
     <col min="52" max="52" width="12.6640625" style="17" customWidth="1"/>
     <col min="53" max="53" width="14.5546875" style="17" customWidth="1"/>
-    <col min="54" max="54" width="13.33203125" style="17" hidden="1" customWidth="1"/>
-    <col min="55" max="55" width="12.21875" style="17" customWidth="1"/>
-    <col min="56" max="56" width="12.44140625" style="17" customWidth="1"/>
-    <col min="57" max="16384" width="10.33203125" style="17"/>
+    <col min="54" max="59" width="13.33203125" style="17" customWidth="1"/>
+    <col min="60" max="60" width="12.21875" style="17" customWidth="1"/>
+    <col min="61" max="61" width="12.44140625" style="17" customWidth="1"/>
+    <col min="62" max="16384" width="10.33203125" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:57" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="59" t="s">
+    <row r="1" spans="1:62" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="55" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
-      <c r="J1" s="59"/>
-      <c r="K1" s="59"/>
-      <c r="L1" s="59"/>
-      <c r="M1" s="59"/>
-      <c r="N1" s="59"/>
-      <c r="O1" s="59"/>
-      <c r="P1" s="59"/>
-      <c r="Q1" s="59"/>
-      <c r="R1" s="59"/>
-      <c r="S1" s="59"/>
-      <c r="T1" s="59"/>
-      <c r="U1" s="59"/>
-      <c r="V1" s="59"/>
-      <c r="W1" s="59"/>
-      <c r="X1" s="59"/>
-      <c r="Y1" s="59"/>
-      <c r="Z1" s="59"/>
-      <c r="AA1" s="59"/>
-      <c r="AB1" s="59"/>
-      <c r="AC1" s="59"/>
-      <c r="AD1" s="59"/>
-      <c r="AE1" s="59"/>
-      <c r="AF1" s="59"/>
-      <c r="AG1" s="59"/>
-      <c r="AH1" s="59"/>
-      <c r="AI1" s="59"/>
-      <c r="AJ1" s="59"/>
-      <c r="AK1" s="59"/>
-      <c r="AL1" s="59"/>
-      <c r="AM1" s="59"/>
-      <c r="AN1" s="59"/>
-      <c r="AO1" s="59"/>
-      <c r="AP1" s="59"/>
-      <c r="AQ1" s="59"/>
-      <c r="AR1" s="59"/>
-      <c r="AS1" s="59"/>
-      <c r="AT1" s="59"/>
-      <c r="AU1" s="59"/>
-      <c r="AV1" s="59"/>
-      <c r="AW1" s="59"/>
-      <c r="AX1" s="59"/>
-      <c r="AY1" s="59"/>
-      <c r="AZ1" s="59"/>
-      <c r="BA1" s="59"/>
-      <c r="BB1" s="59"/>
-      <c r="BC1" s="59"/>
-      <c r="BD1" s="59"/>
-      <c r="BE1" s="59"/>
-    </row>
-    <row r="2" spans="1:57" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="54" t="s">
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="55"/>
+      <c r="P1" s="55"/>
+      <c r="Q1" s="55"/>
+      <c r="R1" s="55"/>
+      <c r="S1" s="55"/>
+      <c r="T1" s="55"/>
+      <c r="U1" s="55"/>
+      <c r="V1" s="55"/>
+      <c r="W1" s="55"/>
+      <c r="X1" s="55"/>
+      <c r="Y1" s="55"/>
+      <c r="Z1" s="55"/>
+      <c r="AA1" s="55"/>
+      <c r="AB1" s="55"/>
+      <c r="AC1" s="55"/>
+      <c r="AD1" s="55"/>
+      <c r="AE1" s="55"/>
+      <c r="AF1" s="55"/>
+      <c r="AG1" s="55"/>
+      <c r="AH1" s="55"/>
+      <c r="AI1" s="55"/>
+      <c r="AJ1" s="55"/>
+      <c r="AK1" s="55"/>
+      <c r="AL1" s="55"/>
+      <c r="AM1" s="55"/>
+      <c r="AN1" s="55"/>
+      <c r="AO1" s="55"/>
+      <c r="AP1" s="55"/>
+      <c r="AQ1" s="55"/>
+      <c r="AR1" s="55"/>
+      <c r="AS1" s="55"/>
+      <c r="AT1" s="55"/>
+      <c r="AU1" s="55"/>
+      <c r="AV1" s="55"/>
+      <c r="AW1" s="55"/>
+      <c r="AX1" s="55"/>
+      <c r="AY1" s="55"/>
+      <c r="AZ1" s="55"/>
+      <c r="BA1" s="55"/>
+      <c r="BB1" s="55"/>
+      <c r="BC1" s="55"/>
+      <c r="BD1" s="55"/>
+      <c r="BE1" s="55"/>
+      <c r="BF1" s="55"/>
+      <c r="BG1" s="55"/>
+      <c r="BH1" s="55"/>
+      <c r="BI1" s="55"/>
+      <c r="BJ1" s="55"/>
+    </row>
+    <row r="2" spans="1:62" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="58" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54" t="s">
+      <c r="C2" s="58"/>
+      <c r="D2" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="54" t="s">
+      <c r="E2" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="54" t="s">
+      <c r="F2" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="57" t="s">
+      <c r="G2" s="62" t="s">
         <v>107</v>
       </c>
-      <c r="H2" s="64" t="s">
+      <c r="H2" s="61" t="s">
         <v>88</v>
       </c>
-      <c r="I2" s="60" t="s">
+      <c r="I2" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="60"/>
-      <c r="K2" s="60"/>
-      <c r="L2" s="60"/>
-      <c r="M2" s="60"/>
-      <c r="N2" s="60"/>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
-      <c r="V2" s="60"/>
-      <c r="W2" s="60"/>
-      <c r="X2" s="60"/>
-      <c r="Y2" s="60"/>
-      <c r="Z2" s="60"/>
-      <c r="AA2" s="60"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="56"/>
+      <c r="Q2" s="56"/>
+      <c r="R2" s="56"/>
+      <c r="S2" s="56"/>
+      <c r="T2" s="56"/>
+      <c r="U2" s="56"/>
+      <c r="V2" s="56"/>
+      <c r="W2" s="56"/>
+      <c r="X2" s="56"/>
+      <c r="Y2" s="56"/>
+      <c r="Z2" s="56"/>
+      <c r="AA2" s="56"/>
       <c r="AB2" s="25"/>
       <c r="AC2" s="25"/>
-      <c r="AD2" s="61" t="s">
+      <c r="AD2" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="AE2" s="61"/>
-      <c r="AF2" s="61"/>
-      <c r="AG2" s="61"/>
-      <c r="AH2" s="61"/>
-      <c r="AI2" s="61"/>
-      <c r="AJ2" s="61"/>
-      <c r="AK2" s="61"/>
-      <c r="AL2" s="61"/>
-      <c r="AM2" s="61"/>
-      <c r="AN2" s="61"/>
-      <c r="AO2" s="61"/>
-      <c r="AP2" s="61"/>
-      <c r="AQ2" s="61"/>
-      <c r="AR2" s="61"/>
-      <c r="AS2" s="61"/>
-      <c r="AT2" s="61"/>
-      <c r="AU2" s="61"/>
-      <c r="AV2" s="61"/>
-      <c r="AW2" s="61"/>
-      <c r="AX2" s="61"/>
-      <c r="AY2" s="61"/>
-      <c r="AZ2" s="61"/>
-      <c r="BA2" s="61"/>
-      <c r="BB2" s="61"/>
-      <c r="BC2" s="55" t="s">
+      <c r="AE2" s="57"/>
+      <c r="AF2" s="57"/>
+      <c r="AG2" s="57"/>
+      <c r="AH2" s="57"/>
+      <c r="AI2" s="57"/>
+      <c r="AJ2" s="57"/>
+      <c r="AK2" s="57"/>
+      <c r="AL2" s="57"/>
+      <c r="AM2" s="57"/>
+      <c r="AN2" s="57"/>
+      <c r="AO2" s="57"/>
+      <c r="AP2" s="57"/>
+      <c r="AQ2" s="57"/>
+      <c r="AR2" s="57"/>
+      <c r="AS2" s="57"/>
+      <c r="AT2" s="57"/>
+      <c r="AU2" s="57"/>
+      <c r="AV2" s="57"/>
+      <c r="AW2" s="57"/>
+      <c r="AX2" s="57"/>
+      <c r="AY2" s="57"/>
+      <c r="AZ2" s="57"/>
+      <c r="BA2" s="57"/>
+      <c r="BB2" s="57"/>
+      <c r="BC2" s="54"/>
+      <c r="BD2" s="54"/>
+      <c r="BE2" s="54"/>
+      <c r="BF2" s="54"/>
+      <c r="BG2" s="54"/>
+      <c r="BH2" s="63" t="s">
         <v>7</v>
       </c>
-      <c r="BD2" s="56" t="s">
+      <c r="BI2" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="BE2" s="54" t="s">
+      <c r="BJ2" s="58" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:57" s="18" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="54"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="54" t="s">
+    <row r="3" spans="1:62" s="18" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="58"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="54"/>
-      <c r="K3" s="54"/>
-      <c r="L3" s="54"/>
-      <c r="M3" s="54"/>
-      <c r="N3" s="54"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="58"/>
+      <c r="L3" s="58"/>
+      <c r="M3" s="58"/>
+      <c r="N3" s="58"/>
       <c r="O3" s="23"/>
       <c r="P3" s="23"/>
-      <c r="Q3" s="54" t="s">
+      <c r="Q3" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="R3" s="54"/>
-      <c r="S3" s="54"/>
-      <c r="T3" s="54"/>
-      <c r="U3" s="54"/>
-      <c r="V3" s="57" t="s">
+      <c r="R3" s="58"/>
+      <c r="S3" s="58"/>
+      <c r="T3" s="58"/>
+      <c r="U3" s="58"/>
+      <c r="V3" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="W3" s="57" t="s">
+      <c r="W3" s="62" t="s">
         <v>13</v>
       </c>
       <c r="X3" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="Y3" s="58" t="s">
+      <c r="Y3" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="Z3" s="58" t="s">
+      <c r="Z3" s="65" t="s">
         <v>15</v>
       </c>
-      <c r="AA3" s="54" t="s">
+      <c r="AA3" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="AB3" s="54" t="s">
+      <c r="AB3" s="58" t="s">
         <v>17</v>
       </c>
-      <c r="AC3" s="54" t="s">
+      <c r="AC3" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="AD3" s="62" t="s">
+      <c r="AD3" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="AE3" s="62"/>
-      <c r="AF3" s="62"/>
-      <c r="AG3" s="62"/>
-      <c r="AH3" s="62"/>
-      <c r="AI3" s="62"/>
-      <c r="AJ3" s="62"/>
-      <c r="AK3" s="62"/>
-      <c r="AL3" s="62"/>
-      <c r="AM3" s="62" t="s">
+      <c r="AE3" s="59"/>
+      <c r="AF3" s="59"/>
+      <c r="AG3" s="59"/>
+      <c r="AH3" s="59"/>
+      <c r="AI3" s="59"/>
+      <c r="AJ3" s="59"/>
+      <c r="AK3" s="59"/>
+      <c r="AL3" s="59"/>
+      <c r="AM3" s="59" t="s">
         <v>20</v>
       </c>
-      <c r="AN3" s="62"/>
-      <c r="AO3" s="62"/>
-      <c r="AP3" s="62"/>
-      <c r="AQ3" s="62"/>
-      <c r="AR3" s="62"/>
-      <c r="AS3" s="62" t="s">
+      <c r="AN3" s="59"/>
+      <c r="AO3" s="59"/>
+      <c r="AP3" s="59"/>
+      <c r="AQ3" s="59"/>
+      <c r="AR3" s="59"/>
+      <c r="AS3" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="AT3" s="62"/>
-      <c r="AU3" s="62"/>
+      <c r="AT3" s="59"/>
+      <c r="AU3" s="59"/>
       <c r="AV3" s="26"/>
-      <c r="AW3" s="63" t="s">
+      <c r="AW3" s="60" t="s">
         <v>22</v>
       </c>
-      <c r="AX3" s="63"/>
-      <c r="AY3" s="62" t="s">
+      <c r="AX3" s="60"/>
+      <c r="AY3" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="AZ3" s="62"/>
-      <c r="BA3" s="62"/>
-      <c r="BB3" s="62"/>
-      <c r="BC3" s="55"/>
-      <c r="BD3" s="56"/>
-      <c r="BE3" s="54"/>
-    </row>
-    <row r="4" spans="1:57" s="18" customFormat="1" ht="87" x14ac:dyDescent="0.25">
-      <c r="A4" s="54"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="64"/>
+      <c r="AZ3" s="59"/>
+      <c r="BA3" s="59"/>
+      <c r="BB3" s="59"/>
+      <c r="BC3" s="69" t="s">
+        <v>109</v>
+      </c>
+      <c r="BD3" s="70"/>
+      <c r="BE3" s="70"/>
+      <c r="BF3" s="70"/>
+      <c r="BG3" s="71"/>
+      <c r="BH3" s="63"/>
+      <c r="BI3" s="64"/>
+      <c r="BJ3" s="58"/>
+    </row>
+    <row r="4" spans="1:62" s="18" customFormat="1" ht="87" x14ac:dyDescent="0.25">
+      <c r="A4" s="58"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="61"/>
       <c r="I4" s="23" t="s">
         <v>23</v>
       </c>
@@ -1474,16 +1568,16 @@
       <c r="U4" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="V4" s="57"/>
-      <c r="W4" s="57"/>
+      <c r="V4" s="62"/>
+      <c r="W4" s="62"/>
       <c r="X4" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="Y4" s="58"/>
-      <c r="Z4" s="58"/>
-      <c r="AA4" s="54"/>
-      <c r="AB4" s="54"/>
-      <c r="AC4" s="54"/>
+      <c r="Y4" s="65"/>
+      <c r="Z4" s="65"/>
+      <c r="AA4" s="58"/>
+      <c r="AB4" s="58"/>
+      <c r="AC4" s="58"/>
       <c r="AD4" s="24" t="s">
         <v>108</v>
       </c>
@@ -1559,11 +1653,26 @@
       <c r="BB4" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="BC4" s="55"/>
-      <c r="BD4" s="56"/>
-      <c r="BE4" s="54"/>
-    </row>
-    <row r="5" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BC4" s="72" t="s">
+        <v>110</v>
+      </c>
+      <c r="BD4" s="72" t="s">
+        <v>112</v>
+      </c>
+      <c r="BE4" s="72" t="s">
+        <v>113</v>
+      </c>
+      <c r="BF4" s="72" t="s">
+        <v>40</v>
+      </c>
+      <c r="BG4" s="34" t="s">
+        <v>111</v>
+      </c>
+      <c r="BH4" s="63"/>
+      <c r="BI4" s="64"/>
+      <c r="BJ4" s="58"/>
+    </row>
+    <row r="5" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="23">
         <f t="shared" ref="A5:A36" si="0">ROW()-4</f>
         <v>1</v>
@@ -1652,17 +1761,25 @@
         <v>0</v>
       </c>
       <c r="BB5" s="41"/>
-      <c r="BC5" s="48">
+      <c r="BC5" s="41"/>
+      <c r="BD5" s="41"/>
+      <c r="BE5" s="41"/>
+      <c r="BF5" s="45">
+        <f>BC5-BD5-BE5</f>
+        <v>0</v>
+      </c>
+      <c r="BG5" s="41"/>
+      <c r="BH5" s="48">
         <f>G5+M5+T5+AK5+AQ5+AU5+AW5+BA5</f>
         <v>0</v>
       </c>
-      <c r="BD5" s="49">
+      <c r="BI5" s="49">
         <f>G5+K5+R5+AE5+AM5+AS5+AW5+AY5</f>
         <v>0</v>
       </c>
-      <c r="BE5" s="37"/>
-    </row>
-    <row r="6" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BJ5" s="37"/>
+    </row>
+    <row r="6" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="23">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -1751,17 +1868,25 @@
         <v>0</v>
       </c>
       <c r="BB6" s="41"/>
-      <c r="BC6" s="48">
-        <f t="shared" ref="BC6:BC35" si="10">G6+M6+T6+AK6+AQ6+AU6+AW6+BA6</f>
-        <v>0</v>
-      </c>
-      <c r="BD6" s="49">
-        <f t="shared" ref="BD6:BD35" si="11">G6+K6+R6+AE6+AM6+AS6+AW6+AY6</f>
-        <v>0</v>
-      </c>
-      <c r="BE6" s="37"/>
-    </row>
-    <row r="7" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BC6" s="41"/>
+      <c r="BD6" s="41"/>
+      <c r="BE6" s="41"/>
+      <c r="BF6" s="45">
+        <f t="shared" ref="BF6:BF35" si="10">BC6-BD6-BE6</f>
+        <v>0</v>
+      </c>
+      <c r="BG6" s="41"/>
+      <c r="BH6" s="48">
+        <f t="shared" ref="BH6:BH35" si="11">G6+M6+T6+AK6+AQ6+AU6+AW6+BA6</f>
+        <v>0</v>
+      </c>
+      <c r="BI6" s="49">
+        <f t="shared" ref="BI6:BI35" si="12">G6+K6+R6+AE6+AM6+AS6+AW6+AY6</f>
+        <v>0</v>
+      </c>
+      <c r="BJ6" s="37"/>
+    </row>
+    <row r="7" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="23">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -1850,17 +1975,25 @@
         <v>0</v>
       </c>
       <c r="BB7" s="41"/>
-      <c r="BC7" s="48">
+      <c r="BC7" s="41"/>
+      <c r="BD7" s="41"/>
+      <c r="BE7" s="41"/>
+      <c r="BF7" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BD7" s="49">
+      <c r="BG7" s="41"/>
+      <c r="BH7" s="48">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BE7" s="38"/>
-    </row>
-    <row r="8" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BI7" s="49">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BJ7" s="38"/>
+    </row>
+    <row r="8" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="23">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1949,17 +2082,25 @@
         <v>0</v>
       </c>
       <c r="BB8" s="41"/>
-      <c r="BC8" s="48">
+      <c r="BC8" s="41"/>
+      <c r="BD8" s="41"/>
+      <c r="BE8" s="41"/>
+      <c r="BF8" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BD8" s="49">
+      <c r="BG8" s="41"/>
+      <c r="BH8" s="48">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BE8" s="39"/>
-    </row>
-    <row r="9" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BI8" s="49">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BJ8" s="39"/>
+    </row>
+    <row r="9" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="23">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2048,17 +2189,25 @@
         <v>0</v>
       </c>
       <c r="BB9" s="41"/>
-      <c r="BC9" s="48">
+      <c r="BC9" s="41"/>
+      <c r="BD9" s="41"/>
+      <c r="BE9" s="41"/>
+      <c r="BF9" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BD9" s="49">
+      <c r="BG9" s="41"/>
+      <c r="BH9" s="48">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BE9" s="37"/>
-    </row>
-    <row r="10" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BI9" s="49">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BJ9" s="37"/>
+    </row>
+    <row r="10" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="23">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2147,17 +2296,25 @@
         <v>0</v>
       </c>
       <c r="BB10" s="41"/>
-      <c r="BC10" s="48">
+      <c r="BC10" s="41"/>
+      <c r="BD10" s="41"/>
+      <c r="BE10" s="41"/>
+      <c r="BF10" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BD10" s="49">
+      <c r="BG10" s="41"/>
+      <c r="BH10" s="48">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BE10" s="37"/>
-    </row>
-    <row r="11" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BI10" s="49">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BJ10" s="37"/>
+    </row>
+    <row r="11" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="23">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2246,17 +2403,25 @@
         <v>0</v>
       </c>
       <c r="BB11" s="41"/>
-      <c r="BC11" s="48">
+      <c r="BC11" s="41"/>
+      <c r="BD11" s="41"/>
+      <c r="BE11" s="41"/>
+      <c r="BF11" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BD11" s="49">
+      <c r="BG11" s="41"/>
+      <c r="BH11" s="48">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BE11" s="37"/>
-    </row>
-    <row r="12" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BI11" s="49">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BJ11" s="37"/>
+    </row>
+    <row r="12" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="23">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2345,17 +2510,25 @@
         <v>0</v>
       </c>
       <c r="BB12" s="41"/>
-      <c r="BC12" s="48">
+      <c r="BC12" s="41"/>
+      <c r="BD12" s="41"/>
+      <c r="BE12" s="41"/>
+      <c r="BF12" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BD12" s="49">
+      <c r="BG12" s="41"/>
+      <c r="BH12" s="48">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BE12" s="37"/>
-    </row>
-    <row r="13" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BI12" s="49">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BJ12" s="37"/>
+    </row>
+    <row r="13" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="23">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2444,17 +2617,25 @@
         <v>0</v>
       </c>
       <c r="BB13" s="41"/>
-      <c r="BC13" s="48">
+      <c r="BC13" s="41"/>
+      <c r="BD13" s="41"/>
+      <c r="BE13" s="41"/>
+      <c r="BF13" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BD13" s="49">
+      <c r="BG13" s="41"/>
+      <c r="BH13" s="48">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BE13" s="37"/>
-    </row>
-    <row r="14" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BI13" s="49">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BJ13" s="37"/>
+    </row>
+    <row r="14" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="23">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2543,17 +2724,25 @@
         <v>0</v>
       </c>
       <c r="BB14" s="41"/>
-      <c r="BC14" s="48">
+      <c r="BC14" s="41"/>
+      <c r="BD14" s="41"/>
+      <c r="BE14" s="41"/>
+      <c r="BF14" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BD14" s="49">
+      <c r="BG14" s="41"/>
+      <c r="BH14" s="48">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BE14" s="37"/>
-    </row>
-    <row r="15" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BI14" s="49">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BJ14" s="37"/>
+    </row>
+    <row r="15" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="23">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2642,17 +2831,25 @@
         <v>0</v>
       </c>
       <c r="BB15" s="41"/>
-      <c r="BC15" s="48">
+      <c r="BC15" s="41"/>
+      <c r="BD15" s="41"/>
+      <c r="BE15" s="41"/>
+      <c r="BF15" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BD15" s="49">
+      <c r="BG15" s="41"/>
+      <c r="BH15" s="48">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BE15" s="37"/>
-    </row>
-    <row r="16" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BI15" s="49">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BJ15" s="37"/>
+    </row>
+    <row r="16" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="23">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2741,17 +2938,25 @@
         <v>0</v>
       </c>
       <c r="BB16" s="41"/>
-      <c r="BC16" s="48">
+      <c r="BC16" s="41"/>
+      <c r="BD16" s="41"/>
+      <c r="BE16" s="41"/>
+      <c r="BF16" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BD16" s="49">
+      <c r="BG16" s="41"/>
+      <c r="BH16" s="48">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BE16" s="37"/>
-    </row>
-    <row r="17" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BI16" s="49">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BJ16" s="37"/>
+    </row>
+    <row r="17" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="23">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2840,17 +3045,25 @@
         <v>0</v>
       </c>
       <c r="BB17" s="50"/>
-      <c r="BC17" s="48">
+      <c r="BC17" s="50"/>
+      <c r="BD17" s="50"/>
+      <c r="BE17" s="50"/>
+      <c r="BF17" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BD17" s="49">
+      <c r="BG17" s="50"/>
+      <c r="BH17" s="48">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BE17" s="37"/>
-    </row>
-    <row r="18" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BI17" s="49">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BJ17" s="37"/>
+    </row>
+    <row r="18" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="23">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2939,17 +3152,25 @@
         <v>0</v>
       </c>
       <c r="BB18" s="50"/>
-      <c r="BC18" s="48">
+      <c r="BC18" s="50"/>
+      <c r="BD18" s="50"/>
+      <c r="BE18" s="50"/>
+      <c r="BF18" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BD18" s="49">
+      <c r="BG18" s="50"/>
+      <c r="BH18" s="48">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BE18" s="37"/>
-    </row>
-    <row r="19" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BI18" s="49">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BJ18" s="37"/>
+    </row>
+    <row r="19" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="23">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -3038,17 +3259,25 @@
         <v>0</v>
       </c>
       <c r="BB19" s="50"/>
-      <c r="BC19" s="48">
+      <c r="BC19" s="50"/>
+      <c r="BD19" s="50"/>
+      <c r="BE19" s="50"/>
+      <c r="BF19" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BD19" s="49">
+      <c r="BG19" s="50"/>
+      <c r="BH19" s="48">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BE19" s="37"/>
-    </row>
-    <row r="20" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BI19" s="49">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BJ19" s="37"/>
+    </row>
+    <row r="20" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="23">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -3137,17 +3366,25 @@
         <v>0</v>
       </c>
       <c r="BB20" s="50"/>
-      <c r="BC20" s="48">
+      <c r="BC20" s="50"/>
+      <c r="BD20" s="50"/>
+      <c r="BE20" s="50"/>
+      <c r="BF20" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BD20" s="49">
+      <c r="BG20" s="50"/>
+      <c r="BH20" s="48">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BE20" s="37"/>
-    </row>
-    <row r="21" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BI20" s="49">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BJ20" s="37"/>
+    </row>
+    <row r="21" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="23">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -3236,17 +3473,25 @@
         <v>0</v>
       </c>
       <c r="BB21" s="50"/>
-      <c r="BC21" s="48">
+      <c r="BC21" s="50"/>
+      <c r="BD21" s="50"/>
+      <c r="BE21" s="50"/>
+      <c r="BF21" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BD21" s="49">
+      <c r="BG21" s="50"/>
+      <c r="BH21" s="48">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BE21" s="37"/>
-    </row>
-    <row r="22" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BI21" s="49">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BJ21" s="37"/>
+    </row>
+    <row r="22" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="23">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -3335,17 +3580,25 @@
         <v>0</v>
       </c>
       <c r="BB22" s="47"/>
-      <c r="BC22" s="48">
+      <c r="BC22" s="47"/>
+      <c r="BD22" s="47"/>
+      <c r="BE22" s="47"/>
+      <c r="BF22" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BD22" s="49">
+      <c r="BG22" s="47"/>
+      <c r="BH22" s="48">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BE22" s="42"/>
-    </row>
-    <row r="23" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BI22" s="49">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BJ22" s="42"/>
+    </row>
+    <row r="23" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="23">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -3434,17 +3687,25 @@
         <v>0</v>
       </c>
       <c r="BB23" s="41"/>
-      <c r="BC23" s="48">
+      <c r="BC23" s="41"/>
+      <c r="BD23" s="41"/>
+      <c r="BE23" s="41"/>
+      <c r="BF23" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BD23" s="49">
+      <c r="BG23" s="41"/>
+      <c r="BH23" s="48">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BE23" s="43"/>
-    </row>
-    <row r="24" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BI23" s="49">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BJ23" s="43"/>
+    </row>
+    <row r="24" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="23">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -3533,17 +3794,25 @@
         <v>0</v>
       </c>
       <c r="BB24" s="41"/>
-      <c r="BC24" s="48">
+      <c r="BC24" s="41"/>
+      <c r="BD24" s="41"/>
+      <c r="BE24" s="41"/>
+      <c r="BF24" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BD24" s="49">
+      <c r="BG24" s="41"/>
+      <c r="BH24" s="48">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BE24" s="43"/>
-    </row>
-    <row r="25" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BI24" s="49">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BJ24" s="43"/>
+    </row>
+    <row r="25" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="23">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -3632,17 +3901,25 @@
         <v>0</v>
       </c>
       <c r="BB25" s="41"/>
-      <c r="BC25" s="48">
+      <c r="BC25" s="41"/>
+      <c r="BD25" s="41"/>
+      <c r="BE25" s="41"/>
+      <c r="BF25" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BD25" s="49">
+      <c r="BG25" s="41"/>
+      <c r="BH25" s="48">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BE25" s="43"/>
-    </row>
-    <row r="26" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BI25" s="49">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BJ25" s="43"/>
+    </row>
+    <row r="26" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="23">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -3731,17 +4008,25 @@
         <v>0</v>
       </c>
       <c r="BB26" s="50"/>
-      <c r="BC26" s="48">
+      <c r="BC26" s="50"/>
+      <c r="BD26" s="50"/>
+      <c r="BE26" s="50"/>
+      <c r="BF26" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BD26" s="49">
+      <c r="BG26" s="50"/>
+      <c r="BH26" s="48">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BE26" s="43"/>
-    </row>
-    <row r="27" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BI26" s="49">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BJ26" s="43"/>
+    </row>
+    <row r="27" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="23">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -3810,7 +4095,7 @@
       <c r="AO27" s="41"/>
       <c r="AP27" s="47"/>
       <c r="AQ27" s="45">
-        <f t="shared" ref="AQ27:AQ35" si="12">AM27-AN27-AO27-AP27</f>
+        <f t="shared" ref="AQ27:AQ35" si="13">AM27-AN27-AO27-AP27</f>
         <v>0</v>
       </c>
       <c r="AR27" s="41"/>
@@ -3830,17 +4115,25 @@
         <v>0</v>
       </c>
       <c r="BB27" s="41"/>
-      <c r="BC27" s="48">
+      <c r="BC27" s="41"/>
+      <c r="BD27" s="41"/>
+      <c r="BE27" s="41"/>
+      <c r="BF27" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BD27" s="49">
+      <c r="BG27" s="41"/>
+      <c r="BH27" s="48">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BE27" s="43"/>
-    </row>
-    <row r="28" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BI27" s="49">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BJ27" s="43"/>
+    </row>
+    <row r="28" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="23">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -3909,7 +4202,7 @@
       <c r="AO28" s="41"/>
       <c r="AP28" s="47"/>
       <c r="AQ28" s="45">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AR28" s="41"/>
@@ -3929,17 +4222,25 @@
         <v>0</v>
       </c>
       <c r="BB28" s="50"/>
-      <c r="BC28" s="48">
+      <c r="BC28" s="50"/>
+      <c r="BD28" s="50"/>
+      <c r="BE28" s="50"/>
+      <c r="BF28" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BD28" s="49">
+      <c r="BG28" s="50"/>
+      <c r="BH28" s="48">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BE28" s="43"/>
-    </row>
-    <row r="29" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BI28" s="49">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BJ28" s="43"/>
+    </row>
+    <row r="29" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="23">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -4008,7 +4309,7 @@
       <c r="AO29" s="41"/>
       <c r="AP29" s="41"/>
       <c r="AQ29" s="45">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AR29" s="41"/>
@@ -4028,17 +4329,25 @@
         <v>0</v>
       </c>
       <c r="BB29" s="41"/>
-      <c r="BC29" s="48">
+      <c r="BC29" s="41"/>
+      <c r="BD29" s="41"/>
+      <c r="BE29" s="41"/>
+      <c r="BF29" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BD29" s="49">
+      <c r="BG29" s="41"/>
+      <c r="BH29" s="48">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BE29" s="43"/>
-    </row>
-    <row r="30" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BI29" s="49">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BJ29" s="43"/>
+    </row>
+    <row r="30" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="23">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -4107,7 +4416,7 @@
       <c r="AO30" s="41"/>
       <c r="AP30" s="41"/>
       <c r="AQ30" s="45">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AR30" s="41"/>
@@ -4127,17 +4436,25 @@
         <v>0</v>
       </c>
       <c r="BB30" s="41"/>
-      <c r="BC30" s="48">
+      <c r="BC30" s="41"/>
+      <c r="BD30" s="41"/>
+      <c r="BE30" s="41"/>
+      <c r="BF30" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BD30" s="49">
+      <c r="BG30" s="41"/>
+      <c r="BH30" s="48">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BE30" s="43"/>
-    </row>
-    <row r="31" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BI30" s="49">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BJ30" s="43"/>
+    </row>
+    <row r="31" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="23">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -4206,7 +4523,7 @@
       <c r="AO31" s="41"/>
       <c r="AP31" s="41"/>
       <c r="AQ31" s="45">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AR31" s="41"/>
@@ -4226,17 +4543,25 @@
         <v>0</v>
       </c>
       <c r="BB31" s="41"/>
-      <c r="BC31" s="48">
+      <c r="BC31" s="41"/>
+      <c r="BD31" s="41"/>
+      <c r="BE31" s="41"/>
+      <c r="BF31" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BD31" s="49">
+      <c r="BG31" s="41"/>
+      <c r="BH31" s="48">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BE31" s="43"/>
-    </row>
-    <row r="32" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BI31" s="49">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BJ31" s="43"/>
+    </row>
+    <row r="32" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="23">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -4305,7 +4630,7 @@
       <c r="AO32" s="41"/>
       <c r="AP32" s="41"/>
       <c r="AQ32" s="45">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AR32" s="41"/>
@@ -4325,17 +4650,25 @@
         <v>0</v>
       </c>
       <c r="BB32" s="41"/>
-      <c r="BC32" s="48">
+      <c r="BC32" s="41"/>
+      <c r="BD32" s="41"/>
+      <c r="BE32" s="41"/>
+      <c r="BF32" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BD32" s="49">
+      <c r="BG32" s="41"/>
+      <c r="BH32" s="48">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BE32" s="37"/>
-    </row>
-    <row r="33" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BI32" s="49">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BJ32" s="37"/>
+    </row>
+    <row r="33" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="23">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -4404,7 +4737,7 @@
       <c r="AO33" s="41"/>
       <c r="AP33" s="41"/>
       <c r="AQ33" s="45">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AR33" s="41"/>
@@ -4424,17 +4757,25 @@
         <v>0</v>
       </c>
       <c r="BB33" s="41"/>
-      <c r="BC33" s="48">
+      <c r="BC33" s="41"/>
+      <c r="BD33" s="41"/>
+      <c r="BE33" s="41"/>
+      <c r="BF33" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BD33" s="49">
+      <c r="BG33" s="41"/>
+      <c r="BH33" s="48">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BE33" s="37"/>
-    </row>
-    <row r="34" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BI33" s="49">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BJ33" s="37"/>
+    </row>
+    <row r="34" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="23">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -4503,7 +4844,7 @@
       <c r="AO34" s="41"/>
       <c r="AP34" s="41"/>
       <c r="AQ34" s="45">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AR34" s="41"/>
@@ -4523,17 +4864,25 @@
         <v>0</v>
       </c>
       <c r="BB34" s="41"/>
-      <c r="BC34" s="48">
+      <c r="BC34" s="41"/>
+      <c r="BD34" s="41"/>
+      <c r="BE34" s="41"/>
+      <c r="BF34" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BD34" s="49">
+      <c r="BG34" s="41"/>
+      <c r="BH34" s="48">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BE34" s="37"/>
-    </row>
-    <row r="35" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BI34" s="49">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BJ34" s="37"/>
+    </row>
+    <row r="35" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="23">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -4598,7 +4947,7 @@
       <c r="AO35" s="41"/>
       <c r="AP35" s="41"/>
       <c r="AQ35" s="45">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AR35" s="41"/>
@@ -4618,17 +4967,25 @@
         <v>0</v>
       </c>
       <c r="BB35" s="41"/>
-      <c r="BC35" s="48">
+      <c r="BC35" s="41"/>
+      <c r="BD35" s="41"/>
+      <c r="BE35" s="41"/>
+      <c r="BF35" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BD35" s="49">
+      <c r="BG35" s="41"/>
+      <c r="BH35" s="48">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BE35" s="37"/>
-    </row>
-    <row r="36" spans="1:57" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BI35" s="49">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BJ35" s="37"/>
+    </row>
+    <row r="36" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="23">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -4638,214 +4995,240 @@
       </c>
       <c r="C36" s="37"/>
       <c r="D36" s="23">
-        <f t="shared" ref="D36:BD36" si="13">SUM(D5:D35)</f>
+        <f t="shared" ref="D36:BI36" si="14">SUM(D5:D35)</f>
         <v>0</v>
       </c>
       <c r="E36" s="23">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="F36" s="23">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="G36" s="23"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="G36" s="23">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="H36" s="23">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="I36" s="23">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="J36" s="23">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="K36" s="53">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="L36" s="53">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M36" s="53">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N36" s="53">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O36" s="53">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="P36" s="53">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Q36" s="53">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="R36" s="53">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S36" s="53">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T36" s="53">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="U36" s="53">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="V36" s="53">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="W36" s="53">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="X36" s="53">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Y36" s="53">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Z36" s="53">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AA36" s="53">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AB36" s="53">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AC36" s="53">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AD36" s="53">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AE36" s="53"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AE36" s="53">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AF36" s="53">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AG36" s="53">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AH36" s="53">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AI36" s="53">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AJ36" s="53">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AK36" s="53">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AL36" s="53">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AM36" s="53">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AN36" s="53">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AO36" s="53">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AP36" s="53">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AQ36" s="53">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AR36" s="53">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AS36" s="53">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AT36" s="53">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AU36" s="53">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AV36" s="53">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AW36" s="53">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AX36" s="53">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AY36" s="53">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AZ36" s="53">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="BA36" s="53">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="BB36" s="53">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="BC36" s="53">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="BD36" s="53">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="BE36" s="37"/>
-    </row>
-    <row r="37" spans="1:57" x14ac:dyDescent="0.25">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="BE36" s="53">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="BF36" s="53">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="BG36" s="53">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="BH36" s="53">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="BI36" s="53">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="BJ36" s="37"/>
+    </row>
+    <row r="37" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A37" s="20"/>
       <c r="B37" s="20"/>
       <c r="C37" s="20"/>
@@ -4900,11 +5283,16 @@
       <c r="AZ37" s="20"/>
       <c r="BA37" s="20"/>
       <c r="BB37" s="20"/>
-      <c r="BC37" s="21"/>
-      <c r="BD37" s="21"/>
+      <c r="BC37" s="20"/>
+      <c r="BD37" s="20"/>
       <c r="BE37" s="20"/>
-    </row>
-    <row r="38" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF37" s="20"/>
+      <c r="BG37" s="20"/>
+      <c r="BH37" s="21"/>
+      <c r="BI37" s="21"/>
+      <c r="BJ37" s="20"/>
+    </row>
+    <row r="38" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A38" s="20"/>
       <c r="B38" s="20"/>
       <c r="C38" s="20"/>
@@ -4959,11 +5347,16 @@
       <c r="AZ38" s="20"/>
       <c r="BA38" s="20"/>
       <c r="BB38" s="20"/>
-      <c r="BC38" s="21"/>
-      <c r="BD38" s="21"/>
+      <c r="BC38" s="20"/>
+      <c r="BD38" s="20"/>
       <c r="BE38" s="20"/>
-    </row>
-    <row r="39" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF38" s="20"/>
+      <c r="BG38" s="20"/>
+      <c r="BH38" s="21"/>
+      <c r="BI38" s="21"/>
+      <c r="BJ38" s="20"/>
+    </row>
+    <row r="39" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A39" s="20"/>
       <c r="B39" s="20"/>
       <c r="C39" s="20"/>
@@ -5018,11 +5411,16 @@
       <c r="AZ39" s="20"/>
       <c r="BA39" s="20"/>
       <c r="BB39" s="20"/>
-      <c r="BC39" s="21"/>
-      <c r="BD39" s="21"/>
+      <c r="BC39" s="20"/>
+      <c r="BD39" s="20"/>
       <c r="BE39" s="20"/>
-    </row>
-    <row r="40" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF39" s="20"/>
+      <c r="BG39" s="20"/>
+      <c r="BH39" s="21"/>
+      <c r="BI39" s="21"/>
+      <c r="BJ39" s="20"/>
+    </row>
+    <row r="40" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A40" s="20"/>
       <c r="B40" s="20"/>
       <c r="C40" s="20"/>
@@ -5076,11 +5474,16 @@
       <c r="AZ40" s="20"/>
       <c r="BA40" s="20"/>
       <c r="BB40" s="20"/>
-      <c r="BC40" s="21"/>
-      <c r="BD40" s="21"/>
+      <c r="BC40" s="20"/>
+      <c r="BD40" s="20"/>
       <c r="BE40" s="20"/>
-    </row>
-    <row r="41" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF40" s="20"/>
+      <c r="BG40" s="20"/>
+      <c r="BH40" s="21"/>
+      <c r="BI40" s="21"/>
+      <c r="BJ40" s="20"/>
+    </row>
+    <row r="41" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A41" s="20"/>
       <c r="B41" s="20"/>
       <c r="C41" s="20"/>
@@ -5134,11 +5537,16 @@
       <c r="AZ41" s="20"/>
       <c r="BA41" s="20"/>
       <c r="BB41" s="20"/>
-      <c r="BC41" s="21"/>
-      <c r="BD41" s="21"/>
+      <c r="BC41" s="20"/>
+      <c r="BD41" s="20"/>
       <c r="BE41" s="20"/>
-    </row>
-    <row r="42" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF41" s="20"/>
+      <c r="BG41" s="20"/>
+      <c r="BH41" s="21"/>
+      <c r="BI41" s="21"/>
+      <c r="BJ41" s="20"/>
+    </row>
+    <row r="42" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A42" s="20"/>
       <c r="B42" s="20"/>
       <c r="C42" s="20"/>
@@ -5191,11 +5599,16 @@
       <c r="AZ42" s="20"/>
       <c r="BA42" s="20"/>
       <c r="BB42" s="20"/>
-      <c r="BC42" s="21"/>
-      <c r="BD42" s="21"/>
+      <c r="BC42" s="20"/>
+      <c r="BD42" s="20"/>
       <c r="BE42" s="20"/>
-    </row>
-    <row r="43" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF42" s="20"/>
+      <c r="BG42" s="20"/>
+      <c r="BH42" s="21"/>
+      <c r="BI42" s="21"/>
+      <c r="BJ42" s="20"/>
+    </row>
+    <row r="43" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A43" s="20"/>
       <c r="B43" s="20"/>
       <c r="C43" s="20"/>
@@ -5249,11 +5662,16 @@
       <c r="AZ43" s="20"/>
       <c r="BA43" s="20"/>
       <c r="BB43" s="20"/>
-      <c r="BC43" s="21"/>
-      <c r="BD43" s="21"/>
+      <c r="BC43" s="20"/>
+      <c r="BD43" s="20"/>
       <c r="BE43" s="20"/>
-    </row>
-    <row r="44" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF43" s="20"/>
+      <c r="BG43" s="20"/>
+      <c r="BH43" s="21"/>
+      <c r="BI43" s="21"/>
+      <c r="BJ43" s="20"/>
+    </row>
+    <row r="44" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A44" s="20"/>
       <c r="B44" s="20"/>
       <c r="C44" s="20"/>
@@ -5308,11 +5726,16 @@
       <c r="AZ44" s="20"/>
       <c r="BA44" s="20"/>
       <c r="BB44" s="20"/>
-      <c r="BC44" s="21"/>
-      <c r="BD44" s="21"/>
+      <c r="BC44" s="20"/>
+      <c r="BD44" s="20"/>
       <c r="BE44" s="20"/>
-    </row>
-    <row r="45" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF44" s="20"/>
+      <c r="BG44" s="20"/>
+      <c r="BH44" s="21"/>
+      <c r="BI44" s="21"/>
+      <c r="BJ44" s="20"/>
+    </row>
+    <row r="45" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A45" s="20"/>
       <c r="B45" s="20"/>
       <c r="C45" s="20"/>
@@ -5367,11 +5790,16 @@
       <c r="AZ45" s="20"/>
       <c r="BA45" s="20"/>
       <c r="BB45" s="20"/>
-      <c r="BC45" s="21"/>
-      <c r="BD45" s="21"/>
+      <c r="BC45" s="20"/>
+      <c r="BD45" s="20"/>
       <c r="BE45" s="20"/>
-    </row>
-    <row r="46" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF45" s="20"/>
+      <c r="BG45" s="20"/>
+      <c r="BH45" s="21"/>
+      <c r="BI45" s="21"/>
+      <c r="BJ45" s="20"/>
+    </row>
+    <row r="46" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A46" s="20"/>
       <c r="B46" s="20"/>
       <c r="C46" s="20"/>
@@ -5426,11 +5854,16 @@
       <c r="AZ46" s="20"/>
       <c r="BA46" s="20"/>
       <c r="BB46" s="20"/>
-      <c r="BC46" s="21"/>
-      <c r="BD46" s="21"/>
+      <c r="BC46" s="20"/>
+      <c r="BD46" s="20"/>
       <c r="BE46" s="20"/>
-    </row>
-    <row r="47" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF46" s="20"/>
+      <c r="BG46" s="20"/>
+      <c r="BH46" s="21"/>
+      <c r="BI46" s="21"/>
+      <c r="BJ46" s="20"/>
+    </row>
+    <row r="47" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A47" s="20"/>
       <c r="B47" s="20"/>
       <c r="C47" s="20"/>
@@ -5485,11 +5918,16 @@
       <c r="AZ47" s="20"/>
       <c r="BA47" s="20"/>
       <c r="BB47" s="20"/>
-      <c r="BC47" s="21"/>
-      <c r="BD47" s="21"/>
+      <c r="BC47" s="20"/>
+      <c r="BD47" s="20"/>
       <c r="BE47" s="20"/>
-    </row>
-    <row r="48" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF47" s="20"/>
+      <c r="BG47" s="20"/>
+      <c r="BH47" s="21"/>
+      <c r="BI47" s="21"/>
+      <c r="BJ47" s="20"/>
+    </row>
+    <row r="48" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A48" s="20"/>
       <c r="B48" s="20"/>
       <c r="C48" s="20"/>
@@ -5544,11 +5982,16 @@
       <c r="AZ48" s="20"/>
       <c r="BA48" s="20"/>
       <c r="BB48" s="20"/>
-      <c r="BC48" s="21"/>
-      <c r="BD48" s="21"/>
+      <c r="BC48" s="20"/>
+      <c r="BD48" s="20"/>
       <c r="BE48" s="20"/>
-    </row>
-    <row r="49" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF48" s="20"/>
+      <c r="BG48" s="20"/>
+      <c r="BH48" s="21"/>
+      <c r="BI48" s="21"/>
+      <c r="BJ48" s="20"/>
+    </row>
+    <row r="49" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A49" s="20"/>
       <c r="B49" s="20"/>
       <c r="C49" s="20"/>
@@ -5603,11 +6046,16 @@
       <c r="AZ49" s="20"/>
       <c r="BA49" s="20"/>
       <c r="BB49" s="20"/>
-      <c r="BC49" s="21"/>
-      <c r="BD49" s="21"/>
+      <c r="BC49" s="20"/>
+      <c r="BD49" s="20"/>
       <c r="BE49" s="20"/>
-    </row>
-    <row r="50" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF49" s="20"/>
+      <c r="BG49" s="20"/>
+      <c r="BH49" s="21"/>
+      <c r="BI49" s="21"/>
+      <c r="BJ49" s="20"/>
+    </row>
+    <row r="50" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A50" s="20"/>
       <c r="B50" s="20"/>
       <c r="C50" s="20"/>
@@ -5662,11 +6110,16 @@
       <c r="AZ50" s="20"/>
       <c r="BA50" s="20"/>
       <c r="BB50" s="20"/>
-      <c r="BC50" s="21"/>
-      <c r="BD50" s="21"/>
+      <c r="BC50" s="20"/>
+      <c r="BD50" s="20"/>
       <c r="BE50" s="20"/>
-    </row>
-    <row r="51" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF50" s="20"/>
+      <c r="BG50" s="20"/>
+      <c r="BH50" s="21"/>
+      <c r="BI50" s="21"/>
+      <c r="BJ50" s="20"/>
+    </row>
+    <row r="51" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A51" s="20"/>
       <c r="B51" s="20"/>
       <c r="C51" s="20"/>
@@ -5721,11 +6174,16 @@
       <c r="AZ51" s="20"/>
       <c r="BA51" s="20"/>
       <c r="BB51" s="20"/>
-      <c r="BC51" s="21"/>
-      <c r="BD51" s="21"/>
+      <c r="BC51" s="20"/>
+      <c r="BD51" s="20"/>
       <c r="BE51" s="20"/>
-    </row>
-    <row r="52" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF51" s="20"/>
+      <c r="BG51" s="20"/>
+      <c r="BH51" s="21"/>
+      <c r="BI51" s="21"/>
+      <c r="BJ51" s="20"/>
+    </row>
+    <row r="52" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A52" s="20"/>
       <c r="B52" s="20"/>
       <c r="C52" s="20"/>
@@ -5780,11 +6238,16 @@
       <c r="AZ52" s="20"/>
       <c r="BA52" s="20"/>
       <c r="BB52" s="20"/>
-      <c r="BC52" s="21"/>
-      <c r="BD52" s="21"/>
+      <c r="BC52" s="20"/>
+      <c r="BD52" s="20"/>
       <c r="BE52" s="20"/>
-    </row>
-    <row r="53" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF52" s="20"/>
+      <c r="BG52" s="20"/>
+      <c r="BH52" s="21"/>
+      <c r="BI52" s="21"/>
+      <c r="BJ52" s="20"/>
+    </row>
+    <row r="53" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A53" s="20"/>
       <c r="B53" s="20"/>
       <c r="C53" s="20"/>
@@ -5839,11 +6302,16 @@
       <c r="AZ53" s="20"/>
       <c r="BA53" s="20"/>
       <c r="BB53" s="20"/>
-      <c r="BC53" s="21"/>
-      <c r="BD53" s="21"/>
+      <c r="BC53" s="20"/>
+      <c r="BD53" s="20"/>
       <c r="BE53" s="20"/>
-    </row>
-    <row r="54" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF53" s="20"/>
+      <c r="BG53" s="20"/>
+      <c r="BH53" s="21"/>
+      <c r="BI53" s="21"/>
+      <c r="BJ53" s="20"/>
+    </row>
+    <row r="54" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A54" s="20"/>
       <c r="B54" s="20"/>
       <c r="C54" s="20"/>
@@ -5898,11 +6366,16 @@
       <c r="AZ54" s="20"/>
       <c r="BA54" s="20"/>
       <c r="BB54" s="20"/>
-      <c r="BC54" s="21"/>
-      <c r="BD54" s="21"/>
+      <c r="BC54" s="20"/>
+      <c r="BD54" s="20"/>
       <c r="BE54" s="20"/>
-    </row>
-    <row r="55" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF54" s="20"/>
+      <c r="BG54" s="20"/>
+      <c r="BH54" s="21"/>
+      <c r="BI54" s="21"/>
+      <c r="BJ54" s="20"/>
+    </row>
+    <row r="55" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A55" s="20"/>
       <c r="B55" s="20"/>
       <c r="C55" s="20"/>
@@ -5957,11 +6430,16 @@
       <c r="AZ55" s="20"/>
       <c r="BA55" s="20"/>
       <c r="BB55" s="20"/>
-      <c r="BC55" s="21"/>
-      <c r="BD55" s="21"/>
+      <c r="BC55" s="20"/>
+      <c r="BD55" s="20"/>
       <c r="BE55" s="20"/>
-    </row>
-    <row r="56" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF55" s="20"/>
+      <c r="BG55" s="20"/>
+      <c r="BH55" s="21"/>
+      <c r="BI55" s="21"/>
+      <c r="BJ55" s="20"/>
+    </row>
+    <row r="56" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A56" s="20"/>
       <c r="B56" s="20"/>
       <c r="C56" s="20"/>
@@ -6016,11 +6494,16 @@
       <c r="AZ56" s="20"/>
       <c r="BA56" s="20"/>
       <c r="BB56" s="20"/>
-      <c r="BC56" s="21"/>
-      <c r="BD56" s="21"/>
+      <c r="BC56" s="20"/>
+      <c r="BD56" s="20"/>
       <c r="BE56" s="20"/>
-    </row>
-    <row r="57" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF56" s="20"/>
+      <c r="BG56" s="20"/>
+      <c r="BH56" s="21"/>
+      <c r="BI56" s="21"/>
+      <c r="BJ56" s="20"/>
+    </row>
+    <row r="57" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A57" s="20"/>
       <c r="B57" s="20"/>
       <c r="C57" s="20"/>
@@ -6075,11 +6558,16 @@
       <c r="AZ57" s="20"/>
       <c r="BA57" s="20"/>
       <c r="BB57" s="20"/>
-      <c r="BC57" s="21"/>
-      <c r="BD57" s="21"/>
+      <c r="BC57" s="20"/>
+      <c r="BD57" s="20"/>
       <c r="BE57" s="20"/>
-    </row>
-    <row r="58" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF57" s="20"/>
+      <c r="BG57" s="20"/>
+      <c r="BH57" s="21"/>
+      <c r="BI57" s="21"/>
+      <c r="BJ57" s="20"/>
+    </row>
+    <row r="58" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A58" s="20"/>
       <c r="B58" s="20"/>
       <c r="C58" s="20"/>
@@ -6134,11 +6622,16 @@
       <c r="AZ58" s="20"/>
       <c r="BA58" s="20"/>
       <c r="BB58" s="20"/>
-      <c r="BC58" s="21"/>
-      <c r="BD58" s="21"/>
+      <c r="BC58" s="20"/>
+      <c r="BD58" s="20"/>
       <c r="BE58" s="20"/>
-    </row>
-    <row r="59" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF58" s="20"/>
+      <c r="BG58" s="20"/>
+      <c r="BH58" s="21"/>
+      <c r="BI58" s="21"/>
+      <c r="BJ58" s="20"/>
+    </row>
+    <row r="59" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A59" s="20"/>
       <c r="B59" s="20"/>
       <c r="C59" s="20"/>
@@ -6193,11 +6686,16 @@
       <c r="AZ59" s="20"/>
       <c r="BA59" s="20"/>
       <c r="BB59" s="20"/>
-      <c r="BC59" s="21"/>
-      <c r="BD59" s="21"/>
+      <c r="BC59" s="20"/>
+      <c r="BD59" s="20"/>
       <c r="BE59" s="20"/>
-    </row>
-    <row r="60" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF59" s="20"/>
+      <c r="BG59" s="20"/>
+      <c r="BH59" s="21"/>
+      <c r="BI59" s="21"/>
+      <c r="BJ59" s="20"/>
+    </row>
+    <row r="60" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A60" s="20"/>
       <c r="B60" s="20"/>
       <c r="C60" s="20"/>
@@ -6252,11 +6750,16 @@
       <c r="AZ60" s="20"/>
       <c r="BA60" s="20"/>
       <c r="BB60" s="20"/>
-      <c r="BC60" s="21"/>
-      <c r="BD60" s="21"/>
+      <c r="BC60" s="20"/>
+      <c r="BD60" s="20"/>
       <c r="BE60" s="20"/>
-    </row>
-    <row r="61" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF60" s="20"/>
+      <c r="BG60" s="20"/>
+      <c r="BH60" s="21"/>
+      <c r="BI60" s="21"/>
+      <c r="BJ60" s="20"/>
+    </row>
+    <row r="61" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A61" s="20"/>
       <c r="B61" s="20"/>
       <c r="C61" s="20"/>
@@ -6311,11 +6814,16 @@
       <c r="AZ61" s="20"/>
       <c r="BA61" s="20"/>
       <c r="BB61" s="20"/>
-      <c r="BC61" s="21"/>
-      <c r="BD61" s="21"/>
+      <c r="BC61" s="20"/>
+      <c r="BD61" s="20"/>
       <c r="BE61" s="20"/>
-    </row>
-    <row r="62" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF61" s="20"/>
+      <c r="BG61" s="20"/>
+      <c r="BH61" s="21"/>
+      <c r="BI61" s="21"/>
+      <c r="BJ61" s="20"/>
+    </row>
+    <row r="62" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A62" s="20"/>
       <c r="B62" s="20"/>
       <c r="C62" s="20"/>
@@ -6370,11 +6878,16 @@
       <c r="AZ62" s="20"/>
       <c r="BA62" s="20"/>
       <c r="BB62" s="20"/>
-      <c r="BC62" s="21"/>
-      <c r="BD62" s="21"/>
+      <c r="BC62" s="20"/>
+      <c r="BD62" s="20"/>
       <c r="BE62" s="20"/>
-    </row>
-    <row r="63" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF62" s="20"/>
+      <c r="BG62" s="20"/>
+      <c r="BH62" s="21"/>
+      <c r="BI62" s="21"/>
+      <c r="BJ62" s="20"/>
+    </row>
+    <row r="63" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A63" s="20"/>
       <c r="B63" s="20"/>
       <c r="C63" s="20"/>
@@ -6429,11 +6942,16 @@
       <c r="AZ63" s="20"/>
       <c r="BA63" s="20"/>
       <c r="BB63" s="20"/>
-      <c r="BC63" s="21"/>
-      <c r="BD63" s="21"/>
+      <c r="BC63" s="20"/>
+      <c r="BD63" s="20"/>
       <c r="BE63" s="20"/>
-    </row>
-    <row r="64" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF63" s="20"/>
+      <c r="BG63" s="20"/>
+      <c r="BH63" s="21"/>
+      <c r="BI63" s="21"/>
+      <c r="BJ63" s="20"/>
+    </row>
+    <row r="64" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A64" s="20"/>
       <c r="B64" s="20"/>
       <c r="C64" s="20"/>
@@ -6488,11 +7006,16 @@
       <c r="AZ64" s="20"/>
       <c r="BA64" s="20"/>
       <c r="BB64" s="20"/>
-      <c r="BC64" s="21"/>
-      <c r="BD64" s="21"/>
+      <c r="BC64" s="20"/>
+      <c r="BD64" s="20"/>
       <c r="BE64" s="20"/>
-    </row>
-    <row r="65" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF64" s="20"/>
+      <c r="BG64" s="20"/>
+      <c r="BH64" s="21"/>
+      <c r="BI64" s="21"/>
+      <c r="BJ64" s="20"/>
+    </row>
+    <row r="65" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A65" s="20"/>
       <c r="B65" s="20"/>
       <c r="C65" s="20"/>
@@ -6547,11 +7070,16 @@
       <c r="AZ65" s="20"/>
       <c r="BA65" s="20"/>
       <c r="BB65" s="20"/>
-      <c r="BC65" s="21"/>
-      <c r="BD65" s="21"/>
+      <c r="BC65" s="20"/>
+      <c r="BD65" s="20"/>
       <c r="BE65" s="20"/>
-    </row>
-    <row r="66" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF65" s="20"/>
+      <c r="BG65" s="20"/>
+      <c r="BH65" s="21"/>
+      <c r="BI65" s="21"/>
+      <c r="BJ65" s="20"/>
+    </row>
+    <row r="66" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A66" s="20"/>
       <c r="B66" s="20"/>
       <c r="C66" s="20"/>
@@ -6606,11 +7134,16 @@
       <c r="AZ66" s="20"/>
       <c r="BA66" s="20"/>
       <c r="BB66" s="20"/>
-      <c r="BC66" s="21"/>
-      <c r="BD66" s="21"/>
+      <c r="BC66" s="20"/>
+      <c r="BD66" s="20"/>
       <c r="BE66" s="20"/>
-    </row>
-    <row r="67" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF66" s="20"/>
+      <c r="BG66" s="20"/>
+      <c r="BH66" s="21"/>
+      <c r="BI66" s="21"/>
+      <c r="BJ66" s="20"/>
+    </row>
+    <row r="67" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A67" s="20"/>
       <c r="B67" s="20"/>
       <c r="C67" s="20"/>
@@ -6665,11 +7198,16 @@
       <c r="AZ67" s="20"/>
       <c r="BA67" s="20"/>
       <c r="BB67" s="20"/>
-      <c r="BC67" s="21"/>
-      <c r="BD67" s="21"/>
+      <c r="BC67" s="20"/>
+      <c r="BD67" s="20"/>
       <c r="BE67" s="20"/>
-    </row>
-    <row r="68" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF67" s="20"/>
+      <c r="BG67" s="20"/>
+      <c r="BH67" s="21"/>
+      <c r="BI67" s="21"/>
+      <c r="BJ67" s="20"/>
+    </row>
+    <row r="68" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A68" s="20"/>
       <c r="B68" s="20"/>
       <c r="C68" s="20"/>
@@ -6724,11 +7262,16 @@
       <c r="AZ68" s="20"/>
       <c r="BA68" s="20"/>
       <c r="BB68" s="20"/>
-      <c r="BC68" s="21"/>
-      <c r="BD68" s="21"/>
+      <c r="BC68" s="20"/>
+      <c r="BD68" s="20"/>
       <c r="BE68" s="20"/>
-    </row>
-    <row r="69" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF68" s="20"/>
+      <c r="BG68" s="20"/>
+      <c r="BH68" s="21"/>
+      <c r="BI68" s="21"/>
+      <c r="BJ68" s="20"/>
+    </row>
+    <row r="69" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A69" s="20"/>
       <c r="B69" s="20"/>
       <c r="C69" s="20"/>
@@ -6783,11 +7326,16 @@
       <c r="AZ69" s="20"/>
       <c r="BA69" s="20"/>
       <c r="BB69" s="20"/>
-      <c r="BC69" s="21"/>
-      <c r="BD69" s="21"/>
+      <c r="BC69" s="20"/>
+      <c r="BD69" s="20"/>
       <c r="BE69" s="20"/>
-    </row>
-    <row r="70" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF69" s="20"/>
+      <c r="BG69" s="20"/>
+      <c r="BH69" s="21"/>
+      <c r="BI69" s="21"/>
+      <c r="BJ69" s="20"/>
+    </row>
+    <row r="70" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A70" s="20"/>
       <c r="B70" s="20"/>
       <c r="C70" s="20"/>
@@ -6842,11 +7390,16 @@
       <c r="AZ70" s="20"/>
       <c r="BA70" s="20"/>
       <c r="BB70" s="20"/>
-      <c r="BC70" s="21"/>
-      <c r="BD70" s="21"/>
+      <c r="BC70" s="20"/>
+      <c r="BD70" s="20"/>
       <c r="BE70" s="20"/>
-    </row>
-    <row r="71" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF70" s="20"/>
+      <c r="BG70" s="20"/>
+      <c r="BH70" s="21"/>
+      <c r="BI70" s="21"/>
+      <c r="BJ70" s="20"/>
+    </row>
+    <row r="71" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A71" s="20"/>
       <c r="B71" s="20"/>
       <c r="C71" s="20"/>
@@ -6901,11 +7454,16 @@
       <c r="AZ71" s="20"/>
       <c r="BA71" s="20"/>
       <c r="BB71" s="20"/>
-      <c r="BC71" s="21"/>
-      <c r="BD71" s="21"/>
+      <c r="BC71" s="20"/>
+      <c r="BD71" s="20"/>
       <c r="BE71" s="20"/>
-    </row>
-    <row r="72" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF71" s="20"/>
+      <c r="BG71" s="20"/>
+      <c r="BH71" s="21"/>
+      <c r="BI71" s="21"/>
+      <c r="BJ71" s="20"/>
+    </row>
+    <row r="72" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A72" s="20"/>
       <c r="B72" s="20"/>
       <c r="C72" s="20"/>
@@ -6960,11 +7518,16 @@
       <c r="AZ72" s="20"/>
       <c r="BA72" s="20"/>
       <c r="BB72" s="20"/>
-      <c r="BC72" s="21"/>
-      <c r="BD72" s="21"/>
+      <c r="BC72" s="20"/>
+      <c r="BD72" s="20"/>
       <c r="BE72" s="20"/>
-    </row>
-    <row r="73" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF72" s="20"/>
+      <c r="BG72" s="20"/>
+      <c r="BH72" s="21"/>
+      <c r="BI72" s="21"/>
+      <c r="BJ72" s="20"/>
+    </row>
+    <row r="73" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A73" s="20"/>
       <c r="B73" s="20"/>
       <c r="C73" s="20"/>
@@ -7019,11 +7582,16 @@
       <c r="AZ73" s="20"/>
       <c r="BA73" s="20"/>
       <c r="BB73" s="20"/>
-      <c r="BC73" s="21"/>
-      <c r="BD73" s="21"/>
+      <c r="BC73" s="20"/>
+      <c r="BD73" s="20"/>
       <c r="BE73" s="20"/>
-    </row>
-    <row r="74" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF73" s="20"/>
+      <c r="BG73" s="20"/>
+      <c r="BH73" s="21"/>
+      <c r="BI73" s="21"/>
+      <c r="BJ73" s="20"/>
+    </row>
+    <row r="74" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A74" s="20"/>
       <c r="B74" s="20"/>
       <c r="C74" s="20"/>
@@ -7078,11 +7646,16 @@
       <c r="AZ74" s="20"/>
       <c r="BA74" s="20"/>
       <c r="BB74" s="20"/>
-      <c r="BC74" s="21"/>
-      <c r="BD74" s="21"/>
+      <c r="BC74" s="20"/>
+      <c r="BD74" s="20"/>
       <c r="BE74" s="20"/>
-    </row>
-    <row r="75" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF74" s="20"/>
+      <c r="BG74" s="20"/>
+      <c r="BH74" s="21"/>
+      <c r="BI74" s="21"/>
+      <c r="BJ74" s="20"/>
+    </row>
+    <row r="75" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A75" s="20"/>
       <c r="B75" s="20"/>
       <c r="C75" s="20"/>
@@ -7137,11 +7710,16 @@
       <c r="AZ75" s="20"/>
       <c r="BA75" s="20"/>
       <c r="BB75" s="20"/>
-      <c r="BC75" s="21"/>
-      <c r="BD75" s="21"/>
+      <c r="BC75" s="20"/>
+      <c r="BD75" s="20"/>
       <c r="BE75" s="20"/>
-    </row>
-    <row r="76" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF75" s="20"/>
+      <c r="BG75" s="20"/>
+      <c r="BH75" s="21"/>
+      <c r="BI75" s="21"/>
+      <c r="BJ75" s="20"/>
+    </row>
+    <row r="76" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A76" s="20"/>
       <c r="B76" s="20"/>
       <c r="C76" s="20"/>
@@ -7196,11 +7774,16 @@
       <c r="AZ76" s="20"/>
       <c r="BA76" s="20"/>
       <c r="BB76" s="20"/>
-      <c r="BC76" s="21"/>
-      <c r="BD76" s="21"/>
+      <c r="BC76" s="20"/>
+      <c r="BD76" s="20"/>
       <c r="BE76" s="20"/>
-    </row>
-    <row r="77" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF76" s="20"/>
+      <c r="BG76" s="20"/>
+      <c r="BH76" s="21"/>
+      <c r="BI76" s="21"/>
+      <c r="BJ76" s="20"/>
+    </row>
+    <row r="77" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A77" s="20"/>
       <c r="B77" s="20"/>
       <c r="C77" s="20"/>
@@ -7255,11 +7838,16 @@
       <c r="AZ77" s="20"/>
       <c r="BA77" s="20"/>
       <c r="BB77" s="20"/>
-      <c r="BC77" s="21"/>
-      <c r="BD77" s="21"/>
+      <c r="BC77" s="20"/>
+      <c r="BD77" s="20"/>
       <c r="BE77" s="20"/>
-    </row>
-    <row r="78" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF77" s="20"/>
+      <c r="BG77" s="20"/>
+      <c r="BH77" s="21"/>
+      <c r="BI77" s="21"/>
+      <c r="BJ77" s="20"/>
+    </row>
+    <row r="78" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A78" s="20"/>
       <c r="B78" s="20"/>
       <c r="C78" s="20"/>
@@ -7314,11 +7902,16 @@
       <c r="AZ78" s="20"/>
       <c r="BA78" s="20"/>
       <c r="BB78" s="20"/>
-      <c r="BC78" s="21"/>
-      <c r="BD78" s="21"/>
+      <c r="BC78" s="20"/>
+      <c r="BD78" s="20"/>
       <c r="BE78" s="20"/>
-    </row>
-    <row r="79" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF78" s="20"/>
+      <c r="BG78" s="20"/>
+      <c r="BH78" s="21"/>
+      <c r="BI78" s="21"/>
+      <c r="BJ78" s="20"/>
+    </row>
+    <row r="79" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A79" s="20"/>
       <c r="B79" s="20"/>
       <c r="C79" s="20"/>
@@ -7373,11 +7966,16 @@
       <c r="AZ79" s="20"/>
       <c r="BA79" s="20"/>
       <c r="BB79" s="20"/>
-      <c r="BC79" s="21"/>
-      <c r="BD79" s="21"/>
+      <c r="BC79" s="20"/>
+      <c r="BD79" s="20"/>
       <c r="BE79" s="20"/>
-    </row>
-    <row r="80" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF79" s="20"/>
+      <c r="BG79" s="20"/>
+      <c r="BH79" s="21"/>
+      <c r="BI79" s="21"/>
+      <c r="BJ79" s="20"/>
+    </row>
+    <row r="80" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A80" s="20"/>
       <c r="B80" s="20"/>
       <c r="C80" s="20"/>
@@ -7432,11 +8030,16 @@
       <c r="AZ80" s="20"/>
       <c r="BA80" s="20"/>
       <c r="BB80" s="20"/>
-      <c r="BC80" s="21"/>
-      <c r="BD80" s="21"/>
+      <c r="BC80" s="20"/>
+      <c r="BD80" s="20"/>
       <c r="BE80" s="20"/>
-    </row>
-    <row r="81" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF80" s="20"/>
+      <c r="BG80" s="20"/>
+      <c r="BH80" s="21"/>
+      <c r="BI80" s="21"/>
+      <c r="BJ80" s="20"/>
+    </row>
+    <row r="81" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A81" s="20"/>
       <c r="B81" s="20"/>
       <c r="C81" s="20"/>
@@ -7491,11 +8094,16 @@
       <c r="AZ81" s="20"/>
       <c r="BA81" s="20"/>
       <c r="BB81" s="20"/>
-      <c r="BC81" s="21"/>
-      <c r="BD81" s="21"/>
+      <c r="BC81" s="20"/>
+      <c r="BD81" s="20"/>
       <c r="BE81" s="20"/>
-    </row>
-    <row r="82" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF81" s="20"/>
+      <c r="BG81" s="20"/>
+      <c r="BH81" s="21"/>
+      <c r="BI81" s="21"/>
+      <c r="BJ81" s="20"/>
+    </row>
+    <row r="82" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A82" s="20"/>
       <c r="B82" s="20"/>
       <c r="C82" s="20"/>
@@ -7550,11 +8158,16 @@
       <c r="AZ82" s="20"/>
       <c r="BA82" s="20"/>
       <c r="BB82" s="20"/>
-      <c r="BC82" s="21"/>
-      <c r="BD82" s="21"/>
+      <c r="BC82" s="20"/>
+      <c r="BD82" s="20"/>
       <c r="BE82" s="20"/>
-    </row>
-    <row r="83" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF82" s="20"/>
+      <c r="BG82" s="20"/>
+      <c r="BH82" s="21"/>
+      <c r="BI82" s="21"/>
+      <c r="BJ82" s="20"/>
+    </row>
+    <row r="83" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A83" s="20"/>
       <c r="B83" s="20"/>
       <c r="C83" s="20"/>
@@ -7609,11 +8222,16 @@
       <c r="AZ83" s="20"/>
       <c r="BA83" s="20"/>
       <c r="BB83" s="20"/>
-      <c r="BC83" s="21"/>
-      <c r="BD83" s="21"/>
+      <c r="BC83" s="20"/>
+      <c r="BD83" s="20"/>
       <c r="BE83" s="20"/>
-    </row>
-    <row r="84" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF83" s="20"/>
+      <c r="BG83" s="20"/>
+      <c r="BH83" s="21"/>
+      <c r="BI83" s="21"/>
+      <c r="BJ83" s="20"/>
+    </row>
+    <row r="84" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A84" s="20"/>
       <c r="B84" s="20"/>
       <c r="C84" s="20"/>
@@ -7668,11 +8286,16 @@
       <c r="AZ84" s="20"/>
       <c r="BA84" s="20"/>
       <c r="BB84" s="20"/>
-      <c r="BC84" s="21"/>
-      <c r="BD84" s="21"/>
+      <c r="BC84" s="20"/>
+      <c r="BD84" s="20"/>
       <c r="BE84" s="20"/>
-    </row>
-    <row r="85" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF84" s="20"/>
+      <c r="BG84" s="20"/>
+      <c r="BH84" s="21"/>
+      <c r="BI84" s="21"/>
+      <c r="BJ84" s="20"/>
+    </row>
+    <row r="85" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A85" s="20"/>
       <c r="B85" s="20"/>
       <c r="C85" s="20"/>
@@ -7727,11 +8350,16 @@
       <c r="AZ85" s="20"/>
       <c r="BA85" s="20"/>
       <c r="BB85" s="20"/>
-      <c r="BC85" s="21"/>
-      <c r="BD85" s="21"/>
+      <c r="BC85" s="20"/>
+      <c r="BD85" s="20"/>
       <c r="BE85" s="20"/>
-    </row>
-    <row r="86" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF85" s="20"/>
+      <c r="BG85" s="20"/>
+      <c r="BH85" s="21"/>
+      <c r="BI85" s="21"/>
+      <c r="BJ85" s="20"/>
+    </row>
+    <row r="86" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A86" s="20"/>
       <c r="B86" s="20"/>
       <c r="C86" s="20"/>
@@ -7786,11 +8414,16 @@
       <c r="AZ86" s="20"/>
       <c r="BA86" s="20"/>
       <c r="BB86" s="20"/>
-      <c r="BC86" s="21"/>
-      <c r="BD86" s="21"/>
+      <c r="BC86" s="20"/>
+      <c r="BD86" s="20"/>
       <c r="BE86" s="20"/>
-    </row>
-    <row r="87" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF86" s="20"/>
+      <c r="BG86" s="20"/>
+      <c r="BH86" s="21"/>
+      <c r="BI86" s="21"/>
+      <c r="BJ86" s="20"/>
+    </row>
+    <row r="87" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A87" s="20"/>
       <c r="B87" s="20"/>
       <c r="C87" s="20"/>
@@ -7845,11 +8478,16 @@
       <c r="AZ87" s="20"/>
       <c r="BA87" s="20"/>
       <c r="BB87" s="20"/>
-      <c r="BC87" s="21"/>
-      <c r="BD87" s="21"/>
+      <c r="BC87" s="20"/>
+      <c r="BD87" s="20"/>
       <c r="BE87" s="20"/>
-    </row>
-    <row r="88" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF87" s="20"/>
+      <c r="BG87" s="20"/>
+      <c r="BH87" s="21"/>
+      <c r="BI87" s="21"/>
+      <c r="BJ87" s="20"/>
+    </row>
+    <row r="88" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A88" s="20"/>
       <c r="B88" s="20"/>
       <c r="C88" s="20"/>
@@ -7904,11 +8542,16 @@
       <c r="AZ88" s="20"/>
       <c r="BA88" s="20"/>
       <c r="BB88" s="20"/>
-      <c r="BC88" s="21"/>
-      <c r="BD88" s="21"/>
+      <c r="BC88" s="20"/>
+      <c r="BD88" s="20"/>
       <c r="BE88" s="20"/>
-    </row>
-    <row r="89" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF88" s="20"/>
+      <c r="BG88" s="20"/>
+      <c r="BH88" s="21"/>
+      <c r="BI88" s="21"/>
+      <c r="BJ88" s="20"/>
+    </row>
+    <row r="89" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A89" s="20"/>
       <c r="B89" s="20"/>
       <c r="C89" s="20"/>
@@ -7963,11 +8606,16 @@
       <c r="AZ89" s="20"/>
       <c r="BA89" s="20"/>
       <c r="BB89" s="20"/>
-      <c r="BC89" s="21"/>
-      <c r="BD89" s="21"/>
+      <c r="BC89" s="20"/>
+      <c r="BD89" s="20"/>
       <c r="BE89" s="20"/>
-    </row>
-    <row r="90" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF89" s="20"/>
+      <c r="BG89" s="20"/>
+      <c r="BH89" s="21"/>
+      <c r="BI89" s="21"/>
+      <c r="BJ89" s="20"/>
+    </row>
+    <row r="90" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A90" s="20"/>
       <c r="B90" s="20"/>
       <c r="C90" s="20"/>
@@ -8022,11 +8670,16 @@
       <c r="AZ90" s="20"/>
       <c r="BA90" s="20"/>
       <c r="BB90" s="20"/>
-      <c r="BC90" s="21"/>
-      <c r="BD90" s="21"/>
+      <c r="BC90" s="20"/>
+      <c r="BD90" s="20"/>
       <c r="BE90" s="20"/>
-    </row>
-    <row r="91" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF90" s="20"/>
+      <c r="BG90" s="20"/>
+      <c r="BH90" s="21"/>
+      <c r="BI90" s="21"/>
+      <c r="BJ90" s="20"/>
+    </row>
+    <row r="91" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A91" s="20"/>
       <c r="B91" s="20"/>
       <c r="C91" s="20"/>
@@ -8081,11 +8734,16 @@
       <c r="AZ91" s="20"/>
       <c r="BA91" s="20"/>
       <c r="BB91" s="20"/>
-      <c r="BC91" s="21"/>
-      <c r="BD91" s="21"/>
+      <c r="BC91" s="20"/>
+      <c r="BD91" s="20"/>
       <c r="BE91" s="20"/>
-    </row>
-    <row r="92" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF91" s="20"/>
+      <c r="BG91" s="20"/>
+      <c r="BH91" s="21"/>
+      <c r="BI91" s="21"/>
+      <c r="BJ91" s="20"/>
+    </row>
+    <row r="92" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A92" s="20"/>
       <c r="B92" s="20"/>
       <c r="C92" s="20"/>
@@ -8140,11 +8798,16 @@
       <c r="AZ92" s="20"/>
       <c r="BA92" s="20"/>
       <c r="BB92" s="20"/>
-      <c r="BC92" s="21"/>
-      <c r="BD92" s="21"/>
+      <c r="BC92" s="20"/>
+      <c r="BD92" s="20"/>
       <c r="BE92" s="20"/>
-    </row>
-    <row r="93" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF92" s="20"/>
+      <c r="BG92" s="20"/>
+      <c r="BH92" s="21"/>
+      <c r="BI92" s="21"/>
+      <c r="BJ92" s="20"/>
+    </row>
+    <row r="93" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A93" s="20"/>
       <c r="B93" s="20"/>
       <c r="C93" s="20"/>
@@ -8199,11 +8862,16 @@
       <c r="AZ93" s="20"/>
       <c r="BA93" s="20"/>
       <c r="BB93" s="20"/>
-      <c r="BC93" s="21"/>
-      <c r="BD93" s="21"/>
+      <c r="BC93" s="20"/>
+      <c r="BD93" s="20"/>
       <c r="BE93" s="20"/>
-    </row>
-    <row r="94" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF93" s="20"/>
+      <c r="BG93" s="20"/>
+      <c r="BH93" s="21"/>
+      <c r="BI93" s="21"/>
+      <c r="BJ93" s="20"/>
+    </row>
+    <row r="94" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A94" s="20"/>
       <c r="B94" s="20"/>
       <c r="C94" s="20"/>
@@ -8258,11 +8926,16 @@
       <c r="AZ94" s="20"/>
       <c r="BA94" s="20"/>
       <c r="BB94" s="20"/>
-      <c r="BC94" s="21"/>
-      <c r="BD94" s="21"/>
+      <c r="BC94" s="20"/>
+      <c r="BD94" s="20"/>
       <c r="BE94" s="20"/>
-    </row>
-    <row r="95" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF94" s="20"/>
+      <c r="BG94" s="20"/>
+      <c r="BH94" s="21"/>
+      <c r="BI94" s="21"/>
+      <c r="BJ94" s="20"/>
+    </row>
+    <row r="95" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A95" s="20"/>
       <c r="B95" s="20"/>
       <c r="C95" s="20"/>
@@ -8317,11 +8990,16 @@
       <c r="AZ95" s="20"/>
       <c r="BA95" s="20"/>
       <c r="BB95" s="20"/>
-      <c r="BC95" s="21"/>
-      <c r="BD95" s="21"/>
+      <c r="BC95" s="20"/>
+      <c r="BD95" s="20"/>
       <c r="BE95" s="20"/>
-    </row>
-    <row r="96" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF95" s="20"/>
+      <c r="BG95" s="20"/>
+      <c r="BH95" s="21"/>
+      <c r="BI95" s="21"/>
+      <c r="BJ95" s="20"/>
+    </row>
+    <row r="96" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A96" s="20"/>
       <c r="B96" s="20"/>
       <c r="C96" s="20"/>
@@ -8376,11 +9054,16 @@
       <c r="AZ96" s="20"/>
       <c r="BA96" s="20"/>
       <c r="BB96" s="20"/>
-      <c r="BC96" s="21"/>
-      <c r="BD96" s="21"/>
+      <c r="BC96" s="20"/>
+      <c r="BD96" s="20"/>
       <c r="BE96" s="20"/>
-    </row>
-    <row r="97" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF96" s="20"/>
+      <c r="BG96" s="20"/>
+      <c r="BH96" s="21"/>
+      <c r="BI96" s="21"/>
+      <c r="BJ96" s="20"/>
+    </row>
+    <row r="97" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A97" s="20"/>
       <c r="B97" s="20"/>
       <c r="C97" s="20"/>
@@ -8435,11 +9118,16 @@
       <c r="AZ97" s="20"/>
       <c r="BA97" s="20"/>
       <c r="BB97" s="20"/>
-      <c r="BC97" s="21"/>
-      <c r="BD97" s="21"/>
+      <c r="BC97" s="20"/>
+      <c r="BD97" s="20"/>
       <c r="BE97" s="20"/>
-    </row>
-    <row r="98" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF97" s="20"/>
+      <c r="BG97" s="20"/>
+      <c r="BH97" s="21"/>
+      <c r="BI97" s="21"/>
+      <c r="BJ97" s="20"/>
+    </row>
+    <row r="98" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A98" s="20"/>
       <c r="B98" s="20"/>
       <c r="C98" s="20"/>
@@ -8494,11 +9182,16 @@
       <c r="AZ98" s="20"/>
       <c r="BA98" s="20"/>
       <c r="BB98" s="20"/>
-      <c r="BC98" s="21"/>
-      <c r="BD98" s="21"/>
+      <c r="BC98" s="20"/>
+      <c r="BD98" s="20"/>
       <c r="BE98" s="20"/>
-    </row>
-    <row r="99" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF98" s="20"/>
+      <c r="BG98" s="20"/>
+      <c r="BH98" s="21"/>
+      <c r="BI98" s="21"/>
+      <c r="BJ98" s="20"/>
+    </row>
+    <row r="99" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A99" s="20"/>
       <c r="B99" s="20"/>
       <c r="C99" s="20"/>
@@ -8553,11 +9246,16 @@
       <c r="AZ99" s="20"/>
       <c r="BA99" s="20"/>
       <c r="BB99" s="20"/>
-      <c r="BC99" s="21"/>
-      <c r="BD99" s="21"/>
+      <c r="BC99" s="20"/>
+      <c r="BD99" s="20"/>
       <c r="BE99" s="20"/>
-    </row>
-    <row r="100" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF99" s="20"/>
+      <c r="BG99" s="20"/>
+      <c r="BH99" s="21"/>
+      <c r="BI99" s="21"/>
+      <c r="BJ99" s="20"/>
+    </row>
+    <row r="100" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A100" s="20"/>
       <c r="B100" s="20"/>
       <c r="C100" s="20"/>
@@ -8612,11 +9310,16 @@
       <c r="AZ100" s="20"/>
       <c r="BA100" s="20"/>
       <c r="BB100" s="20"/>
-      <c r="BC100" s="21"/>
-      <c r="BD100" s="21"/>
+      <c r="BC100" s="20"/>
+      <c r="BD100" s="20"/>
       <c r="BE100" s="20"/>
-    </row>
-    <row r="101" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF100" s="20"/>
+      <c r="BG100" s="20"/>
+      <c r="BH100" s="21"/>
+      <c r="BI100" s="21"/>
+      <c r="BJ100" s="20"/>
+    </row>
+    <row r="101" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A101" s="20"/>
       <c r="B101" s="20"/>
       <c r="C101" s="20"/>
@@ -8671,11 +9374,16 @@
       <c r="AZ101" s="20"/>
       <c r="BA101" s="20"/>
       <c r="BB101" s="20"/>
-      <c r="BC101" s="21"/>
-      <c r="BD101" s="21"/>
+      <c r="BC101" s="20"/>
+      <c r="BD101" s="20"/>
       <c r="BE101" s="20"/>
-    </row>
-    <row r="102" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF101" s="20"/>
+      <c r="BG101" s="20"/>
+      <c r="BH101" s="21"/>
+      <c r="BI101" s="21"/>
+      <c r="BJ101" s="20"/>
+    </row>
+    <row r="102" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A102" s="20"/>
       <c r="B102" s="20"/>
       <c r="C102" s="20"/>
@@ -8730,11 +9438,16 @@
       <c r="AZ102" s="20"/>
       <c r="BA102" s="20"/>
       <c r="BB102" s="20"/>
-      <c r="BC102" s="21"/>
-      <c r="BD102" s="21"/>
+      <c r="BC102" s="20"/>
+      <c r="BD102" s="20"/>
       <c r="BE102" s="20"/>
-    </row>
-    <row r="103" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF102" s="20"/>
+      <c r="BG102" s="20"/>
+      <c r="BH102" s="21"/>
+      <c r="BI102" s="21"/>
+      <c r="BJ102" s="20"/>
+    </row>
+    <row r="103" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A103" s="20"/>
       <c r="B103" s="20"/>
       <c r="C103" s="20"/>
@@ -8789,11 +9502,16 @@
       <c r="AZ103" s="20"/>
       <c r="BA103" s="20"/>
       <c r="BB103" s="20"/>
-      <c r="BC103" s="21"/>
-      <c r="BD103" s="21"/>
+      <c r="BC103" s="20"/>
+      <c r="BD103" s="20"/>
       <c r="BE103" s="20"/>
-    </row>
-    <row r="104" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF103" s="20"/>
+      <c r="BG103" s="20"/>
+      <c r="BH103" s="21"/>
+      <c r="BI103" s="21"/>
+      <c r="BJ103" s="20"/>
+    </row>
+    <row r="104" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A104" s="20"/>
       <c r="B104" s="20"/>
       <c r="C104" s="20"/>
@@ -8848,11 +9566,16 @@
       <c r="AZ104" s="20"/>
       <c r="BA104" s="20"/>
       <c r="BB104" s="20"/>
-      <c r="BC104" s="21"/>
-      <c r="BD104" s="21"/>
+      <c r="BC104" s="20"/>
+      <c r="BD104" s="20"/>
       <c r="BE104" s="20"/>
-    </row>
-    <row r="105" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF104" s="20"/>
+      <c r="BG104" s="20"/>
+      <c r="BH104" s="21"/>
+      <c r="BI104" s="21"/>
+      <c r="BJ104" s="20"/>
+    </row>
+    <row r="105" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A105" s="20"/>
       <c r="B105" s="20"/>
       <c r="C105" s="20"/>
@@ -8907,11 +9630,16 @@
       <c r="AZ105" s="20"/>
       <c r="BA105" s="20"/>
       <c r="BB105" s="20"/>
-      <c r="BC105" s="21"/>
-      <c r="BD105" s="21"/>
+      <c r="BC105" s="20"/>
+      <c r="BD105" s="20"/>
       <c r="BE105" s="20"/>
-    </row>
-    <row r="106" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF105" s="20"/>
+      <c r="BG105" s="20"/>
+      <c r="BH105" s="21"/>
+      <c r="BI105" s="21"/>
+      <c r="BJ105" s="20"/>
+    </row>
+    <row r="106" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A106" s="20"/>
       <c r="B106" s="20"/>
       <c r="C106" s="20"/>
@@ -8966,11 +9694,16 @@
       <c r="AZ106" s="20"/>
       <c r="BA106" s="20"/>
       <c r="BB106" s="20"/>
-      <c r="BC106" s="21"/>
-      <c r="BD106" s="21"/>
+      <c r="BC106" s="20"/>
+      <c r="BD106" s="20"/>
       <c r="BE106" s="20"/>
-    </row>
-    <row r="107" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF106" s="20"/>
+      <c r="BG106" s="20"/>
+      <c r="BH106" s="21"/>
+      <c r="BI106" s="21"/>
+      <c r="BJ106" s="20"/>
+    </row>
+    <row r="107" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A107" s="20"/>
       <c r="B107" s="20"/>
       <c r="C107" s="20"/>
@@ -9025,11 +9758,16 @@
       <c r="AZ107" s="20"/>
       <c r="BA107" s="20"/>
       <c r="BB107" s="20"/>
-      <c r="BC107" s="21"/>
-      <c r="BD107" s="21"/>
+      <c r="BC107" s="20"/>
+      <c r="BD107" s="20"/>
       <c r="BE107" s="20"/>
-    </row>
-    <row r="108" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF107" s="20"/>
+      <c r="BG107" s="20"/>
+      <c r="BH107" s="21"/>
+      <c r="BI107" s="21"/>
+      <c r="BJ107" s="20"/>
+    </row>
+    <row r="108" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A108" s="20"/>
       <c r="B108" s="20"/>
       <c r="C108" s="20"/>
@@ -9084,11 +9822,16 @@
       <c r="AZ108" s="20"/>
       <c r="BA108" s="20"/>
       <c r="BB108" s="20"/>
-      <c r="BC108" s="21"/>
-      <c r="BD108" s="21"/>
+      <c r="BC108" s="20"/>
+      <c r="BD108" s="20"/>
       <c r="BE108" s="20"/>
-    </row>
-    <row r="109" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF108" s="20"/>
+      <c r="BG108" s="20"/>
+      <c r="BH108" s="21"/>
+      <c r="BI108" s="21"/>
+      <c r="BJ108" s="20"/>
+    </row>
+    <row r="109" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A109" s="20"/>
       <c r="B109" s="20"/>
       <c r="C109" s="20"/>
@@ -9143,11 +9886,16 @@
       <c r="AZ109" s="20"/>
       <c r="BA109" s="20"/>
       <c r="BB109" s="20"/>
-      <c r="BC109" s="21"/>
-      <c r="BD109" s="21"/>
+      <c r="BC109" s="20"/>
+      <c r="BD109" s="20"/>
       <c r="BE109" s="20"/>
-    </row>
-    <row r="110" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF109" s="20"/>
+      <c r="BG109" s="20"/>
+      <c r="BH109" s="21"/>
+      <c r="BI109" s="21"/>
+      <c r="BJ109" s="20"/>
+    </row>
+    <row r="110" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A110" s="20"/>
       <c r="B110" s="20"/>
       <c r="C110" s="20"/>
@@ -9202,11 +9950,16 @@
       <c r="AZ110" s="20"/>
       <c r="BA110" s="20"/>
       <c r="BB110" s="20"/>
-      <c r="BC110" s="21"/>
-      <c r="BD110" s="21"/>
+      <c r="BC110" s="20"/>
+      <c r="BD110" s="20"/>
       <c r="BE110" s="20"/>
-    </row>
-    <row r="111" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF110" s="20"/>
+      <c r="BG110" s="20"/>
+      <c r="BH110" s="21"/>
+      <c r="BI110" s="21"/>
+      <c r="BJ110" s="20"/>
+    </row>
+    <row r="111" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A111" s="20"/>
       <c r="B111" s="20"/>
       <c r="C111" s="20"/>
@@ -9261,11 +10014,16 @@
       <c r="AZ111" s="20"/>
       <c r="BA111" s="20"/>
       <c r="BB111" s="20"/>
-      <c r="BC111" s="21"/>
-      <c r="BD111" s="21"/>
+      <c r="BC111" s="20"/>
+      <c r="BD111" s="20"/>
       <c r="BE111" s="20"/>
-    </row>
-    <row r="112" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF111" s="20"/>
+      <c r="BG111" s="20"/>
+      <c r="BH111" s="21"/>
+      <c r="BI111" s="21"/>
+      <c r="BJ111" s="20"/>
+    </row>
+    <row r="112" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A112" s="20"/>
       <c r="B112" s="20"/>
       <c r="C112" s="20"/>
@@ -9320,11 +10078,16 @@
       <c r="AZ112" s="20"/>
       <c r="BA112" s="20"/>
       <c r="BB112" s="20"/>
-      <c r="BC112" s="21"/>
-      <c r="BD112" s="21"/>
+      <c r="BC112" s="20"/>
+      <c r="BD112" s="20"/>
       <c r="BE112" s="20"/>
-    </row>
-    <row r="113" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF112" s="20"/>
+      <c r="BG112" s="20"/>
+      <c r="BH112" s="21"/>
+      <c r="BI112" s="21"/>
+      <c r="BJ112" s="20"/>
+    </row>
+    <row r="113" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A113" s="20"/>
       <c r="B113" s="20"/>
       <c r="C113" s="20"/>
@@ -9379,11 +10142,16 @@
       <c r="AZ113" s="20"/>
       <c r="BA113" s="20"/>
       <c r="BB113" s="20"/>
-      <c r="BC113" s="21"/>
-      <c r="BD113" s="21"/>
+      <c r="BC113" s="20"/>
+      <c r="BD113" s="20"/>
       <c r="BE113" s="20"/>
-    </row>
-    <row r="114" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF113" s="20"/>
+      <c r="BG113" s="20"/>
+      <c r="BH113" s="21"/>
+      <c r="BI113" s="21"/>
+      <c r="BJ113" s="20"/>
+    </row>
+    <row r="114" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A114" s="20"/>
       <c r="B114" s="20"/>
       <c r="C114" s="20"/>
@@ -9438,11 +10206,16 @@
       <c r="AZ114" s="20"/>
       <c r="BA114" s="20"/>
       <c r="BB114" s="20"/>
-      <c r="BC114" s="21"/>
-      <c r="BD114" s="21"/>
+      <c r="BC114" s="20"/>
+      <c r="BD114" s="20"/>
       <c r="BE114" s="20"/>
-    </row>
-    <row r="115" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF114" s="20"/>
+      <c r="BG114" s="20"/>
+      <c r="BH114" s="21"/>
+      <c r="BI114" s="21"/>
+      <c r="BJ114" s="20"/>
+    </row>
+    <row r="115" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A115" s="20"/>
       <c r="B115" s="20"/>
       <c r="C115" s="20"/>
@@ -9497,11 +10270,16 @@
       <c r="AZ115" s="20"/>
       <c r="BA115" s="20"/>
       <c r="BB115" s="20"/>
-      <c r="BC115" s="21"/>
-      <c r="BD115" s="21"/>
+      <c r="BC115" s="20"/>
+      <c r="BD115" s="20"/>
       <c r="BE115" s="20"/>
-    </row>
-    <row r="116" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF115" s="20"/>
+      <c r="BG115" s="20"/>
+      <c r="BH115" s="21"/>
+      <c r="BI115" s="21"/>
+      <c r="BJ115" s="20"/>
+    </row>
+    <row r="116" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A116" s="20"/>
       <c r="B116" s="20"/>
       <c r="C116" s="20"/>
@@ -9556,11 +10334,16 @@
       <c r="AZ116" s="20"/>
       <c r="BA116" s="20"/>
       <c r="BB116" s="20"/>
-      <c r="BC116" s="21"/>
-      <c r="BD116" s="21"/>
+      <c r="BC116" s="20"/>
+      <c r="BD116" s="20"/>
       <c r="BE116" s="20"/>
-    </row>
-    <row r="117" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF116" s="20"/>
+      <c r="BG116" s="20"/>
+      <c r="BH116" s="21"/>
+      <c r="BI116" s="21"/>
+      <c r="BJ116" s="20"/>
+    </row>
+    <row r="117" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A117" s="20"/>
       <c r="B117" s="20"/>
       <c r="C117" s="20"/>
@@ -9615,11 +10398,16 @@
       <c r="AZ117" s="20"/>
       <c r="BA117" s="20"/>
       <c r="BB117" s="20"/>
-      <c r="BC117" s="21"/>
-      <c r="BD117" s="21"/>
+      <c r="BC117" s="20"/>
+      <c r="BD117" s="20"/>
       <c r="BE117" s="20"/>
-    </row>
-    <row r="118" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF117" s="20"/>
+      <c r="BG117" s="20"/>
+      <c r="BH117" s="21"/>
+      <c r="BI117" s="21"/>
+      <c r="BJ117" s="20"/>
+    </row>
+    <row r="118" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A118" s="20"/>
       <c r="B118" s="20"/>
       <c r="C118" s="20"/>
@@ -9674,11 +10462,16 @@
       <c r="AZ118" s="20"/>
       <c r="BA118" s="20"/>
       <c r="BB118" s="20"/>
-      <c r="BC118" s="21"/>
-      <c r="BD118" s="21"/>
+      <c r="BC118" s="20"/>
+      <c r="BD118" s="20"/>
       <c r="BE118" s="20"/>
-    </row>
-    <row r="119" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF118" s="20"/>
+      <c r="BG118" s="20"/>
+      <c r="BH118" s="21"/>
+      <c r="BI118" s="21"/>
+      <c r="BJ118" s="20"/>
+    </row>
+    <row r="119" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A119" s="20"/>
       <c r="B119" s="20"/>
       <c r="C119" s="20"/>
@@ -9733,11 +10526,16 @@
       <c r="AZ119" s="20"/>
       <c r="BA119" s="20"/>
       <c r="BB119" s="20"/>
-      <c r="BC119" s="21"/>
-      <c r="BD119" s="21"/>
+      <c r="BC119" s="20"/>
+      <c r="BD119" s="20"/>
       <c r="BE119" s="20"/>
-    </row>
-    <row r="120" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF119" s="20"/>
+      <c r="BG119" s="20"/>
+      <c r="BH119" s="21"/>
+      <c r="BI119" s="21"/>
+      <c r="BJ119" s="20"/>
+    </row>
+    <row r="120" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A120" s="20"/>
       <c r="B120" s="20"/>
       <c r="C120" s="20"/>
@@ -9792,11 +10590,16 @@
       <c r="AZ120" s="20"/>
       <c r="BA120" s="20"/>
       <c r="BB120" s="20"/>
-      <c r="BC120" s="21"/>
-      <c r="BD120" s="21"/>
+      <c r="BC120" s="20"/>
+      <c r="BD120" s="20"/>
       <c r="BE120" s="20"/>
-    </row>
-    <row r="121" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF120" s="20"/>
+      <c r="BG120" s="20"/>
+      <c r="BH120" s="21"/>
+      <c r="BI120" s="21"/>
+      <c r="BJ120" s="20"/>
+    </row>
+    <row r="121" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A121" s="20"/>
       <c r="B121" s="20"/>
       <c r="C121" s="20"/>
@@ -9851,11 +10654,16 @@
       <c r="AZ121" s="20"/>
       <c r="BA121" s="20"/>
       <c r="BB121" s="20"/>
-      <c r="BC121" s="21"/>
-      <c r="BD121" s="21"/>
+      <c r="BC121" s="20"/>
+      <c r="BD121" s="20"/>
       <c r="BE121" s="20"/>
-    </row>
-    <row r="122" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF121" s="20"/>
+      <c r="BG121" s="20"/>
+      <c r="BH121" s="21"/>
+      <c r="BI121" s="21"/>
+      <c r="BJ121" s="20"/>
+    </row>
+    <row r="122" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A122" s="20"/>
       <c r="B122" s="20"/>
       <c r="C122" s="20"/>
@@ -9910,11 +10718,16 @@
       <c r="AZ122" s="20"/>
       <c r="BA122" s="20"/>
       <c r="BB122" s="20"/>
-      <c r="BC122" s="21"/>
-      <c r="BD122" s="21"/>
+      <c r="BC122" s="20"/>
+      <c r="BD122" s="20"/>
       <c r="BE122" s="20"/>
-    </row>
-    <row r="123" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF122" s="20"/>
+      <c r="BG122" s="20"/>
+      <c r="BH122" s="21"/>
+      <c r="BI122" s="21"/>
+      <c r="BJ122" s="20"/>
+    </row>
+    <row r="123" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A123" s="20"/>
       <c r="B123" s="20"/>
       <c r="C123" s="20"/>
@@ -9969,11 +10782,16 @@
       <c r="AZ123" s="20"/>
       <c r="BA123" s="20"/>
       <c r="BB123" s="20"/>
-      <c r="BC123" s="21"/>
-      <c r="BD123" s="21"/>
+      <c r="BC123" s="20"/>
+      <c r="BD123" s="20"/>
       <c r="BE123" s="20"/>
-    </row>
-    <row r="124" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF123" s="20"/>
+      <c r="BG123" s="20"/>
+      <c r="BH123" s="21"/>
+      <c r="BI123" s="21"/>
+      <c r="BJ123" s="20"/>
+    </row>
+    <row r="124" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A124" s="20"/>
       <c r="B124" s="20"/>
       <c r="C124" s="20"/>
@@ -10028,11 +10846,16 @@
       <c r="AZ124" s="20"/>
       <c r="BA124" s="20"/>
       <c r="BB124" s="20"/>
-      <c r="BC124" s="21"/>
-      <c r="BD124" s="21"/>
+      <c r="BC124" s="20"/>
+      <c r="BD124" s="20"/>
       <c r="BE124" s="20"/>
-    </row>
-    <row r="125" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF124" s="20"/>
+      <c r="BG124" s="20"/>
+      <c r="BH124" s="21"/>
+      <c r="BI124" s="21"/>
+      <c r="BJ124" s="20"/>
+    </row>
+    <row r="125" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A125" s="20"/>
       <c r="B125" s="20"/>
       <c r="C125" s="20"/>
@@ -10087,11 +10910,16 @@
       <c r="AZ125" s="20"/>
       <c r="BA125" s="20"/>
       <c r="BB125" s="20"/>
-      <c r="BC125" s="21"/>
-      <c r="BD125" s="21"/>
+      <c r="BC125" s="20"/>
+      <c r="BD125" s="20"/>
       <c r="BE125" s="20"/>
-    </row>
-    <row r="126" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF125" s="20"/>
+      <c r="BG125" s="20"/>
+      <c r="BH125" s="21"/>
+      <c r="BI125" s="21"/>
+      <c r="BJ125" s="20"/>
+    </row>
+    <row r="126" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A126" s="20"/>
       <c r="B126" s="20"/>
       <c r="C126" s="20"/>
@@ -10146,11 +10974,16 @@
       <c r="AZ126" s="20"/>
       <c r="BA126" s="20"/>
       <c r="BB126" s="20"/>
-      <c r="BC126" s="21"/>
-      <c r="BD126" s="21"/>
+      <c r="BC126" s="20"/>
+      <c r="BD126" s="20"/>
       <c r="BE126" s="20"/>
-    </row>
-    <row r="127" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF126" s="20"/>
+      <c r="BG126" s="20"/>
+      <c r="BH126" s="21"/>
+      <c r="BI126" s="21"/>
+      <c r="BJ126" s="20"/>
+    </row>
+    <row r="127" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A127" s="20"/>
       <c r="B127" s="20"/>
       <c r="C127" s="20"/>
@@ -10205,11 +11038,16 @@
       <c r="AZ127" s="20"/>
       <c r="BA127" s="20"/>
       <c r="BB127" s="20"/>
-      <c r="BC127" s="21"/>
-      <c r="BD127" s="21"/>
+      <c r="BC127" s="20"/>
+      <c r="BD127" s="20"/>
       <c r="BE127" s="20"/>
-    </row>
-    <row r="128" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF127" s="20"/>
+      <c r="BG127" s="20"/>
+      <c r="BH127" s="21"/>
+      <c r="BI127" s="21"/>
+      <c r="BJ127" s="20"/>
+    </row>
+    <row r="128" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A128" s="20"/>
       <c r="B128" s="20"/>
       <c r="C128" s="20"/>
@@ -10264,11 +11102,16 @@
       <c r="AZ128" s="20"/>
       <c r="BA128" s="20"/>
       <c r="BB128" s="20"/>
-      <c r="BC128" s="21"/>
-      <c r="BD128" s="21"/>
+      <c r="BC128" s="20"/>
+      <c r="BD128" s="20"/>
       <c r="BE128" s="20"/>
-    </row>
-    <row r="129" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF128" s="20"/>
+      <c r="BG128" s="20"/>
+      <c r="BH128" s="21"/>
+      <c r="BI128" s="21"/>
+      <c r="BJ128" s="20"/>
+    </row>
+    <row r="129" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A129" s="20"/>
       <c r="B129" s="20"/>
       <c r="C129" s="20"/>
@@ -10323,11 +11166,16 @@
       <c r="AZ129" s="20"/>
       <c r="BA129" s="20"/>
       <c r="BB129" s="20"/>
-      <c r="BC129" s="21"/>
-      <c r="BD129" s="21"/>
+      <c r="BC129" s="20"/>
+      <c r="BD129" s="20"/>
       <c r="BE129" s="20"/>
-    </row>
-    <row r="130" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF129" s="20"/>
+      <c r="BG129" s="20"/>
+      <c r="BH129" s="21"/>
+      <c r="BI129" s="21"/>
+      <c r="BJ129" s="20"/>
+    </row>
+    <row r="130" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A130" s="20"/>
       <c r="B130" s="20"/>
       <c r="C130" s="20"/>
@@ -10382,11 +11230,16 @@
       <c r="AZ130" s="20"/>
       <c r="BA130" s="20"/>
       <c r="BB130" s="20"/>
-      <c r="BC130" s="21"/>
-      <c r="BD130" s="21"/>
+      <c r="BC130" s="20"/>
+      <c r="BD130" s="20"/>
       <c r="BE130" s="20"/>
-    </row>
-    <row r="131" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF130" s="20"/>
+      <c r="BG130" s="20"/>
+      <c r="BH130" s="21"/>
+      <c r="BI130" s="21"/>
+      <c r="BJ130" s="20"/>
+    </row>
+    <row r="131" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A131" s="20"/>
       <c r="B131" s="20"/>
       <c r="C131" s="20"/>
@@ -10441,11 +11294,16 @@
       <c r="AZ131" s="20"/>
       <c r="BA131" s="20"/>
       <c r="BB131" s="20"/>
-      <c r="BC131" s="21"/>
-      <c r="BD131" s="21"/>
+      <c r="BC131" s="20"/>
+      <c r="BD131" s="20"/>
       <c r="BE131" s="20"/>
-    </row>
-    <row r="132" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF131" s="20"/>
+      <c r="BG131" s="20"/>
+      <c r="BH131" s="21"/>
+      <c r="BI131" s="21"/>
+      <c r="BJ131" s="20"/>
+    </row>
+    <row r="132" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A132" s="20"/>
       <c r="B132" s="20"/>
       <c r="C132" s="20"/>
@@ -10500,11 +11358,16 @@
       <c r="AZ132" s="20"/>
       <c r="BA132" s="20"/>
       <c r="BB132" s="20"/>
-      <c r="BC132" s="21"/>
-      <c r="BD132" s="21"/>
+      <c r="BC132" s="20"/>
+      <c r="BD132" s="20"/>
       <c r="BE132" s="20"/>
-    </row>
-    <row r="133" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF132" s="20"/>
+      <c r="BG132" s="20"/>
+      <c r="BH132" s="21"/>
+      <c r="BI132" s="21"/>
+      <c r="BJ132" s="20"/>
+    </row>
+    <row r="133" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A133" s="20"/>
       <c r="B133" s="20"/>
       <c r="C133" s="20"/>
@@ -10559,11 +11422,16 @@
       <c r="AZ133" s="20"/>
       <c r="BA133" s="20"/>
       <c r="BB133" s="20"/>
-      <c r="BC133" s="21"/>
-      <c r="BD133" s="21"/>
+      <c r="BC133" s="20"/>
+      <c r="BD133" s="20"/>
       <c r="BE133" s="20"/>
-    </row>
-    <row r="134" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF133" s="20"/>
+      <c r="BG133" s="20"/>
+      <c r="BH133" s="21"/>
+      <c r="BI133" s="21"/>
+      <c r="BJ133" s="20"/>
+    </row>
+    <row r="134" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A134" s="20"/>
       <c r="B134" s="20"/>
       <c r="C134" s="20"/>
@@ -10618,11 +11486,16 @@
       <c r="AZ134" s="20"/>
       <c r="BA134" s="20"/>
       <c r="BB134" s="20"/>
-      <c r="BC134" s="21"/>
-      <c r="BD134" s="21"/>
+      <c r="BC134" s="20"/>
+      <c r="BD134" s="20"/>
       <c r="BE134" s="20"/>
-    </row>
-    <row r="135" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF134" s="20"/>
+      <c r="BG134" s="20"/>
+      <c r="BH134" s="21"/>
+      <c r="BI134" s="21"/>
+      <c r="BJ134" s="20"/>
+    </row>
+    <row r="135" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A135" s="20"/>
       <c r="B135" s="20"/>
       <c r="C135" s="20"/>
@@ -10677,11 +11550,16 @@
       <c r="AZ135" s="20"/>
       <c r="BA135" s="20"/>
       <c r="BB135" s="20"/>
-      <c r="BC135" s="21"/>
-      <c r="BD135" s="21"/>
+      <c r="BC135" s="20"/>
+      <c r="BD135" s="20"/>
       <c r="BE135" s="20"/>
-    </row>
-    <row r="136" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF135" s="20"/>
+      <c r="BG135" s="20"/>
+      <c r="BH135" s="21"/>
+      <c r="BI135" s="21"/>
+      <c r="BJ135" s="20"/>
+    </row>
+    <row r="136" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A136" s="20"/>
       <c r="B136" s="20"/>
       <c r="C136" s="20"/>
@@ -10736,11 +11614,16 @@
       <c r="AZ136" s="20"/>
       <c r="BA136" s="20"/>
       <c r="BB136" s="20"/>
-      <c r="BC136" s="21"/>
-      <c r="BD136" s="21"/>
+      <c r="BC136" s="20"/>
+      <c r="BD136" s="20"/>
       <c r="BE136" s="20"/>
-    </row>
-    <row r="137" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF136" s="20"/>
+      <c r="BG136" s="20"/>
+      <c r="BH136" s="21"/>
+      <c r="BI136" s="21"/>
+      <c r="BJ136" s="20"/>
+    </row>
+    <row r="137" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A137" s="20"/>
       <c r="B137" s="20"/>
       <c r="C137" s="20"/>
@@ -10795,11 +11678,16 @@
       <c r="AZ137" s="20"/>
       <c r="BA137" s="20"/>
       <c r="BB137" s="20"/>
-      <c r="BC137" s="21"/>
-      <c r="BD137" s="21"/>
+      <c r="BC137" s="20"/>
+      <c r="BD137" s="20"/>
       <c r="BE137" s="20"/>
-    </row>
-    <row r="138" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF137" s="20"/>
+      <c r="BG137" s="20"/>
+      <c r="BH137" s="21"/>
+      <c r="BI137" s="21"/>
+      <c r="BJ137" s="20"/>
+    </row>
+    <row r="138" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A138" s="20"/>
       <c r="B138" s="20"/>
       <c r="C138" s="20"/>
@@ -10854,11 +11742,16 @@
       <c r="AZ138" s="20"/>
       <c r="BA138" s="20"/>
       <c r="BB138" s="20"/>
-      <c r="BC138" s="21"/>
-      <c r="BD138" s="21"/>
+      <c r="BC138" s="20"/>
+      <c r="BD138" s="20"/>
       <c r="BE138" s="20"/>
-    </row>
-    <row r="139" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF138" s="20"/>
+      <c r="BG138" s="20"/>
+      <c r="BH138" s="21"/>
+      <c r="BI138" s="21"/>
+      <c r="BJ138" s="20"/>
+    </row>
+    <row r="139" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A139" s="20"/>
       <c r="B139" s="20"/>
       <c r="C139" s="20"/>
@@ -10913,11 +11806,16 @@
       <c r="AZ139" s="20"/>
       <c r="BA139" s="20"/>
       <c r="BB139" s="20"/>
-      <c r="BC139" s="21"/>
-      <c r="BD139" s="21"/>
+      <c r="BC139" s="20"/>
+      <c r="BD139" s="20"/>
       <c r="BE139" s="20"/>
-    </row>
-    <row r="140" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF139" s="20"/>
+      <c r="BG139" s="20"/>
+      <c r="BH139" s="21"/>
+      <c r="BI139" s="21"/>
+      <c r="BJ139" s="20"/>
+    </row>
+    <row r="140" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A140" s="20"/>
       <c r="B140" s="20"/>
       <c r="C140" s="20"/>
@@ -10972,11 +11870,16 @@
       <c r="AZ140" s="20"/>
       <c r="BA140" s="20"/>
       <c r="BB140" s="20"/>
-      <c r="BC140" s="21"/>
-      <c r="BD140" s="21"/>
+      <c r="BC140" s="20"/>
+      <c r="BD140" s="20"/>
       <c r="BE140" s="20"/>
-    </row>
-    <row r="141" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF140" s="20"/>
+      <c r="BG140" s="20"/>
+      <c r="BH140" s="21"/>
+      <c r="BI140" s="21"/>
+      <c r="BJ140" s="20"/>
+    </row>
+    <row r="141" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A141" s="20"/>
       <c r="B141" s="20"/>
       <c r="C141" s="20"/>
@@ -11031,11 +11934,16 @@
       <c r="AZ141" s="20"/>
       <c r="BA141" s="20"/>
       <c r="BB141" s="20"/>
-      <c r="BC141" s="21"/>
-      <c r="BD141" s="21"/>
+      <c r="BC141" s="20"/>
+      <c r="BD141" s="20"/>
       <c r="BE141" s="20"/>
-    </row>
-    <row r="142" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF141" s="20"/>
+      <c r="BG141" s="20"/>
+      <c r="BH141" s="21"/>
+      <c r="BI141" s="21"/>
+      <c r="BJ141" s="20"/>
+    </row>
+    <row r="142" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A142" s="20"/>
       <c r="B142" s="20"/>
       <c r="C142" s="20"/>
@@ -11090,11 +11998,16 @@
       <c r="AZ142" s="20"/>
       <c r="BA142" s="20"/>
       <c r="BB142" s="20"/>
-      <c r="BC142" s="21"/>
-      <c r="BD142" s="21"/>
+      <c r="BC142" s="20"/>
+      <c r="BD142" s="20"/>
       <c r="BE142" s="20"/>
-    </row>
-    <row r="143" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF142" s="20"/>
+      <c r="BG142" s="20"/>
+      <c r="BH142" s="21"/>
+      <c r="BI142" s="21"/>
+      <c r="BJ142" s="20"/>
+    </row>
+    <row r="143" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A143" s="20"/>
       <c r="B143" s="20"/>
       <c r="C143" s="20"/>
@@ -11149,11 +12062,16 @@
       <c r="AZ143" s="20"/>
       <c r="BA143" s="20"/>
       <c r="BB143" s="20"/>
-      <c r="BC143" s="21"/>
-      <c r="BD143" s="21"/>
+      <c r="BC143" s="20"/>
+      <c r="BD143" s="20"/>
       <c r="BE143" s="20"/>
-    </row>
-    <row r="144" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF143" s="20"/>
+      <c r="BG143" s="20"/>
+      <c r="BH143" s="21"/>
+      <c r="BI143" s="21"/>
+      <c r="BJ143" s="20"/>
+    </row>
+    <row r="144" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A144" s="20"/>
       <c r="B144" s="20"/>
       <c r="C144" s="20"/>
@@ -11208,11 +12126,16 @@
       <c r="AZ144" s="20"/>
       <c r="BA144" s="20"/>
       <c r="BB144" s="20"/>
-      <c r="BC144" s="21"/>
-      <c r="BD144" s="21"/>
+      <c r="BC144" s="20"/>
+      <c r="BD144" s="20"/>
       <c r="BE144" s="20"/>
-    </row>
-    <row r="145" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF144" s="20"/>
+      <c r="BG144" s="20"/>
+      <c r="BH144" s="21"/>
+      <c r="BI144" s="21"/>
+      <c r="BJ144" s="20"/>
+    </row>
+    <row r="145" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A145" s="20"/>
       <c r="B145" s="20"/>
       <c r="C145" s="20"/>
@@ -11267,11 +12190,16 @@
       <c r="AZ145" s="20"/>
       <c r="BA145" s="20"/>
       <c r="BB145" s="20"/>
-      <c r="BC145" s="21"/>
-      <c r="BD145" s="21"/>
+      <c r="BC145" s="20"/>
+      <c r="BD145" s="20"/>
       <c r="BE145" s="20"/>
-    </row>
-    <row r="146" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF145" s="20"/>
+      <c r="BG145" s="20"/>
+      <c r="BH145" s="21"/>
+      <c r="BI145" s="21"/>
+      <c r="BJ145" s="20"/>
+    </row>
+    <row r="146" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A146" s="20"/>
       <c r="B146" s="20"/>
       <c r="C146" s="20"/>
@@ -11326,11 +12254,16 @@
       <c r="AZ146" s="20"/>
       <c r="BA146" s="20"/>
       <c r="BB146" s="20"/>
-      <c r="BC146" s="21"/>
-      <c r="BD146" s="21"/>
+      <c r="BC146" s="20"/>
+      <c r="BD146" s="20"/>
       <c r="BE146" s="20"/>
-    </row>
-    <row r="147" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF146" s="20"/>
+      <c r="BG146" s="20"/>
+      <c r="BH146" s="21"/>
+      <c r="BI146" s="21"/>
+      <c r="BJ146" s="20"/>
+    </row>
+    <row r="147" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A147" s="20"/>
       <c r="B147" s="20"/>
       <c r="C147" s="20"/>
@@ -11385,11 +12318,16 @@
       <c r="AZ147" s="20"/>
       <c r="BA147" s="20"/>
       <c r="BB147" s="20"/>
-      <c r="BC147" s="21"/>
-      <c r="BD147" s="21"/>
+      <c r="BC147" s="20"/>
+      <c r="BD147" s="20"/>
       <c r="BE147" s="20"/>
-    </row>
-    <row r="148" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF147" s="20"/>
+      <c r="BG147" s="20"/>
+      <c r="BH147" s="21"/>
+      <c r="BI147" s="21"/>
+      <c r="BJ147" s="20"/>
+    </row>
+    <row r="148" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A148" s="20"/>
       <c r="B148" s="20"/>
       <c r="C148" s="20"/>
@@ -11444,11 +12382,16 @@
       <c r="AZ148" s="20"/>
       <c r="BA148" s="20"/>
       <c r="BB148" s="20"/>
-      <c r="BC148" s="21"/>
-      <c r="BD148" s="21"/>
+      <c r="BC148" s="20"/>
+      <c r="BD148" s="20"/>
       <c r="BE148" s="20"/>
-    </row>
-    <row r="149" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF148" s="20"/>
+      <c r="BG148" s="20"/>
+      <c r="BH148" s="21"/>
+      <c r="BI148" s="21"/>
+      <c r="BJ148" s="20"/>
+    </row>
+    <row r="149" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A149" s="20"/>
       <c r="B149" s="20"/>
       <c r="C149" s="20"/>
@@ -11503,11 +12446,16 @@
       <c r="AZ149" s="20"/>
       <c r="BA149" s="20"/>
       <c r="BB149" s="20"/>
-      <c r="BC149" s="21"/>
-      <c r="BD149" s="21"/>
+      <c r="BC149" s="20"/>
+      <c r="BD149" s="20"/>
       <c r="BE149" s="20"/>
-    </row>
-    <row r="150" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF149" s="20"/>
+      <c r="BG149" s="20"/>
+      <c r="BH149" s="21"/>
+      <c r="BI149" s="21"/>
+      <c r="BJ149" s="20"/>
+    </row>
+    <row r="150" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A150" s="20"/>
       <c r="B150" s="20"/>
       <c r="C150" s="20"/>
@@ -11562,11 +12510,16 @@
       <c r="AZ150" s="20"/>
       <c r="BA150" s="20"/>
       <c r="BB150" s="20"/>
-      <c r="BC150" s="21"/>
-      <c r="BD150" s="21"/>
+      <c r="BC150" s="20"/>
+      <c r="BD150" s="20"/>
       <c r="BE150" s="20"/>
-    </row>
-    <row r="151" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF150" s="20"/>
+      <c r="BG150" s="20"/>
+      <c r="BH150" s="21"/>
+      <c r="BI150" s="21"/>
+      <c r="BJ150" s="20"/>
+    </row>
+    <row r="151" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A151" s="20"/>
       <c r="B151" s="20"/>
       <c r="C151" s="20"/>
@@ -11621,11 +12574,16 @@
       <c r="AZ151" s="20"/>
       <c r="BA151" s="20"/>
       <c r="BB151" s="20"/>
-      <c r="BC151" s="21"/>
-      <c r="BD151" s="21"/>
+      <c r="BC151" s="20"/>
+      <c r="BD151" s="20"/>
       <c r="BE151" s="20"/>
-    </row>
-    <row r="152" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF151" s="20"/>
+      <c r="BG151" s="20"/>
+      <c r="BH151" s="21"/>
+      <c r="BI151" s="21"/>
+      <c r="BJ151" s="20"/>
+    </row>
+    <row r="152" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A152" s="20"/>
       <c r="B152" s="20"/>
       <c r="C152" s="20"/>
@@ -11680,11 +12638,16 @@
       <c r="AZ152" s="20"/>
       <c r="BA152" s="20"/>
       <c r="BB152" s="20"/>
-      <c r="BC152" s="21"/>
-      <c r="BD152" s="21"/>
+      <c r="BC152" s="20"/>
+      <c r="BD152" s="20"/>
       <c r="BE152" s="20"/>
-    </row>
-    <row r="153" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF152" s="20"/>
+      <c r="BG152" s="20"/>
+      <c r="BH152" s="21"/>
+      <c r="BI152" s="21"/>
+      <c r="BJ152" s="20"/>
+    </row>
+    <row r="153" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A153" s="20"/>
       <c r="B153" s="20"/>
       <c r="C153" s="20"/>
@@ -11739,11 +12702,16 @@
       <c r="AZ153" s="20"/>
       <c r="BA153" s="20"/>
       <c r="BB153" s="20"/>
-      <c r="BC153" s="21"/>
-      <c r="BD153" s="21"/>
+      <c r="BC153" s="20"/>
+      <c r="BD153" s="20"/>
       <c r="BE153" s="20"/>
-    </row>
-    <row r="154" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF153" s="20"/>
+      <c r="BG153" s="20"/>
+      <c r="BH153" s="21"/>
+      <c r="BI153" s="21"/>
+      <c r="BJ153" s="20"/>
+    </row>
+    <row r="154" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A154" s="20"/>
       <c r="B154" s="20"/>
       <c r="C154" s="20"/>
@@ -11798,11 +12766,16 @@
       <c r="AZ154" s="20"/>
       <c r="BA154" s="20"/>
       <c r="BB154" s="20"/>
-      <c r="BC154" s="21"/>
-      <c r="BD154" s="21"/>
+      <c r="BC154" s="20"/>
+      <c r="BD154" s="20"/>
       <c r="BE154" s="20"/>
-    </row>
-    <row r="155" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF154" s="20"/>
+      <c r="BG154" s="20"/>
+      <c r="BH154" s="21"/>
+      <c r="BI154" s="21"/>
+      <c r="BJ154" s="20"/>
+    </row>
+    <row r="155" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A155" s="20"/>
       <c r="B155" s="20"/>
       <c r="C155" s="20"/>
@@ -11857,11 +12830,16 @@
       <c r="AZ155" s="20"/>
       <c r="BA155" s="20"/>
       <c r="BB155" s="20"/>
-      <c r="BC155" s="21"/>
-      <c r="BD155" s="21"/>
+      <c r="BC155" s="20"/>
+      <c r="BD155" s="20"/>
       <c r="BE155" s="20"/>
-    </row>
-    <row r="156" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF155" s="20"/>
+      <c r="BG155" s="20"/>
+      <c r="BH155" s="21"/>
+      <c r="BI155" s="21"/>
+      <c r="BJ155" s="20"/>
+    </row>
+    <row r="156" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A156" s="20"/>
       <c r="B156" s="20"/>
       <c r="C156" s="20"/>
@@ -11916,11 +12894,16 @@
       <c r="AZ156" s="20"/>
       <c r="BA156" s="20"/>
       <c r="BB156" s="20"/>
-      <c r="BC156" s="21"/>
-      <c r="BD156" s="21"/>
+      <c r="BC156" s="20"/>
+      <c r="BD156" s="20"/>
       <c r="BE156" s="20"/>
-    </row>
-    <row r="157" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF156" s="20"/>
+      <c r="BG156" s="20"/>
+      <c r="BH156" s="21"/>
+      <c r="BI156" s="21"/>
+      <c r="BJ156" s="20"/>
+    </row>
+    <row r="157" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A157" s="20"/>
       <c r="B157" s="20"/>
       <c r="C157" s="20"/>
@@ -11975,11 +12958,16 @@
       <c r="AZ157" s="20"/>
       <c r="BA157" s="20"/>
       <c r="BB157" s="20"/>
-      <c r="BC157" s="21"/>
-      <c r="BD157" s="21"/>
+      <c r="BC157" s="20"/>
+      <c r="BD157" s="20"/>
       <c r="BE157" s="20"/>
-    </row>
-    <row r="158" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF157" s="20"/>
+      <c r="BG157" s="20"/>
+      <c r="BH157" s="21"/>
+      <c r="BI157" s="21"/>
+      <c r="BJ157" s="20"/>
+    </row>
+    <row r="158" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A158" s="20"/>
       <c r="B158" s="20"/>
       <c r="C158" s="20"/>
@@ -12034,11 +13022,16 @@
       <c r="AZ158" s="20"/>
       <c r="BA158" s="20"/>
       <c r="BB158" s="20"/>
-      <c r="BC158" s="21"/>
-      <c r="BD158" s="21"/>
+      <c r="BC158" s="20"/>
+      <c r="BD158" s="20"/>
       <c r="BE158" s="20"/>
-    </row>
-    <row r="159" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF158" s="20"/>
+      <c r="BG158" s="20"/>
+      <c r="BH158" s="21"/>
+      <c r="BI158" s="21"/>
+      <c r="BJ158" s="20"/>
+    </row>
+    <row r="159" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A159" s="20"/>
       <c r="B159" s="20"/>
       <c r="C159" s="20"/>
@@ -12093,11 +13086,16 @@
       <c r="AZ159" s="20"/>
       <c r="BA159" s="20"/>
       <c r="BB159" s="20"/>
-      <c r="BC159" s="21"/>
-      <c r="BD159" s="21"/>
+      <c r="BC159" s="20"/>
+      <c r="BD159" s="20"/>
       <c r="BE159" s="20"/>
-    </row>
-    <row r="160" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF159" s="20"/>
+      <c r="BG159" s="20"/>
+      <c r="BH159" s="21"/>
+      <c r="BI159" s="21"/>
+      <c r="BJ159" s="20"/>
+    </row>
+    <row r="160" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A160" s="20"/>
       <c r="B160" s="20"/>
       <c r="C160" s="20"/>
@@ -12152,11 +13150,16 @@
       <c r="AZ160" s="20"/>
       <c r="BA160" s="20"/>
       <c r="BB160" s="20"/>
-      <c r="BC160" s="21"/>
-      <c r="BD160" s="21"/>
+      <c r="BC160" s="20"/>
+      <c r="BD160" s="20"/>
       <c r="BE160" s="20"/>
-    </row>
-    <row r="161" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF160" s="20"/>
+      <c r="BG160" s="20"/>
+      <c r="BH160" s="21"/>
+      <c r="BI160" s="21"/>
+      <c r="BJ160" s="20"/>
+    </row>
+    <row r="161" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A161" s="20"/>
       <c r="B161" s="20"/>
       <c r="C161" s="20"/>
@@ -12211,11 +13214,16 @@
       <c r="AZ161" s="20"/>
       <c r="BA161" s="20"/>
       <c r="BB161" s="20"/>
-      <c r="BC161" s="21"/>
-      <c r="BD161" s="21"/>
+      <c r="BC161" s="20"/>
+      <c r="BD161" s="20"/>
       <c r="BE161" s="20"/>
-    </row>
-    <row r="162" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF161" s="20"/>
+      <c r="BG161" s="20"/>
+      <c r="BH161" s="21"/>
+      <c r="BI161" s="21"/>
+      <c r="BJ161" s="20"/>
+    </row>
+    <row r="162" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A162" s="20"/>
       <c r="B162" s="20"/>
       <c r="C162" s="20"/>
@@ -12270,11 +13278,16 @@
       <c r="AZ162" s="20"/>
       <c r="BA162" s="20"/>
       <c r="BB162" s="20"/>
-      <c r="BC162" s="21"/>
-      <c r="BD162" s="21"/>
+      <c r="BC162" s="20"/>
+      <c r="BD162" s="20"/>
       <c r="BE162" s="20"/>
-    </row>
-    <row r="163" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF162" s="20"/>
+      <c r="BG162" s="20"/>
+      <c r="BH162" s="21"/>
+      <c r="BI162" s="21"/>
+      <c r="BJ162" s="20"/>
+    </row>
+    <row r="163" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A163" s="20"/>
       <c r="B163" s="20"/>
       <c r="C163" s="20"/>
@@ -12329,11 +13342,16 @@
       <c r="AZ163" s="20"/>
       <c r="BA163" s="20"/>
       <c r="BB163" s="20"/>
-      <c r="BC163" s="21"/>
-      <c r="BD163" s="21"/>
+      <c r="BC163" s="20"/>
+      <c r="BD163" s="20"/>
       <c r="BE163" s="20"/>
-    </row>
-    <row r="164" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF163" s="20"/>
+      <c r="BG163" s="20"/>
+      <c r="BH163" s="21"/>
+      <c r="BI163" s="21"/>
+      <c r="BJ163" s="20"/>
+    </row>
+    <row r="164" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A164" s="20"/>
       <c r="B164" s="20"/>
       <c r="C164" s="20"/>
@@ -12388,11 +13406,16 @@
       <c r="AZ164" s="20"/>
       <c r="BA164" s="20"/>
       <c r="BB164" s="20"/>
-      <c r="BC164" s="21"/>
-      <c r="BD164" s="21"/>
+      <c r="BC164" s="20"/>
+      <c r="BD164" s="20"/>
       <c r="BE164" s="20"/>
-    </row>
-    <row r="165" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF164" s="20"/>
+      <c r="BG164" s="20"/>
+      <c r="BH164" s="21"/>
+      <c r="BI164" s="21"/>
+      <c r="BJ164" s="20"/>
+    </row>
+    <row r="165" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A165" s="20"/>
       <c r="B165" s="20"/>
       <c r="C165" s="20"/>
@@ -12447,11 +13470,16 @@
       <c r="AZ165" s="20"/>
       <c r="BA165" s="20"/>
       <c r="BB165" s="20"/>
-      <c r="BC165" s="21"/>
-      <c r="BD165" s="21"/>
+      <c r="BC165" s="20"/>
+      <c r="BD165" s="20"/>
       <c r="BE165" s="20"/>
-    </row>
-    <row r="166" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF165" s="20"/>
+      <c r="BG165" s="20"/>
+      <c r="BH165" s="21"/>
+      <c r="BI165" s="21"/>
+      <c r="BJ165" s="20"/>
+    </row>
+    <row r="166" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A166" s="20"/>
       <c r="B166" s="20"/>
       <c r="C166" s="20"/>
@@ -12506,11 +13534,16 @@
       <c r="AZ166" s="20"/>
       <c r="BA166" s="20"/>
       <c r="BB166" s="20"/>
-      <c r="BC166" s="21"/>
-      <c r="BD166" s="21"/>
+      <c r="BC166" s="20"/>
+      <c r="BD166" s="20"/>
       <c r="BE166" s="20"/>
-    </row>
-    <row r="167" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF166" s="20"/>
+      <c r="BG166" s="20"/>
+      <c r="BH166" s="21"/>
+      <c r="BI166" s="21"/>
+      <c r="BJ166" s="20"/>
+    </row>
+    <row r="167" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A167" s="20"/>
       <c r="B167" s="20"/>
       <c r="C167" s="20"/>
@@ -12565,11 +13598,16 @@
       <c r="AZ167" s="20"/>
       <c r="BA167" s="20"/>
       <c r="BB167" s="20"/>
-      <c r="BC167" s="21"/>
-      <c r="BD167" s="21"/>
+      <c r="BC167" s="20"/>
+      <c r="BD167" s="20"/>
       <c r="BE167" s="20"/>
-    </row>
-    <row r="168" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF167" s="20"/>
+      <c r="BG167" s="20"/>
+      <c r="BH167" s="21"/>
+      <c r="BI167" s="21"/>
+      <c r="BJ167" s="20"/>
+    </row>
+    <row r="168" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A168" s="20"/>
       <c r="B168" s="20"/>
       <c r="C168" s="20"/>
@@ -12624,11 +13662,16 @@
       <c r="AZ168" s="20"/>
       <c r="BA168" s="20"/>
       <c r="BB168" s="20"/>
-      <c r="BC168" s="21"/>
-      <c r="BD168" s="21"/>
+      <c r="BC168" s="20"/>
+      <c r="BD168" s="20"/>
       <c r="BE168" s="20"/>
-    </row>
-    <row r="169" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF168" s="20"/>
+      <c r="BG168" s="20"/>
+      <c r="BH168" s="21"/>
+      <c r="BI168" s="21"/>
+      <c r="BJ168" s="20"/>
+    </row>
+    <row r="169" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A169" s="20"/>
       <c r="B169" s="20"/>
       <c r="C169" s="20"/>
@@ -12683,11 +13726,16 @@
       <c r="AZ169" s="20"/>
       <c r="BA169" s="20"/>
       <c r="BB169" s="20"/>
-      <c r="BC169" s="21"/>
-      <c r="BD169" s="21"/>
+      <c r="BC169" s="20"/>
+      <c r="BD169" s="20"/>
       <c r="BE169" s="20"/>
-    </row>
-    <row r="170" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF169" s="20"/>
+      <c r="BG169" s="20"/>
+      <c r="BH169" s="21"/>
+      <c r="BI169" s="21"/>
+      <c r="BJ169" s="20"/>
+    </row>
+    <row r="170" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A170" s="20"/>
       <c r="B170" s="20"/>
       <c r="C170" s="20"/>
@@ -12742,11 +13790,16 @@
       <c r="AZ170" s="20"/>
       <c r="BA170" s="20"/>
       <c r="BB170" s="20"/>
-      <c r="BC170" s="21"/>
-      <c r="BD170" s="21"/>
+      <c r="BC170" s="20"/>
+      <c r="BD170" s="20"/>
       <c r="BE170" s="20"/>
-    </row>
-    <row r="171" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF170" s="20"/>
+      <c r="BG170" s="20"/>
+      <c r="BH170" s="21"/>
+      <c r="BI170" s="21"/>
+      <c r="BJ170" s="20"/>
+    </row>
+    <row r="171" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A171" s="20"/>
       <c r="B171" s="20"/>
       <c r="C171" s="20"/>
@@ -12801,11 +13854,16 @@
       <c r="AZ171" s="20"/>
       <c r="BA171" s="20"/>
       <c r="BB171" s="20"/>
-      <c r="BC171" s="21"/>
-      <c r="BD171" s="21"/>
+      <c r="BC171" s="20"/>
+      <c r="BD171" s="20"/>
       <c r="BE171" s="20"/>
-    </row>
-    <row r="172" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF171" s="20"/>
+      <c r="BG171" s="20"/>
+      <c r="BH171" s="21"/>
+      <c r="BI171" s="21"/>
+      <c r="BJ171" s="20"/>
+    </row>
+    <row r="172" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A172" s="20"/>
       <c r="B172" s="20"/>
       <c r="C172" s="20"/>
@@ -12860,11 +13918,16 @@
       <c r="AZ172" s="20"/>
       <c r="BA172" s="20"/>
       <c r="BB172" s="20"/>
-      <c r="BC172" s="21"/>
-      <c r="BD172" s="21"/>
+      <c r="BC172" s="20"/>
+      <c r="BD172" s="20"/>
       <c r="BE172" s="20"/>
-    </row>
-    <row r="173" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF172" s="20"/>
+      <c r="BG172" s="20"/>
+      <c r="BH172" s="21"/>
+      <c r="BI172" s="21"/>
+      <c r="BJ172" s="20"/>
+    </row>
+    <row r="173" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A173" s="20"/>
       <c r="B173" s="20"/>
       <c r="C173" s="20"/>
@@ -12919,11 +13982,16 @@
       <c r="AZ173" s="20"/>
       <c r="BA173" s="20"/>
       <c r="BB173" s="20"/>
-      <c r="BC173" s="21"/>
-      <c r="BD173" s="21"/>
+      <c r="BC173" s="20"/>
+      <c r="BD173" s="20"/>
       <c r="BE173" s="20"/>
-    </row>
-    <row r="174" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF173" s="20"/>
+      <c r="BG173" s="20"/>
+      <c r="BH173" s="21"/>
+      <c r="BI173" s="21"/>
+      <c r="BJ173" s="20"/>
+    </row>
+    <row r="174" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A174" s="20"/>
       <c r="B174" s="20"/>
       <c r="C174" s="20"/>
@@ -12978,11 +14046,16 @@
       <c r="AZ174" s="20"/>
       <c r="BA174" s="20"/>
       <c r="BB174" s="20"/>
-      <c r="BC174" s="21"/>
-      <c r="BD174" s="21"/>
+      <c r="BC174" s="20"/>
+      <c r="BD174" s="20"/>
       <c r="BE174" s="20"/>
-    </row>
-    <row r="175" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF174" s="20"/>
+      <c r="BG174" s="20"/>
+      <c r="BH174" s="21"/>
+      <c r="BI174" s="21"/>
+      <c r="BJ174" s="20"/>
+    </row>
+    <row r="175" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A175" s="20"/>
       <c r="B175" s="20"/>
       <c r="C175" s="20"/>
@@ -13037,11 +14110,16 @@
       <c r="AZ175" s="20"/>
       <c r="BA175" s="20"/>
       <c r="BB175" s="20"/>
-      <c r="BC175" s="21"/>
-      <c r="BD175" s="21"/>
+      <c r="BC175" s="20"/>
+      <c r="BD175" s="20"/>
       <c r="BE175" s="20"/>
-    </row>
-    <row r="176" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF175" s="20"/>
+      <c r="BG175" s="20"/>
+      <c r="BH175" s="21"/>
+      <c r="BI175" s="21"/>
+      <c r="BJ175" s="20"/>
+    </row>
+    <row r="176" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A176" s="20"/>
       <c r="B176" s="20"/>
       <c r="C176" s="20"/>
@@ -13096,11 +14174,16 @@
       <c r="AZ176" s="20"/>
       <c r="BA176" s="20"/>
       <c r="BB176" s="20"/>
-      <c r="BC176" s="21"/>
-      <c r="BD176" s="21"/>
+      <c r="BC176" s="20"/>
+      <c r="BD176" s="20"/>
       <c r="BE176" s="20"/>
-    </row>
-    <row r="177" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF176" s="20"/>
+      <c r="BG176" s="20"/>
+      <c r="BH176" s="21"/>
+      <c r="BI176" s="21"/>
+      <c r="BJ176" s="20"/>
+    </row>
+    <row r="177" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A177" s="20"/>
       <c r="B177" s="20"/>
       <c r="C177" s="20"/>
@@ -13155,11 +14238,16 @@
       <c r="AZ177" s="20"/>
       <c r="BA177" s="20"/>
       <c r="BB177" s="20"/>
-      <c r="BC177" s="21"/>
-      <c r="BD177" s="21"/>
+      <c r="BC177" s="20"/>
+      <c r="BD177" s="20"/>
       <c r="BE177" s="20"/>
-    </row>
-    <row r="178" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF177" s="20"/>
+      <c r="BG177" s="20"/>
+      <c r="BH177" s="21"/>
+      <c r="BI177" s="21"/>
+      <c r="BJ177" s="20"/>
+    </row>
+    <row r="178" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A178" s="20"/>
       <c r="B178" s="20"/>
       <c r="C178" s="20"/>
@@ -13214,11 +14302,16 @@
       <c r="AZ178" s="20"/>
       <c r="BA178" s="20"/>
       <c r="BB178" s="20"/>
-      <c r="BC178" s="21"/>
-      <c r="BD178" s="21"/>
+      <c r="BC178" s="20"/>
+      <c r="BD178" s="20"/>
       <c r="BE178" s="20"/>
-    </row>
-    <row r="179" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF178" s="20"/>
+      <c r="BG178" s="20"/>
+      <c r="BH178" s="21"/>
+      <c r="BI178" s="21"/>
+      <c r="BJ178" s="20"/>
+    </row>
+    <row r="179" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A179" s="20"/>
       <c r="B179" s="20"/>
       <c r="C179" s="20"/>
@@ -13273,11 +14366,16 @@
       <c r="AZ179" s="20"/>
       <c r="BA179" s="20"/>
       <c r="BB179" s="20"/>
-      <c r="BC179" s="21"/>
-      <c r="BD179" s="21"/>
+      <c r="BC179" s="20"/>
+      <c r="BD179" s="20"/>
       <c r="BE179" s="20"/>
-    </row>
-    <row r="180" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF179" s="20"/>
+      <c r="BG179" s="20"/>
+      <c r="BH179" s="21"/>
+      <c r="BI179" s="21"/>
+      <c r="BJ179" s="20"/>
+    </row>
+    <row r="180" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A180" s="20"/>
       <c r="B180" s="20"/>
       <c r="C180" s="20"/>
@@ -13332,11 +14430,16 @@
       <c r="AZ180" s="20"/>
       <c r="BA180" s="20"/>
       <c r="BB180" s="20"/>
-      <c r="BC180" s="21"/>
-      <c r="BD180" s="21"/>
+      <c r="BC180" s="20"/>
+      <c r="BD180" s="20"/>
       <c r="BE180" s="20"/>
-    </row>
-    <row r="181" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF180" s="20"/>
+      <c r="BG180" s="20"/>
+      <c r="BH180" s="21"/>
+      <c r="BI180" s="21"/>
+      <c r="BJ180" s="20"/>
+    </row>
+    <row r="181" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A181" s="20"/>
       <c r="B181" s="20"/>
       <c r="C181" s="20"/>
@@ -13391,11 +14494,16 @@
       <c r="AZ181" s="20"/>
       <c r="BA181" s="20"/>
       <c r="BB181" s="20"/>
-      <c r="BC181" s="21"/>
-      <c r="BD181" s="21"/>
+      <c r="BC181" s="20"/>
+      <c r="BD181" s="20"/>
       <c r="BE181" s="20"/>
-    </row>
-    <row r="182" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF181" s="20"/>
+      <c r="BG181" s="20"/>
+      <c r="BH181" s="21"/>
+      <c r="BI181" s="21"/>
+      <c r="BJ181" s="20"/>
+    </row>
+    <row r="182" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A182" s="20"/>
       <c r="B182" s="20"/>
       <c r="C182" s="20"/>
@@ -13450,11 +14558,16 @@
       <c r="AZ182" s="20"/>
       <c r="BA182" s="20"/>
       <c r="BB182" s="20"/>
-      <c r="BC182" s="21"/>
-      <c r="BD182" s="21"/>
+      <c r="BC182" s="20"/>
+      <c r="BD182" s="20"/>
       <c r="BE182" s="20"/>
-    </row>
-    <row r="183" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF182" s="20"/>
+      <c r="BG182" s="20"/>
+      <c r="BH182" s="21"/>
+      <c r="BI182" s="21"/>
+      <c r="BJ182" s="20"/>
+    </row>
+    <row r="183" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A183" s="20"/>
       <c r="B183" s="20"/>
       <c r="C183" s="20"/>
@@ -13509,11 +14622,16 @@
       <c r="AZ183" s="20"/>
       <c r="BA183" s="20"/>
       <c r="BB183" s="20"/>
-      <c r="BC183" s="21"/>
-      <c r="BD183" s="21"/>
+      <c r="BC183" s="20"/>
+      <c r="BD183" s="20"/>
       <c r="BE183" s="20"/>
-    </row>
-    <row r="184" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF183" s="20"/>
+      <c r="BG183" s="20"/>
+      <c r="BH183" s="21"/>
+      <c r="BI183" s="21"/>
+      <c r="BJ183" s="20"/>
+    </row>
+    <row r="184" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A184" s="20"/>
       <c r="B184" s="20"/>
       <c r="C184" s="20"/>
@@ -13568,11 +14686,16 @@
       <c r="AZ184" s="20"/>
       <c r="BA184" s="20"/>
       <c r="BB184" s="20"/>
-      <c r="BC184" s="21"/>
-      <c r="BD184" s="21"/>
+      <c r="BC184" s="20"/>
+      <c r="BD184" s="20"/>
       <c r="BE184" s="20"/>
-    </row>
-    <row r="185" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF184" s="20"/>
+      <c r="BG184" s="20"/>
+      <c r="BH184" s="21"/>
+      <c r="BI184" s="21"/>
+      <c r="BJ184" s="20"/>
+    </row>
+    <row r="185" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A185" s="20"/>
       <c r="B185" s="20"/>
       <c r="C185" s="20"/>
@@ -13627,11 +14750,16 @@
       <c r="AZ185" s="20"/>
       <c r="BA185" s="20"/>
       <c r="BB185" s="20"/>
-      <c r="BC185" s="21"/>
-      <c r="BD185" s="21"/>
+      <c r="BC185" s="20"/>
+      <c r="BD185" s="20"/>
       <c r="BE185" s="20"/>
-    </row>
-    <row r="186" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF185" s="20"/>
+      <c r="BG185" s="20"/>
+      <c r="BH185" s="21"/>
+      <c r="BI185" s="21"/>
+      <c r="BJ185" s="20"/>
+    </row>
+    <row r="186" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A186" s="20"/>
       <c r="B186" s="20"/>
       <c r="C186" s="20"/>
@@ -13686,11 +14814,16 @@
       <c r="AZ186" s="20"/>
       <c r="BA186" s="20"/>
       <c r="BB186" s="20"/>
-      <c r="BC186" s="21"/>
-      <c r="BD186" s="21"/>
+      <c r="BC186" s="20"/>
+      <c r="BD186" s="20"/>
       <c r="BE186" s="20"/>
-    </row>
-    <row r="187" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF186" s="20"/>
+      <c r="BG186" s="20"/>
+      <c r="BH186" s="21"/>
+      <c r="BI186" s="21"/>
+      <c r="BJ186" s="20"/>
+    </row>
+    <row r="187" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A187" s="20"/>
       <c r="B187" s="20"/>
       <c r="C187" s="20"/>
@@ -13745,11 +14878,16 @@
       <c r="AZ187" s="20"/>
       <c r="BA187" s="20"/>
       <c r="BB187" s="20"/>
-      <c r="BC187" s="21"/>
-      <c r="BD187" s="21"/>
+      <c r="BC187" s="20"/>
+      <c r="BD187" s="20"/>
       <c r="BE187" s="20"/>
-    </row>
-    <row r="188" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF187" s="20"/>
+      <c r="BG187" s="20"/>
+      <c r="BH187" s="21"/>
+      <c r="BI187" s="21"/>
+      <c r="BJ187" s="20"/>
+    </row>
+    <row r="188" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A188" s="20"/>
       <c r="B188" s="20"/>
       <c r="C188" s="20"/>
@@ -13804,11 +14942,16 @@
       <c r="AZ188" s="20"/>
       <c r="BA188" s="20"/>
       <c r="BB188" s="20"/>
-      <c r="BC188" s="21"/>
-      <c r="BD188" s="21"/>
+      <c r="BC188" s="20"/>
+      <c r="BD188" s="20"/>
       <c r="BE188" s="20"/>
-    </row>
-    <row r="189" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF188" s="20"/>
+      <c r="BG188" s="20"/>
+      <c r="BH188" s="21"/>
+      <c r="BI188" s="21"/>
+      <c r="BJ188" s="20"/>
+    </row>
+    <row r="189" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A189" s="20"/>
       <c r="B189" s="20"/>
       <c r="C189" s="20"/>
@@ -13863,11 +15006,16 @@
       <c r="AZ189" s="20"/>
       <c r="BA189" s="20"/>
       <c r="BB189" s="20"/>
-      <c r="BC189" s="21"/>
-      <c r="BD189" s="21"/>
+      <c r="BC189" s="20"/>
+      <c r="BD189" s="20"/>
       <c r="BE189" s="20"/>
-    </row>
-    <row r="190" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF189" s="20"/>
+      <c r="BG189" s="20"/>
+      <c r="BH189" s="21"/>
+      <c r="BI189" s="21"/>
+      <c r="BJ189" s="20"/>
+    </row>
+    <row r="190" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A190" s="20"/>
       <c r="B190" s="20"/>
       <c r="C190" s="20"/>
@@ -13922,11 +15070,16 @@
       <c r="AZ190" s="20"/>
       <c r="BA190" s="20"/>
       <c r="BB190" s="20"/>
-      <c r="BC190" s="21"/>
-      <c r="BD190" s="21"/>
+      <c r="BC190" s="20"/>
+      <c r="BD190" s="20"/>
       <c r="BE190" s="20"/>
-    </row>
-    <row r="191" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF190" s="20"/>
+      <c r="BG190" s="20"/>
+      <c r="BH190" s="21"/>
+      <c r="BI190" s="21"/>
+      <c r="BJ190" s="20"/>
+    </row>
+    <row r="191" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A191" s="20"/>
       <c r="B191" s="20"/>
       <c r="C191" s="20"/>
@@ -13981,11 +15134,16 @@
       <c r="AZ191" s="20"/>
       <c r="BA191" s="20"/>
       <c r="BB191" s="20"/>
-      <c r="BC191" s="21"/>
-      <c r="BD191" s="21"/>
+      <c r="BC191" s="20"/>
+      <c r="BD191" s="20"/>
       <c r="BE191" s="20"/>
-    </row>
-    <row r="192" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF191" s="20"/>
+      <c r="BG191" s="20"/>
+      <c r="BH191" s="21"/>
+      <c r="BI191" s="21"/>
+      <c r="BJ191" s="20"/>
+    </row>
+    <row r="192" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A192" s="20"/>
       <c r="B192" s="20"/>
       <c r="C192" s="20"/>
@@ -14040,11 +15198,16 @@
       <c r="AZ192" s="20"/>
       <c r="BA192" s="20"/>
       <c r="BB192" s="20"/>
-      <c r="BC192" s="21"/>
-      <c r="BD192" s="21"/>
+      <c r="BC192" s="20"/>
+      <c r="BD192" s="20"/>
       <c r="BE192" s="20"/>
-    </row>
-    <row r="193" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF192" s="20"/>
+      <c r="BG192" s="20"/>
+      <c r="BH192" s="21"/>
+      <c r="BI192" s="21"/>
+      <c r="BJ192" s="20"/>
+    </row>
+    <row r="193" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A193" s="20"/>
       <c r="B193" s="20"/>
       <c r="C193" s="20"/>
@@ -14099,11 +15262,16 @@
       <c r="AZ193" s="20"/>
       <c r="BA193" s="20"/>
       <c r="BB193" s="20"/>
-      <c r="BC193" s="21"/>
-      <c r="BD193" s="21"/>
+      <c r="BC193" s="20"/>
+      <c r="BD193" s="20"/>
       <c r="BE193" s="20"/>
-    </row>
-    <row r="194" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF193" s="20"/>
+      <c r="BG193" s="20"/>
+      <c r="BH193" s="21"/>
+      <c r="BI193" s="21"/>
+      <c r="BJ193" s="20"/>
+    </row>
+    <row r="194" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A194" s="20"/>
       <c r="B194" s="20"/>
       <c r="C194" s="20"/>
@@ -14158,11 +15326,16 @@
       <c r="AZ194" s="20"/>
       <c r="BA194" s="20"/>
       <c r="BB194" s="20"/>
-      <c r="BC194" s="21"/>
-      <c r="BD194" s="21"/>
+      <c r="BC194" s="20"/>
+      <c r="BD194" s="20"/>
       <c r="BE194" s="20"/>
-    </row>
-    <row r="195" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF194" s="20"/>
+      <c r="BG194" s="20"/>
+      <c r="BH194" s="21"/>
+      <c r="BI194" s="21"/>
+      <c r="BJ194" s="20"/>
+    </row>
+    <row r="195" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A195" s="20"/>
       <c r="B195" s="20"/>
       <c r="C195" s="20"/>
@@ -14217,11 +15390,16 @@
       <c r="AZ195" s="20"/>
       <c r="BA195" s="20"/>
       <c r="BB195" s="20"/>
-      <c r="BC195" s="21"/>
-      <c r="BD195" s="21"/>
+      <c r="BC195" s="20"/>
+      <c r="BD195" s="20"/>
       <c r="BE195" s="20"/>
-    </row>
-    <row r="196" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF195" s="20"/>
+      <c r="BG195" s="20"/>
+      <c r="BH195" s="21"/>
+      <c r="BI195" s="21"/>
+      <c r="BJ195" s="20"/>
+    </row>
+    <row r="196" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A196" s="20"/>
       <c r="B196" s="20"/>
       <c r="C196" s="20"/>
@@ -14276,11 +15454,16 @@
       <c r="AZ196" s="20"/>
       <c r="BA196" s="20"/>
       <c r="BB196" s="20"/>
-      <c r="BC196" s="21"/>
-      <c r="BD196" s="21"/>
+      <c r="BC196" s="20"/>
+      <c r="BD196" s="20"/>
       <c r="BE196" s="20"/>
-    </row>
-    <row r="197" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF196" s="20"/>
+      <c r="BG196" s="20"/>
+      <c r="BH196" s="21"/>
+      <c r="BI196" s="21"/>
+      <c r="BJ196" s="20"/>
+    </row>
+    <row r="197" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A197" s="20"/>
       <c r="B197" s="20"/>
       <c r="C197" s="20"/>
@@ -14335,11 +15518,16 @@
       <c r="AZ197" s="20"/>
       <c r="BA197" s="20"/>
       <c r="BB197" s="20"/>
-      <c r="BC197" s="21"/>
-      <c r="BD197" s="21"/>
+      <c r="BC197" s="20"/>
+      <c r="BD197" s="20"/>
       <c r="BE197" s="20"/>
-    </row>
-    <row r="198" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF197" s="20"/>
+      <c r="BG197" s="20"/>
+      <c r="BH197" s="21"/>
+      <c r="BI197" s="21"/>
+      <c r="BJ197" s="20"/>
+    </row>
+    <row r="198" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A198" s="20"/>
       <c r="B198" s="20"/>
       <c r="C198" s="20"/>
@@ -14394,11 +15582,16 @@
       <c r="AZ198" s="20"/>
       <c r="BA198" s="20"/>
       <c r="BB198" s="20"/>
-      <c r="BC198" s="21"/>
-      <c r="BD198" s="21"/>
+      <c r="BC198" s="20"/>
+      <c r="BD198" s="20"/>
       <c r="BE198" s="20"/>
-    </row>
-    <row r="199" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF198" s="20"/>
+      <c r="BG198" s="20"/>
+      <c r="BH198" s="21"/>
+      <c r="BI198" s="21"/>
+      <c r="BJ198" s="20"/>
+    </row>
+    <row r="199" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A199" s="20"/>
       <c r="B199" s="20"/>
       <c r="C199" s="20"/>
@@ -14453,13 +15646,30 @@
       <c r="AZ199" s="20"/>
       <c r="BA199" s="20"/>
       <c r="BB199" s="20"/>
-      <c r="BC199" s="21"/>
-      <c r="BD199" s="21"/>
+      <c r="BC199" s="20"/>
+      <c r="BD199" s="20"/>
       <c r="BE199" s="20"/>
+      <c r="BF199" s="20"/>
+      <c r="BG199" s="20"/>
+      <c r="BH199" s="21"/>
+      <c r="BI199" s="21"/>
+      <c r="BJ199" s="20"/>
     </row>
   </sheetData>
-  <mergeCells count="27">
-    <mergeCell ref="A1:BE1"/>
+  <mergeCells count="28">
+    <mergeCell ref="AC3:AC4"/>
+    <mergeCell ref="BH2:BH4"/>
+    <mergeCell ref="BI2:BI4"/>
+    <mergeCell ref="BJ2:BJ4"/>
+    <mergeCell ref="B2:C4"/>
+    <mergeCell ref="G2:G4"/>
+    <mergeCell ref="W3:W4"/>
+    <mergeCell ref="Y3:Y4"/>
+    <mergeCell ref="Z3:Z4"/>
+    <mergeCell ref="AA3:AA4"/>
+    <mergeCell ref="AB3:AB4"/>
+    <mergeCell ref="BC3:BG3"/>
+    <mergeCell ref="A1:BJ1"/>
     <mergeCell ref="I2:AA2"/>
     <mergeCell ref="AD2:BB2"/>
     <mergeCell ref="I3:N3"/>
@@ -14475,21 +15685,10 @@
     <mergeCell ref="F2:F4"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="V3:V4"/>
-    <mergeCell ref="AC3:AC4"/>
-    <mergeCell ref="BC2:BC4"/>
-    <mergeCell ref="BD2:BD4"/>
-    <mergeCell ref="BE2:BE4"/>
-    <mergeCell ref="B2:C4"/>
-    <mergeCell ref="G2:G4"/>
-    <mergeCell ref="W3:W4"/>
-    <mergeCell ref="Y3:Y4"/>
-    <mergeCell ref="Z3:Z4"/>
-    <mergeCell ref="AA3:AA4"/>
-    <mergeCell ref="AB3:AB4"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -14512,23 +15711,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="66" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
     </row>
     <row r="2" spans="1:9" s="2" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="67" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="66"/>
+      <c r="B2" s="67"/>
       <c r="C2" s="3" t="s">
         <v>82</v>
       </c>
@@ -15219,10 +16418,10 @@
       <c r="I33" s="11"/>
     </row>
     <row r="34" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="67" t="s">
+      <c r="A34" s="68" t="s">
         <v>86</v>
       </c>
-      <c r="B34" s="67"/>
+      <c r="B34" s="68"/>
       <c r="C34" s="9"/>
       <c r="D34" s="9">
         <f>SUM(D3:D33)</f>

--- a/finance/麦安研营业统计_格式化模板.xlsx
+++ b/finance/麦安研营业统计_格式化模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wadec\Documents\projects\mainyan-auto\finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD1B87E2-8E11-422C-9050-E5CF39032FCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8751272A-EA07-46E5-8618-20517DE1E795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,9 +39,6 @@
   </si>
   <si>
     <t>银豹收银系统后台收入</t>
-  </si>
-  <si>
-    <t>美团优惠、建设银行、招商优惠卷、抖音卷系统后台收入</t>
   </si>
   <si>
     <t>总营业实收</t>
@@ -371,15 +368,18 @@
     <t>服务费</t>
     <phoneticPr fontId="23" type="noConversion"/>
   </si>
+  <si>
+    <t>美团优惠、建设银行、招商优惠卷、抖音卷系统后台、高德口碑后台收入</t>
+    <phoneticPr fontId="23" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="176" formatCode="0.00_ "/>
     <numFmt numFmtId="177" formatCode="0.00_);\(0.00\)"/>
-    <numFmt numFmtId="178" formatCode="0.0_ "/>
   </numFmts>
   <fonts count="26" x14ac:knownFonts="1">
     <font>
@@ -732,7 +732,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -841,9 +841,6 @@
     <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -853,9 +850,6 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -864,9 +858,6 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="17" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -895,19 +886,37 @@
     <xf numFmtId="176" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="11" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -919,18 +928,6 @@
     <xf numFmtId="176" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="11" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -940,17 +937,17 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1271,406 +1268,406 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:62" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="60" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="60"/>
+      <c r="L1" s="60"/>
+      <c r="M1" s="60"/>
+      <c r="N1" s="60"/>
+      <c r="O1" s="60"/>
+      <c r="P1" s="60"/>
+      <c r="Q1" s="60"/>
+      <c r="R1" s="60"/>
+      <c r="S1" s="60"/>
+      <c r="T1" s="60"/>
+      <c r="U1" s="60"/>
+      <c r="V1" s="60"/>
+      <c r="W1" s="60"/>
+      <c r="X1" s="60"/>
+      <c r="Y1" s="60"/>
+      <c r="Z1" s="60"/>
+      <c r="AA1" s="60"/>
+      <c r="AB1" s="60"/>
+      <c r="AC1" s="60"/>
+      <c r="AD1" s="60"/>
+      <c r="AE1" s="60"/>
+      <c r="AF1" s="60"/>
+      <c r="AG1" s="60"/>
+      <c r="AH1" s="60"/>
+      <c r="AI1" s="60"/>
+      <c r="AJ1" s="60"/>
+      <c r="AK1" s="60"/>
+      <c r="AL1" s="60"/>
+      <c r="AM1" s="60"/>
+      <c r="AN1" s="60"/>
+      <c r="AO1" s="60"/>
+      <c r="AP1" s="60"/>
+      <c r="AQ1" s="60"/>
+      <c r="AR1" s="60"/>
+      <c r="AS1" s="60"/>
+      <c r="AT1" s="60"/>
+      <c r="AU1" s="60"/>
+      <c r="AV1" s="60"/>
+      <c r="AW1" s="60"/>
+      <c r="AX1" s="60"/>
+      <c r="AY1" s="60"/>
+      <c r="AZ1" s="60"/>
+      <c r="BA1" s="60"/>
+      <c r="BB1" s="60"/>
+      <c r="BC1" s="60"/>
+      <c r="BD1" s="60"/>
+      <c r="BE1" s="60"/>
+      <c r="BF1" s="60"/>
+      <c r="BG1" s="60"/>
+      <c r="BH1" s="60"/>
+      <c r="BI1" s="60"/>
+      <c r="BJ1" s="60"/>
+    </row>
+    <row r="2" spans="1:62" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="52" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="52" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="55" t="s">
+        <v>106</v>
+      </c>
+      <c r="H2" s="64" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="55"/>
-      <c r="P1" s="55"/>
-      <c r="Q1" s="55"/>
-      <c r="R1" s="55"/>
-      <c r="S1" s="55"/>
-      <c r="T1" s="55"/>
-      <c r="U1" s="55"/>
-      <c r="V1" s="55"/>
-      <c r="W1" s="55"/>
-      <c r="X1" s="55"/>
-      <c r="Y1" s="55"/>
-      <c r="Z1" s="55"/>
-      <c r="AA1" s="55"/>
-      <c r="AB1" s="55"/>
-      <c r="AC1" s="55"/>
-      <c r="AD1" s="55"/>
-      <c r="AE1" s="55"/>
-      <c r="AF1" s="55"/>
-      <c r="AG1" s="55"/>
-      <c r="AH1" s="55"/>
-      <c r="AI1" s="55"/>
-      <c r="AJ1" s="55"/>
-      <c r="AK1" s="55"/>
-      <c r="AL1" s="55"/>
-      <c r="AM1" s="55"/>
-      <c r="AN1" s="55"/>
-      <c r="AO1" s="55"/>
-      <c r="AP1" s="55"/>
-      <c r="AQ1" s="55"/>
-      <c r="AR1" s="55"/>
-      <c r="AS1" s="55"/>
-      <c r="AT1" s="55"/>
-      <c r="AU1" s="55"/>
-      <c r="AV1" s="55"/>
-      <c r="AW1" s="55"/>
-      <c r="AX1" s="55"/>
-      <c r="AY1" s="55"/>
-      <c r="AZ1" s="55"/>
-      <c r="BA1" s="55"/>
-      <c r="BB1" s="55"/>
-      <c r="BC1" s="55"/>
-      <c r="BD1" s="55"/>
-      <c r="BE1" s="55"/>
-      <c r="BF1" s="55"/>
-      <c r="BG1" s="55"/>
-      <c r="BH1" s="55"/>
-      <c r="BI1" s="55"/>
-      <c r="BJ1" s="55"/>
-    </row>
-    <row r="2" spans="1:62" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="58" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="58" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="58" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="62" t="s">
-        <v>107</v>
-      </c>
-      <c r="H2" s="61" t="s">
-        <v>88</v>
-      </c>
-      <c r="I2" s="56" t="s">
+      <c r="I2" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56"/>
-      <c r="M2" s="56"/>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="56"/>
-      <c r="Q2" s="56"/>
-      <c r="R2" s="56"/>
-      <c r="S2" s="56"/>
-      <c r="T2" s="56"/>
-      <c r="U2" s="56"/>
-      <c r="V2" s="56"/>
-      <c r="W2" s="56"/>
-      <c r="X2" s="56"/>
-      <c r="Y2" s="56"/>
-      <c r="Z2" s="56"/>
-      <c r="AA2" s="56"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
+      <c r="L2" s="61"/>
+      <c r="M2" s="61"/>
+      <c r="N2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="61"/>
+      <c r="V2" s="61"/>
+      <c r="W2" s="61"/>
+      <c r="X2" s="61"/>
+      <c r="Y2" s="61"/>
+      <c r="Z2" s="61"/>
+      <c r="AA2" s="61"/>
       <c r="AB2" s="25"/>
       <c r="AC2" s="25"/>
-      <c r="AD2" s="57" t="s">
+      <c r="AD2" s="69" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE2" s="70"/>
+      <c r="AF2" s="70"/>
+      <c r="AG2" s="70"/>
+      <c r="AH2" s="70"/>
+      <c r="AI2" s="70"/>
+      <c r="AJ2" s="70"/>
+      <c r="AK2" s="70"/>
+      <c r="AL2" s="70"/>
+      <c r="AM2" s="70"/>
+      <c r="AN2" s="70"/>
+      <c r="AO2" s="70"/>
+      <c r="AP2" s="70"/>
+      <c r="AQ2" s="70"/>
+      <c r="AR2" s="70"/>
+      <c r="AS2" s="70"/>
+      <c r="AT2" s="70"/>
+      <c r="AU2" s="70"/>
+      <c r="AV2" s="70"/>
+      <c r="AW2" s="70"/>
+      <c r="AX2" s="70"/>
+      <c r="AY2" s="70"/>
+      <c r="AZ2" s="70"/>
+      <c r="BA2" s="70"/>
+      <c r="BB2" s="70"/>
+      <c r="BC2" s="70"/>
+      <c r="BD2" s="70"/>
+      <c r="BE2" s="70"/>
+      <c r="BF2" s="70"/>
+      <c r="BG2" s="71"/>
+      <c r="BH2" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="AE2" s="57"/>
-      <c r="AF2" s="57"/>
-      <c r="AG2" s="57"/>
-      <c r="AH2" s="57"/>
-      <c r="AI2" s="57"/>
-      <c r="AJ2" s="57"/>
-      <c r="AK2" s="57"/>
-      <c r="AL2" s="57"/>
-      <c r="AM2" s="57"/>
-      <c r="AN2" s="57"/>
-      <c r="AO2" s="57"/>
-      <c r="AP2" s="57"/>
-      <c r="AQ2" s="57"/>
-      <c r="AR2" s="57"/>
-      <c r="AS2" s="57"/>
-      <c r="AT2" s="57"/>
-      <c r="AU2" s="57"/>
-      <c r="AV2" s="57"/>
-      <c r="AW2" s="57"/>
-      <c r="AX2" s="57"/>
-      <c r="AY2" s="57"/>
-      <c r="AZ2" s="57"/>
-      <c r="BA2" s="57"/>
-      <c r="BB2" s="57"/>
-      <c r="BC2" s="54"/>
-      <c r="BD2" s="54"/>
-      <c r="BE2" s="54"/>
-      <c r="BF2" s="54"/>
-      <c r="BG2" s="54"/>
-      <c r="BH2" s="63" t="s">
+      <c r="BI2" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="BI2" s="64" t="s">
+      <c r="BJ2" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="BJ2" s="58" t="s">
+    </row>
+    <row r="3" spans="1:62" s="18" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="52"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="52" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:62" s="18" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="58"/>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="61"/>
-      <c r="I3" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="J3" s="58"/>
-      <c r="K3" s="58"/>
-      <c r="L3" s="58"/>
-      <c r="M3" s="58"/>
-      <c r="N3" s="58"/>
+      <c r="J3" s="52"/>
+      <c r="K3" s="52"/>
+      <c r="L3" s="52"/>
+      <c r="M3" s="52"/>
+      <c r="N3" s="52"/>
       <c r="O3" s="23"/>
       <c r="P3" s="23"/>
-      <c r="Q3" s="58" t="s">
+      <c r="Q3" s="52" t="s">
+        <v>10</v>
+      </c>
+      <c r="R3" s="52"/>
+      <c r="S3" s="52"/>
+      <c r="T3" s="52"/>
+      <c r="U3" s="52"/>
+      <c r="V3" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="R3" s="58"/>
-      <c r="S3" s="58"/>
-      <c r="T3" s="58"/>
-      <c r="U3" s="58"/>
-      <c r="V3" s="62" t="s">
+      <c r="W3" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="W3" s="62" t="s">
+      <c r="X3" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y3" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="X3" s="23" t="s">
+      <c r="Z3" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA3" s="52" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB3" s="52" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC3" s="52" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD3" s="62" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE3" s="62"/>
+      <c r="AF3" s="62"/>
+      <c r="AG3" s="62"/>
+      <c r="AH3" s="62"/>
+      <c r="AI3" s="62"/>
+      <c r="AJ3" s="62"/>
+      <c r="AK3" s="62"/>
+      <c r="AL3" s="62"/>
+      <c r="AM3" s="62" t="s">
+        <v>19</v>
+      </c>
+      <c r="AN3" s="62"/>
+      <c r="AO3" s="62"/>
+      <c r="AP3" s="62"/>
+      <c r="AQ3" s="62"/>
+      <c r="AR3" s="62"/>
+      <c r="AS3" s="62" t="s">
+        <v>20</v>
+      </c>
+      <c r="AT3" s="62"/>
+      <c r="AU3" s="62"/>
+      <c r="AV3" s="26"/>
+      <c r="AW3" s="63" t="s">
+        <v>21</v>
+      </c>
+      <c r="AX3" s="63"/>
+      <c r="AY3" s="62" t="s">
         <v>89</v>
       </c>
-      <c r="Y3" s="65" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z3" s="65" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA3" s="58" t="s">
-        <v>16</v>
-      </c>
-      <c r="AB3" s="58" t="s">
-        <v>17</v>
-      </c>
-      <c r="AC3" s="58" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD3" s="59" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE3" s="59"/>
-      <c r="AF3" s="59"/>
-      <c r="AG3" s="59"/>
-      <c r="AH3" s="59"/>
-      <c r="AI3" s="59"/>
-      <c r="AJ3" s="59"/>
-      <c r="AK3" s="59"/>
-      <c r="AL3" s="59"/>
-      <c r="AM3" s="59" t="s">
-        <v>20</v>
-      </c>
-      <c r="AN3" s="59"/>
-      <c r="AO3" s="59"/>
-      <c r="AP3" s="59"/>
-      <c r="AQ3" s="59"/>
-      <c r="AR3" s="59"/>
-      <c r="AS3" s="59" t="s">
-        <v>21</v>
-      </c>
-      <c r="AT3" s="59"/>
-      <c r="AU3" s="59"/>
-      <c r="AV3" s="26"/>
-      <c r="AW3" s="60" t="s">
+      <c r="AZ3" s="62"/>
+      <c r="BA3" s="62"/>
+      <c r="BB3" s="62"/>
+      <c r="BC3" s="57" t="s">
+        <v>108</v>
+      </c>
+      <c r="BD3" s="58"/>
+      <c r="BE3" s="58"/>
+      <c r="BF3" s="58"/>
+      <c r="BG3" s="59"/>
+      <c r="BH3" s="53"/>
+      <c r="BI3" s="54"/>
+      <c r="BJ3" s="52"/>
+    </row>
+    <row r="4" spans="1:62" s="18" customFormat="1" ht="87" x14ac:dyDescent="0.25">
+      <c r="A4" s="52"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="AX3" s="60"/>
-      <c r="AY3" s="59" t="s">
+      <c r="J4" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="K4" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="AZ3" s="59"/>
-      <c r="BA3" s="59"/>
-      <c r="BB3" s="59"/>
-      <c r="BC3" s="69" t="s">
+      <c r="M4" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="N4" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="O4" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="P4" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q4" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="R4" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="S4" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="T4" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="U4" s="31" t="s">
+        <v>94</v>
+      </c>
+      <c r="V4" s="55"/>
+      <c r="W4" s="55"/>
+      <c r="X4" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="Y4" s="56"/>
+      <c r="Z4" s="56"/>
+      <c r="AA4" s="52"/>
+      <c r="AB4" s="52"/>
+      <c r="AC4" s="52"/>
+      <c r="AD4" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="AE4" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="AF4" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AG4" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="AH4" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI4" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ4" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="AK4" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="AL4" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="AM4" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="AN4" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="AO4" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="AP4" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="AQ4" s="35" t="s">
+        <v>99</v>
+      </c>
+      <c r="AR4" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="AS4" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="AT4" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="AU4" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="AV4" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="AW4" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="AX4" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="AY4" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="AZ4" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="BA4" s="35" t="s">
+        <v>104</v>
+      </c>
+      <c r="BB4" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="BC4" s="51" t="s">
         <v>109</v>
       </c>
-      <c r="BD3" s="70"/>
-      <c r="BE3" s="70"/>
-      <c r="BF3" s="70"/>
-      <c r="BG3" s="71"/>
-      <c r="BH3" s="63"/>
-      <c r="BI3" s="64"/>
-      <c r="BJ3" s="58"/>
-    </row>
-    <row r="4" spans="1:62" s="18" customFormat="1" ht="87" x14ac:dyDescent="0.25">
-      <c r="A4" s="58"/>
-      <c r="B4" s="58"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="61"/>
-      <c r="I4" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="J4" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="K4" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="L4" s="27" t="s">
-        <v>91</v>
-      </c>
-      <c r="M4" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="N4" s="28" t="s">
-        <v>93</v>
-      </c>
-      <c r="O4" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="P4" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q4" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="R4" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="S4" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="T4" s="30" t="s">
-        <v>94</v>
-      </c>
-      <c r="U4" s="31" t="s">
-        <v>95</v>
-      </c>
-      <c r="V4" s="62"/>
-      <c r="W4" s="62"/>
-      <c r="X4" s="32" t="s">
-        <v>96</v>
-      </c>
-      <c r="Y4" s="65"/>
-      <c r="Z4" s="65"/>
-      <c r="AA4" s="58"/>
-      <c r="AB4" s="58"/>
-      <c r="AC4" s="58"/>
-      <c r="AD4" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="AE4" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="AF4" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG4" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="AH4" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="AI4" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="AJ4" s="24" t="s">
-        <v>97</v>
-      </c>
-      <c r="AK4" s="33" t="s">
-        <v>98</v>
-      </c>
-      <c r="AL4" s="34" t="s">
-        <v>99</v>
-      </c>
-      <c r="AM4" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="AN4" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="AO4" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="AP4" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="AQ4" s="35" t="s">
-        <v>100</v>
-      </c>
-      <c r="AR4" s="34" t="s">
-        <v>101</v>
-      </c>
-      <c r="AS4" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="AT4" s="27" t="s">
+      <c r="BD4" s="51" t="s">
+        <v>111</v>
+      </c>
+      <c r="BE4" s="51" t="s">
+        <v>112</v>
+      </c>
+      <c r="BF4" s="51" t="s">
         <v>39</v>
       </c>
-      <c r="AU4" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="AV4" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="AW4" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="AX4" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="AY4" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="AZ4" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="BA4" s="35" t="s">
-        <v>105</v>
-      </c>
-      <c r="BB4" s="34" t="s">
-        <v>106</v>
-      </c>
-      <c r="BC4" s="72" t="s">
+      <c r="BG4" s="34" t="s">
         <v>110</v>
       </c>
-      <c r="BD4" s="72" t="s">
-        <v>112</v>
-      </c>
-      <c r="BE4" s="72" t="s">
-        <v>113</v>
-      </c>
-      <c r="BF4" s="72" t="s">
-        <v>40</v>
-      </c>
-      <c r="BG4" s="34" t="s">
-        <v>111</v>
-      </c>
-      <c r="BH4" s="63"/>
-      <c r="BI4" s="64"/>
-      <c r="BJ4" s="58"/>
+      <c r="BH4" s="53"/>
+      <c r="BI4" s="54"/>
+      <c r="BJ4" s="52"/>
     </row>
     <row r="5" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="23">
@@ -1678,106 +1675,106 @@
         <v>1</v>
       </c>
       <c r="B5" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" s="36">
+      <c r="D5" s="42">
         <f>F5-E5</f>
         <v>0</v>
       </c>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="37"/>
-      <c r="I5" s="37"/>
-      <c r="J5" s="37"/>
-      <c r="K5" s="45">
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="39"/>
+      <c r="J5" s="39"/>
+      <c r="K5" s="42">
         <f>I5-J5</f>
         <v>0</v>
       </c>
-      <c r="L5" s="41"/>
-      <c r="M5" s="45">
+      <c r="L5" s="39"/>
+      <c r="M5" s="42">
         <f t="shared" ref="M5:M35" si="1">K5-L5</f>
         <v>0</v>
       </c>
-      <c r="N5" s="41"/>
-      <c r="O5" s="41"/>
-      <c r="P5" s="41"/>
-      <c r="Q5" s="41"/>
-      <c r="R5" s="45">
+      <c r="N5" s="39"/>
+      <c r="O5" s="39"/>
+      <c r="P5" s="39"/>
+      <c r="Q5" s="39"/>
+      <c r="R5" s="42">
         <f t="shared" ref="R5:R35" si="2">P5-Q5</f>
         <v>0</v>
       </c>
-      <c r="S5" s="41"/>
-      <c r="T5" s="45">
+      <c r="S5" s="39"/>
+      <c r="T5" s="42">
         <f t="shared" ref="T5:T35" si="3">R5-S5</f>
         <v>0</v>
       </c>
-      <c r="U5" s="41"/>
-      <c r="V5" s="41"/>
-      <c r="W5" s="41"/>
-      <c r="X5" s="41"/>
-      <c r="Y5" s="41"/>
-      <c r="Z5" s="41"/>
-      <c r="AA5" s="41"/>
-      <c r="AB5" s="41"/>
-      <c r="AC5" s="41"/>
-      <c r="AD5" s="46"/>
-      <c r="AE5" s="46"/>
-      <c r="AF5" s="41"/>
-      <c r="AG5" s="41"/>
-      <c r="AH5" s="41"/>
-      <c r="AI5" s="41"/>
-      <c r="AJ5" s="41"/>
-      <c r="AK5" s="45">
+      <c r="U5" s="39"/>
+      <c r="V5" s="39"/>
+      <c r="W5" s="39"/>
+      <c r="X5" s="39"/>
+      <c r="Y5" s="39"/>
+      <c r="Z5" s="39"/>
+      <c r="AA5" s="39"/>
+      <c r="AB5" s="39"/>
+      <c r="AC5" s="39"/>
+      <c r="AD5" s="43"/>
+      <c r="AE5" s="43"/>
+      <c r="AF5" s="39"/>
+      <c r="AG5" s="39"/>
+      <c r="AH5" s="39"/>
+      <c r="AI5" s="39"/>
+      <c r="AJ5" s="39"/>
+      <c r="AK5" s="42">
         <f>AE5+AF5-AG5-AH5-AI5-AJ5</f>
         <v>0</v>
       </c>
-      <c r="AL5" s="41"/>
-      <c r="AM5" s="41"/>
-      <c r="AN5" s="41"/>
-      <c r="AO5" s="41"/>
-      <c r="AP5" s="47"/>
-      <c r="AQ5" s="45">
+      <c r="AL5" s="39"/>
+      <c r="AM5" s="39"/>
+      <c r="AN5" s="39"/>
+      <c r="AO5" s="39"/>
+      <c r="AP5" s="44"/>
+      <c r="AQ5" s="42">
         <f t="shared" ref="AQ5:AQ26" si="4">AM5-AN5-AO5-AP5</f>
         <v>0</v>
       </c>
-      <c r="AR5" s="41"/>
-      <c r="AS5" s="41"/>
-      <c r="AT5" s="41"/>
-      <c r="AU5" s="45">
+      <c r="AR5" s="39"/>
+      <c r="AS5" s="39"/>
+      <c r="AT5" s="39"/>
+      <c r="AU5" s="42">
         <f t="shared" ref="AU5:AU35" si="5">AS5-AT5</f>
         <v>0</v>
       </c>
-      <c r="AV5" s="41"/>
-      <c r="AW5" s="41"/>
-      <c r="AX5" s="41"/>
-      <c r="AY5" s="47"/>
-      <c r="AZ5" s="41"/>
-      <c r="BA5" s="45">
+      <c r="AV5" s="39"/>
+      <c r="AW5" s="39"/>
+      <c r="AX5" s="39"/>
+      <c r="AY5" s="44"/>
+      <c r="AZ5" s="39"/>
+      <c r="BA5" s="42">
         <f t="shared" ref="BA5:BA35" si="6">AY5-AZ5</f>
         <v>0</v>
       </c>
-      <c r="BB5" s="41"/>
-      <c r="BC5" s="41"/>
-      <c r="BD5" s="41"/>
-      <c r="BE5" s="41"/>
-      <c r="BF5" s="45">
+      <c r="BB5" s="39"/>
+      <c r="BC5" s="39"/>
+      <c r="BD5" s="39"/>
+      <c r="BE5" s="39"/>
+      <c r="BF5" s="42">
         <f>BC5-BD5-BE5</f>
         <v>0</v>
       </c>
-      <c r="BG5" s="41"/>
-      <c r="BH5" s="48">
+      <c r="BG5" s="39"/>
+      <c r="BH5" s="45">
         <f>G5+M5+T5+AK5+AQ5+AU5+AW5+BA5</f>
         <v>0</v>
       </c>
-      <c r="BI5" s="49">
+      <c r="BI5" s="46">
         <f>G5+K5+R5+AE5+AM5+AS5+AW5+AY5</f>
         <v>0</v>
       </c>
-      <c r="BJ5" s="37"/>
+      <c r="BJ5" s="36"/>
     </row>
     <row r="6" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="23">
@@ -1785,106 +1782,106 @@
         <v>2</v>
       </c>
       <c r="B6" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="D6" s="36">
+      <c r="D6" s="42">
         <f t="shared" ref="D6:D35" si="7">F6-E6</f>
         <v>0</v>
       </c>
-      <c r="E6" s="37"/>
-      <c r="F6" s="37"/>
-      <c r="G6" s="37"/>
-      <c r="H6" s="37"/>
-      <c r="I6" s="37"/>
-      <c r="J6" s="37"/>
-      <c r="K6" s="45">
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="39"/>
+      <c r="K6" s="42">
         <f t="shared" ref="K6:K35" si="8">I6-J6</f>
         <v>0</v>
       </c>
-      <c r="L6" s="41"/>
-      <c r="M6" s="45">
+      <c r="L6" s="39"/>
+      <c r="M6" s="42">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N6" s="41"/>
-      <c r="O6" s="41"/>
-      <c r="P6" s="41"/>
-      <c r="Q6" s="41"/>
-      <c r="R6" s="45">
+      <c r="N6" s="39"/>
+      <c r="O6" s="39"/>
+      <c r="P6" s="39"/>
+      <c r="Q6" s="39"/>
+      <c r="R6" s="42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S6" s="41"/>
-      <c r="T6" s="45">
+      <c r="S6" s="39"/>
+      <c r="T6" s="42">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U6" s="41"/>
-      <c r="V6" s="41"/>
-      <c r="W6" s="41"/>
-      <c r="X6" s="41"/>
-      <c r="Y6" s="41"/>
-      <c r="Z6" s="41"/>
-      <c r="AA6" s="41"/>
-      <c r="AB6" s="41"/>
-      <c r="AC6" s="41"/>
-      <c r="AD6" s="41"/>
-      <c r="AE6" s="41"/>
-      <c r="AF6" s="41"/>
-      <c r="AG6" s="41"/>
-      <c r="AH6" s="41"/>
-      <c r="AI6" s="41"/>
-      <c r="AJ6" s="41"/>
-      <c r="AK6" s="45">
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="W6" s="39"/>
+      <c r="X6" s="39"/>
+      <c r="Y6" s="39"/>
+      <c r="Z6" s="39"/>
+      <c r="AA6" s="39"/>
+      <c r="AB6" s="39"/>
+      <c r="AC6" s="39"/>
+      <c r="AD6" s="39"/>
+      <c r="AE6" s="39"/>
+      <c r="AF6" s="39"/>
+      <c r="AG6" s="39"/>
+      <c r="AH6" s="39"/>
+      <c r="AI6" s="39"/>
+      <c r="AJ6" s="39"/>
+      <c r="AK6" s="42">
         <f t="shared" ref="AK6:AK35" si="9">AE6+AF6-AG6-AH6-AI6-AJ6</f>
         <v>0</v>
       </c>
-      <c r="AL6" s="41"/>
-      <c r="AM6" s="41"/>
-      <c r="AN6" s="41"/>
-      <c r="AO6" s="41"/>
-      <c r="AP6" s="47"/>
-      <c r="AQ6" s="45">
+      <c r="AL6" s="39"/>
+      <c r="AM6" s="39"/>
+      <c r="AN6" s="39"/>
+      <c r="AO6" s="39"/>
+      <c r="AP6" s="44"/>
+      <c r="AQ6" s="42">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AR6" s="41"/>
-      <c r="AS6" s="41"/>
-      <c r="AT6" s="41"/>
-      <c r="AU6" s="45">
+      <c r="AR6" s="39"/>
+      <c r="AS6" s="39"/>
+      <c r="AT6" s="39"/>
+      <c r="AU6" s="42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV6" s="41"/>
-      <c r="AW6" s="41"/>
-      <c r="AX6" s="41"/>
-      <c r="AY6" s="47"/>
-      <c r="AZ6" s="41"/>
-      <c r="BA6" s="45">
+      <c r="AV6" s="39"/>
+      <c r="AW6" s="39"/>
+      <c r="AX6" s="39"/>
+      <c r="AY6" s="44"/>
+      <c r="AZ6" s="39"/>
+      <c r="BA6" s="42">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB6" s="41"/>
-      <c r="BC6" s="41"/>
-      <c r="BD6" s="41"/>
-      <c r="BE6" s="41"/>
-      <c r="BF6" s="45">
+      <c r="BB6" s="39"/>
+      <c r="BC6" s="39"/>
+      <c r="BD6" s="39"/>
+      <c r="BE6" s="39"/>
+      <c r="BF6" s="42">
         <f t="shared" ref="BF6:BF35" si="10">BC6-BD6-BE6</f>
         <v>0</v>
       </c>
-      <c r="BG6" s="41"/>
-      <c r="BH6" s="48">
+      <c r="BG6" s="39"/>
+      <c r="BH6" s="45">
         <f t="shared" ref="BH6:BH35" si="11">G6+M6+T6+AK6+AQ6+AU6+AW6+BA6</f>
         <v>0</v>
       </c>
-      <c r="BI6" s="49">
+      <c r="BI6" s="46">
         <f t="shared" ref="BI6:BI35" si="12">G6+K6+R6+AE6+AM6+AS6+AW6+AY6</f>
         <v>0</v>
       </c>
-      <c r="BJ6" s="37"/>
+      <c r="BJ6" s="36"/>
     </row>
     <row r="7" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="23">
@@ -1892,106 +1889,106 @@
         <v>3</v>
       </c>
       <c r="B7" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" s="36">
+      <c r="D7" s="42">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="37"/>
-      <c r="I7" s="37"/>
-      <c r="J7" s="37"/>
-      <c r="K7" s="45">
+      <c r="E7" s="39"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="39"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="39"/>
+      <c r="K7" s="42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L7" s="41"/>
-      <c r="M7" s="45">
+      <c r="L7" s="39"/>
+      <c r="M7" s="42">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N7" s="41"/>
-      <c r="O7" s="41"/>
-      <c r="P7" s="41"/>
-      <c r="Q7" s="41"/>
-      <c r="R7" s="45">
+      <c r="N7" s="39"/>
+      <c r="O7" s="39"/>
+      <c r="P7" s="39"/>
+      <c r="Q7" s="39"/>
+      <c r="R7" s="42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S7" s="41"/>
-      <c r="T7" s="45">
+      <c r="S7" s="39"/>
+      <c r="T7" s="42">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U7" s="41"/>
-      <c r="V7" s="41"/>
-      <c r="W7" s="41"/>
-      <c r="X7" s="41"/>
-      <c r="Y7" s="41"/>
-      <c r="Z7" s="41"/>
-      <c r="AA7" s="41"/>
-      <c r="AB7" s="41"/>
-      <c r="AC7" s="41"/>
-      <c r="AD7" s="41"/>
-      <c r="AE7" s="41"/>
-      <c r="AF7" s="41"/>
-      <c r="AG7" s="41"/>
-      <c r="AH7" s="41"/>
-      <c r="AI7" s="41"/>
-      <c r="AJ7" s="41"/>
-      <c r="AK7" s="45">
+      <c r="U7" s="39"/>
+      <c r="V7" s="39"/>
+      <c r="W7" s="39"/>
+      <c r="X7" s="39"/>
+      <c r="Y7" s="39"/>
+      <c r="Z7" s="39"/>
+      <c r="AA7" s="39"/>
+      <c r="AB7" s="39"/>
+      <c r="AC7" s="39"/>
+      <c r="AD7" s="39"/>
+      <c r="AE7" s="39"/>
+      <c r="AF7" s="39"/>
+      <c r="AG7" s="39"/>
+      <c r="AH7" s="39"/>
+      <c r="AI7" s="39"/>
+      <c r="AJ7" s="39"/>
+      <c r="AK7" s="42">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AL7" s="41"/>
-      <c r="AM7" s="41"/>
-      <c r="AN7" s="47"/>
-      <c r="AO7" s="47"/>
-      <c r="AP7" s="47"/>
-      <c r="AQ7" s="45">
+      <c r="AL7" s="39"/>
+      <c r="AM7" s="39"/>
+      <c r="AN7" s="44"/>
+      <c r="AO7" s="44"/>
+      <c r="AP7" s="44"/>
+      <c r="AQ7" s="42">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AR7" s="41"/>
-      <c r="AS7" s="41"/>
-      <c r="AT7" s="41"/>
-      <c r="AU7" s="45">
+      <c r="AR7" s="39"/>
+      <c r="AS7" s="39"/>
+      <c r="AT7" s="39"/>
+      <c r="AU7" s="42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV7" s="41"/>
-      <c r="AW7" s="41"/>
-      <c r="AX7" s="41"/>
-      <c r="AY7" s="47"/>
-      <c r="AZ7" s="41"/>
-      <c r="BA7" s="45">
+      <c r="AV7" s="39"/>
+      <c r="AW7" s="39"/>
+      <c r="AX7" s="39"/>
+      <c r="AY7" s="44"/>
+      <c r="AZ7" s="39"/>
+      <c r="BA7" s="42">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB7" s="41"/>
-      <c r="BC7" s="41"/>
-      <c r="BD7" s="41"/>
-      <c r="BE7" s="41"/>
-      <c r="BF7" s="45">
+      <c r="BB7" s="39"/>
+      <c r="BC7" s="39"/>
+      <c r="BD7" s="39"/>
+      <c r="BE7" s="39"/>
+      <c r="BF7" s="42">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BG7" s="41"/>
-      <c r="BH7" s="48">
+      <c r="BG7" s="39"/>
+      <c r="BH7" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI7" s="49">
+      <c r="BI7" s="46">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ7" s="38"/>
+      <c r="BJ7" s="37"/>
     </row>
     <row r="8" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="23">
@@ -1999,106 +1996,106 @@
         <v>4</v>
       </c>
       <c r="B8" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" s="36">
+      <c r="D8" s="42">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="37"/>
-      <c r="I8" s="37"/>
-      <c r="J8" s="37"/>
-      <c r="K8" s="45">
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="39"/>
+      <c r="K8" s="42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L8" s="41"/>
-      <c r="M8" s="45">
+      <c r="L8" s="39"/>
+      <c r="M8" s="42">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N8" s="41"/>
-      <c r="O8" s="41"/>
-      <c r="P8" s="41"/>
-      <c r="Q8" s="41"/>
-      <c r="R8" s="45">
+      <c r="N8" s="39"/>
+      <c r="O8" s="39"/>
+      <c r="P8" s="39"/>
+      <c r="Q8" s="39"/>
+      <c r="R8" s="42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S8" s="41"/>
-      <c r="T8" s="45">
+      <c r="S8" s="39"/>
+      <c r="T8" s="42">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U8" s="41"/>
-      <c r="V8" s="41"/>
-      <c r="W8" s="41"/>
-      <c r="X8" s="41"/>
-      <c r="Y8" s="41"/>
-      <c r="Z8" s="41"/>
-      <c r="AA8" s="41"/>
-      <c r="AB8" s="41"/>
-      <c r="AC8" s="41"/>
-      <c r="AD8" s="41"/>
-      <c r="AE8" s="41"/>
-      <c r="AF8" s="41"/>
-      <c r="AG8" s="41"/>
-      <c r="AH8" s="41"/>
-      <c r="AI8" s="41"/>
-      <c r="AJ8" s="41"/>
-      <c r="AK8" s="45">
+      <c r="U8" s="39"/>
+      <c r="V8" s="39"/>
+      <c r="W8" s="39"/>
+      <c r="X8" s="39"/>
+      <c r="Y8" s="39"/>
+      <c r="Z8" s="39"/>
+      <c r="AA8" s="39"/>
+      <c r="AB8" s="39"/>
+      <c r="AC8" s="39"/>
+      <c r="AD8" s="39"/>
+      <c r="AE8" s="39"/>
+      <c r="AF8" s="39"/>
+      <c r="AG8" s="39"/>
+      <c r="AH8" s="39"/>
+      <c r="AI8" s="39"/>
+      <c r="AJ8" s="39"/>
+      <c r="AK8" s="42">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AL8" s="41"/>
-      <c r="AM8" s="41"/>
-      <c r="AN8" s="41"/>
-      <c r="AO8" s="41"/>
-      <c r="AP8" s="47"/>
-      <c r="AQ8" s="45">
+      <c r="AL8" s="39"/>
+      <c r="AM8" s="39"/>
+      <c r="AN8" s="39"/>
+      <c r="AO8" s="39"/>
+      <c r="AP8" s="44"/>
+      <c r="AQ8" s="42">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AR8" s="41"/>
-      <c r="AS8" s="41"/>
-      <c r="AT8" s="41"/>
-      <c r="AU8" s="45">
+      <c r="AR8" s="39"/>
+      <c r="AS8" s="39"/>
+      <c r="AT8" s="39"/>
+      <c r="AU8" s="42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV8" s="41"/>
-      <c r="AW8" s="41"/>
-      <c r="AX8" s="41"/>
-      <c r="AY8" s="47"/>
-      <c r="AZ8" s="47"/>
-      <c r="BA8" s="45">
+      <c r="AV8" s="39"/>
+      <c r="AW8" s="39"/>
+      <c r="AX8" s="39"/>
+      <c r="AY8" s="44"/>
+      <c r="AZ8" s="44"/>
+      <c r="BA8" s="42">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB8" s="41"/>
-      <c r="BC8" s="41"/>
-      <c r="BD8" s="41"/>
-      <c r="BE8" s="41"/>
-      <c r="BF8" s="45">
+      <c r="BB8" s="39"/>
+      <c r="BC8" s="39"/>
+      <c r="BD8" s="39"/>
+      <c r="BE8" s="39"/>
+      <c r="BF8" s="42">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BG8" s="41"/>
-      <c r="BH8" s="48">
+      <c r="BG8" s="39"/>
+      <c r="BH8" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI8" s="49">
+      <c r="BI8" s="46">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ8" s="39"/>
+      <c r="BJ8" s="38"/>
     </row>
     <row r="9" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="23">
@@ -2106,106 +2103,106 @@
         <v>5</v>
       </c>
       <c r="B9" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" s="36">
+      <c r="D9" s="42">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="E9" s="37"/>
-      <c r="F9" s="37"/>
-      <c r="G9" s="37"/>
-      <c r="H9" s="37"/>
-      <c r="I9" s="37"/>
-      <c r="J9" s="37"/>
-      <c r="K9" s="45">
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="39"/>
+      <c r="I9" s="39"/>
+      <c r="J9" s="39"/>
+      <c r="K9" s="42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L9" s="41"/>
-      <c r="M9" s="45">
+      <c r="L9" s="39"/>
+      <c r="M9" s="42">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N9" s="41"/>
-      <c r="O9" s="41"/>
-      <c r="P9" s="41"/>
-      <c r="Q9" s="41"/>
-      <c r="R9" s="45">
+      <c r="N9" s="39"/>
+      <c r="O9" s="39"/>
+      <c r="P9" s="39"/>
+      <c r="Q9" s="39"/>
+      <c r="R9" s="42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S9" s="41"/>
-      <c r="T9" s="45">
+      <c r="S9" s="39"/>
+      <c r="T9" s="42">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U9" s="41"/>
-      <c r="V9" s="41"/>
-      <c r="W9" s="41"/>
-      <c r="X9" s="41"/>
-      <c r="Y9" s="41"/>
-      <c r="Z9" s="41"/>
-      <c r="AA9" s="41"/>
-      <c r="AB9" s="41"/>
-      <c r="AC9" s="41"/>
-      <c r="AD9" s="41"/>
-      <c r="AE9" s="41"/>
-      <c r="AF9" s="41"/>
-      <c r="AG9" s="41"/>
-      <c r="AH9" s="41"/>
-      <c r="AI9" s="41"/>
-      <c r="AJ9" s="41"/>
-      <c r="AK9" s="45">
+      <c r="U9" s="39"/>
+      <c r="V9" s="39"/>
+      <c r="W9" s="39"/>
+      <c r="X9" s="39"/>
+      <c r="Y9" s="39"/>
+      <c r="Z9" s="39"/>
+      <c r="AA9" s="39"/>
+      <c r="AB9" s="39"/>
+      <c r="AC9" s="39"/>
+      <c r="AD9" s="39"/>
+      <c r="AE9" s="39"/>
+      <c r="AF9" s="39"/>
+      <c r="AG9" s="39"/>
+      <c r="AH9" s="39"/>
+      <c r="AI9" s="39"/>
+      <c r="AJ9" s="39"/>
+      <c r="AK9" s="42">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AL9" s="41"/>
-      <c r="AM9" s="41"/>
-      <c r="AN9" s="41"/>
-      <c r="AO9" s="41"/>
-      <c r="AP9" s="41"/>
-      <c r="AQ9" s="45">
+      <c r="AL9" s="39"/>
+      <c r="AM9" s="39"/>
+      <c r="AN9" s="39"/>
+      <c r="AO9" s="39"/>
+      <c r="AP9" s="39"/>
+      <c r="AQ9" s="42">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AR9" s="41"/>
-      <c r="AS9" s="41"/>
-      <c r="AT9" s="41"/>
-      <c r="AU9" s="45">
+      <c r="AR9" s="39"/>
+      <c r="AS9" s="39"/>
+      <c r="AT9" s="39"/>
+      <c r="AU9" s="42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV9" s="41"/>
-      <c r="AW9" s="41"/>
-      <c r="AX9" s="41"/>
-      <c r="AY9" s="47"/>
-      <c r="AZ9" s="47"/>
-      <c r="BA9" s="45">
+      <c r="AV9" s="39"/>
+      <c r="AW9" s="39"/>
+      <c r="AX9" s="39"/>
+      <c r="AY9" s="44"/>
+      <c r="AZ9" s="44"/>
+      <c r="BA9" s="42">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB9" s="41"/>
-      <c r="BC9" s="41"/>
-      <c r="BD9" s="41"/>
-      <c r="BE9" s="41"/>
-      <c r="BF9" s="45">
+      <c r="BB9" s="39"/>
+      <c r="BC9" s="39"/>
+      <c r="BD9" s="39"/>
+      <c r="BE9" s="39"/>
+      <c r="BF9" s="42">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BG9" s="41"/>
-      <c r="BH9" s="48">
+      <c r="BG9" s="39"/>
+      <c r="BH9" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI9" s="49">
+      <c r="BI9" s="46">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ9" s="37"/>
+      <c r="BJ9" s="36"/>
     </row>
     <row r="10" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="23">
@@ -2213,106 +2210,106 @@
         <v>6</v>
       </c>
       <c r="B10" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="C10" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="D10" s="36">
+      <c r="D10" s="42">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="E10" s="37"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="37"/>
-      <c r="I10" s="40"/>
-      <c r="J10" s="37"/>
-      <c r="K10" s="45">
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="68"/>
+      <c r="J10" s="39"/>
+      <c r="K10" s="42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L10" s="41"/>
-      <c r="M10" s="45">
+      <c r="L10" s="39"/>
+      <c r="M10" s="42">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N10" s="41"/>
-      <c r="O10" s="41"/>
-      <c r="P10" s="41"/>
-      <c r="Q10" s="41"/>
-      <c r="R10" s="45">
+      <c r="N10" s="39"/>
+      <c r="O10" s="39"/>
+      <c r="P10" s="39"/>
+      <c r="Q10" s="39"/>
+      <c r="R10" s="42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S10" s="41"/>
-      <c r="T10" s="45">
+      <c r="S10" s="39"/>
+      <c r="T10" s="42">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U10" s="50"/>
-      <c r="V10" s="41"/>
-      <c r="W10" s="41"/>
-      <c r="X10" s="41"/>
-      <c r="Y10" s="41"/>
-      <c r="Z10" s="41"/>
-      <c r="AA10" s="41"/>
-      <c r="AB10" s="41"/>
-      <c r="AC10" s="41"/>
-      <c r="AD10" s="41"/>
-      <c r="AE10" s="41"/>
-      <c r="AF10" s="41"/>
-      <c r="AG10" s="41"/>
-      <c r="AH10" s="41"/>
-      <c r="AI10" s="41"/>
-      <c r="AJ10" s="41"/>
-      <c r="AK10" s="45">
+      <c r="U10" s="47"/>
+      <c r="V10" s="39"/>
+      <c r="W10" s="39"/>
+      <c r="X10" s="39"/>
+      <c r="Y10" s="39"/>
+      <c r="Z10" s="39"/>
+      <c r="AA10" s="39"/>
+      <c r="AB10" s="39"/>
+      <c r="AC10" s="39"/>
+      <c r="AD10" s="39"/>
+      <c r="AE10" s="39"/>
+      <c r="AF10" s="39"/>
+      <c r="AG10" s="39"/>
+      <c r="AH10" s="39"/>
+      <c r="AI10" s="39"/>
+      <c r="AJ10" s="39"/>
+      <c r="AK10" s="42">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AL10" s="41"/>
-      <c r="AM10" s="41"/>
-      <c r="AN10" s="41"/>
-      <c r="AO10" s="41"/>
-      <c r="AP10" s="41"/>
-      <c r="AQ10" s="45">
+      <c r="AL10" s="39"/>
+      <c r="AM10" s="39"/>
+      <c r="AN10" s="39"/>
+      <c r="AO10" s="39"/>
+      <c r="AP10" s="39"/>
+      <c r="AQ10" s="42">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AR10" s="41"/>
-      <c r="AS10" s="41"/>
-      <c r="AT10" s="41"/>
-      <c r="AU10" s="45">
+      <c r="AR10" s="39"/>
+      <c r="AS10" s="39"/>
+      <c r="AT10" s="39"/>
+      <c r="AU10" s="42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV10" s="41"/>
-      <c r="AW10" s="41"/>
-      <c r="AX10" s="41"/>
-      <c r="AY10" s="47"/>
-      <c r="AZ10" s="41"/>
-      <c r="BA10" s="45">
+      <c r="AV10" s="39"/>
+      <c r="AW10" s="39"/>
+      <c r="AX10" s="39"/>
+      <c r="AY10" s="44"/>
+      <c r="AZ10" s="39"/>
+      <c r="BA10" s="42">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB10" s="41"/>
-      <c r="BC10" s="41"/>
-      <c r="BD10" s="41"/>
-      <c r="BE10" s="41"/>
-      <c r="BF10" s="45">
+      <c r="BB10" s="39"/>
+      <c r="BC10" s="39"/>
+      <c r="BD10" s="39"/>
+      <c r="BE10" s="39"/>
+      <c r="BF10" s="42">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BG10" s="41"/>
-      <c r="BH10" s="48">
+      <c r="BG10" s="39"/>
+      <c r="BH10" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI10" s="49">
+      <c r="BI10" s="46">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ10" s="37"/>
+      <c r="BJ10" s="36"/>
     </row>
     <row r="11" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="23">
@@ -2320,106 +2317,106 @@
         <v>7</v>
       </c>
       <c r="B11" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="C11" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="D11" s="36">
+      <c r="D11" s="42">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="E11" s="37"/>
-      <c r="F11" s="37"/>
-      <c r="G11" s="37"/>
-      <c r="H11" s="37"/>
-      <c r="I11" s="37"/>
-      <c r="J11" s="37"/>
-      <c r="K11" s="45">
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="39"/>
+      <c r="I11" s="39"/>
+      <c r="J11" s="39"/>
+      <c r="K11" s="42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L11" s="41"/>
-      <c r="M11" s="45">
+      <c r="L11" s="39"/>
+      <c r="M11" s="42">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N11" s="41"/>
-      <c r="O11" s="41"/>
-      <c r="P11" s="41"/>
-      <c r="Q11" s="41"/>
-      <c r="R11" s="45">
+      <c r="N11" s="39"/>
+      <c r="O11" s="39"/>
+      <c r="P11" s="39"/>
+      <c r="Q11" s="39"/>
+      <c r="R11" s="42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S11" s="41"/>
-      <c r="T11" s="45">
+      <c r="S11" s="39"/>
+      <c r="T11" s="42">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U11" s="50"/>
-      <c r="V11" s="41"/>
-      <c r="W11" s="41"/>
-      <c r="X11" s="41"/>
-      <c r="Y11" s="41"/>
-      <c r="Z11" s="41"/>
-      <c r="AA11" s="41"/>
-      <c r="AB11" s="41"/>
-      <c r="AC11" s="41"/>
-      <c r="AD11" s="41"/>
-      <c r="AE11" s="41"/>
-      <c r="AF11" s="41"/>
-      <c r="AG11" s="41"/>
-      <c r="AH11" s="41"/>
-      <c r="AI11" s="41"/>
-      <c r="AJ11" s="41"/>
-      <c r="AK11" s="45">
+      <c r="U11" s="47"/>
+      <c r="V11" s="39"/>
+      <c r="W11" s="39"/>
+      <c r="X11" s="39"/>
+      <c r="Y11" s="39"/>
+      <c r="Z11" s="39"/>
+      <c r="AA11" s="39"/>
+      <c r="AB11" s="39"/>
+      <c r="AC11" s="39"/>
+      <c r="AD11" s="39"/>
+      <c r="AE11" s="39"/>
+      <c r="AF11" s="39"/>
+      <c r="AG11" s="39"/>
+      <c r="AH11" s="39"/>
+      <c r="AI11" s="39"/>
+      <c r="AJ11" s="39"/>
+      <c r="AK11" s="42">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AL11" s="41"/>
-      <c r="AM11" s="41"/>
-      <c r="AN11" s="41"/>
-      <c r="AO11" s="41"/>
-      <c r="AP11" s="47"/>
-      <c r="AQ11" s="45">
+      <c r="AL11" s="39"/>
+      <c r="AM11" s="39"/>
+      <c r="AN11" s="39"/>
+      <c r="AO11" s="39"/>
+      <c r="AP11" s="44"/>
+      <c r="AQ11" s="42">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AR11" s="41"/>
-      <c r="AS11" s="41"/>
-      <c r="AT11" s="41"/>
-      <c r="AU11" s="45">
+      <c r="AR11" s="39"/>
+      <c r="AS11" s="39"/>
+      <c r="AT11" s="39"/>
+      <c r="AU11" s="42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV11" s="41"/>
-      <c r="AW11" s="41"/>
-      <c r="AX11" s="41"/>
-      <c r="AY11" s="47"/>
-      <c r="AZ11" s="41"/>
-      <c r="BA11" s="45">
+      <c r="AV11" s="39"/>
+      <c r="AW11" s="39"/>
+      <c r="AX11" s="39"/>
+      <c r="AY11" s="44"/>
+      <c r="AZ11" s="39"/>
+      <c r="BA11" s="42">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB11" s="41"/>
-      <c r="BC11" s="41"/>
-      <c r="BD11" s="41"/>
-      <c r="BE11" s="41"/>
-      <c r="BF11" s="45">
+      <c r="BB11" s="39"/>
+      <c r="BC11" s="39"/>
+      <c r="BD11" s="39"/>
+      <c r="BE11" s="39"/>
+      <c r="BF11" s="42">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BG11" s="41"/>
-      <c r="BH11" s="48">
+      <c r="BG11" s="39"/>
+      <c r="BH11" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI11" s="49">
+      <c r="BI11" s="46">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ11" s="37"/>
+      <c r="BJ11" s="36"/>
     </row>
     <row r="12" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="23">
@@ -2427,106 +2424,106 @@
         <v>8</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" s="36">
+        <v>43</v>
+      </c>
+      <c r="D12" s="42">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="E12" s="37"/>
-      <c r="F12" s="37"/>
-      <c r="G12" s="37"/>
-      <c r="H12" s="37"/>
-      <c r="I12" s="37"/>
-      <c r="J12" s="37"/>
-      <c r="K12" s="45">
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="39"/>
+      <c r="K12" s="42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L12" s="41"/>
-      <c r="M12" s="45">
+      <c r="L12" s="39"/>
+      <c r="M12" s="42">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N12" s="41"/>
-      <c r="O12" s="41"/>
-      <c r="P12" s="41"/>
-      <c r="Q12" s="41"/>
-      <c r="R12" s="45">
+      <c r="N12" s="39"/>
+      <c r="O12" s="39"/>
+      <c r="P12" s="39"/>
+      <c r="Q12" s="39"/>
+      <c r="R12" s="42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S12" s="41"/>
-      <c r="T12" s="45">
+      <c r="S12" s="39"/>
+      <c r="T12" s="42">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U12" s="50"/>
-      <c r="V12" s="41"/>
-      <c r="W12" s="41"/>
-      <c r="X12" s="41"/>
-      <c r="Y12" s="41"/>
-      <c r="Z12" s="41"/>
-      <c r="AA12" s="41"/>
-      <c r="AB12" s="41"/>
-      <c r="AC12" s="41"/>
-      <c r="AD12" s="41"/>
-      <c r="AE12" s="41"/>
-      <c r="AF12" s="41"/>
-      <c r="AG12" s="41"/>
-      <c r="AH12" s="41"/>
-      <c r="AI12" s="41"/>
-      <c r="AJ12" s="41"/>
-      <c r="AK12" s="45">
+      <c r="U12" s="47"/>
+      <c r="V12" s="39"/>
+      <c r="W12" s="39"/>
+      <c r="X12" s="39"/>
+      <c r="Y12" s="39"/>
+      <c r="Z12" s="39"/>
+      <c r="AA12" s="39"/>
+      <c r="AB12" s="39"/>
+      <c r="AC12" s="39"/>
+      <c r="AD12" s="39"/>
+      <c r="AE12" s="39"/>
+      <c r="AF12" s="39"/>
+      <c r="AG12" s="39"/>
+      <c r="AH12" s="39"/>
+      <c r="AI12" s="39"/>
+      <c r="AJ12" s="39"/>
+      <c r="AK12" s="42">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AL12" s="41"/>
-      <c r="AM12" s="41"/>
-      <c r="AN12" s="41"/>
-      <c r="AO12" s="41"/>
-      <c r="AP12" s="41"/>
-      <c r="AQ12" s="45">
+      <c r="AL12" s="39"/>
+      <c r="AM12" s="39"/>
+      <c r="AN12" s="39"/>
+      <c r="AO12" s="39"/>
+      <c r="AP12" s="39"/>
+      <c r="AQ12" s="42">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AR12" s="41"/>
-      <c r="AS12" s="41"/>
-      <c r="AT12" s="41"/>
-      <c r="AU12" s="45">
+      <c r="AR12" s="39"/>
+      <c r="AS12" s="39"/>
+      <c r="AT12" s="39"/>
+      <c r="AU12" s="42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV12" s="41"/>
-      <c r="AW12" s="41"/>
-      <c r="AX12" s="41"/>
-      <c r="AY12" s="47"/>
-      <c r="AZ12" s="41"/>
-      <c r="BA12" s="45">
+      <c r="AV12" s="39"/>
+      <c r="AW12" s="39"/>
+      <c r="AX12" s="39"/>
+      <c r="AY12" s="44"/>
+      <c r="AZ12" s="39"/>
+      <c r="BA12" s="42">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB12" s="41"/>
-      <c r="BC12" s="41"/>
-      <c r="BD12" s="41"/>
-      <c r="BE12" s="41"/>
-      <c r="BF12" s="45">
+      <c r="BB12" s="39"/>
+      <c r="BC12" s="39"/>
+      <c r="BD12" s="39"/>
+      <c r="BE12" s="39"/>
+      <c r="BF12" s="42">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BG12" s="41"/>
-      <c r="BH12" s="48">
+      <c r="BG12" s="39"/>
+      <c r="BH12" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI12" s="49">
+      <c r="BI12" s="46">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ12" s="37"/>
+      <c r="BJ12" s="36"/>
     </row>
     <row r="13" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="23">
@@ -2534,106 +2531,106 @@
         <v>9</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" s="36">
+        <v>45</v>
+      </c>
+      <c r="D13" s="42">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="E13" s="37"/>
-      <c r="F13" s="37"/>
-      <c r="G13" s="37"/>
-      <c r="H13" s="37"/>
-      <c r="I13" s="37"/>
-      <c r="J13" s="37"/>
-      <c r="K13" s="45">
+      <c r="E13" s="39"/>
+      <c r="F13" s="39"/>
+      <c r="G13" s="39"/>
+      <c r="H13" s="39"/>
+      <c r="I13" s="39"/>
+      <c r="J13" s="39"/>
+      <c r="K13" s="42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L13" s="41"/>
-      <c r="M13" s="45">
+      <c r="L13" s="39"/>
+      <c r="M13" s="42">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N13" s="41"/>
-      <c r="O13" s="41"/>
-      <c r="P13" s="41"/>
-      <c r="Q13" s="41"/>
-      <c r="R13" s="45">
+      <c r="N13" s="39"/>
+      <c r="O13" s="39"/>
+      <c r="P13" s="39"/>
+      <c r="Q13" s="39"/>
+      <c r="R13" s="42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S13" s="41"/>
-      <c r="T13" s="45">
+      <c r="S13" s="39"/>
+      <c r="T13" s="42">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U13" s="50"/>
-      <c r="V13" s="41"/>
-      <c r="W13" s="41"/>
-      <c r="X13" s="41"/>
-      <c r="Y13" s="41"/>
-      <c r="Z13" s="41"/>
-      <c r="AA13" s="41"/>
-      <c r="AB13" s="41"/>
-      <c r="AC13" s="41"/>
-      <c r="AD13" s="41"/>
-      <c r="AE13" s="41"/>
-      <c r="AF13" s="41"/>
-      <c r="AG13" s="41"/>
-      <c r="AH13" s="41"/>
-      <c r="AI13" s="41"/>
-      <c r="AJ13" s="41"/>
-      <c r="AK13" s="45">
+      <c r="U13" s="47"/>
+      <c r="V13" s="39"/>
+      <c r="W13" s="39"/>
+      <c r="X13" s="39"/>
+      <c r="Y13" s="39"/>
+      <c r="Z13" s="39"/>
+      <c r="AA13" s="39"/>
+      <c r="AB13" s="39"/>
+      <c r="AC13" s="39"/>
+      <c r="AD13" s="39"/>
+      <c r="AE13" s="39"/>
+      <c r="AF13" s="39"/>
+      <c r="AG13" s="39"/>
+      <c r="AH13" s="39"/>
+      <c r="AI13" s="39"/>
+      <c r="AJ13" s="39"/>
+      <c r="AK13" s="42">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AL13" s="41"/>
-      <c r="AM13" s="41"/>
-      <c r="AN13" s="41"/>
-      <c r="AO13" s="41"/>
-      <c r="AP13" s="41"/>
-      <c r="AQ13" s="45">
+      <c r="AL13" s="39"/>
+      <c r="AM13" s="39"/>
+      <c r="AN13" s="39"/>
+      <c r="AO13" s="39"/>
+      <c r="AP13" s="39"/>
+      <c r="AQ13" s="42">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AR13" s="41"/>
-      <c r="AS13" s="41"/>
-      <c r="AT13" s="41"/>
-      <c r="AU13" s="45">
+      <c r="AR13" s="39"/>
+      <c r="AS13" s="39"/>
+      <c r="AT13" s="39"/>
+      <c r="AU13" s="42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV13" s="41"/>
-      <c r="AW13" s="41"/>
-      <c r="AX13" s="41"/>
-      <c r="AY13" s="47"/>
-      <c r="AZ13" s="41"/>
-      <c r="BA13" s="45">
+      <c r="AV13" s="39"/>
+      <c r="AW13" s="39"/>
+      <c r="AX13" s="39"/>
+      <c r="AY13" s="44"/>
+      <c r="AZ13" s="39"/>
+      <c r="BA13" s="42">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB13" s="41"/>
-      <c r="BC13" s="41"/>
-      <c r="BD13" s="41"/>
-      <c r="BE13" s="41"/>
-      <c r="BF13" s="45">
+      <c r="BB13" s="39"/>
+      <c r="BC13" s="39"/>
+      <c r="BD13" s="39"/>
+      <c r="BE13" s="39"/>
+      <c r="BF13" s="42">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BG13" s="41"/>
-      <c r="BH13" s="48">
+      <c r="BG13" s="39"/>
+      <c r="BH13" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI13" s="49">
+      <c r="BI13" s="46">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ13" s="37"/>
+      <c r="BJ13" s="36"/>
     </row>
     <row r="14" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="23">
@@ -2641,106 +2638,106 @@
         <v>10</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" s="36">
+        <v>47</v>
+      </c>
+      <c r="D14" s="42">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="E14" s="37"/>
-      <c r="F14" s="37"/>
-      <c r="G14" s="37"/>
-      <c r="H14" s="37"/>
-      <c r="I14" s="37"/>
-      <c r="J14" s="37"/>
-      <c r="K14" s="45">
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="39"/>
+      <c r="J14" s="39"/>
+      <c r="K14" s="42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L14" s="41"/>
-      <c r="M14" s="45">
+      <c r="L14" s="39"/>
+      <c r="M14" s="42">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N14" s="41"/>
-      <c r="O14" s="41"/>
-      <c r="P14" s="41"/>
-      <c r="Q14" s="41"/>
-      <c r="R14" s="45">
+      <c r="N14" s="39"/>
+      <c r="O14" s="39"/>
+      <c r="P14" s="39"/>
+      <c r="Q14" s="39"/>
+      <c r="R14" s="42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S14" s="41"/>
-      <c r="T14" s="45">
+      <c r="S14" s="39"/>
+      <c r="T14" s="42">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U14" s="50"/>
-      <c r="V14" s="41"/>
-      <c r="W14" s="41"/>
-      <c r="X14" s="41"/>
-      <c r="Y14" s="41"/>
-      <c r="Z14" s="41"/>
-      <c r="AA14" s="41"/>
-      <c r="AB14" s="41"/>
-      <c r="AC14" s="41"/>
-      <c r="AD14" s="41"/>
-      <c r="AE14" s="41"/>
-      <c r="AF14" s="41"/>
-      <c r="AG14" s="41"/>
-      <c r="AH14" s="41"/>
-      <c r="AI14" s="41"/>
-      <c r="AJ14" s="41"/>
-      <c r="AK14" s="45">
+      <c r="U14" s="47"/>
+      <c r="V14" s="39"/>
+      <c r="W14" s="39"/>
+      <c r="X14" s="39"/>
+      <c r="Y14" s="39"/>
+      <c r="Z14" s="39"/>
+      <c r="AA14" s="39"/>
+      <c r="AB14" s="39"/>
+      <c r="AC14" s="39"/>
+      <c r="AD14" s="39"/>
+      <c r="AE14" s="39"/>
+      <c r="AF14" s="39"/>
+      <c r="AG14" s="39"/>
+      <c r="AH14" s="39"/>
+      <c r="AI14" s="39"/>
+      <c r="AJ14" s="39"/>
+      <c r="AK14" s="42">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AL14" s="41"/>
-      <c r="AM14" s="41"/>
-      <c r="AN14" s="41"/>
-      <c r="AO14" s="41"/>
-      <c r="AP14" s="41"/>
-      <c r="AQ14" s="45">
+      <c r="AL14" s="39"/>
+      <c r="AM14" s="39"/>
+      <c r="AN14" s="39"/>
+      <c r="AO14" s="39"/>
+      <c r="AP14" s="39"/>
+      <c r="AQ14" s="42">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AR14" s="41"/>
-      <c r="AS14" s="41"/>
-      <c r="AT14" s="41"/>
-      <c r="AU14" s="45">
+      <c r="AR14" s="39"/>
+      <c r="AS14" s="39"/>
+      <c r="AT14" s="39"/>
+      <c r="AU14" s="42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV14" s="41"/>
-      <c r="AW14" s="41"/>
-      <c r="AX14" s="41"/>
-      <c r="AY14" s="47"/>
-      <c r="AZ14" s="41"/>
-      <c r="BA14" s="45">
+      <c r="AV14" s="39"/>
+      <c r="AW14" s="39"/>
+      <c r="AX14" s="39"/>
+      <c r="AY14" s="44"/>
+      <c r="AZ14" s="39"/>
+      <c r="BA14" s="42">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB14" s="41"/>
-      <c r="BC14" s="41"/>
-      <c r="BD14" s="41"/>
-      <c r="BE14" s="41"/>
-      <c r="BF14" s="45">
+      <c r="BB14" s="39"/>
+      <c r="BC14" s="39"/>
+      <c r="BD14" s="39"/>
+      <c r="BE14" s="39"/>
+      <c r="BF14" s="42">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BG14" s="41"/>
-      <c r="BH14" s="48">
+      <c r="BG14" s="39"/>
+      <c r="BH14" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI14" s="49">
+      <c r="BI14" s="46">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ14" s="37"/>
+      <c r="BJ14" s="36"/>
     </row>
     <row r="15" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="23">
@@ -2748,106 +2745,106 @@
         <v>11</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="D15" s="36">
+        <v>49</v>
+      </c>
+      <c r="D15" s="42">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="E15" s="37"/>
-      <c r="F15" s="37"/>
-      <c r="G15" s="37"/>
-      <c r="H15" s="37"/>
-      <c r="I15" s="37"/>
-      <c r="J15" s="37"/>
-      <c r="K15" s="45">
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L15" s="41"/>
-      <c r="M15" s="45">
+      <c r="L15" s="39"/>
+      <c r="M15" s="42">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N15" s="41"/>
-      <c r="O15" s="41"/>
-      <c r="P15" s="41"/>
-      <c r="Q15" s="41"/>
-      <c r="R15" s="45">
+      <c r="N15" s="39"/>
+      <c r="O15" s="39"/>
+      <c r="P15" s="39"/>
+      <c r="Q15" s="39"/>
+      <c r="R15" s="42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S15" s="41"/>
-      <c r="T15" s="45">
+      <c r="S15" s="39"/>
+      <c r="T15" s="42">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U15" s="50"/>
-      <c r="V15" s="41"/>
-      <c r="W15" s="41"/>
-      <c r="X15" s="41"/>
-      <c r="Y15" s="41"/>
-      <c r="Z15" s="41"/>
-      <c r="AA15" s="41"/>
-      <c r="AB15" s="41"/>
-      <c r="AC15" s="41"/>
-      <c r="AD15" s="41"/>
-      <c r="AE15" s="41"/>
-      <c r="AF15" s="41"/>
-      <c r="AG15" s="41"/>
-      <c r="AH15" s="41"/>
-      <c r="AI15" s="41"/>
-      <c r="AJ15" s="41"/>
-      <c r="AK15" s="45">
+      <c r="U15" s="47"/>
+      <c r="V15" s="39"/>
+      <c r="W15" s="39"/>
+      <c r="X15" s="39"/>
+      <c r="Y15" s="39"/>
+      <c r="Z15" s="39"/>
+      <c r="AA15" s="39"/>
+      <c r="AB15" s="39"/>
+      <c r="AC15" s="39"/>
+      <c r="AD15" s="39"/>
+      <c r="AE15" s="39"/>
+      <c r="AF15" s="39"/>
+      <c r="AG15" s="39"/>
+      <c r="AH15" s="39"/>
+      <c r="AI15" s="39"/>
+      <c r="AJ15" s="39"/>
+      <c r="AK15" s="42">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AL15" s="41"/>
-      <c r="AM15" s="41"/>
-      <c r="AN15" s="41"/>
-      <c r="AO15" s="41"/>
-      <c r="AP15" s="41"/>
-      <c r="AQ15" s="45">
+      <c r="AL15" s="39"/>
+      <c r="AM15" s="39"/>
+      <c r="AN15" s="39"/>
+      <c r="AO15" s="39"/>
+      <c r="AP15" s="39"/>
+      <c r="AQ15" s="42">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AR15" s="41"/>
-      <c r="AS15" s="41"/>
-      <c r="AT15" s="41"/>
-      <c r="AU15" s="45">
+      <c r="AR15" s="39"/>
+      <c r="AS15" s="39"/>
+      <c r="AT15" s="39"/>
+      <c r="AU15" s="42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV15" s="41"/>
-      <c r="AW15" s="41"/>
-      <c r="AX15" s="41"/>
-      <c r="AY15" s="47"/>
-      <c r="AZ15" s="41"/>
-      <c r="BA15" s="45">
+      <c r="AV15" s="39"/>
+      <c r="AW15" s="39"/>
+      <c r="AX15" s="39"/>
+      <c r="AY15" s="44"/>
+      <c r="AZ15" s="39"/>
+      <c r="BA15" s="42">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB15" s="41"/>
-      <c r="BC15" s="41"/>
-      <c r="BD15" s="41"/>
-      <c r="BE15" s="41"/>
-      <c r="BF15" s="45">
+      <c r="BB15" s="39"/>
+      <c r="BC15" s="39"/>
+      <c r="BD15" s="39"/>
+      <c r="BE15" s="39"/>
+      <c r="BF15" s="42">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BG15" s="41"/>
-      <c r="BH15" s="48">
+      <c r="BG15" s="39"/>
+      <c r="BH15" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI15" s="49">
+      <c r="BI15" s="46">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ15" s="37"/>
+      <c r="BJ15" s="36"/>
     </row>
     <row r="16" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="23">
@@ -2855,106 +2852,106 @@
         <v>12</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="D16" s="36">
+        <v>51</v>
+      </c>
+      <c r="D16" s="42">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="E16" s="37"/>
-      <c r="F16" s="37"/>
-      <c r="G16" s="37"/>
-      <c r="H16" s="37"/>
-      <c r="I16" s="37"/>
-      <c r="J16" s="37"/>
-      <c r="K16" s="45">
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="39"/>
+      <c r="K16" s="42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L16" s="41"/>
-      <c r="M16" s="45">
+      <c r="L16" s="39"/>
+      <c r="M16" s="42">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N16" s="41"/>
-      <c r="O16" s="41"/>
-      <c r="P16" s="41"/>
-      <c r="Q16" s="41"/>
-      <c r="R16" s="45">
+      <c r="N16" s="39"/>
+      <c r="O16" s="39"/>
+      <c r="P16" s="39"/>
+      <c r="Q16" s="39"/>
+      <c r="R16" s="42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S16" s="41"/>
-      <c r="T16" s="45">
+      <c r="S16" s="39"/>
+      <c r="T16" s="42">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U16" s="50"/>
-      <c r="V16" s="41"/>
-      <c r="W16" s="41"/>
-      <c r="X16" s="41"/>
-      <c r="Y16" s="41"/>
-      <c r="Z16" s="41"/>
-      <c r="AA16" s="41"/>
-      <c r="AB16" s="41"/>
-      <c r="AC16" s="41"/>
-      <c r="AD16" s="41"/>
-      <c r="AE16" s="41"/>
-      <c r="AF16" s="41"/>
-      <c r="AG16" s="41"/>
-      <c r="AH16" s="41"/>
-      <c r="AI16" s="41"/>
-      <c r="AJ16" s="41"/>
-      <c r="AK16" s="45">
+      <c r="U16" s="47"/>
+      <c r="V16" s="39"/>
+      <c r="W16" s="39"/>
+      <c r="X16" s="39"/>
+      <c r="Y16" s="39"/>
+      <c r="Z16" s="39"/>
+      <c r="AA16" s="39"/>
+      <c r="AB16" s="39"/>
+      <c r="AC16" s="39"/>
+      <c r="AD16" s="39"/>
+      <c r="AE16" s="39"/>
+      <c r="AF16" s="39"/>
+      <c r="AG16" s="39"/>
+      <c r="AH16" s="39"/>
+      <c r="AI16" s="39"/>
+      <c r="AJ16" s="39"/>
+      <c r="AK16" s="42">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AL16" s="41"/>
-      <c r="AM16" s="41"/>
-      <c r="AN16" s="41"/>
-      <c r="AO16" s="41"/>
-      <c r="AP16" s="41"/>
-      <c r="AQ16" s="45">
+      <c r="AL16" s="39"/>
+      <c r="AM16" s="39"/>
+      <c r="AN16" s="39"/>
+      <c r="AO16" s="39"/>
+      <c r="AP16" s="39"/>
+      <c r="AQ16" s="42">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AR16" s="41"/>
-      <c r="AS16" s="41"/>
-      <c r="AT16" s="41"/>
-      <c r="AU16" s="45">
+      <c r="AR16" s="39"/>
+      <c r="AS16" s="39"/>
+      <c r="AT16" s="39"/>
+      <c r="AU16" s="42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV16" s="41"/>
-      <c r="AW16" s="41"/>
-      <c r="AX16" s="41"/>
-      <c r="AY16" s="47"/>
-      <c r="AZ16" s="41"/>
-      <c r="BA16" s="45">
+      <c r="AV16" s="39"/>
+      <c r="AW16" s="39"/>
+      <c r="AX16" s="39"/>
+      <c r="AY16" s="44"/>
+      <c r="AZ16" s="39"/>
+      <c r="BA16" s="42">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB16" s="41"/>
-      <c r="BC16" s="41"/>
-      <c r="BD16" s="41"/>
-      <c r="BE16" s="41"/>
-      <c r="BF16" s="45">
+      <c r="BB16" s="39"/>
+      <c r="BC16" s="39"/>
+      <c r="BD16" s="39"/>
+      <c r="BE16" s="39"/>
+      <c r="BF16" s="42">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BG16" s="41"/>
-      <c r="BH16" s="48">
+      <c r="BG16" s="39"/>
+      <c r="BH16" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI16" s="49">
+      <c r="BI16" s="46">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ16" s="37"/>
+      <c r="BJ16" s="36"/>
     </row>
     <row r="17" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="23">
@@ -2962,106 +2959,106 @@
         <v>13</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="D17" s="36">
+        <v>53</v>
+      </c>
+      <c r="D17" s="42">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="E17" s="37"/>
-      <c r="F17" s="37"/>
-      <c r="G17" s="37"/>
-      <c r="H17" s="37"/>
-      <c r="I17" s="37"/>
-      <c r="J17" s="37"/>
-      <c r="K17" s="45">
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L17" s="41"/>
-      <c r="M17" s="45">
+      <c r="L17" s="39"/>
+      <c r="M17" s="42">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N17" s="41"/>
-      <c r="O17" s="41"/>
-      <c r="P17" s="41"/>
-      <c r="Q17" s="41"/>
-      <c r="R17" s="45">
+      <c r="N17" s="39"/>
+      <c r="O17" s="39"/>
+      <c r="P17" s="39"/>
+      <c r="Q17" s="39"/>
+      <c r="R17" s="42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S17" s="41"/>
-      <c r="T17" s="45">
+      <c r="S17" s="39"/>
+      <c r="T17" s="42">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U17" s="50"/>
-      <c r="V17" s="41"/>
-      <c r="W17" s="41"/>
-      <c r="X17" s="41"/>
-      <c r="Y17" s="41"/>
-      <c r="Z17" s="41"/>
-      <c r="AA17" s="41"/>
-      <c r="AB17" s="41"/>
-      <c r="AC17" s="41"/>
-      <c r="AD17" s="41"/>
-      <c r="AE17" s="41"/>
-      <c r="AF17" s="41"/>
-      <c r="AG17" s="41"/>
-      <c r="AH17" s="41"/>
-      <c r="AI17" s="41"/>
-      <c r="AJ17" s="41"/>
-      <c r="AK17" s="45">
+      <c r="U17" s="47"/>
+      <c r="V17" s="39"/>
+      <c r="W17" s="39"/>
+      <c r="X17" s="39"/>
+      <c r="Y17" s="39"/>
+      <c r="Z17" s="39"/>
+      <c r="AA17" s="39"/>
+      <c r="AB17" s="39"/>
+      <c r="AC17" s="39"/>
+      <c r="AD17" s="39"/>
+      <c r="AE17" s="39"/>
+      <c r="AF17" s="39"/>
+      <c r="AG17" s="39"/>
+      <c r="AH17" s="39"/>
+      <c r="AI17" s="39"/>
+      <c r="AJ17" s="39"/>
+      <c r="AK17" s="42">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AL17" s="41"/>
-      <c r="AM17" s="41"/>
-      <c r="AN17" s="41"/>
-      <c r="AO17" s="41"/>
-      <c r="AP17" s="41"/>
-      <c r="AQ17" s="45">
+      <c r="AL17" s="39"/>
+      <c r="AM17" s="39"/>
+      <c r="AN17" s="39"/>
+      <c r="AO17" s="39"/>
+      <c r="AP17" s="39"/>
+      <c r="AQ17" s="42">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AR17" s="41"/>
-      <c r="AS17" s="41"/>
-      <c r="AT17" s="41"/>
-      <c r="AU17" s="45">
+      <c r="AR17" s="39"/>
+      <c r="AS17" s="39"/>
+      <c r="AT17" s="39"/>
+      <c r="AU17" s="42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV17" s="41"/>
-      <c r="AW17" s="41"/>
-      <c r="AX17" s="41"/>
-      <c r="AY17" s="47"/>
-      <c r="AZ17" s="41"/>
-      <c r="BA17" s="45">
+      <c r="AV17" s="39"/>
+      <c r="AW17" s="39"/>
+      <c r="AX17" s="39"/>
+      <c r="AY17" s="44"/>
+      <c r="AZ17" s="39"/>
+      <c r="BA17" s="42">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB17" s="50"/>
-      <c r="BC17" s="50"/>
-      <c r="BD17" s="50"/>
-      <c r="BE17" s="50"/>
-      <c r="BF17" s="45">
+      <c r="BB17" s="47"/>
+      <c r="BC17" s="47"/>
+      <c r="BD17" s="47"/>
+      <c r="BE17" s="47"/>
+      <c r="BF17" s="42">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BG17" s="50"/>
-      <c r="BH17" s="48">
+      <c r="BG17" s="47"/>
+      <c r="BH17" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI17" s="49">
+      <c r="BI17" s="46">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ17" s="37"/>
+      <c r="BJ17" s="36"/>
     </row>
     <row r="18" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="23">
@@ -3069,106 +3066,106 @@
         <v>14</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="D18" s="36">
+        <v>55</v>
+      </c>
+      <c r="D18" s="42">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="37"/>
-      <c r="H18" s="37"/>
-      <c r="I18" s="37"/>
-      <c r="J18" s="37"/>
-      <c r="K18" s="45">
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="39"/>
+      <c r="K18" s="42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L18" s="41"/>
-      <c r="M18" s="45">
+      <c r="L18" s="39"/>
+      <c r="M18" s="42">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N18" s="51"/>
-      <c r="O18" s="51"/>
-      <c r="P18" s="41"/>
-      <c r="Q18" s="41"/>
-      <c r="R18" s="45">
+      <c r="N18" s="48"/>
+      <c r="O18" s="48"/>
+      <c r="P18" s="39"/>
+      <c r="Q18" s="39"/>
+      <c r="R18" s="42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S18" s="41"/>
-      <c r="T18" s="45">
+      <c r="S18" s="39"/>
+      <c r="T18" s="42">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U18" s="50"/>
-      <c r="V18" s="41"/>
-      <c r="W18" s="41"/>
-      <c r="X18" s="41"/>
-      <c r="Y18" s="41"/>
-      <c r="Z18" s="41"/>
-      <c r="AA18" s="41"/>
-      <c r="AB18" s="41"/>
-      <c r="AC18" s="41"/>
-      <c r="AD18" s="41"/>
-      <c r="AE18" s="41"/>
-      <c r="AF18" s="41"/>
-      <c r="AG18" s="41"/>
-      <c r="AH18" s="41"/>
-      <c r="AI18" s="41"/>
-      <c r="AJ18" s="41"/>
-      <c r="AK18" s="45">
+      <c r="U18" s="47"/>
+      <c r="V18" s="39"/>
+      <c r="W18" s="39"/>
+      <c r="X18" s="39"/>
+      <c r="Y18" s="39"/>
+      <c r="Z18" s="39"/>
+      <c r="AA18" s="39"/>
+      <c r="AB18" s="39"/>
+      <c r="AC18" s="39"/>
+      <c r="AD18" s="39"/>
+      <c r="AE18" s="39"/>
+      <c r="AF18" s="39"/>
+      <c r="AG18" s="39"/>
+      <c r="AH18" s="39"/>
+      <c r="AI18" s="39"/>
+      <c r="AJ18" s="39"/>
+      <c r="AK18" s="42">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AL18" s="41"/>
-      <c r="AM18" s="47"/>
-      <c r="AN18" s="41"/>
-      <c r="AO18" s="41"/>
-      <c r="AP18" s="41"/>
-      <c r="AQ18" s="45">
+      <c r="AL18" s="39"/>
+      <c r="AM18" s="44"/>
+      <c r="AN18" s="39"/>
+      <c r="AO18" s="39"/>
+      <c r="AP18" s="39"/>
+      <c r="AQ18" s="42">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AR18" s="41"/>
-      <c r="AS18" s="41"/>
-      <c r="AT18" s="41"/>
-      <c r="AU18" s="45">
+      <c r="AR18" s="39"/>
+      <c r="AS18" s="39"/>
+      <c r="AT18" s="39"/>
+      <c r="AU18" s="42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV18" s="41"/>
-      <c r="AW18" s="41"/>
-      <c r="AX18" s="41"/>
-      <c r="AY18" s="47"/>
-      <c r="AZ18" s="41"/>
-      <c r="BA18" s="45">
+      <c r="AV18" s="39"/>
+      <c r="AW18" s="39"/>
+      <c r="AX18" s="39"/>
+      <c r="AY18" s="44"/>
+      <c r="AZ18" s="39"/>
+      <c r="BA18" s="42">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB18" s="50"/>
-      <c r="BC18" s="50"/>
-      <c r="BD18" s="50"/>
-      <c r="BE18" s="50"/>
-      <c r="BF18" s="45">
+      <c r="BB18" s="47"/>
+      <c r="BC18" s="47"/>
+      <c r="BD18" s="47"/>
+      <c r="BE18" s="47"/>
+      <c r="BF18" s="42">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BG18" s="50"/>
-      <c r="BH18" s="48">
+      <c r="BG18" s="47"/>
+      <c r="BH18" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI18" s="49">
+      <c r="BI18" s="46">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ18" s="37"/>
+      <c r="BJ18" s="36"/>
     </row>
     <row r="19" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="23">
@@ -3176,106 +3173,106 @@
         <v>15</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" s="36">
+        <v>43</v>
+      </c>
+      <c r="D19" s="42">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="E19" s="37"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="37"/>
-      <c r="H19" s="37"/>
-      <c r="I19" s="41"/>
-      <c r="J19" s="37"/>
-      <c r="K19" s="45">
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="39"/>
+      <c r="K19" s="42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L19" s="41"/>
-      <c r="M19" s="45">
+      <c r="L19" s="39"/>
+      <c r="M19" s="42">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N19" s="41"/>
-      <c r="O19" s="41"/>
-      <c r="P19" s="41"/>
-      <c r="Q19" s="41"/>
-      <c r="R19" s="45">
+      <c r="N19" s="39"/>
+      <c r="O19" s="39"/>
+      <c r="P19" s="39"/>
+      <c r="Q19" s="39"/>
+      <c r="R19" s="42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S19" s="41"/>
-      <c r="T19" s="45">
+      <c r="S19" s="39"/>
+      <c r="T19" s="42">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U19" s="50"/>
-      <c r="V19" s="41"/>
-      <c r="W19" s="41"/>
-      <c r="X19" s="41"/>
-      <c r="Y19" s="41"/>
-      <c r="Z19" s="41"/>
-      <c r="AA19" s="41"/>
-      <c r="AB19" s="41"/>
-      <c r="AC19" s="41"/>
-      <c r="AD19" s="41"/>
-      <c r="AE19" s="41"/>
-      <c r="AF19" s="41"/>
-      <c r="AG19" s="41"/>
-      <c r="AH19" s="41"/>
-      <c r="AI19" s="41"/>
-      <c r="AJ19" s="41"/>
-      <c r="AK19" s="45">
+      <c r="U19" s="47"/>
+      <c r="V19" s="39"/>
+      <c r="W19" s="39"/>
+      <c r="X19" s="39"/>
+      <c r="Y19" s="39"/>
+      <c r="Z19" s="39"/>
+      <c r="AA19" s="39"/>
+      <c r="AB19" s="39"/>
+      <c r="AC19" s="39"/>
+      <c r="AD19" s="39"/>
+      <c r="AE19" s="39"/>
+      <c r="AF19" s="39"/>
+      <c r="AG19" s="39"/>
+      <c r="AH19" s="39"/>
+      <c r="AI19" s="39"/>
+      <c r="AJ19" s="39"/>
+      <c r="AK19" s="42">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AL19" s="41"/>
-      <c r="AM19" s="41"/>
-      <c r="AN19" s="41"/>
-      <c r="AO19" s="41"/>
-      <c r="AP19" s="41"/>
-      <c r="AQ19" s="45">
+      <c r="AL19" s="39"/>
+      <c r="AM19" s="39"/>
+      <c r="AN19" s="39"/>
+      <c r="AO19" s="39"/>
+      <c r="AP19" s="39"/>
+      <c r="AQ19" s="42">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AR19" s="41"/>
-      <c r="AS19" s="41"/>
-      <c r="AT19" s="41"/>
-      <c r="AU19" s="45">
+      <c r="AR19" s="39"/>
+      <c r="AS19" s="39"/>
+      <c r="AT19" s="39"/>
+      <c r="AU19" s="42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV19" s="41"/>
-      <c r="AW19" s="41"/>
-      <c r="AX19" s="41"/>
-      <c r="AY19" s="41"/>
-      <c r="AZ19" s="41"/>
-      <c r="BA19" s="45">
+      <c r="AV19" s="39"/>
+      <c r="AW19" s="39"/>
+      <c r="AX19" s="39"/>
+      <c r="AY19" s="39"/>
+      <c r="AZ19" s="39"/>
+      <c r="BA19" s="42">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB19" s="50"/>
-      <c r="BC19" s="50"/>
-      <c r="BD19" s="50"/>
-      <c r="BE19" s="50"/>
-      <c r="BF19" s="45">
+      <c r="BB19" s="47"/>
+      <c r="BC19" s="47"/>
+      <c r="BD19" s="47"/>
+      <c r="BE19" s="47"/>
+      <c r="BF19" s="42">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BG19" s="50"/>
-      <c r="BH19" s="48">
+      <c r="BG19" s="47"/>
+      <c r="BH19" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI19" s="49">
+      <c r="BI19" s="46">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ19" s="37"/>
+      <c r="BJ19" s="36"/>
     </row>
     <row r="20" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="23">
@@ -3283,106 +3280,106 @@
         <v>16</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="D20" s="36">
+        <v>45</v>
+      </c>
+      <c r="D20" s="42">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="E20" s="37"/>
-      <c r="F20" s="37"/>
-      <c r="G20" s="37"/>
-      <c r="H20" s="37"/>
-      <c r="I20" s="37"/>
-      <c r="J20" s="37"/>
-      <c r="K20" s="45">
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="39"/>
+      <c r="K20" s="42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L20" s="41"/>
-      <c r="M20" s="45">
+      <c r="L20" s="39"/>
+      <c r="M20" s="42">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N20" s="41"/>
-      <c r="O20" s="41"/>
-      <c r="P20" s="41"/>
-      <c r="Q20" s="41"/>
-      <c r="R20" s="45">
+      <c r="N20" s="39"/>
+      <c r="O20" s="39"/>
+      <c r="P20" s="39"/>
+      <c r="Q20" s="39"/>
+      <c r="R20" s="42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S20" s="41"/>
-      <c r="T20" s="45">
+      <c r="S20" s="39"/>
+      <c r="T20" s="42">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U20" s="50"/>
-      <c r="V20" s="41"/>
-      <c r="W20" s="41"/>
-      <c r="X20" s="41"/>
-      <c r="Y20" s="41"/>
-      <c r="Z20" s="41"/>
-      <c r="AA20" s="41"/>
-      <c r="AB20" s="41"/>
-      <c r="AC20" s="41"/>
-      <c r="AD20" s="41"/>
-      <c r="AE20" s="41"/>
-      <c r="AF20" s="41"/>
-      <c r="AG20" s="41"/>
-      <c r="AH20" s="41"/>
-      <c r="AI20" s="41"/>
-      <c r="AJ20" s="41"/>
-      <c r="AK20" s="45">
+      <c r="U20" s="47"/>
+      <c r="V20" s="39"/>
+      <c r="W20" s="39"/>
+      <c r="X20" s="39"/>
+      <c r="Y20" s="39"/>
+      <c r="Z20" s="39"/>
+      <c r="AA20" s="39"/>
+      <c r="AB20" s="39"/>
+      <c r="AC20" s="39"/>
+      <c r="AD20" s="39"/>
+      <c r="AE20" s="39"/>
+      <c r="AF20" s="39"/>
+      <c r="AG20" s="39"/>
+      <c r="AH20" s="39"/>
+      <c r="AI20" s="39"/>
+      <c r="AJ20" s="39"/>
+      <c r="AK20" s="42">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AL20" s="41"/>
-      <c r="AM20" s="41"/>
-      <c r="AN20" s="41"/>
-      <c r="AO20" s="41"/>
-      <c r="AP20" s="47"/>
-      <c r="AQ20" s="45">
+      <c r="AL20" s="39"/>
+      <c r="AM20" s="39"/>
+      <c r="AN20" s="39"/>
+      <c r="AO20" s="39"/>
+      <c r="AP20" s="44"/>
+      <c r="AQ20" s="42">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AR20" s="41"/>
-      <c r="AS20" s="41"/>
-      <c r="AT20" s="41"/>
-      <c r="AU20" s="45">
+      <c r="AR20" s="39"/>
+      <c r="AS20" s="39"/>
+      <c r="AT20" s="39"/>
+      <c r="AU20" s="42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV20" s="41"/>
-      <c r="AW20" s="41"/>
-      <c r="AX20" s="41"/>
-      <c r="AY20" s="41"/>
-      <c r="AZ20" s="41"/>
-      <c r="BA20" s="45">
+      <c r="AV20" s="39"/>
+      <c r="AW20" s="39"/>
+      <c r="AX20" s="39"/>
+      <c r="AY20" s="39"/>
+      <c r="AZ20" s="39"/>
+      <c r="BA20" s="42">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB20" s="50"/>
-      <c r="BC20" s="50"/>
-      <c r="BD20" s="50"/>
-      <c r="BE20" s="50"/>
-      <c r="BF20" s="45">
+      <c r="BB20" s="47"/>
+      <c r="BC20" s="47"/>
+      <c r="BD20" s="47"/>
+      <c r="BE20" s="47"/>
+      <c r="BF20" s="42">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BG20" s="50"/>
-      <c r="BH20" s="48">
+      <c r="BG20" s="47"/>
+      <c r="BH20" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI20" s="49">
+      <c r="BI20" s="46">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ20" s="37"/>
+      <c r="BJ20" s="36"/>
     </row>
     <row r="21" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="23">
@@ -3390,106 +3387,106 @@
         <v>17</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="D21" s="36">
+        <v>47</v>
+      </c>
+      <c r="D21" s="42">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="E21" s="37"/>
-      <c r="F21" s="37"/>
-      <c r="G21" s="37"/>
-      <c r="H21" s="37"/>
-      <c r="I21" s="37"/>
-      <c r="J21" s="37"/>
-      <c r="K21" s="45">
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="39"/>
+      <c r="K21" s="42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L21" s="41"/>
-      <c r="M21" s="45">
+      <c r="L21" s="39"/>
+      <c r="M21" s="42">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N21" s="41"/>
-      <c r="O21" s="41"/>
-      <c r="P21" s="41"/>
-      <c r="Q21" s="41"/>
-      <c r="R21" s="45">
+      <c r="N21" s="39"/>
+      <c r="O21" s="39"/>
+      <c r="P21" s="39"/>
+      <c r="Q21" s="39"/>
+      <c r="R21" s="42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S21" s="41"/>
-      <c r="T21" s="45">
+      <c r="S21" s="39"/>
+      <c r="T21" s="42">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U21" s="50"/>
-      <c r="V21" s="41"/>
-      <c r="W21" s="41"/>
-      <c r="X21" s="41"/>
-      <c r="Y21" s="41"/>
-      <c r="Z21" s="41"/>
-      <c r="AA21" s="41"/>
-      <c r="AB21" s="41"/>
-      <c r="AC21" s="41"/>
-      <c r="AD21" s="41"/>
-      <c r="AE21" s="41"/>
-      <c r="AF21" s="41"/>
-      <c r="AG21" s="41"/>
-      <c r="AH21" s="41"/>
-      <c r="AI21" s="41"/>
-      <c r="AJ21" s="41"/>
-      <c r="AK21" s="45">
+      <c r="U21" s="47"/>
+      <c r="V21" s="39"/>
+      <c r="W21" s="39"/>
+      <c r="X21" s="39"/>
+      <c r="Y21" s="39"/>
+      <c r="Z21" s="39"/>
+      <c r="AA21" s="39"/>
+      <c r="AB21" s="39"/>
+      <c r="AC21" s="39"/>
+      <c r="AD21" s="39"/>
+      <c r="AE21" s="39"/>
+      <c r="AF21" s="39"/>
+      <c r="AG21" s="39"/>
+      <c r="AH21" s="39"/>
+      <c r="AI21" s="39"/>
+      <c r="AJ21" s="39"/>
+      <c r="AK21" s="42">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AL21" s="41"/>
-      <c r="AM21" s="47"/>
-      <c r="AN21" s="41"/>
-      <c r="AO21" s="41"/>
-      <c r="AP21" s="47"/>
-      <c r="AQ21" s="45">
+      <c r="AL21" s="39"/>
+      <c r="AM21" s="44"/>
+      <c r="AN21" s="39"/>
+      <c r="AO21" s="39"/>
+      <c r="AP21" s="44"/>
+      <c r="AQ21" s="42">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AR21" s="41"/>
-      <c r="AS21" s="41"/>
-      <c r="AT21" s="41"/>
-      <c r="AU21" s="45">
+      <c r="AR21" s="39"/>
+      <c r="AS21" s="39"/>
+      <c r="AT21" s="39"/>
+      <c r="AU21" s="42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV21" s="41"/>
-      <c r="AW21" s="41"/>
-      <c r="AX21" s="41"/>
-      <c r="AY21" s="47"/>
-      <c r="AZ21" s="41"/>
-      <c r="BA21" s="45">
+      <c r="AV21" s="39"/>
+      <c r="AW21" s="39"/>
+      <c r="AX21" s="39"/>
+      <c r="AY21" s="44"/>
+      <c r="AZ21" s="39"/>
+      <c r="BA21" s="42">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB21" s="50"/>
-      <c r="BC21" s="50"/>
-      <c r="BD21" s="50"/>
-      <c r="BE21" s="50"/>
-      <c r="BF21" s="45">
+      <c r="BB21" s="47"/>
+      <c r="BC21" s="47"/>
+      <c r="BD21" s="47"/>
+      <c r="BE21" s="47"/>
+      <c r="BF21" s="42">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BG21" s="50"/>
-      <c r="BH21" s="48">
+      <c r="BG21" s="47"/>
+      <c r="BH21" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI21" s="49">
+      <c r="BI21" s="46">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ21" s="37"/>
+      <c r="BJ21" s="36"/>
     </row>
     <row r="22" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="23">
@@ -3497,106 +3494,106 @@
         <v>18</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="D22" s="36">
+        <v>49</v>
+      </c>
+      <c r="D22" s="42">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="E22" s="37"/>
-      <c r="F22" s="37"/>
-      <c r="G22" s="37"/>
-      <c r="H22" s="37"/>
-      <c r="I22" s="37"/>
-      <c r="J22" s="37"/>
-      <c r="K22" s="45">
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="39"/>
+      <c r="K22" s="42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L22" s="41"/>
-      <c r="M22" s="45">
+      <c r="L22" s="39"/>
+      <c r="M22" s="42">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N22" s="41"/>
-      <c r="O22" s="41"/>
-      <c r="P22" s="41"/>
-      <c r="Q22" s="41"/>
-      <c r="R22" s="45">
+      <c r="N22" s="39"/>
+      <c r="O22" s="39"/>
+      <c r="P22" s="39"/>
+      <c r="Q22" s="39"/>
+      <c r="R22" s="42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S22" s="41"/>
-      <c r="T22" s="45">
+      <c r="S22" s="39"/>
+      <c r="T22" s="42">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U22" s="50"/>
-      <c r="V22" s="41"/>
-      <c r="W22" s="41"/>
-      <c r="X22" s="41"/>
-      <c r="Y22" s="41"/>
-      <c r="Z22" s="41"/>
-      <c r="AA22" s="41"/>
-      <c r="AB22" s="41"/>
-      <c r="AC22" s="41"/>
-      <c r="AD22" s="41"/>
-      <c r="AE22" s="41"/>
-      <c r="AF22" s="41"/>
-      <c r="AG22" s="41"/>
-      <c r="AH22" s="41"/>
-      <c r="AI22" s="41"/>
-      <c r="AJ22" s="41"/>
-      <c r="AK22" s="45">
+      <c r="U22" s="47"/>
+      <c r="V22" s="39"/>
+      <c r="W22" s="39"/>
+      <c r="X22" s="39"/>
+      <c r="Y22" s="39"/>
+      <c r="Z22" s="39"/>
+      <c r="AA22" s="39"/>
+      <c r="AB22" s="39"/>
+      <c r="AC22" s="39"/>
+      <c r="AD22" s="39"/>
+      <c r="AE22" s="39"/>
+      <c r="AF22" s="39"/>
+      <c r="AG22" s="39"/>
+      <c r="AH22" s="39"/>
+      <c r="AI22" s="39"/>
+      <c r="AJ22" s="39"/>
+      <c r="AK22" s="42">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AL22" s="41"/>
-      <c r="AM22" s="41"/>
-      <c r="AN22" s="47"/>
-      <c r="AO22" s="41"/>
-      <c r="AP22" s="47"/>
-      <c r="AQ22" s="45">
+      <c r="AL22" s="39"/>
+      <c r="AM22" s="39"/>
+      <c r="AN22" s="44"/>
+      <c r="AO22" s="39"/>
+      <c r="AP22" s="44"/>
+      <c r="AQ22" s="42">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AR22" s="41"/>
-      <c r="AS22" s="41"/>
-      <c r="AT22" s="41"/>
-      <c r="AU22" s="45">
+      <c r="AR22" s="39"/>
+      <c r="AS22" s="39"/>
+      <c r="AT22" s="39"/>
+      <c r="AU22" s="42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV22" s="41"/>
-      <c r="AW22" s="41"/>
-      <c r="AX22" s="41"/>
-      <c r="AY22" s="47"/>
-      <c r="AZ22" s="52"/>
-      <c r="BA22" s="45">
+      <c r="AV22" s="39"/>
+      <c r="AW22" s="39"/>
+      <c r="AX22" s="39"/>
+      <c r="AY22" s="44"/>
+      <c r="AZ22" s="49"/>
+      <c r="BA22" s="42">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB22" s="47"/>
-      <c r="BC22" s="47"/>
-      <c r="BD22" s="47"/>
-      <c r="BE22" s="47"/>
-      <c r="BF22" s="45">
+      <c r="BB22" s="44"/>
+      <c r="BC22" s="44"/>
+      <c r="BD22" s="44"/>
+      <c r="BE22" s="44"/>
+      <c r="BF22" s="42">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BG22" s="47"/>
-      <c r="BH22" s="48">
+      <c r="BG22" s="44"/>
+      <c r="BH22" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI22" s="49">
+      <c r="BI22" s="46">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ22" s="42"/>
+      <c r="BJ22" s="40"/>
     </row>
     <row r="23" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="23">
@@ -3604,106 +3601,106 @@
         <v>19</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="D23" s="36">
+        <v>51</v>
+      </c>
+      <c r="D23" s="42">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="E23" s="37"/>
-      <c r="F23" s="37"/>
-      <c r="G23" s="37"/>
-      <c r="H23" s="37"/>
-      <c r="I23" s="37"/>
-      <c r="J23" s="37"/>
-      <c r="K23" s="45">
+      <c r="E23" s="39"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="39"/>
+      <c r="K23" s="42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L23" s="41"/>
-      <c r="M23" s="45">
+      <c r="L23" s="39"/>
+      <c r="M23" s="42">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N23" s="41"/>
-      <c r="O23" s="41"/>
-      <c r="P23" s="41"/>
-      <c r="Q23" s="41"/>
-      <c r="R23" s="45">
+      <c r="N23" s="39"/>
+      <c r="O23" s="39"/>
+      <c r="P23" s="39"/>
+      <c r="Q23" s="39"/>
+      <c r="R23" s="42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S23" s="41"/>
-      <c r="T23" s="45">
+      <c r="S23" s="39"/>
+      <c r="T23" s="42">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U23" s="50"/>
-      <c r="V23" s="41"/>
-      <c r="W23" s="41"/>
-      <c r="X23" s="41"/>
-      <c r="Y23" s="41"/>
-      <c r="Z23" s="41"/>
-      <c r="AA23" s="41"/>
-      <c r="AB23" s="41"/>
-      <c r="AC23" s="41"/>
-      <c r="AD23" s="41"/>
-      <c r="AE23" s="41"/>
-      <c r="AF23" s="41"/>
-      <c r="AG23" s="41"/>
-      <c r="AH23" s="41"/>
-      <c r="AI23" s="41"/>
-      <c r="AJ23" s="41"/>
-      <c r="AK23" s="45">
+      <c r="U23" s="47"/>
+      <c r="V23" s="39"/>
+      <c r="W23" s="39"/>
+      <c r="X23" s="39"/>
+      <c r="Y23" s="39"/>
+      <c r="Z23" s="39"/>
+      <c r="AA23" s="39"/>
+      <c r="AB23" s="39"/>
+      <c r="AC23" s="39"/>
+      <c r="AD23" s="39"/>
+      <c r="AE23" s="39"/>
+      <c r="AF23" s="39"/>
+      <c r="AG23" s="39"/>
+      <c r="AH23" s="39"/>
+      <c r="AI23" s="39"/>
+      <c r="AJ23" s="39"/>
+      <c r="AK23" s="42">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AL23" s="41"/>
-      <c r="AM23" s="41"/>
-      <c r="AN23" s="41"/>
-      <c r="AO23" s="47"/>
-      <c r="AP23" s="41"/>
-      <c r="AQ23" s="45">
+      <c r="AL23" s="39"/>
+      <c r="AM23" s="39"/>
+      <c r="AN23" s="39"/>
+      <c r="AO23" s="44"/>
+      <c r="AP23" s="39"/>
+      <c r="AQ23" s="42">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AR23" s="41"/>
-      <c r="AS23" s="41"/>
-      <c r="AT23" s="41"/>
-      <c r="AU23" s="45">
+      <c r="AR23" s="39"/>
+      <c r="AS23" s="39"/>
+      <c r="AT23" s="39"/>
+      <c r="AU23" s="42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV23" s="41"/>
-      <c r="AW23" s="41"/>
-      <c r="AX23" s="41"/>
-      <c r="AY23" s="47"/>
-      <c r="AZ23" s="47"/>
-      <c r="BA23" s="45">
+      <c r="AV23" s="39"/>
+      <c r="AW23" s="39"/>
+      <c r="AX23" s="39"/>
+      <c r="AY23" s="44"/>
+      <c r="AZ23" s="44"/>
+      <c r="BA23" s="42">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB23" s="41"/>
-      <c r="BC23" s="41"/>
-      <c r="BD23" s="41"/>
-      <c r="BE23" s="41"/>
-      <c r="BF23" s="45">
+      <c r="BB23" s="39"/>
+      <c r="BC23" s="39"/>
+      <c r="BD23" s="39"/>
+      <c r="BE23" s="39"/>
+      <c r="BF23" s="42">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BG23" s="41"/>
-      <c r="BH23" s="48">
+      <c r="BG23" s="39"/>
+      <c r="BH23" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI23" s="49">
+      <c r="BI23" s="46">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ23" s="43"/>
+      <c r="BJ23" s="41"/>
     </row>
     <row r="24" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="23">
@@ -3711,106 +3708,106 @@
         <v>20</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="D24" s="36">
+        <v>53</v>
+      </c>
+      <c r="D24" s="42">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="E24" s="37"/>
-      <c r="F24" s="37"/>
-      <c r="G24" s="37"/>
-      <c r="H24" s="37"/>
-      <c r="I24" s="37"/>
-      <c r="J24" s="37"/>
-      <c r="K24" s="45">
+      <c r="E24" s="39"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="39"/>
+      <c r="K24" s="42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L24" s="41"/>
-      <c r="M24" s="45">
+      <c r="L24" s="39"/>
+      <c r="M24" s="42">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N24" s="41"/>
-      <c r="O24" s="41"/>
-      <c r="P24" s="41"/>
-      <c r="Q24" s="41"/>
-      <c r="R24" s="45">
+      <c r="N24" s="39"/>
+      <c r="O24" s="39"/>
+      <c r="P24" s="39"/>
+      <c r="Q24" s="39"/>
+      <c r="R24" s="42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S24" s="41"/>
-      <c r="T24" s="45">
+      <c r="S24" s="39"/>
+      <c r="T24" s="42">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U24" s="50"/>
-      <c r="V24" s="41"/>
-      <c r="W24" s="41"/>
-      <c r="X24" s="41"/>
-      <c r="Y24" s="41"/>
-      <c r="Z24" s="41"/>
-      <c r="AA24" s="41"/>
-      <c r="AB24" s="41"/>
-      <c r="AC24" s="41"/>
-      <c r="AD24" s="41"/>
-      <c r="AE24" s="41"/>
-      <c r="AF24" s="41"/>
-      <c r="AG24" s="41"/>
-      <c r="AH24" s="41"/>
-      <c r="AI24" s="41"/>
-      <c r="AJ24" s="41"/>
-      <c r="AK24" s="45">
+      <c r="U24" s="47"/>
+      <c r="V24" s="39"/>
+      <c r="W24" s="39"/>
+      <c r="X24" s="39"/>
+      <c r="Y24" s="39"/>
+      <c r="Z24" s="39"/>
+      <c r="AA24" s="39"/>
+      <c r="AB24" s="39"/>
+      <c r="AC24" s="39"/>
+      <c r="AD24" s="39"/>
+      <c r="AE24" s="39"/>
+      <c r="AF24" s="39"/>
+      <c r="AG24" s="39"/>
+      <c r="AH24" s="39"/>
+      <c r="AI24" s="39"/>
+      <c r="AJ24" s="39"/>
+      <c r="AK24" s="42">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AL24" s="41"/>
-      <c r="AM24" s="41"/>
-      <c r="AN24" s="41"/>
-      <c r="AO24" s="41"/>
-      <c r="AP24" s="47"/>
-      <c r="AQ24" s="45">
+      <c r="AL24" s="39"/>
+      <c r="AM24" s="39"/>
+      <c r="AN24" s="39"/>
+      <c r="AO24" s="39"/>
+      <c r="AP24" s="44"/>
+      <c r="AQ24" s="42">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AR24" s="41"/>
-      <c r="AS24" s="41"/>
-      <c r="AT24" s="41"/>
-      <c r="AU24" s="45">
+      <c r="AR24" s="39"/>
+      <c r="AS24" s="39"/>
+      <c r="AT24" s="39"/>
+      <c r="AU24" s="42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV24" s="41"/>
-      <c r="AW24" s="41"/>
-      <c r="AX24" s="41"/>
-      <c r="AY24" s="47"/>
-      <c r="AZ24" s="41"/>
-      <c r="BA24" s="45">
+      <c r="AV24" s="39"/>
+      <c r="AW24" s="39"/>
+      <c r="AX24" s="39"/>
+      <c r="AY24" s="44"/>
+      <c r="AZ24" s="39"/>
+      <c r="BA24" s="42">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB24" s="41"/>
-      <c r="BC24" s="41"/>
-      <c r="BD24" s="41"/>
-      <c r="BE24" s="41"/>
-      <c r="BF24" s="45">
+      <c r="BB24" s="39"/>
+      <c r="BC24" s="39"/>
+      <c r="BD24" s="39"/>
+      <c r="BE24" s="39"/>
+      <c r="BF24" s="42">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BG24" s="41"/>
-      <c r="BH24" s="48">
+      <c r="BG24" s="39"/>
+      <c r="BH24" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI24" s="49">
+      <c r="BI24" s="46">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ24" s="43"/>
+      <c r="BJ24" s="41"/>
     </row>
     <row r="25" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="23">
@@ -3818,106 +3815,106 @@
         <v>21</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="D25" s="36">
+        <v>55</v>
+      </c>
+      <c r="D25" s="42">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="E25" s="44"/>
-      <c r="F25" s="37"/>
-      <c r="G25" s="37"/>
-      <c r="H25" s="44"/>
-      <c r="I25" s="37"/>
-      <c r="J25" s="41"/>
-      <c r="K25" s="45">
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="39"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="39"/>
+      <c r="K25" s="42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L25" s="41"/>
-      <c r="M25" s="45">
+      <c r="L25" s="39"/>
+      <c r="M25" s="42">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N25" s="41"/>
-      <c r="O25" s="41"/>
-      <c r="P25" s="41"/>
-      <c r="Q25" s="41"/>
-      <c r="R25" s="45">
+      <c r="N25" s="39"/>
+      <c r="O25" s="39"/>
+      <c r="P25" s="39"/>
+      <c r="Q25" s="39"/>
+      <c r="R25" s="42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S25" s="41"/>
-      <c r="T25" s="45">
+      <c r="S25" s="39"/>
+      <c r="T25" s="42">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U25" s="50"/>
-      <c r="V25" s="41"/>
-      <c r="W25" s="41"/>
-      <c r="X25" s="41"/>
-      <c r="Y25" s="41"/>
-      <c r="Z25" s="41"/>
-      <c r="AA25" s="41"/>
-      <c r="AB25" s="41"/>
-      <c r="AC25" s="41"/>
-      <c r="AD25" s="41"/>
-      <c r="AE25" s="41"/>
-      <c r="AF25" s="41"/>
-      <c r="AG25" s="41"/>
-      <c r="AH25" s="41"/>
-      <c r="AI25" s="41"/>
-      <c r="AJ25" s="41"/>
-      <c r="AK25" s="45">
+      <c r="U25" s="47"/>
+      <c r="V25" s="39"/>
+      <c r="W25" s="39"/>
+      <c r="X25" s="39"/>
+      <c r="Y25" s="39"/>
+      <c r="Z25" s="39"/>
+      <c r="AA25" s="39"/>
+      <c r="AB25" s="39"/>
+      <c r="AC25" s="39"/>
+      <c r="AD25" s="39"/>
+      <c r="AE25" s="39"/>
+      <c r="AF25" s="39"/>
+      <c r="AG25" s="39"/>
+      <c r="AH25" s="39"/>
+      <c r="AI25" s="39"/>
+      <c r="AJ25" s="39"/>
+      <c r="AK25" s="42">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AL25" s="41"/>
-      <c r="AM25" s="41"/>
-      <c r="AN25" s="41"/>
-      <c r="AO25" s="41"/>
-      <c r="AP25" s="41"/>
-      <c r="AQ25" s="45">
+      <c r="AL25" s="39"/>
+      <c r="AM25" s="39"/>
+      <c r="AN25" s="39"/>
+      <c r="AO25" s="39"/>
+      <c r="AP25" s="39"/>
+      <c r="AQ25" s="42">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AR25" s="41"/>
-      <c r="AS25" s="41"/>
-      <c r="AT25" s="41"/>
-      <c r="AU25" s="45">
+      <c r="AR25" s="39"/>
+      <c r="AS25" s="39"/>
+      <c r="AT25" s="39"/>
+      <c r="AU25" s="42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV25" s="41"/>
-      <c r="AW25" s="41"/>
-      <c r="AX25" s="41"/>
-      <c r="AY25" s="47"/>
-      <c r="AZ25" s="41"/>
-      <c r="BA25" s="45">
+      <c r="AV25" s="39"/>
+      <c r="AW25" s="39"/>
+      <c r="AX25" s="39"/>
+      <c r="AY25" s="44"/>
+      <c r="AZ25" s="39"/>
+      <c r="BA25" s="42">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB25" s="41"/>
-      <c r="BC25" s="41"/>
-      <c r="BD25" s="41"/>
-      <c r="BE25" s="41"/>
-      <c r="BF25" s="45">
+      <c r="BB25" s="39"/>
+      <c r="BC25" s="39"/>
+      <c r="BD25" s="39"/>
+      <c r="BE25" s="39"/>
+      <c r="BF25" s="42">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BG25" s="41"/>
-      <c r="BH25" s="48">
+      <c r="BG25" s="39"/>
+      <c r="BH25" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI25" s="49">
+      <c r="BI25" s="46">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ25" s="43"/>
+      <c r="BJ25" s="41"/>
     </row>
     <row r="26" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="23">
@@ -3925,106 +3922,106 @@
         <v>22</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="D26" s="36">
+        <v>43</v>
+      </c>
+      <c r="D26" s="42">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="E26" s="37"/>
-      <c r="F26" s="37"/>
-      <c r="G26" s="37"/>
-      <c r="H26" s="37"/>
-      <c r="I26" s="37"/>
-      <c r="J26" s="37"/>
-      <c r="K26" s="45">
+      <c r="E26" s="39"/>
+      <c r="F26" s="39"/>
+      <c r="G26" s="39"/>
+      <c r="H26" s="39"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="39"/>
+      <c r="K26" s="42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L26" s="41"/>
-      <c r="M26" s="45">
+      <c r="L26" s="39"/>
+      <c r="M26" s="42">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N26" s="41"/>
-      <c r="O26" s="41"/>
-      <c r="P26" s="41"/>
-      <c r="Q26" s="41"/>
-      <c r="R26" s="45">
+      <c r="N26" s="39"/>
+      <c r="O26" s="39"/>
+      <c r="P26" s="39"/>
+      <c r="Q26" s="39"/>
+      <c r="R26" s="42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S26" s="41"/>
-      <c r="T26" s="45">
+      <c r="S26" s="39"/>
+      <c r="T26" s="42">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U26" s="50"/>
-      <c r="V26" s="41"/>
-      <c r="W26" s="41"/>
-      <c r="X26" s="41"/>
-      <c r="Y26" s="41"/>
-      <c r="Z26" s="41"/>
-      <c r="AA26" s="41"/>
-      <c r="AB26" s="41"/>
-      <c r="AC26" s="41"/>
-      <c r="AD26" s="41"/>
-      <c r="AE26" s="41"/>
-      <c r="AF26" s="41"/>
-      <c r="AG26" s="41"/>
-      <c r="AH26" s="41"/>
-      <c r="AI26" s="41"/>
-      <c r="AJ26" s="41"/>
-      <c r="AK26" s="45">
+      <c r="U26" s="47"/>
+      <c r="V26" s="39"/>
+      <c r="W26" s="39"/>
+      <c r="X26" s="39"/>
+      <c r="Y26" s="39"/>
+      <c r="Z26" s="39"/>
+      <c r="AA26" s="39"/>
+      <c r="AB26" s="39"/>
+      <c r="AC26" s="39"/>
+      <c r="AD26" s="39"/>
+      <c r="AE26" s="39"/>
+      <c r="AF26" s="39"/>
+      <c r="AG26" s="39"/>
+      <c r="AH26" s="39"/>
+      <c r="AI26" s="39"/>
+      <c r="AJ26" s="39"/>
+      <c r="AK26" s="42">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AL26" s="41"/>
-      <c r="AM26" s="41"/>
-      <c r="AN26" s="41"/>
-      <c r="AO26" s="41"/>
-      <c r="AP26" s="41"/>
-      <c r="AQ26" s="45">
+      <c r="AL26" s="39"/>
+      <c r="AM26" s="39"/>
+      <c r="AN26" s="39"/>
+      <c r="AO26" s="39"/>
+      <c r="AP26" s="39"/>
+      <c r="AQ26" s="42">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AR26" s="41"/>
-      <c r="AS26" s="41"/>
-      <c r="AT26" s="41"/>
-      <c r="AU26" s="45">
+      <c r="AR26" s="39"/>
+      <c r="AS26" s="39"/>
+      <c r="AT26" s="39"/>
+      <c r="AU26" s="42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV26" s="41"/>
-      <c r="AW26" s="41"/>
-      <c r="AX26" s="41"/>
-      <c r="AY26" s="47"/>
-      <c r="AZ26" s="41"/>
-      <c r="BA26" s="45">
+      <c r="AV26" s="39"/>
+      <c r="AW26" s="39"/>
+      <c r="AX26" s="39"/>
+      <c r="AY26" s="44"/>
+      <c r="AZ26" s="39"/>
+      <c r="BA26" s="42">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB26" s="50"/>
-      <c r="BC26" s="50"/>
-      <c r="BD26" s="50"/>
-      <c r="BE26" s="50"/>
-      <c r="BF26" s="45">
+      <c r="BB26" s="47"/>
+      <c r="BC26" s="47"/>
+      <c r="BD26" s="47"/>
+      <c r="BE26" s="47"/>
+      <c r="BF26" s="42">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BG26" s="50"/>
-      <c r="BH26" s="48">
+      <c r="BG26" s="47"/>
+      <c r="BH26" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI26" s="49">
+      <c r="BI26" s="46">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ26" s="43"/>
+      <c r="BJ26" s="41"/>
     </row>
     <row r="27" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="23">
@@ -4032,106 +4029,106 @@
         <v>23</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="D27" s="36">
+        <v>45</v>
+      </c>
+      <c r="D27" s="42">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="E27" s="37"/>
-      <c r="F27" s="37"/>
-      <c r="G27" s="37"/>
-      <c r="H27" s="37"/>
-      <c r="I27" s="37"/>
-      <c r="J27" s="37"/>
-      <c r="K27" s="45">
+      <c r="E27" s="39"/>
+      <c r="F27" s="39"/>
+      <c r="G27" s="39"/>
+      <c r="H27" s="39"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="39"/>
+      <c r="K27" s="42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L27" s="41"/>
-      <c r="M27" s="45">
+      <c r="L27" s="39"/>
+      <c r="M27" s="42">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N27" s="41"/>
-      <c r="O27" s="41"/>
-      <c r="P27" s="41"/>
-      <c r="Q27" s="41"/>
-      <c r="R27" s="45">
+      <c r="N27" s="39"/>
+      <c r="O27" s="39"/>
+      <c r="P27" s="39"/>
+      <c r="Q27" s="39"/>
+      <c r="R27" s="42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S27" s="41"/>
-      <c r="T27" s="45">
+      <c r="S27" s="39"/>
+      <c r="T27" s="42">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U27" s="50"/>
-      <c r="V27" s="41"/>
-      <c r="W27" s="41"/>
-      <c r="X27" s="41"/>
-      <c r="Y27" s="41"/>
-      <c r="Z27" s="41"/>
-      <c r="AA27" s="41"/>
-      <c r="AB27" s="41"/>
-      <c r="AC27" s="41"/>
-      <c r="AD27" s="41"/>
-      <c r="AE27" s="41"/>
-      <c r="AF27" s="41"/>
-      <c r="AG27" s="41"/>
-      <c r="AH27" s="41"/>
-      <c r="AI27" s="41"/>
-      <c r="AJ27" s="41"/>
-      <c r="AK27" s="45">
+      <c r="U27" s="47"/>
+      <c r="V27" s="39"/>
+      <c r="W27" s="39"/>
+      <c r="X27" s="39"/>
+      <c r="Y27" s="39"/>
+      <c r="Z27" s="39"/>
+      <c r="AA27" s="39"/>
+      <c r="AB27" s="39"/>
+      <c r="AC27" s="39"/>
+      <c r="AD27" s="39"/>
+      <c r="AE27" s="39"/>
+      <c r="AF27" s="39"/>
+      <c r="AG27" s="39"/>
+      <c r="AH27" s="39"/>
+      <c r="AI27" s="39"/>
+      <c r="AJ27" s="39"/>
+      <c r="AK27" s="42">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AL27" s="41"/>
-      <c r="AM27" s="41"/>
-      <c r="AN27" s="41"/>
-      <c r="AO27" s="41"/>
-      <c r="AP27" s="47"/>
-      <c r="AQ27" s="45">
+      <c r="AL27" s="39"/>
+      <c r="AM27" s="39"/>
+      <c r="AN27" s="39"/>
+      <c r="AO27" s="39"/>
+      <c r="AP27" s="44"/>
+      <c r="AQ27" s="42">
         <f t="shared" ref="AQ27:AQ35" si="13">AM27-AN27-AO27-AP27</f>
         <v>0</v>
       </c>
-      <c r="AR27" s="41"/>
-      <c r="AS27" s="41"/>
-      <c r="AT27" s="41"/>
-      <c r="AU27" s="45">
+      <c r="AR27" s="39"/>
+      <c r="AS27" s="39"/>
+      <c r="AT27" s="39"/>
+      <c r="AU27" s="42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV27" s="41"/>
-      <c r="AW27" s="41"/>
-      <c r="AX27" s="41"/>
-      <c r="AY27" s="47"/>
-      <c r="AZ27" s="41"/>
-      <c r="BA27" s="45">
+      <c r="AV27" s="39"/>
+      <c r="AW27" s="39"/>
+      <c r="AX27" s="39"/>
+      <c r="AY27" s="44"/>
+      <c r="AZ27" s="39"/>
+      <c r="BA27" s="42">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB27" s="41"/>
-      <c r="BC27" s="41"/>
-      <c r="BD27" s="41"/>
-      <c r="BE27" s="41"/>
-      <c r="BF27" s="45">
+      <c r="BB27" s="39"/>
+      <c r="BC27" s="39"/>
+      <c r="BD27" s="39"/>
+      <c r="BE27" s="39"/>
+      <c r="BF27" s="42">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BG27" s="41"/>
-      <c r="BH27" s="48">
+      <c r="BG27" s="39"/>
+      <c r="BH27" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI27" s="49">
+      <c r="BI27" s="46">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ27" s="43"/>
+      <c r="BJ27" s="41"/>
     </row>
     <row r="28" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="23">
@@ -4139,106 +4136,106 @@
         <v>24</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="D28" s="36">
+        <v>47</v>
+      </c>
+      <c r="D28" s="42">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="E28" s="37"/>
-      <c r="F28" s="37"/>
-      <c r="G28" s="37"/>
-      <c r="H28" s="37"/>
-      <c r="I28" s="37"/>
-      <c r="J28" s="37"/>
-      <c r="K28" s="45">
+      <c r="E28" s="39"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="39"/>
+      <c r="H28" s="39"/>
+      <c r="I28" s="39"/>
+      <c r="J28" s="39"/>
+      <c r="K28" s="42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L28" s="41"/>
-      <c r="M28" s="45">
+      <c r="L28" s="39"/>
+      <c r="M28" s="42">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N28" s="41"/>
-      <c r="O28" s="41"/>
-      <c r="P28" s="41"/>
-      <c r="Q28" s="41"/>
-      <c r="R28" s="45">
+      <c r="N28" s="39"/>
+      <c r="O28" s="39"/>
+      <c r="P28" s="39"/>
+      <c r="Q28" s="39"/>
+      <c r="R28" s="42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S28" s="41"/>
-      <c r="T28" s="45">
+      <c r="S28" s="39"/>
+      <c r="T28" s="42">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U28" s="50"/>
-      <c r="V28" s="41"/>
-      <c r="W28" s="41"/>
-      <c r="X28" s="41"/>
-      <c r="Y28" s="41"/>
-      <c r="Z28" s="41"/>
-      <c r="AA28" s="41"/>
-      <c r="AB28" s="41"/>
-      <c r="AC28" s="41"/>
-      <c r="AD28" s="41"/>
-      <c r="AE28" s="41"/>
-      <c r="AF28" s="41"/>
-      <c r="AG28" s="41"/>
-      <c r="AH28" s="41"/>
-      <c r="AI28" s="41"/>
-      <c r="AJ28" s="41"/>
-      <c r="AK28" s="45">
+      <c r="U28" s="47"/>
+      <c r="V28" s="39"/>
+      <c r="W28" s="39"/>
+      <c r="X28" s="39"/>
+      <c r="Y28" s="39"/>
+      <c r="Z28" s="39"/>
+      <c r="AA28" s="39"/>
+      <c r="AB28" s="39"/>
+      <c r="AC28" s="39"/>
+      <c r="AD28" s="39"/>
+      <c r="AE28" s="39"/>
+      <c r="AF28" s="39"/>
+      <c r="AG28" s="39"/>
+      <c r="AH28" s="39"/>
+      <c r="AI28" s="39"/>
+      <c r="AJ28" s="39"/>
+      <c r="AK28" s="42">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AL28" s="41"/>
-      <c r="AM28" s="47"/>
-      <c r="AN28" s="41"/>
-      <c r="AO28" s="41"/>
-      <c r="AP28" s="47"/>
-      <c r="AQ28" s="45">
+      <c r="AL28" s="39"/>
+      <c r="AM28" s="44"/>
+      <c r="AN28" s="39"/>
+      <c r="AO28" s="39"/>
+      <c r="AP28" s="44"/>
+      <c r="AQ28" s="42">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AR28" s="41"/>
-      <c r="AS28" s="41"/>
-      <c r="AT28" s="41"/>
-      <c r="AU28" s="45">
+      <c r="AR28" s="39"/>
+      <c r="AS28" s="39"/>
+      <c r="AT28" s="39"/>
+      <c r="AU28" s="42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV28" s="41"/>
-      <c r="AW28" s="41"/>
-      <c r="AX28" s="41"/>
-      <c r="AY28" s="47"/>
-      <c r="AZ28" s="47"/>
-      <c r="BA28" s="45">
+      <c r="AV28" s="39"/>
+      <c r="AW28" s="39"/>
+      <c r="AX28" s="39"/>
+      <c r="AY28" s="44"/>
+      <c r="AZ28" s="44"/>
+      <c r="BA28" s="42">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB28" s="50"/>
-      <c r="BC28" s="50"/>
-      <c r="BD28" s="50"/>
-      <c r="BE28" s="50"/>
-      <c r="BF28" s="45">
+      <c r="BB28" s="47"/>
+      <c r="BC28" s="47"/>
+      <c r="BD28" s="47"/>
+      <c r="BE28" s="47"/>
+      <c r="BF28" s="42">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BG28" s="50"/>
-      <c r="BH28" s="48">
+      <c r="BG28" s="47"/>
+      <c r="BH28" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI28" s="49">
+      <c r="BI28" s="46">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ28" s="43"/>
+      <c r="BJ28" s="41"/>
     </row>
     <row r="29" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="23">
@@ -4246,106 +4243,106 @@
         <v>25</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="D29" s="36">
+        <v>49</v>
+      </c>
+      <c r="D29" s="42">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="E29" s="37"/>
-      <c r="F29" s="37"/>
-      <c r="G29" s="37"/>
-      <c r="H29" s="37"/>
-      <c r="I29" s="37"/>
-      <c r="J29" s="37"/>
-      <c r="K29" s="45">
+      <c r="E29" s="39"/>
+      <c r="F29" s="39"/>
+      <c r="G29" s="39"/>
+      <c r="H29" s="39"/>
+      <c r="I29" s="39"/>
+      <c r="J29" s="39"/>
+      <c r="K29" s="42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L29" s="41"/>
-      <c r="M29" s="45">
+      <c r="L29" s="39"/>
+      <c r="M29" s="42">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N29" s="41"/>
-      <c r="O29" s="41"/>
-      <c r="P29" s="41"/>
-      <c r="Q29" s="41"/>
-      <c r="R29" s="45">
+      <c r="N29" s="39"/>
+      <c r="O29" s="39"/>
+      <c r="P29" s="39"/>
+      <c r="Q29" s="39"/>
+      <c r="R29" s="42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S29" s="41"/>
-      <c r="T29" s="45">
+      <c r="S29" s="39"/>
+      <c r="T29" s="42">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U29" s="50"/>
-      <c r="V29" s="41"/>
-      <c r="W29" s="41"/>
-      <c r="X29" s="41"/>
-      <c r="Y29" s="41"/>
-      <c r="Z29" s="41"/>
-      <c r="AA29" s="41"/>
-      <c r="AB29" s="41"/>
-      <c r="AC29" s="41"/>
-      <c r="AD29" s="41"/>
-      <c r="AE29" s="41"/>
-      <c r="AF29" s="41"/>
-      <c r="AG29" s="41"/>
-      <c r="AH29" s="41"/>
-      <c r="AI29" s="41"/>
-      <c r="AJ29" s="41"/>
-      <c r="AK29" s="45">
+      <c r="U29" s="47"/>
+      <c r="V29" s="39"/>
+      <c r="W29" s="39"/>
+      <c r="X29" s="39"/>
+      <c r="Y29" s="39"/>
+      <c r="Z29" s="39"/>
+      <c r="AA29" s="39"/>
+      <c r="AB29" s="39"/>
+      <c r="AC29" s="39"/>
+      <c r="AD29" s="39"/>
+      <c r="AE29" s="39"/>
+      <c r="AF29" s="39"/>
+      <c r="AG29" s="39"/>
+      <c r="AH29" s="39"/>
+      <c r="AI29" s="39"/>
+      <c r="AJ29" s="39"/>
+      <c r="AK29" s="42">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AL29" s="41"/>
-      <c r="AM29" s="47"/>
-      <c r="AN29" s="47"/>
-      <c r="AO29" s="41"/>
-      <c r="AP29" s="41"/>
-      <c r="AQ29" s="45">
+      <c r="AL29" s="39"/>
+      <c r="AM29" s="44"/>
+      <c r="AN29" s="44"/>
+      <c r="AO29" s="39"/>
+      <c r="AP29" s="39"/>
+      <c r="AQ29" s="42">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AR29" s="41"/>
-      <c r="AS29" s="41"/>
-      <c r="AT29" s="41"/>
-      <c r="AU29" s="45">
+      <c r="AR29" s="39"/>
+      <c r="AS29" s="39"/>
+      <c r="AT29" s="39"/>
+      <c r="AU29" s="42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV29" s="41"/>
-      <c r="AW29" s="41"/>
-      <c r="AX29" s="41"/>
-      <c r="AY29" s="47"/>
-      <c r="AZ29" s="41"/>
-      <c r="BA29" s="45">
+      <c r="AV29" s="39"/>
+      <c r="AW29" s="39"/>
+      <c r="AX29" s="39"/>
+      <c r="AY29" s="44"/>
+      <c r="AZ29" s="39"/>
+      <c r="BA29" s="42">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB29" s="41"/>
-      <c r="BC29" s="41"/>
-      <c r="BD29" s="41"/>
-      <c r="BE29" s="41"/>
-      <c r="BF29" s="45">
+      <c r="BB29" s="39"/>
+      <c r="BC29" s="39"/>
+      <c r="BD29" s="39"/>
+      <c r="BE29" s="39"/>
+      <c r="BF29" s="42">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BG29" s="41"/>
-      <c r="BH29" s="48">
+      <c r="BG29" s="39"/>
+      <c r="BH29" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI29" s="49">
+      <c r="BI29" s="46">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ29" s="43"/>
+      <c r="BJ29" s="41"/>
     </row>
     <row r="30" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="23">
@@ -4353,106 +4350,106 @@
         <v>26</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="D30" s="36">
+        <v>51</v>
+      </c>
+      <c r="D30" s="42">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="E30" s="37"/>
-      <c r="F30" s="37"/>
-      <c r="G30" s="37"/>
-      <c r="H30" s="37"/>
-      <c r="I30" s="37"/>
-      <c r="J30" s="37"/>
-      <c r="K30" s="45">
+      <c r="E30" s="39"/>
+      <c r="F30" s="39"/>
+      <c r="G30" s="39"/>
+      <c r="H30" s="39"/>
+      <c r="I30" s="39"/>
+      <c r="J30" s="39"/>
+      <c r="K30" s="42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L30" s="41"/>
-      <c r="M30" s="45">
+      <c r="L30" s="39"/>
+      <c r="M30" s="42">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N30" s="41"/>
-      <c r="O30" s="41"/>
-      <c r="P30" s="41"/>
-      <c r="Q30" s="41"/>
-      <c r="R30" s="45">
+      <c r="N30" s="39"/>
+      <c r="O30" s="39"/>
+      <c r="P30" s="39"/>
+      <c r="Q30" s="39"/>
+      <c r="R30" s="42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S30" s="41"/>
-      <c r="T30" s="45">
+      <c r="S30" s="39"/>
+      <c r="T30" s="42">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U30" s="50"/>
-      <c r="V30" s="41"/>
-      <c r="W30" s="41"/>
-      <c r="X30" s="41"/>
-      <c r="Y30" s="41"/>
-      <c r="Z30" s="41"/>
-      <c r="AA30" s="41"/>
-      <c r="AB30" s="41"/>
-      <c r="AC30" s="41"/>
-      <c r="AD30" s="41"/>
-      <c r="AE30" s="41"/>
-      <c r="AF30" s="41"/>
-      <c r="AG30" s="41"/>
-      <c r="AH30" s="41"/>
-      <c r="AI30" s="41"/>
-      <c r="AJ30" s="41"/>
-      <c r="AK30" s="45">
+      <c r="U30" s="47"/>
+      <c r="V30" s="39"/>
+      <c r="W30" s="39"/>
+      <c r="X30" s="39"/>
+      <c r="Y30" s="39"/>
+      <c r="Z30" s="39"/>
+      <c r="AA30" s="39"/>
+      <c r="AB30" s="39"/>
+      <c r="AC30" s="39"/>
+      <c r="AD30" s="39"/>
+      <c r="AE30" s="39"/>
+      <c r="AF30" s="39"/>
+      <c r="AG30" s="39"/>
+      <c r="AH30" s="39"/>
+      <c r="AI30" s="39"/>
+      <c r="AJ30" s="39"/>
+      <c r="AK30" s="42">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AL30" s="41"/>
-      <c r="AM30" s="41"/>
-      <c r="AN30" s="41"/>
-      <c r="AO30" s="41"/>
-      <c r="AP30" s="41"/>
-      <c r="AQ30" s="45">
+      <c r="AL30" s="39"/>
+      <c r="AM30" s="39"/>
+      <c r="AN30" s="39"/>
+      <c r="AO30" s="39"/>
+      <c r="AP30" s="39"/>
+      <c r="AQ30" s="42">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AR30" s="41"/>
-      <c r="AS30" s="41"/>
-      <c r="AT30" s="41"/>
-      <c r="AU30" s="45">
+      <c r="AR30" s="39"/>
+      <c r="AS30" s="39"/>
+      <c r="AT30" s="39"/>
+      <c r="AU30" s="42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV30" s="41"/>
-      <c r="AW30" s="41"/>
-      <c r="AX30" s="41"/>
-      <c r="AY30" s="47"/>
-      <c r="AZ30" s="41"/>
-      <c r="BA30" s="45">
+      <c r="AV30" s="39"/>
+      <c r="AW30" s="39"/>
+      <c r="AX30" s="39"/>
+      <c r="AY30" s="44"/>
+      <c r="AZ30" s="39"/>
+      <c r="BA30" s="42">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB30" s="41"/>
-      <c r="BC30" s="41"/>
-      <c r="BD30" s="41"/>
-      <c r="BE30" s="41"/>
-      <c r="BF30" s="45">
+      <c r="BB30" s="39"/>
+      <c r="BC30" s="39"/>
+      <c r="BD30" s="39"/>
+      <c r="BE30" s="39"/>
+      <c r="BF30" s="42">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BG30" s="41"/>
-      <c r="BH30" s="48">
+      <c r="BG30" s="39"/>
+      <c r="BH30" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI30" s="49">
+      <c r="BI30" s="46">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ30" s="43"/>
+      <c r="BJ30" s="41"/>
     </row>
     <row r="31" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="23">
@@ -4460,106 +4457,106 @@
         <v>27</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="D31" s="36">
+        <v>53</v>
+      </c>
+      <c r="D31" s="42">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="E31" s="37"/>
-      <c r="F31" s="37"/>
-      <c r="G31" s="37"/>
-      <c r="H31" s="37"/>
-      <c r="I31" s="37"/>
-      <c r="J31" s="37"/>
-      <c r="K31" s="45">
+      <c r="E31" s="39"/>
+      <c r="F31" s="39"/>
+      <c r="G31" s="39"/>
+      <c r="H31" s="39"/>
+      <c r="I31" s="39"/>
+      <c r="J31" s="39"/>
+      <c r="K31" s="42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L31" s="41"/>
-      <c r="M31" s="45">
+      <c r="L31" s="39"/>
+      <c r="M31" s="42">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N31" s="41"/>
-      <c r="O31" s="41"/>
-      <c r="P31" s="41"/>
-      <c r="Q31" s="41"/>
-      <c r="R31" s="45">
+      <c r="N31" s="39"/>
+      <c r="O31" s="39"/>
+      <c r="P31" s="39"/>
+      <c r="Q31" s="39"/>
+      <c r="R31" s="42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S31" s="41"/>
-      <c r="T31" s="45">
+      <c r="S31" s="39"/>
+      <c r="T31" s="42">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U31" s="50"/>
-      <c r="V31" s="41"/>
-      <c r="W31" s="41"/>
-      <c r="X31" s="41"/>
-      <c r="Y31" s="41"/>
-      <c r="Z31" s="41"/>
-      <c r="AA31" s="41"/>
-      <c r="AB31" s="41"/>
-      <c r="AC31" s="41"/>
-      <c r="AD31" s="41"/>
-      <c r="AE31" s="41"/>
-      <c r="AF31" s="41"/>
-      <c r="AG31" s="41"/>
-      <c r="AH31" s="41"/>
-      <c r="AI31" s="41"/>
-      <c r="AJ31" s="41"/>
-      <c r="AK31" s="45">
+      <c r="U31" s="47"/>
+      <c r="V31" s="39"/>
+      <c r="W31" s="39"/>
+      <c r="X31" s="39"/>
+      <c r="Y31" s="39"/>
+      <c r="Z31" s="39"/>
+      <c r="AA31" s="39"/>
+      <c r="AB31" s="39"/>
+      <c r="AC31" s="39"/>
+      <c r="AD31" s="39"/>
+      <c r="AE31" s="39"/>
+      <c r="AF31" s="39"/>
+      <c r="AG31" s="39"/>
+      <c r="AH31" s="39"/>
+      <c r="AI31" s="39"/>
+      <c r="AJ31" s="39"/>
+      <c r="AK31" s="42">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AL31" s="50"/>
-      <c r="AM31" s="41"/>
-      <c r="AN31" s="41"/>
-      <c r="AO31" s="41"/>
-      <c r="AP31" s="41"/>
-      <c r="AQ31" s="45">
+      <c r="AL31" s="47"/>
+      <c r="AM31" s="39"/>
+      <c r="AN31" s="39"/>
+      <c r="AO31" s="39"/>
+      <c r="AP31" s="39"/>
+      <c r="AQ31" s="42">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AR31" s="41"/>
-      <c r="AS31" s="41"/>
-      <c r="AT31" s="41"/>
-      <c r="AU31" s="45">
+      <c r="AR31" s="39"/>
+      <c r="AS31" s="39"/>
+      <c r="AT31" s="39"/>
+      <c r="AU31" s="42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV31" s="41"/>
-      <c r="AW31" s="41"/>
-      <c r="AX31" s="41"/>
-      <c r="AY31" s="47"/>
-      <c r="AZ31" s="47"/>
-      <c r="BA31" s="45">
+      <c r="AV31" s="39"/>
+      <c r="AW31" s="39"/>
+      <c r="AX31" s="39"/>
+      <c r="AY31" s="44"/>
+      <c r="AZ31" s="44"/>
+      <c r="BA31" s="42">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB31" s="41"/>
-      <c r="BC31" s="41"/>
-      <c r="BD31" s="41"/>
-      <c r="BE31" s="41"/>
-      <c r="BF31" s="45">
+      <c r="BB31" s="39"/>
+      <c r="BC31" s="39"/>
+      <c r="BD31" s="39"/>
+      <c r="BE31" s="39"/>
+      <c r="BF31" s="42">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BG31" s="41"/>
-      <c r="BH31" s="48">
+      <c r="BG31" s="39"/>
+      <c r="BH31" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI31" s="49">
+      <c r="BI31" s="46">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ31" s="43"/>
+      <c r="BJ31" s="41"/>
     </row>
     <row r="32" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="23">
@@ -4567,106 +4564,106 @@
         <v>28</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="D32" s="36">
+        <v>55</v>
+      </c>
+      <c r="D32" s="42">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="E32" s="37"/>
-      <c r="F32" s="37"/>
-      <c r="G32" s="37"/>
-      <c r="H32" s="37"/>
-      <c r="I32" s="37"/>
-      <c r="J32" s="37"/>
-      <c r="K32" s="45">
+      <c r="E32" s="39"/>
+      <c r="F32" s="39"/>
+      <c r="G32" s="39"/>
+      <c r="H32" s="39"/>
+      <c r="I32" s="39"/>
+      <c r="J32" s="39"/>
+      <c r="K32" s="42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L32" s="41"/>
-      <c r="M32" s="45">
+      <c r="L32" s="39"/>
+      <c r="M32" s="42">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N32" s="41"/>
-      <c r="O32" s="41"/>
-      <c r="P32" s="41"/>
-      <c r="Q32" s="41"/>
-      <c r="R32" s="45">
+      <c r="N32" s="39"/>
+      <c r="O32" s="39"/>
+      <c r="P32" s="39"/>
+      <c r="Q32" s="39"/>
+      <c r="R32" s="42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S32" s="41"/>
-      <c r="T32" s="45">
+      <c r="S32" s="39"/>
+      <c r="T32" s="42">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U32" s="50"/>
-      <c r="V32" s="41"/>
-      <c r="W32" s="41"/>
-      <c r="X32" s="41"/>
-      <c r="Y32" s="41"/>
-      <c r="Z32" s="41"/>
-      <c r="AA32" s="41"/>
-      <c r="AB32" s="41"/>
-      <c r="AC32" s="41"/>
-      <c r="AD32" s="41"/>
-      <c r="AE32" s="41"/>
-      <c r="AF32" s="41"/>
-      <c r="AG32" s="41"/>
-      <c r="AH32" s="41"/>
-      <c r="AI32" s="41"/>
-      <c r="AJ32" s="41"/>
-      <c r="AK32" s="45">
+      <c r="U32" s="47"/>
+      <c r="V32" s="39"/>
+      <c r="W32" s="39"/>
+      <c r="X32" s="39"/>
+      <c r="Y32" s="39"/>
+      <c r="Z32" s="39"/>
+      <c r="AA32" s="39"/>
+      <c r="AB32" s="39"/>
+      <c r="AC32" s="39"/>
+      <c r="AD32" s="39"/>
+      <c r="AE32" s="39"/>
+      <c r="AF32" s="39"/>
+      <c r="AG32" s="39"/>
+      <c r="AH32" s="39"/>
+      <c r="AI32" s="39"/>
+      <c r="AJ32" s="39"/>
+      <c r="AK32" s="42">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AL32" s="50"/>
-      <c r="AM32" s="47"/>
-      <c r="AN32" s="41"/>
-      <c r="AO32" s="41"/>
-      <c r="AP32" s="41"/>
-      <c r="AQ32" s="45">
+      <c r="AL32" s="47"/>
+      <c r="AM32" s="44"/>
+      <c r="AN32" s="39"/>
+      <c r="AO32" s="39"/>
+      <c r="AP32" s="39"/>
+      <c r="AQ32" s="42">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AR32" s="41"/>
-      <c r="AS32" s="41"/>
-      <c r="AT32" s="41"/>
-      <c r="AU32" s="45">
+      <c r="AR32" s="39"/>
+      <c r="AS32" s="39"/>
+      <c r="AT32" s="39"/>
+      <c r="AU32" s="42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV32" s="41"/>
-      <c r="AW32" s="41"/>
-      <c r="AX32" s="41"/>
-      <c r="AY32" s="47"/>
-      <c r="AZ32" s="41"/>
-      <c r="BA32" s="45">
+      <c r="AV32" s="39"/>
+      <c r="AW32" s="39"/>
+      <c r="AX32" s="39"/>
+      <c r="AY32" s="44"/>
+      <c r="AZ32" s="39"/>
+      <c r="BA32" s="42">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB32" s="41"/>
-      <c r="BC32" s="41"/>
-      <c r="BD32" s="41"/>
-      <c r="BE32" s="41"/>
-      <c r="BF32" s="45">
+      <c r="BB32" s="39"/>
+      <c r="BC32" s="39"/>
+      <c r="BD32" s="39"/>
+      <c r="BE32" s="39"/>
+      <c r="BF32" s="42">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BG32" s="41"/>
-      <c r="BH32" s="48">
+      <c r="BG32" s="39"/>
+      <c r="BH32" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI32" s="49">
+      <c r="BI32" s="46">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ32" s="37"/>
+      <c r="BJ32" s="36"/>
     </row>
     <row r="33" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="23">
@@ -4674,106 +4671,106 @@
         <v>29</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="D33" s="36">
+        <v>43</v>
+      </c>
+      <c r="D33" s="42">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="E33" s="37"/>
-      <c r="F33" s="37"/>
-      <c r="G33" s="37"/>
-      <c r="H33" s="37"/>
-      <c r="I33" s="37"/>
-      <c r="J33" s="37"/>
-      <c r="K33" s="45">
+      <c r="E33" s="39"/>
+      <c r="F33" s="39"/>
+      <c r="G33" s="39"/>
+      <c r="H33" s="39"/>
+      <c r="I33" s="39"/>
+      <c r="J33" s="39"/>
+      <c r="K33" s="42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L33" s="41"/>
-      <c r="M33" s="45">
+      <c r="L33" s="39"/>
+      <c r="M33" s="42">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N33" s="41"/>
-      <c r="O33" s="41"/>
-      <c r="P33" s="41"/>
-      <c r="Q33" s="41"/>
-      <c r="R33" s="45">
+      <c r="N33" s="39"/>
+      <c r="O33" s="39"/>
+      <c r="P33" s="39"/>
+      <c r="Q33" s="39"/>
+      <c r="R33" s="42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S33" s="41"/>
-      <c r="T33" s="45">
+      <c r="S33" s="39"/>
+      <c r="T33" s="42">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U33" s="50"/>
-      <c r="V33" s="41"/>
-      <c r="W33" s="41"/>
-      <c r="X33" s="41"/>
-      <c r="Y33" s="41"/>
-      <c r="Z33" s="41"/>
-      <c r="AA33" s="41"/>
-      <c r="AB33" s="41"/>
-      <c r="AC33" s="41"/>
-      <c r="AD33" s="41"/>
-      <c r="AE33" s="41"/>
-      <c r="AF33" s="41"/>
-      <c r="AG33" s="41"/>
-      <c r="AH33" s="41"/>
-      <c r="AI33" s="41"/>
-      <c r="AJ33" s="41"/>
-      <c r="AK33" s="45">
+      <c r="U33" s="47"/>
+      <c r="V33" s="39"/>
+      <c r="W33" s="39"/>
+      <c r="X33" s="39"/>
+      <c r="Y33" s="39"/>
+      <c r="Z33" s="39"/>
+      <c r="AA33" s="39"/>
+      <c r="AB33" s="39"/>
+      <c r="AC33" s="39"/>
+      <c r="AD33" s="39"/>
+      <c r="AE33" s="39"/>
+      <c r="AF33" s="39"/>
+      <c r="AG33" s="39"/>
+      <c r="AH33" s="39"/>
+      <c r="AI33" s="39"/>
+      <c r="AJ33" s="39"/>
+      <c r="AK33" s="42">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AL33" s="50"/>
-      <c r="AM33" s="47"/>
-      <c r="AN33" s="41"/>
-      <c r="AO33" s="41"/>
-      <c r="AP33" s="41"/>
-      <c r="AQ33" s="45">
+      <c r="AL33" s="47"/>
+      <c r="AM33" s="44"/>
+      <c r="AN33" s="39"/>
+      <c r="AO33" s="39"/>
+      <c r="AP33" s="39"/>
+      <c r="AQ33" s="42">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AR33" s="41"/>
-      <c r="AS33" s="41"/>
-      <c r="AT33" s="41"/>
-      <c r="AU33" s="45">
+      <c r="AR33" s="39"/>
+      <c r="AS33" s="39"/>
+      <c r="AT33" s="39"/>
+      <c r="AU33" s="42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV33" s="41"/>
-      <c r="AW33" s="41"/>
-      <c r="AX33" s="41"/>
-      <c r="AY33" s="47"/>
-      <c r="AZ33" s="41"/>
-      <c r="BA33" s="45">
+      <c r="AV33" s="39"/>
+      <c r="AW33" s="39"/>
+      <c r="AX33" s="39"/>
+      <c r="AY33" s="44"/>
+      <c r="AZ33" s="39"/>
+      <c r="BA33" s="42">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB33" s="41"/>
-      <c r="BC33" s="41"/>
-      <c r="BD33" s="41"/>
-      <c r="BE33" s="41"/>
-      <c r="BF33" s="45">
+      <c r="BB33" s="39"/>
+      <c r="BC33" s="39"/>
+      <c r="BD33" s="39"/>
+      <c r="BE33" s="39"/>
+      <c r="BF33" s="42">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BG33" s="41"/>
-      <c r="BH33" s="48">
+      <c r="BG33" s="39"/>
+      <c r="BH33" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI33" s="49">
+      <c r="BI33" s="46">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ33" s="37"/>
+      <c r="BJ33" s="36"/>
     </row>
     <row r="34" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="23">
@@ -4781,106 +4778,106 @@
         <v>30</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="D34" s="36">
+        <v>45</v>
+      </c>
+      <c r="D34" s="42">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="E34" s="37"/>
-      <c r="F34" s="37"/>
-      <c r="G34" s="37"/>
-      <c r="H34" s="37"/>
-      <c r="I34" s="37"/>
-      <c r="J34" s="37"/>
-      <c r="K34" s="45">
+      <c r="E34" s="39"/>
+      <c r="F34" s="39"/>
+      <c r="G34" s="39"/>
+      <c r="H34" s="39"/>
+      <c r="I34" s="39"/>
+      <c r="J34" s="39"/>
+      <c r="K34" s="42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L34" s="41"/>
-      <c r="M34" s="45">
+      <c r="L34" s="39"/>
+      <c r="M34" s="42">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N34" s="41"/>
-      <c r="O34" s="41"/>
-      <c r="P34" s="41"/>
-      <c r="Q34" s="41"/>
-      <c r="R34" s="45">
+      <c r="N34" s="39"/>
+      <c r="O34" s="39"/>
+      <c r="P34" s="39"/>
+      <c r="Q34" s="39"/>
+      <c r="R34" s="42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S34" s="41"/>
-      <c r="T34" s="45">
+      <c r="S34" s="39"/>
+      <c r="T34" s="42">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U34" s="50"/>
-      <c r="V34" s="41"/>
-      <c r="W34" s="41"/>
-      <c r="X34" s="41"/>
-      <c r="Y34" s="41"/>
-      <c r="Z34" s="41"/>
-      <c r="AA34" s="41"/>
-      <c r="AB34" s="41"/>
-      <c r="AC34" s="41"/>
-      <c r="AD34" s="41"/>
-      <c r="AE34" s="41"/>
-      <c r="AF34" s="41"/>
-      <c r="AG34" s="41"/>
-      <c r="AH34" s="41"/>
-      <c r="AI34" s="41"/>
-      <c r="AJ34" s="41"/>
-      <c r="AK34" s="45">
+      <c r="U34" s="47"/>
+      <c r="V34" s="39"/>
+      <c r="W34" s="39"/>
+      <c r="X34" s="39"/>
+      <c r="Y34" s="39"/>
+      <c r="Z34" s="39"/>
+      <c r="AA34" s="39"/>
+      <c r="AB34" s="39"/>
+      <c r="AC34" s="39"/>
+      <c r="AD34" s="39"/>
+      <c r="AE34" s="39"/>
+      <c r="AF34" s="39"/>
+      <c r="AG34" s="39"/>
+      <c r="AH34" s="39"/>
+      <c r="AI34" s="39"/>
+      <c r="AJ34" s="39"/>
+      <c r="AK34" s="42">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AL34" s="50"/>
-      <c r="AM34" s="47"/>
-      <c r="AN34" s="41"/>
-      <c r="AO34" s="41"/>
-      <c r="AP34" s="41"/>
-      <c r="AQ34" s="45">
+      <c r="AL34" s="47"/>
+      <c r="AM34" s="44"/>
+      <c r="AN34" s="39"/>
+      <c r="AO34" s="39"/>
+      <c r="AP34" s="39"/>
+      <c r="AQ34" s="42">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AR34" s="41"/>
-      <c r="AS34" s="41"/>
-      <c r="AT34" s="41"/>
-      <c r="AU34" s="45">
+      <c r="AR34" s="39"/>
+      <c r="AS34" s="39"/>
+      <c r="AT34" s="39"/>
+      <c r="AU34" s="42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV34" s="41"/>
-      <c r="AW34" s="41"/>
-      <c r="AX34" s="41"/>
-      <c r="AY34" s="47"/>
-      <c r="AZ34" s="41"/>
-      <c r="BA34" s="45">
+      <c r="AV34" s="39"/>
+      <c r="AW34" s="39"/>
+      <c r="AX34" s="39"/>
+      <c r="AY34" s="44"/>
+      <c r="AZ34" s="39"/>
+      <c r="BA34" s="42">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB34" s="41"/>
-      <c r="BC34" s="41"/>
-      <c r="BD34" s="41"/>
-      <c r="BE34" s="41"/>
-      <c r="BF34" s="45">
+      <c r="BB34" s="39"/>
+      <c r="BC34" s="39"/>
+      <c r="BD34" s="39"/>
+      <c r="BE34" s="39"/>
+      <c r="BF34" s="42">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BG34" s="41"/>
-      <c r="BH34" s="48">
+      <c r="BG34" s="39"/>
+      <c r="BH34" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI34" s="49">
+      <c r="BI34" s="46">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ34" s="37"/>
+      <c r="BJ34" s="36"/>
     </row>
     <row r="35" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="23">
@@ -4889,101 +4886,101 @@
       </c>
       <c r="B35" s="19"/>
       <c r="C35" s="19"/>
-      <c r="D35" s="36">
+      <c r="D35" s="42">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="E35" s="37"/>
-      <c r="F35" s="37"/>
-      <c r="G35" s="37"/>
-      <c r="H35" s="37"/>
-      <c r="I35" s="37"/>
-      <c r="J35" s="37"/>
-      <c r="K35" s="45">
+      <c r="E35" s="39"/>
+      <c r="F35" s="39"/>
+      <c r="G35" s="39"/>
+      <c r="H35" s="39"/>
+      <c r="I35" s="39"/>
+      <c r="J35" s="39"/>
+      <c r="K35" s="42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L35" s="41"/>
-      <c r="M35" s="45">
+      <c r="L35" s="39"/>
+      <c r="M35" s="42">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N35" s="41"/>
-      <c r="O35" s="41"/>
-      <c r="P35" s="41"/>
-      <c r="Q35" s="41"/>
-      <c r="R35" s="45">
+      <c r="N35" s="39"/>
+      <c r="O35" s="39"/>
+      <c r="P35" s="39"/>
+      <c r="Q35" s="39"/>
+      <c r="R35" s="42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S35" s="41"/>
-      <c r="T35" s="45">
+      <c r="S35" s="39"/>
+      <c r="T35" s="42">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U35" s="50"/>
-      <c r="V35" s="41"/>
-      <c r="W35" s="41"/>
-      <c r="X35" s="41"/>
-      <c r="Y35" s="41"/>
-      <c r="Z35" s="41"/>
-      <c r="AA35" s="41"/>
-      <c r="AB35" s="41"/>
-      <c r="AC35" s="41"/>
-      <c r="AD35" s="41"/>
-      <c r="AE35" s="41"/>
-      <c r="AF35" s="41"/>
-      <c r="AG35" s="41"/>
-      <c r="AH35" s="41"/>
-      <c r="AI35" s="41"/>
-      <c r="AJ35" s="41"/>
-      <c r="AK35" s="45">
+      <c r="U35" s="47"/>
+      <c r="V35" s="39"/>
+      <c r="W35" s="39"/>
+      <c r="X35" s="39"/>
+      <c r="Y35" s="39"/>
+      <c r="Z35" s="39"/>
+      <c r="AA35" s="39"/>
+      <c r="AB35" s="39"/>
+      <c r="AC35" s="39"/>
+      <c r="AD35" s="39"/>
+      <c r="AE35" s="39"/>
+      <c r="AF35" s="39"/>
+      <c r="AG35" s="39"/>
+      <c r="AH35" s="39"/>
+      <c r="AI35" s="39"/>
+      <c r="AJ35" s="39"/>
+      <c r="AK35" s="42">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AL35" s="50"/>
-      <c r="AM35" s="47"/>
-      <c r="AN35" s="41"/>
-      <c r="AO35" s="41"/>
-      <c r="AP35" s="41"/>
-      <c r="AQ35" s="45">
+      <c r="AL35" s="47"/>
+      <c r="AM35" s="44"/>
+      <c r="AN35" s="39"/>
+      <c r="AO35" s="39"/>
+      <c r="AP35" s="39"/>
+      <c r="AQ35" s="42">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AR35" s="41"/>
-      <c r="AS35" s="41"/>
-      <c r="AT35" s="41"/>
-      <c r="AU35" s="45">
+      <c r="AR35" s="39"/>
+      <c r="AS35" s="39"/>
+      <c r="AT35" s="39"/>
+      <c r="AU35" s="42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AV35" s="41"/>
-      <c r="AW35" s="41"/>
-      <c r="AX35" s="41"/>
-      <c r="AY35" s="47"/>
-      <c r="AZ35" s="41"/>
-      <c r="BA35" s="45">
+      <c r="AV35" s="39"/>
+      <c r="AW35" s="39"/>
+      <c r="AX35" s="39"/>
+      <c r="AY35" s="44"/>
+      <c r="AZ35" s="39"/>
+      <c r="BA35" s="42">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB35" s="41"/>
-      <c r="BC35" s="41"/>
-      <c r="BD35" s="41"/>
-      <c r="BE35" s="41"/>
-      <c r="BF35" s="45">
+      <c r="BB35" s="39"/>
+      <c r="BC35" s="39"/>
+      <c r="BD35" s="39"/>
+      <c r="BE35" s="39"/>
+      <c r="BF35" s="42">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BG35" s="41"/>
-      <c r="BH35" s="48">
+      <c r="BG35" s="39"/>
+      <c r="BH35" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI35" s="49">
+      <c r="BI35" s="46">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ35" s="37"/>
+      <c r="BJ35" s="36"/>
     </row>
     <row r="36" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="23">
@@ -4991,242 +4988,242 @@
         <v>32</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>80</v>
-      </c>
-      <c r="C36" s="37"/>
-      <c r="D36" s="23">
+        <v>79</v>
+      </c>
+      <c r="C36" s="36"/>
+      <c r="D36" s="50">
         <f t="shared" ref="D36:BI36" si="14">SUM(D5:D35)</f>
         <v>0</v>
       </c>
-      <c r="E36" s="23">
+      <c r="E36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="F36" s="23">
+      <c r="F36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G36" s="23">
+      <c r="G36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="H36" s="23">
+      <c r="H36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="I36" s="23">
+      <c r="I36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="J36" s="23">
+      <c r="J36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="K36" s="53">
+      <c r="K36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="L36" s="53">
+      <c r="L36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="M36" s="53">
+      <c r="M36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="N36" s="53">
+      <c r="N36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="O36" s="53">
+      <c r="O36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="P36" s="53">
+      <c r="P36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="Q36" s="53">
+      <c r="Q36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="R36" s="53">
+      <c r="R36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="S36" s="53">
+      <c r="S36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="T36" s="53">
+      <c r="T36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="U36" s="53">
+      <c r="U36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="V36" s="53">
+      <c r="V36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="W36" s="53">
+      <c r="W36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="X36" s="53">
+      <c r="X36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="Y36" s="53">
+      <c r="Y36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="Z36" s="53">
+      <c r="Z36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AA36" s="53">
+      <c r="AA36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AB36" s="53">
+      <c r="AB36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AC36" s="53">
+      <c r="AC36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AD36" s="53">
+      <c r="AD36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AE36" s="53">
+      <c r="AE36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AF36" s="53">
+      <c r="AF36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AG36" s="53">
+      <c r="AG36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AH36" s="53">
+      <c r="AH36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AI36" s="53">
+      <c r="AI36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AJ36" s="53">
+      <c r="AJ36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AK36" s="53">
+      <c r="AK36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AL36" s="53">
+      <c r="AL36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AM36" s="53">
+      <c r="AM36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AN36" s="53">
+      <c r="AN36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AO36" s="53">
+      <c r="AO36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AP36" s="53">
+      <c r="AP36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AQ36" s="53">
+      <c r="AQ36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AR36" s="53">
+      <c r="AR36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AS36" s="53">
+      <c r="AS36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AT36" s="53">
+      <c r="AT36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AU36" s="53">
+      <c r="AU36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AV36" s="53">
+      <c r="AV36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AW36" s="53">
+      <c r="AW36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AX36" s="53">
+      <c r="AX36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AY36" s="53">
+      <c r="AY36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AZ36" s="53">
+      <c r="AZ36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BA36" s="53">
+      <c r="BA36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB36" s="53">
+      <c r="BB36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC36" s="53">
+      <c r="BC36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BD36" s="53">
+      <c r="BD36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BE36" s="53">
+      <c r="BE36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BF36" s="53">
+      <c r="BF36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BG36" s="53">
+      <c r="BG36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BH36" s="53">
+      <c r="BH36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BI36" s="53">
+      <c r="BI36" s="50">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BJ36" s="37"/>
+      <c r="BJ36" s="36"/>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A37" s="20"/>
@@ -15657,21 +15654,8 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="AC3:AC4"/>
-    <mergeCell ref="BH2:BH4"/>
-    <mergeCell ref="BI2:BI4"/>
-    <mergeCell ref="BJ2:BJ4"/>
-    <mergeCell ref="B2:C4"/>
-    <mergeCell ref="G2:G4"/>
-    <mergeCell ref="W3:W4"/>
-    <mergeCell ref="Y3:Y4"/>
-    <mergeCell ref="Z3:Z4"/>
-    <mergeCell ref="AA3:AA4"/>
-    <mergeCell ref="AB3:AB4"/>
-    <mergeCell ref="BC3:BG3"/>
     <mergeCell ref="A1:BJ1"/>
     <mergeCell ref="I2:AA2"/>
-    <mergeCell ref="AD2:BB2"/>
     <mergeCell ref="I3:N3"/>
     <mergeCell ref="Q3:U3"/>
     <mergeCell ref="AD3:AL3"/>
@@ -15685,6 +15669,19 @@
     <mergeCell ref="F2:F4"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="V3:V4"/>
+    <mergeCell ref="AC3:AC4"/>
+    <mergeCell ref="BH2:BH4"/>
+    <mergeCell ref="BI2:BI4"/>
+    <mergeCell ref="BJ2:BJ4"/>
+    <mergeCell ref="B2:C4"/>
+    <mergeCell ref="G2:G4"/>
+    <mergeCell ref="W3:W4"/>
+    <mergeCell ref="Y3:Y4"/>
+    <mergeCell ref="Z3:Z4"/>
+    <mergeCell ref="AA3:AA4"/>
+    <mergeCell ref="AB3:AB4"/>
+    <mergeCell ref="BC3:BG3"/>
+    <mergeCell ref="AD2:BG2"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15711,25 +15708,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="65" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+    </row>
+    <row r="2" spans="1:9" s="2" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="66"/>
+      <c r="C2" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
-    </row>
-    <row r="2" spans="1:9" s="2" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="67"/>
-      <c r="C2" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>3</v>
@@ -15738,24 +15735,24 @@
         <v>2</v>
       </c>
       <c r="F2" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>85</v>
-      </c>
       <c r="I2" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>43</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>44</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="7"/>
@@ -15777,10 +15774,10 @@
     </row>
     <row r="4" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>45</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>46</v>
       </c>
       <c r="C4" s="6"/>
       <c r="D4" s="8"/>
@@ -15802,10 +15799,10 @@
     </row>
     <row r="5" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>47</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>48</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="8"/>
@@ -15827,10 +15824,10 @@
     </row>
     <row r="6" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>49</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>50</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="8"/>
@@ -15852,10 +15849,10 @@
     </row>
     <row r="7" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>51</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>52</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="8"/>
@@ -15877,10 +15874,10 @@
     </row>
     <row r="8" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="8"/>
@@ -15898,10 +15895,10 @@
     </row>
     <row r="9" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>55</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>56</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="8"/>
@@ -15919,10 +15916,10 @@
     </row>
     <row r="10" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="8"/>
@@ -15940,10 +15937,10 @@
     </row>
     <row r="11" spans="1:9" ht="18" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
@@ -15961,10 +15958,10 @@
     </row>
     <row r="12" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="9"/>
@@ -15982,10 +15979,10 @@
     </row>
     <row r="13" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C13" s="6"/>
       <c r="D13" s="8"/>
@@ -16003,10 +16000,10 @@
     </row>
     <row r="14" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="8"/>
@@ -16024,10 +16021,10 @@
     </row>
     <row r="15" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="8"/>
@@ -16045,10 +16042,10 @@
     </row>
     <row r="16" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="8"/>
@@ -16066,10 +16063,10 @@
     </row>
     <row r="17" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C17" s="6"/>
       <c r="D17" s="8"/>
@@ -16087,10 +16084,10 @@
     </row>
     <row r="18" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="8"/>
@@ -16108,10 +16105,10 @@
     </row>
     <row r="19" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="8"/>
@@ -16129,10 +16126,10 @@
     </row>
     <row r="20" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="8"/>
@@ -16150,10 +16147,10 @@
     </row>
     <row r="21" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C21" s="6"/>
       <c r="D21" s="8"/>
@@ -16171,10 +16168,10 @@
     </row>
     <row r="22" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="8"/>
@@ -16192,10 +16189,10 @@
     </row>
     <row r="23" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="8"/>
@@ -16213,10 +16210,10 @@
     </row>
     <row r="24" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="8"/>
@@ -16234,10 +16231,10 @@
     </row>
     <row r="25" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C25" s="6"/>
       <c r="D25" s="8"/>
@@ -16255,10 +16252,10 @@
     </row>
     <row r="26" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="8"/>
@@ -16276,10 +16273,10 @@
     </row>
     <row r="27" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C27" s="6"/>
       <c r="D27" s="8"/>
@@ -16297,10 +16294,10 @@
     </row>
     <row r="28" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="8"/>
@@ -16318,10 +16315,10 @@
     </row>
     <row r="29" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C29" s="6"/>
       <c r="D29" s="8"/>
@@ -16339,10 +16336,10 @@
     </row>
     <row r="30" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="8"/>
@@ -16360,10 +16357,10 @@
     </row>
     <row r="31" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C31" s="6"/>
       <c r="D31" s="8"/>
@@ -16381,10 +16378,10 @@
     </row>
     <row r="32" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="8"/>
@@ -16418,10 +16415,10 @@
       <c r="I33" s="11"/>
     </row>
     <row r="34" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="68" t="s">
-        <v>86</v>
-      </c>
-      <c r="B34" s="68"/>
+      <c r="A34" s="67" t="s">
+        <v>85</v>
+      </c>
+      <c r="B34" s="67"/>
       <c r="C34" s="9"/>
       <c r="D34" s="9">
         <f>SUM(D3:D33)</f>

--- a/finance/麦安研营业统计_格式化模板.xlsx
+++ b/finance/麦安研营业统计_格式化模板.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wadec\Documents\projects\mainyan-auto\finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8751272A-EA07-46E5-8618-20517DE1E795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E73BB79-C2F2-4558-95F0-D7C65E2CE8F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026年6月东方宝泰店营业额明细统计表" sheetId="1" r:id="rId1"/>
@@ -889,17 +889,35 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="176" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="177" fontId="11" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -913,20 +931,14 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -935,18 +947,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1268,264 +1268,264 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:62" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="53" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
-      <c r="K1" s="60"/>
-      <c r="L1" s="60"/>
-      <c r="M1" s="60"/>
-      <c r="N1" s="60"/>
-      <c r="O1" s="60"/>
-      <c r="P1" s="60"/>
-      <c r="Q1" s="60"/>
-      <c r="R1" s="60"/>
-      <c r="S1" s="60"/>
-      <c r="T1" s="60"/>
-      <c r="U1" s="60"/>
-      <c r="V1" s="60"/>
-      <c r="W1" s="60"/>
-      <c r="X1" s="60"/>
-      <c r="Y1" s="60"/>
-      <c r="Z1" s="60"/>
-      <c r="AA1" s="60"/>
-      <c r="AB1" s="60"/>
-      <c r="AC1" s="60"/>
-      <c r="AD1" s="60"/>
-      <c r="AE1" s="60"/>
-      <c r="AF1" s="60"/>
-      <c r="AG1" s="60"/>
-      <c r="AH1" s="60"/>
-      <c r="AI1" s="60"/>
-      <c r="AJ1" s="60"/>
-      <c r="AK1" s="60"/>
-      <c r="AL1" s="60"/>
-      <c r="AM1" s="60"/>
-      <c r="AN1" s="60"/>
-      <c r="AO1" s="60"/>
-      <c r="AP1" s="60"/>
-      <c r="AQ1" s="60"/>
-      <c r="AR1" s="60"/>
-      <c r="AS1" s="60"/>
-      <c r="AT1" s="60"/>
-      <c r="AU1" s="60"/>
-      <c r="AV1" s="60"/>
-      <c r="AW1" s="60"/>
-      <c r="AX1" s="60"/>
-      <c r="AY1" s="60"/>
-      <c r="AZ1" s="60"/>
-      <c r="BA1" s="60"/>
-      <c r="BB1" s="60"/>
-      <c r="BC1" s="60"/>
-      <c r="BD1" s="60"/>
-      <c r="BE1" s="60"/>
-      <c r="BF1" s="60"/>
-      <c r="BG1" s="60"/>
-      <c r="BH1" s="60"/>
-      <c r="BI1" s="60"/>
-      <c r="BJ1" s="60"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
+      <c r="N1" s="53"/>
+      <c r="O1" s="53"/>
+      <c r="P1" s="53"/>
+      <c r="Q1" s="53"/>
+      <c r="R1" s="53"/>
+      <c r="S1" s="53"/>
+      <c r="T1" s="53"/>
+      <c r="U1" s="53"/>
+      <c r="V1" s="53"/>
+      <c r="W1" s="53"/>
+      <c r="X1" s="53"/>
+      <c r="Y1" s="53"/>
+      <c r="Z1" s="53"/>
+      <c r="AA1" s="53"/>
+      <c r="AB1" s="53"/>
+      <c r="AC1" s="53"/>
+      <c r="AD1" s="53"/>
+      <c r="AE1" s="53"/>
+      <c r="AF1" s="53"/>
+      <c r="AG1" s="53"/>
+      <c r="AH1" s="53"/>
+      <c r="AI1" s="53"/>
+      <c r="AJ1" s="53"/>
+      <c r="AK1" s="53"/>
+      <c r="AL1" s="53"/>
+      <c r="AM1" s="53"/>
+      <c r="AN1" s="53"/>
+      <c r="AO1" s="53"/>
+      <c r="AP1" s="53"/>
+      <c r="AQ1" s="53"/>
+      <c r="AR1" s="53"/>
+      <c r="AS1" s="53"/>
+      <c r="AT1" s="53"/>
+      <c r="AU1" s="53"/>
+      <c r="AV1" s="53"/>
+      <c r="AW1" s="53"/>
+      <c r="AX1" s="53"/>
+      <c r="AY1" s="53"/>
+      <c r="AZ1" s="53"/>
+      <c r="BA1" s="53"/>
+      <c r="BB1" s="53"/>
+      <c r="BC1" s="53"/>
+      <c r="BD1" s="53"/>
+      <c r="BE1" s="53"/>
+      <c r="BF1" s="53"/>
+      <c r="BG1" s="53"/>
+      <c r="BH1" s="53"/>
+      <c r="BI1" s="53"/>
+      <c r="BJ1" s="53"/>
     </row>
     <row r="2" spans="1:62" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="52" t="s">
+      <c r="A2" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52" t="s">
+      <c r="C2" s="55"/>
+      <c r="D2" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="52" t="s">
+      <c r="E2" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="52" t="s">
+      <c r="F2" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="55" t="s">
+      <c r="G2" s="59" t="s">
         <v>106</v>
       </c>
-      <c r="H2" s="64" t="s">
+      <c r="H2" s="58" t="s">
         <v>87</v>
       </c>
-      <c r="I2" s="61" t="s">
+      <c r="I2" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="61"/>
-      <c r="M2" s="61"/>
-      <c r="N2" s="61"/>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="61"/>
-      <c r="W2" s="61"/>
-      <c r="X2" s="61"/>
-      <c r="Y2" s="61"/>
-      <c r="Z2" s="61"/>
-      <c r="AA2" s="61"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="54"/>
+      <c r="N2" s="54"/>
+      <c r="O2" s="54"/>
+      <c r="P2" s="54"/>
+      <c r="Q2" s="54"/>
+      <c r="R2" s="54"/>
+      <c r="S2" s="54"/>
+      <c r="T2" s="54"/>
+      <c r="U2" s="54"/>
+      <c r="V2" s="54"/>
+      <c r="W2" s="54"/>
+      <c r="X2" s="54"/>
+      <c r="Y2" s="54"/>
+      <c r="Z2" s="54"/>
+      <c r="AA2" s="54"/>
       <c r="AB2" s="25"/>
       <c r="AC2" s="25"/>
-      <c r="AD2" s="69" t="s">
+      <c r="AD2" s="66" t="s">
         <v>113</v>
       </c>
-      <c r="AE2" s="70"/>
-      <c r="AF2" s="70"/>
-      <c r="AG2" s="70"/>
-      <c r="AH2" s="70"/>
-      <c r="AI2" s="70"/>
-      <c r="AJ2" s="70"/>
-      <c r="AK2" s="70"/>
-      <c r="AL2" s="70"/>
-      <c r="AM2" s="70"/>
-      <c r="AN2" s="70"/>
-      <c r="AO2" s="70"/>
-      <c r="AP2" s="70"/>
-      <c r="AQ2" s="70"/>
-      <c r="AR2" s="70"/>
-      <c r="AS2" s="70"/>
-      <c r="AT2" s="70"/>
-      <c r="AU2" s="70"/>
-      <c r="AV2" s="70"/>
-      <c r="AW2" s="70"/>
-      <c r="AX2" s="70"/>
-      <c r="AY2" s="70"/>
-      <c r="AZ2" s="70"/>
-      <c r="BA2" s="70"/>
-      <c r="BB2" s="70"/>
-      <c r="BC2" s="70"/>
-      <c r="BD2" s="70"/>
-      <c r="BE2" s="70"/>
-      <c r="BF2" s="70"/>
-      <c r="BG2" s="71"/>
-      <c r="BH2" s="53" t="s">
+      <c r="AE2" s="67"/>
+      <c r="AF2" s="67"/>
+      <c r="AG2" s="67"/>
+      <c r="AH2" s="67"/>
+      <c r="AI2" s="67"/>
+      <c r="AJ2" s="67"/>
+      <c r="AK2" s="67"/>
+      <c r="AL2" s="67"/>
+      <c r="AM2" s="67"/>
+      <c r="AN2" s="67"/>
+      <c r="AO2" s="67"/>
+      <c r="AP2" s="67"/>
+      <c r="AQ2" s="67"/>
+      <c r="AR2" s="67"/>
+      <c r="AS2" s="67"/>
+      <c r="AT2" s="67"/>
+      <c r="AU2" s="67"/>
+      <c r="AV2" s="67"/>
+      <c r="AW2" s="67"/>
+      <c r="AX2" s="67"/>
+      <c r="AY2" s="67"/>
+      <c r="AZ2" s="67"/>
+      <c r="BA2" s="67"/>
+      <c r="BB2" s="67"/>
+      <c r="BC2" s="67"/>
+      <c r="BD2" s="67"/>
+      <c r="BE2" s="67"/>
+      <c r="BF2" s="67"/>
+      <c r="BG2" s="68"/>
+      <c r="BH2" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="BI2" s="54" t="s">
+      <c r="BI2" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="BJ2" s="52" t="s">
+      <c r="BJ2" s="55" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:62" s="18" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="52"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="52" t="s">
+      <c r="A3" s="55"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="52"/>
-      <c r="K3" s="52"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="52"/>
-      <c r="N3" s="52"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="55"/>
+      <c r="L3" s="55"/>
+      <c r="M3" s="55"/>
+      <c r="N3" s="55"/>
       <c r="O3" s="23"/>
       <c r="P3" s="23"/>
-      <c r="Q3" s="52" t="s">
+      <c r="Q3" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="R3" s="52"/>
-      <c r="S3" s="52"/>
-      <c r="T3" s="52"/>
-      <c r="U3" s="52"/>
-      <c r="V3" s="55" t="s">
+      <c r="R3" s="55"/>
+      <c r="S3" s="55"/>
+      <c r="T3" s="55"/>
+      <c r="U3" s="55"/>
+      <c r="V3" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="W3" s="55" t="s">
+      <c r="W3" s="59" t="s">
         <v>12</v>
       </c>
       <c r="X3" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="Y3" s="56" t="s">
+      <c r="Y3" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="Z3" s="56" t="s">
+      <c r="Z3" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="AA3" s="52" t="s">
+      <c r="AA3" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="AB3" s="52" t="s">
+      <c r="AB3" s="55" t="s">
         <v>16</v>
       </c>
-      <c r="AC3" s="52" t="s">
+      <c r="AC3" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="AD3" s="62" t="s">
+      <c r="AD3" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="AE3" s="62"/>
-      <c r="AF3" s="62"/>
-      <c r="AG3" s="62"/>
-      <c r="AH3" s="62"/>
-      <c r="AI3" s="62"/>
-      <c r="AJ3" s="62"/>
-      <c r="AK3" s="62"/>
-      <c r="AL3" s="62"/>
-      <c r="AM3" s="62" t="s">
+      <c r="AE3" s="56"/>
+      <c r="AF3" s="56"/>
+      <c r="AG3" s="56"/>
+      <c r="AH3" s="56"/>
+      <c r="AI3" s="56"/>
+      <c r="AJ3" s="56"/>
+      <c r="AK3" s="56"/>
+      <c r="AL3" s="56"/>
+      <c r="AM3" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="AN3" s="62"/>
-      <c r="AO3" s="62"/>
-      <c r="AP3" s="62"/>
-      <c r="AQ3" s="62"/>
-      <c r="AR3" s="62"/>
-      <c r="AS3" s="62" t="s">
+      <c r="AN3" s="56"/>
+      <c r="AO3" s="56"/>
+      <c r="AP3" s="56"/>
+      <c r="AQ3" s="56"/>
+      <c r="AR3" s="56"/>
+      <c r="AS3" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="AT3" s="62"/>
-      <c r="AU3" s="62"/>
+      <c r="AT3" s="56"/>
+      <c r="AU3" s="56"/>
       <c r="AV3" s="26"/>
-      <c r="AW3" s="63" t="s">
+      <c r="AW3" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="AX3" s="63"/>
-      <c r="AY3" s="62" t="s">
+      <c r="AX3" s="57"/>
+      <c r="AY3" s="56" t="s">
         <v>89</v>
       </c>
-      <c r="AZ3" s="62"/>
-      <c r="BA3" s="62"/>
-      <c r="BB3" s="62"/>
-      <c r="BC3" s="57" t="s">
+      <c r="AZ3" s="56"/>
+      <c r="BA3" s="56"/>
+      <c r="BB3" s="56"/>
+      <c r="BC3" s="63" t="s">
         <v>108</v>
       </c>
-      <c r="BD3" s="58"/>
-      <c r="BE3" s="58"/>
-      <c r="BF3" s="58"/>
-      <c r="BG3" s="59"/>
-      <c r="BH3" s="53"/>
-      <c r="BI3" s="54"/>
-      <c r="BJ3" s="52"/>
+      <c r="BD3" s="64"/>
+      <c r="BE3" s="64"/>
+      <c r="BF3" s="64"/>
+      <c r="BG3" s="65"/>
+      <c r="BH3" s="60"/>
+      <c r="BI3" s="61"/>
+      <c r="BJ3" s="55"/>
     </row>
     <row r="4" spans="1:62" s="18" customFormat="1" ht="87" x14ac:dyDescent="0.25">
-      <c r="A4" s="52"/>
-      <c r="B4" s="52"/>
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="64"/>
+      <c r="A4" s="55"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="58"/>
       <c r="I4" s="23" t="s">
         <v>22</v>
       </c>
@@ -1565,16 +1565,16 @@
       <c r="U4" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="V4" s="55"/>
-      <c r="W4" s="55"/>
+      <c r="V4" s="59"/>
+      <c r="W4" s="59"/>
       <c r="X4" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="Y4" s="56"/>
-      <c r="Z4" s="56"/>
-      <c r="AA4" s="52"/>
-      <c r="AB4" s="52"/>
-      <c r="AC4" s="52"/>
+      <c r="Y4" s="62"/>
+      <c r="Z4" s="62"/>
+      <c r="AA4" s="55"/>
+      <c r="AB4" s="55"/>
+      <c r="AC4" s="55"/>
       <c r="AD4" s="24" t="s">
         <v>107</v>
       </c>
@@ -1665,9 +1665,9 @@
       <c r="BG4" s="34" t="s">
         <v>110</v>
       </c>
-      <c r="BH4" s="53"/>
-      <c r="BI4" s="54"/>
-      <c r="BJ4" s="52"/>
+      <c r="BH4" s="60"/>
+      <c r="BI4" s="61"/>
+      <c r="BJ4" s="55"/>
     </row>
     <row r="5" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="23">
@@ -1767,11 +1767,11 @@
       </c>
       <c r="BG5" s="39"/>
       <c r="BH5" s="45">
-        <f>G5+M5+T5+AK5+AQ5+AU5+AW5+BA5</f>
+        <f>G5+M5+T5+AK5+AQ5+AU5+AW5+BA5+BF5</f>
         <v>0</v>
       </c>
       <c r="BI5" s="46">
-        <f>G5+K5+R5+AE5+AM5+AS5+AW5+AY5</f>
+        <f>G5+K5+R5+AE5+AM5+AS5+AW5+AY5+BC5</f>
         <v>0</v>
       </c>
       <c r="BJ5" s="36"/>
@@ -1874,11 +1874,11 @@
       </c>
       <c r="BG6" s="39"/>
       <c r="BH6" s="45">
-        <f t="shared" ref="BH6:BH35" si="11">G6+M6+T6+AK6+AQ6+AU6+AW6+BA6</f>
+        <f t="shared" ref="BH6:BH35" si="11">G6+M6+T6+AK6+AQ6+AU6+AW6+BA6+BF6</f>
         <v>0</v>
       </c>
       <c r="BI6" s="46">
-        <f t="shared" ref="BI6:BI35" si="12">G6+K6+R6+AE6+AM6+AS6+AW6+AY6</f>
+        <f t="shared" ref="BI6:BI35" si="12">G6+K6+R6+AE6+AM6+AS6+AW6+AY6+BC6</f>
         <v>0</v>
       </c>
       <c r="BJ6" s="36"/>
@@ -2223,7 +2223,7 @@
       <c r="F10" s="39"/>
       <c r="G10" s="39"/>
       <c r="H10" s="39"/>
-      <c r="I10" s="68"/>
+      <c r="I10" s="52"/>
       <c r="J10" s="39"/>
       <c r="K10" s="42">
         <f t="shared" si="8"/>
@@ -15654,6 +15654,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="BH2:BH4"/>
+    <mergeCell ref="BI2:BI4"/>
+    <mergeCell ref="BJ2:BJ4"/>
+    <mergeCell ref="B2:C4"/>
+    <mergeCell ref="G2:G4"/>
+    <mergeCell ref="W3:W4"/>
+    <mergeCell ref="Y3:Y4"/>
+    <mergeCell ref="Z3:Z4"/>
+    <mergeCell ref="AA3:AA4"/>
+    <mergeCell ref="AB3:AB4"/>
+    <mergeCell ref="BC3:BG3"/>
+    <mergeCell ref="AD2:BG2"/>
     <mergeCell ref="A1:BJ1"/>
     <mergeCell ref="I2:AA2"/>
     <mergeCell ref="I3:N3"/>
@@ -15670,18 +15682,6 @@
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="V3:V4"/>
     <mergeCell ref="AC3:AC4"/>
-    <mergeCell ref="BH2:BH4"/>
-    <mergeCell ref="BI2:BI4"/>
-    <mergeCell ref="BJ2:BJ4"/>
-    <mergeCell ref="B2:C4"/>
-    <mergeCell ref="G2:G4"/>
-    <mergeCell ref="W3:W4"/>
-    <mergeCell ref="Y3:Y4"/>
-    <mergeCell ref="Z3:Z4"/>
-    <mergeCell ref="AA3:AA4"/>
-    <mergeCell ref="AB3:AB4"/>
-    <mergeCell ref="BC3:BG3"/>
-    <mergeCell ref="AD2:BG2"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15708,23 +15708,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="69" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
     </row>
     <row r="2" spans="1:9" s="2" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="66"/>
+      <c r="B2" s="70"/>
       <c r="C2" s="3" t="s">
         <v>81</v>
       </c>
@@ -16415,10 +16415,10 @@
       <c r="I33" s="11"/>
     </row>
     <row r="34" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="67" t="s">
+      <c r="A34" s="71" t="s">
         <v>85</v>
       </c>
-      <c r="B34" s="67"/>
+      <c r="B34" s="71"/>
       <c r="C34" s="9"/>
       <c r="D34" s="9">
         <f>SUM(D3:D33)</f>

--- a/finance/麦安研营业统计_格式化模板.xlsx
+++ b/finance/麦安研营业统计_格式化模板.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wadec\Documents\projects\mainyan-auto\finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E73BB79-C2F2-4558-95F0-D7C65E2CE8F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5B1448C-1485-4627-B62D-69761D8822C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026年6月东方宝泰店营业额明细统计表" sheetId="1" r:id="rId1"/>
@@ -344,15 +344,15 @@
   <si>
     <t>现金合计
 （人工）</t>
-    <phoneticPr fontId="23" type="noConversion"/>
+    <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
     <t>美团推广费</t>
-    <phoneticPr fontId="23" type="noConversion"/>
+    <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
     <t>高德口碑外卖后台</t>
-    <phoneticPr fontId="23" type="noConversion"/>
+    <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
     <t>订单金额</t>
@@ -362,15 +362,15 @@
   </si>
   <si>
     <t>商家优惠</t>
-    <phoneticPr fontId="23" type="noConversion"/>
+    <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
     <t>服务费</t>
-    <phoneticPr fontId="23" type="noConversion"/>
+    <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
     <t>美团优惠、建设银行、招商优惠卷、抖音卷系统后台、高德口碑后台收入</t>
-    <phoneticPr fontId="23" type="noConversion"/>
+    <phoneticPr fontId="20" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -381,7 +381,7 @@
     <numFmt numFmtId="176" formatCode="0.00_ "/>
     <numFmt numFmtId="177" formatCode="0.00_);\(0.00\)"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -518,27 +518,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF222222"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF1D2129"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
@@ -560,14 +539,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="12"/>
-      <color rgb="FF3F4156"/>
       <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="12"/>
       <name val="微软雅黑"/>
       <family val="2"/>
@@ -732,7 +710,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -793,13 +771,13 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -844,52 +822,37 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="22" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="22" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="22" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="17" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="17" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="17" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1268,264 +1231,264 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:62" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
-      <c r="N1" s="53"/>
-      <c r="O1" s="53"/>
-      <c r="P1" s="53"/>
-      <c r="Q1" s="53"/>
-      <c r="R1" s="53"/>
-      <c r="S1" s="53"/>
-      <c r="T1" s="53"/>
-      <c r="U1" s="53"/>
-      <c r="V1" s="53"/>
-      <c r="W1" s="53"/>
-      <c r="X1" s="53"/>
-      <c r="Y1" s="53"/>
-      <c r="Z1" s="53"/>
-      <c r="AA1" s="53"/>
-      <c r="AB1" s="53"/>
-      <c r="AC1" s="53"/>
-      <c r="AD1" s="53"/>
-      <c r="AE1" s="53"/>
-      <c r="AF1" s="53"/>
-      <c r="AG1" s="53"/>
-      <c r="AH1" s="53"/>
-      <c r="AI1" s="53"/>
-      <c r="AJ1" s="53"/>
-      <c r="AK1" s="53"/>
-      <c r="AL1" s="53"/>
-      <c r="AM1" s="53"/>
-      <c r="AN1" s="53"/>
-      <c r="AO1" s="53"/>
-      <c r="AP1" s="53"/>
-      <c r="AQ1" s="53"/>
-      <c r="AR1" s="53"/>
-      <c r="AS1" s="53"/>
-      <c r="AT1" s="53"/>
-      <c r="AU1" s="53"/>
-      <c r="AV1" s="53"/>
-      <c r="AW1" s="53"/>
-      <c r="AX1" s="53"/>
-      <c r="AY1" s="53"/>
-      <c r="AZ1" s="53"/>
-      <c r="BA1" s="53"/>
-      <c r="BB1" s="53"/>
-      <c r="BC1" s="53"/>
-      <c r="BD1" s="53"/>
-      <c r="BE1" s="53"/>
-      <c r="BF1" s="53"/>
-      <c r="BG1" s="53"/>
-      <c r="BH1" s="53"/>
-      <c r="BI1" s="53"/>
-      <c r="BJ1" s="53"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="48"/>
+      <c r="P1" s="48"/>
+      <c r="Q1" s="48"/>
+      <c r="R1" s="48"/>
+      <c r="S1" s="48"/>
+      <c r="T1" s="48"/>
+      <c r="U1" s="48"/>
+      <c r="V1" s="48"/>
+      <c r="W1" s="48"/>
+      <c r="X1" s="48"/>
+      <c r="Y1" s="48"/>
+      <c r="Z1" s="48"/>
+      <c r="AA1" s="48"/>
+      <c r="AB1" s="48"/>
+      <c r="AC1" s="48"/>
+      <c r="AD1" s="48"/>
+      <c r="AE1" s="48"/>
+      <c r="AF1" s="48"/>
+      <c r="AG1" s="48"/>
+      <c r="AH1" s="48"/>
+      <c r="AI1" s="48"/>
+      <c r="AJ1" s="48"/>
+      <c r="AK1" s="48"/>
+      <c r="AL1" s="48"/>
+      <c r="AM1" s="48"/>
+      <c r="AN1" s="48"/>
+      <c r="AO1" s="48"/>
+      <c r="AP1" s="48"/>
+      <c r="AQ1" s="48"/>
+      <c r="AR1" s="48"/>
+      <c r="AS1" s="48"/>
+      <c r="AT1" s="48"/>
+      <c r="AU1" s="48"/>
+      <c r="AV1" s="48"/>
+      <c r="AW1" s="48"/>
+      <c r="AX1" s="48"/>
+      <c r="AY1" s="48"/>
+      <c r="AZ1" s="48"/>
+      <c r="BA1" s="48"/>
+      <c r="BB1" s="48"/>
+      <c r="BC1" s="48"/>
+      <c r="BD1" s="48"/>
+      <c r="BE1" s="48"/>
+      <c r="BF1" s="48"/>
+      <c r="BG1" s="48"/>
+      <c r="BH1" s="48"/>
+      <c r="BI1" s="48"/>
+      <c r="BJ1" s="48"/>
     </row>
     <row r="2" spans="1:62" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="55" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="55" t="s">
+      <c r="A2" s="50" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55" t="s">
+      <c r="C2" s="50"/>
+      <c r="D2" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="55" t="s">
+      <c r="E2" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="55" t="s">
+      <c r="F2" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="59" t="s">
+      <c r="G2" s="54" t="s">
         <v>106</v>
       </c>
-      <c r="H2" s="58" t="s">
+      <c r="H2" s="53" t="s">
         <v>87</v>
       </c>
-      <c r="I2" s="54" t="s">
+      <c r="I2" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
-      <c r="M2" s="54"/>
-      <c r="N2" s="54"/>
-      <c r="O2" s="54"/>
-      <c r="P2" s="54"/>
-      <c r="Q2" s="54"/>
-      <c r="R2" s="54"/>
-      <c r="S2" s="54"/>
-      <c r="T2" s="54"/>
-      <c r="U2" s="54"/>
-      <c r="V2" s="54"/>
-      <c r="W2" s="54"/>
-      <c r="X2" s="54"/>
-      <c r="Y2" s="54"/>
-      <c r="Z2" s="54"/>
-      <c r="AA2" s="54"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="49"/>
+      <c r="L2" s="49"/>
+      <c r="M2" s="49"/>
+      <c r="N2" s="49"/>
+      <c r="O2" s="49"/>
+      <c r="P2" s="49"/>
+      <c r="Q2" s="49"/>
+      <c r="R2" s="49"/>
+      <c r="S2" s="49"/>
+      <c r="T2" s="49"/>
+      <c r="U2" s="49"/>
+      <c r="V2" s="49"/>
+      <c r="W2" s="49"/>
+      <c r="X2" s="49"/>
+      <c r="Y2" s="49"/>
+      <c r="Z2" s="49"/>
+      <c r="AA2" s="49"/>
       <c r="AB2" s="25"/>
       <c r="AC2" s="25"/>
-      <c r="AD2" s="66" t="s">
+      <c r="AD2" s="61" t="s">
         <v>113</v>
       </c>
-      <c r="AE2" s="67"/>
-      <c r="AF2" s="67"/>
-      <c r="AG2" s="67"/>
-      <c r="AH2" s="67"/>
-      <c r="AI2" s="67"/>
-      <c r="AJ2" s="67"/>
-      <c r="AK2" s="67"/>
-      <c r="AL2" s="67"/>
-      <c r="AM2" s="67"/>
-      <c r="AN2" s="67"/>
-      <c r="AO2" s="67"/>
-      <c r="AP2" s="67"/>
-      <c r="AQ2" s="67"/>
-      <c r="AR2" s="67"/>
-      <c r="AS2" s="67"/>
-      <c r="AT2" s="67"/>
-      <c r="AU2" s="67"/>
-      <c r="AV2" s="67"/>
-      <c r="AW2" s="67"/>
-      <c r="AX2" s="67"/>
-      <c r="AY2" s="67"/>
-      <c r="AZ2" s="67"/>
-      <c r="BA2" s="67"/>
-      <c r="BB2" s="67"/>
-      <c r="BC2" s="67"/>
-      <c r="BD2" s="67"/>
-      <c r="BE2" s="67"/>
-      <c r="BF2" s="67"/>
-      <c r="BG2" s="68"/>
-      <c r="BH2" s="60" t="s">
+      <c r="AE2" s="62"/>
+      <c r="AF2" s="62"/>
+      <c r="AG2" s="62"/>
+      <c r="AH2" s="62"/>
+      <c r="AI2" s="62"/>
+      <c r="AJ2" s="62"/>
+      <c r="AK2" s="62"/>
+      <c r="AL2" s="62"/>
+      <c r="AM2" s="62"/>
+      <c r="AN2" s="62"/>
+      <c r="AO2" s="62"/>
+      <c r="AP2" s="62"/>
+      <c r="AQ2" s="62"/>
+      <c r="AR2" s="62"/>
+      <c r="AS2" s="62"/>
+      <c r="AT2" s="62"/>
+      <c r="AU2" s="62"/>
+      <c r="AV2" s="62"/>
+      <c r="AW2" s="62"/>
+      <c r="AX2" s="62"/>
+      <c r="AY2" s="62"/>
+      <c r="AZ2" s="62"/>
+      <c r="BA2" s="62"/>
+      <c r="BB2" s="62"/>
+      <c r="BC2" s="62"/>
+      <c r="BD2" s="62"/>
+      <c r="BE2" s="62"/>
+      <c r="BF2" s="62"/>
+      <c r="BG2" s="63"/>
+      <c r="BH2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="BI2" s="61" t="s">
+      <c r="BI2" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="BJ2" s="55" t="s">
+      <c r="BJ2" s="50" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:62" s="18" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="55"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="55" t="s">
+      <c r="A3" s="50"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="55"/>
-      <c r="K3" s="55"/>
-      <c r="L3" s="55"/>
-      <c r="M3" s="55"/>
-      <c r="N3" s="55"/>
+      <c r="J3" s="50"/>
+      <c r="K3" s="50"/>
+      <c r="L3" s="50"/>
+      <c r="M3" s="50"/>
+      <c r="N3" s="50"/>
       <c r="O3" s="23"/>
       <c r="P3" s="23"/>
-      <c r="Q3" s="55" t="s">
+      <c r="Q3" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="R3" s="55"/>
-      <c r="S3" s="55"/>
-      <c r="T3" s="55"/>
-      <c r="U3" s="55"/>
-      <c r="V3" s="59" t="s">
+      <c r="R3" s="50"/>
+      <c r="S3" s="50"/>
+      <c r="T3" s="50"/>
+      <c r="U3" s="50"/>
+      <c r="V3" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="W3" s="59" t="s">
+      <c r="W3" s="54" t="s">
         <v>12</v>
       </c>
       <c r="X3" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="Y3" s="62" t="s">
+      <c r="Y3" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="Z3" s="62" t="s">
+      <c r="Z3" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="AA3" s="55" t="s">
+      <c r="AA3" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="AB3" s="55" t="s">
+      <c r="AB3" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="AC3" s="55" t="s">
+      <c r="AC3" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="AD3" s="56" t="s">
+      <c r="AD3" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="AE3" s="56"/>
-      <c r="AF3" s="56"/>
-      <c r="AG3" s="56"/>
-      <c r="AH3" s="56"/>
-      <c r="AI3" s="56"/>
-      <c r="AJ3" s="56"/>
-      <c r="AK3" s="56"/>
-      <c r="AL3" s="56"/>
-      <c r="AM3" s="56" t="s">
+      <c r="AE3" s="51"/>
+      <c r="AF3" s="51"/>
+      <c r="AG3" s="51"/>
+      <c r="AH3" s="51"/>
+      <c r="AI3" s="51"/>
+      <c r="AJ3" s="51"/>
+      <c r="AK3" s="51"/>
+      <c r="AL3" s="51"/>
+      <c r="AM3" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="AN3" s="56"/>
-      <c r="AO3" s="56"/>
-      <c r="AP3" s="56"/>
-      <c r="AQ3" s="56"/>
-      <c r="AR3" s="56"/>
-      <c r="AS3" s="56" t="s">
+      <c r="AN3" s="51"/>
+      <c r="AO3" s="51"/>
+      <c r="AP3" s="51"/>
+      <c r="AQ3" s="51"/>
+      <c r="AR3" s="51"/>
+      <c r="AS3" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="AT3" s="56"/>
-      <c r="AU3" s="56"/>
+      <c r="AT3" s="51"/>
+      <c r="AU3" s="51"/>
       <c r="AV3" s="26"/>
-      <c r="AW3" s="57" t="s">
+      <c r="AW3" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="AX3" s="57"/>
-      <c r="AY3" s="56" t="s">
+      <c r="AX3" s="52"/>
+      <c r="AY3" s="51" t="s">
         <v>89</v>
       </c>
-      <c r="AZ3" s="56"/>
-      <c r="BA3" s="56"/>
-      <c r="BB3" s="56"/>
-      <c r="BC3" s="63" t="s">
+      <c r="AZ3" s="51"/>
+      <c r="BA3" s="51"/>
+      <c r="BB3" s="51"/>
+      <c r="BC3" s="58" t="s">
         <v>108</v>
       </c>
-      <c r="BD3" s="64"/>
-      <c r="BE3" s="64"/>
-      <c r="BF3" s="64"/>
-      <c r="BG3" s="65"/>
-      <c r="BH3" s="60"/>
-      <c r="BI3" s="61"/>
-      <c r="BJ3" s="55"/>
+      <c r="BD3" s="59"/>
+      <c r="BE3" s="59"/>
+      <c r="BF3" s="59"/>
+      <c r="BG3" s="60"/>
+      <c r="BH3" s="55"/>
+      <c r="BI3" s="56"/>
+      <c r="BJ3" s="50"/>
     </row>
     <row r="4" spans="1:62" s="18" customFormat="1" ht="87" x14ac:dyDescent="0.25">
-      <c r="A4" s="55"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="58"/>
+      <c r="A4" s="50"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="50"/>
+      <c r="H4" s="53"/>
       <c r="I4" s="23" t="s">
         <v>22</v>
       </c>
@@ -1565,16 +1528,16 @@
       <c r="U4" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="V4" s="59"/>
-      <c r="W4" s="59"/>
+      <c r="V4" s="54"/>
+      <c r="W4" s="54"/>
       <c r="X4" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="Y4" s="62"/>
-      <c r="Z4" s="62"/>
-      <c r="AA4" s="55"/>
-      <c r="AB4" s="55"/>
-      <c r="AC4" s="55"/>
+      <c r="Y4" s="57"/>
+      <c r="Z4" s="57"/>
+      <c r="AA4" s="50"/>
+      <c r="AB4" s="50"/>
+      <c r="AC4" s="50"/>
       <c r="AD4" s="24" t="s">
         <v>107</v>
       </c>
@@ -1650,24 +1613,24 @@
       <c r="BB4" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="BC4" s="51" t="s">
+      <c r="BC4" s="37" t="s">
         <v>109</v>
       </c>
-      <c r="BD4" s="51" t="s">
+      <c r="BD4" s="37" t="s">
         <v>111</v>
       </c>
-      <c r="BE4" s="51" t="s">
+      <c r="BE4" s="37" t="s">
         <v>112</v>
       </c>
-      <c r="BF4" s="51" t="s">
+      <c r="BF4" s="37" t="s">
         <v>39</v>
       </c>
       <c r="BG4" s="34" t="s">
         <v>110</v>
       </c>
-      <c r="BH4" s="60"/>
-      <c r="BI4" s="61"/>
-      <c r="BJ4" s="55"/>
+      <c r="BH4" s="55"/>
+      <c r="BI4" s="56"/>
+      <c r="BJ4" s="50"/>
     </row>
     <row r="5" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="23">
@@ -1680,7 +1643,7 @@
       <c r="C5" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="42">
+      <c r="D5" s="38">
         <f>F5-E5</f>
         <v>0</v>
       </c>
@@ -1690,12 +1653,12 @@
       <c r="H5" s="39"/>
       <c r="I5" s="39"/>
       <c r="J5" s="39"/>
-      <c r="K5" s="42">
+      <c r="K5" s="38">
         <f>I5-J5</f>
         <v>0</v>
       </c>
       <c r="L5" s="39"/>
-      <c r="M5" s="42">
+      <c r="M5" s="38">
         <f t="shared" ref="M5:M35" si="1">K5-L5</f>
         <v>0</v>
       </c>
@@ -1703,12 +1666,12 @@
       <c r="O5" s="39"/>
       <c r="P5" s="39"/>
       <c r="Q5" s="39"/>
-      <c r="R5" s="42">
+      <c r="R5" s="38">
         <f t="shared" ref="R5:R35" si="2">P5-Q5</f>
         <v>0</v>
       </c>
       <c r="S5" s="39"/>
-      <c r="T5" s="42">
+      <c r="T5" s="38">
         <f t="shared" ref="T5:T35" si="3">R5-S5</f>
         <v>0</v>
       </c>
@@ -1721,14 +1684,14 @@
       <c r="AA5" s="39"/>
       <c r="AB5" s="39"/>
       <c r="AC5" s="39"/>
-      <c r="AD5" s="43"/>
-      <c r="AE5" s="43"/>
+      <c r="AD5" s="39"/>
+      <c r="AE5" s="39"/>
       <c r="AF5" s="39"/>
       <c r="AG5" s="39"/>
       <c r="AH5" s="39"/>
       <c r="AI5" s="39"/>
       <c r="AJ5" s="39"/>
-      <c r="AK5" s="42">
+      <c r="AK5" s="38">
         <f>AE5+AF5-AG5-AH5-AI5-AJ5</f>
         <v>0</v>
       </c>
@@ -1736,24 +1699,24 @@
       <c r="AM5" s="39"/>
       <c r="AN5" s="39"/>
       <c r="AO5" s="39"/>
-      <c r="AP5" s="44"/>
-      <c r="AQ5" s="42">
+      <c r="AP5" s="40"/>
+      <c r="AQ5" s="38">
         <f t="shared" ref="AQ5:AQ26" si="4">AM5-AN5-AO5-AP5</f>
         <v>0</v>
       </c>
       <c r="AR5" s="39"/>
       <c r="AS5" s="39"/>
       <c r="AT5" s="39"/>
-      <c r="AU5" s="42">
+      <c r="AU5" s="38">
         <f t="shared" ref="AU5:AU35" si="5">AS5-AT5</f>
         <v>0</v>
       </c>
       <c r="AV5" s="39"/>
       <c r="AW5" s="39"/>
       <c r="AX5" s="39"/>
-      <c r="AY5" s="44"/>
+      <c r="AY5" s="40"/>
       <c r="AZ5" s="39"/>
-      <c r="BA5" s="42">
+      <c r="BA5" s="38">
         <f t="shared" ref="BA5:BA35" si="6">AY5-AZ5</f>
         <v>0</v>
       </c>
@@ -1761,20 +1724,20 @@
       <c r="BC5" s="39"/>
       <c r="BD5" s="39"/>
       <c r="BE5" s="39"/>
-      <c r="BF5" s="42">
+      <c r="BF5" s="38">
         <f>BC5-BD5-BE5</f>
         <v>0</v>
       </c>
       <c r="BG5" s="39"/>
-      <c r="BH5" s="45">
+      <c r="BH5" s="41">
         <f>G5+M5+T5+AK5+AQ5+AU5+AW5+BA5+BF5</f>
         <v>0</v>
       </c>
-      <c r="BI5" s="46">
+      <c r="BI5" s="42">
         <f>G5+K5+R5+AE5+AM5+AS5+AW5+AY5+BC5</f>
         <v>0</v>
       </c>
-      <c r="BJ5" s="36"/>
+      <c r="BJ5" s="43"/>
     </row>
     <row r="6" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="23">
@@ -1787,7 +1750,7 @@
       <c r="C6" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="42">
+      <c r="D6" s="38">
         <f t="shared" ref="D6:D35" si="7">F6-E6</f>
         <v>0</v>
       </c>
@@ -1797,12 +1760,12 @@
       <c r="H6" s="39"/>
       <c r="I6" s="39"/>
       <c r="J6" s="39"/>
-      <c r="K6" s="42">
+      <c r="K6" s="38">
         <f t="shared" ref="K6:K35" si="8">I6-J6</f>
         <v>0</v>
       </c>
       <c r="L6" s="39"/>
-      <c r="M6" s="42">
+      <c r="M6" s="38">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1810,12 +1773,12 @@
       <c r="O6" s="39"/>
       <c r="P6" s="39"/>
       <c r="Q6" s="39"/>
-      <c r="R6" s="42">
+      <c r="R6" s="38">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S6" s="39"/>
-      <c r="T6" s="42">
+      <c r="T6" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -1835,7 +1798,7 @@
       <c r="AH6" s="39"/>
       <c r="AI6" s="39"/>
       <c r="AJ6" s="39"/>
-      <c r="AK6" s="42">
+      <c r="AK6" s="38">
         <f t="shared" ref="AK6:AK35" si="9">AE6+AF6-AG6-AH6-AI6-AJ6</f>
         <v>0</v>
       </c>
@@ -1843,24 +1806,24 @@
       <c r="AM6" s="39"/>
       <c r="AN6" s="39"/>
       <c r="AO6" s="39"/>
-      <c r="AP6" s="44"/>
-      <c r="AQ6" s="42">
+      <c r="AP6" s="40"/>
+      <c r="AQ6" s="38">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AR6" s="39"/>
       <c r="AS6" s="39"/>
       <c r="AT6" s="39"/>
-      <c r="AU6" s="42">
+      <c r="AU6" s="38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV6" s="39"/>
       <c r="AW6" s="39"/>
       <c r="AX6" s="39"/>
-      <c r="AY6" s="44"/>
+      <c r="AY6" s="40"/>
       <c r="AZ6" s="39"/>
-      <c r="BA6" s="42">
+      <c r="BA6" s="38">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -1868,20 +1831,20 @@
       <c r="BC6" s="39"/>
       <c r="BD6" s="39"/>
       <c r="BE6" s="39"/>
-      <c r="BF6" s="42">
+      <c r="BF6" s="38">
         <f t="shared" ref="BF6:BF35" si="10">BC6-BD6-BE6</f>
         <v>0</v>
       </c>
       <c r="BG6" s="39"/>
-      <c r="BH6" s="45">
+      <c r="BH6" s="41">
         <f t="shared" ref="BH6:BH35" si="11">G6+M6+T6+AK6+AQ6+AU6+AW6+BA6+BF6</f>
         <v>0</v>
       </c>
-      <c r="BI6" s="46">
+      <c r="BI6" s="42">
         <f t="shared" ref="BI6:BI35" si="12">G6+K6+R6+AE6+AM6+AS6+AW6+AY6+BC6</f>
         <v>0</v>
       </c>
-      <c r="BJ6" s="36"/>
+      <c r="BJ6" s="43"/>
     </row>
     <row r="7" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="23">
@@ -1894,7 +1857,7 @@
       <c r="C7" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="D7" s="42">
+      <c r="D7" s="38">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -1904,12 +1867,12 @@
       <c r="H7" s="39"/>
       <c r="I7" s="39"/>
       <c r="J7" s="39"/>
-      <c r="K7" s="42">
+      <c r="K7" s="38">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L7" s="39"/>
-      <c r="M7" s="42">
+      <c r="M7" s="38">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1917,12 +1880,12 @@
       <c r="O7" s="39"/>
       <c r="P7" s="39"/>
       <c r="Q7" s="39"/>
-      <c r="R7" s="42">
+      <c r="R7" s="38">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S7" s="39"/>
-      <c r="T7" s="42">
+      <c r="T7" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -1942,32 +1905,32 @@
       <c r="AH7" s="39"/>
       <c r="AI7" s="39"/>
       <c r="AJ7" s="39"/>
-      <c r="AK7" s="42">
+      <c r="AK7" s="38">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AL7" s="39"/>
       <c r="AM7" s="39"/>
-      <c r="AN7" s="44"/>
-      <c r="AO7" s="44"/>
-      <c r="AP7" s="44"/>
-      <c r="AQ7" s="42">
+      <c r="AN7" s="40"/>
+      <c r="AO7" s="40"/>
+      <c r="AP7" s="40"/>
+      <c r="AQ7" s="38">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AR7" s="39"/>
       <c r="AS7" s="39"/>
       <c r="AT7" s="39"/>
-      <c r="AU7" s="42">
+      <c r="AU7" s="38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV7" s="39"/>
       <c r="AW7" s="39"/>
       <c r="AX7" s="39"/>
-      <c r="AY7" s="44"/>
+      <c r="AY7" s="40"/>
       <c r="AZ7" s="39"/>
-      <c r="BA7" s="42">
+      <c r="BA7" s="38">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -1975,20 +1938,20 @@
       <c r="BC7" s="39"/>
       <c r="BD7" s="39"/>
       <c r="BE7" s="39"/>
-      <c r="BF7" s="42">
+      <c r="BF7" s="38">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BG7" s="39"/>
-      <c r="BH7" s="45">
+      <c r="BH7" s="41">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI7" s="46">
+      <c r="BI7" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ7" s="37"/>
+      <c r="BJ7" s="44"/>
     </row>
     <row r="8" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="23">
@@ -2001,7 +1964,7 @@
       <c r="C8" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="42">
+      <c r="D8" s="38">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -2011,12 +1974,12 @@
       <c r="H8" s="39"/>
       <c r="I8" s="39"/>
       <c r="J8" s="39"/>
-      <c r="K8" s="42">
+      <c r="K8" s="38">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L8" s="39"/>
-      <c r="M8" s="42">
+      <c r="M8" s="38">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2024,12 +1987,12 @@
       <c r="O8" s="39"/>
       <c r="P8" s="39"/>
       <c r="Q8" s="39"/>
-      <c r="R8" s="42">
+      <c r="R8" s="38">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S8" s="39"/>
-      <c r="T8" s="42">
+      <c r="T8" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -2049,7 +2012,7 @@
       <c r="AH8" s="39"/>
       <c r="AI8" s="39"/>
       <c r="AJ8" s="39"/>
-      <c r="AK8" s="42">
+      <c r="AK8" s="38">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -2057,24 +2020,24 @@
       <c r="AM8" s="39"/>
       <c r="AN8" s="39"/>
       <c r="AO8" s="39"/>
-      <c r="AP8" s="44"/>
-      <c r="AQ8" s="42">
+      <c r="AP8" s="40"/>
+      <c r="AQ8" s="38">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AR8" s="39"/>
       <c r="AS8" s="39"/>
       <c r="AT8" s="39"/>
-      <c r="AU8" s="42">
+      <c r="AU8" s="38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV8" s="39"/>
       <c r="AW8" s="39"/>
       <c r="AX8" s="39"/>
-      <c r="AY8" s="44"/>
-      <c r="AZ8" s="44"/>
-      <c r="BA8" s="42">
+      <c r="AY8" s="40"/>
+      <c r="AZ8" s="40"/>
+      <c r="BA8" s="38">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -2082,20 +2045,20 @@
       <c r="BC8" s="39"/>
       <c r="BD8" s="39"/>
       <c r="BE8" s="39"/>
-      <c r="BF8" s="42">
+      <c r="BF8" s="38">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BG8" s="39"/>
-      <c r="BH8" s="45">
+      <c r="BH8" s="41">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI8" s="46">
+      <c r="BI8" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ8" s="38"/>
+      <c r="BJ8" s="45"/>
     </row>
     <row r="9" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="23">
@@ -2108,7 +2071,7 @@
       <c r="C9" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="D9" s="42">
+      <c r="D9" s="38">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -2118,12 +2081,12 @@
       <c r="H9" s="39"/>
       <c r="I9" s="39"/>
       <c r="J9" s="39"/>
-      <c r="K9" s="42">
+      <c r="K9" s="38">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L9" s="39"/>
-      <c r="M9" s="42">
+      <c r="M9" s="38">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2131,12 +2094,12 @@
       <c r="O9" s="39"/>
       <c r="P9" s="39"/>
       <c r="Q9" s="39"/>
-      <c r="R9" s="42">
+      <c r="R9" s="38">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S9" s="39"/>
-      <c r="T9" s="42">
+      <c r="T9" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -2156,7 +2119,7 @@
       <c r="AH9" s="39"/>
       <c r="AI9" s="39"/>
       <c r="AJ9" s="39"/>
-      <c r="AK9" s="42">
+      <c r="AK9" s="38">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -2165,23 +2128,23 @@
       <c r="AN9" s="39"/>
       <c r="AO9" s="39"/>
       <c r="AP9" s="39"/>
-      <c r="AQ9" s="42">
+      <c r="AQ9" s="38">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AR9" s="39"/>
       <c r="AS9" s="39"/>
       <c r="AT9" s="39"/>
-      <c r="AU9" s="42">
+      <c r="AU9" s="38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV9" s="39"/>
       <c r="AW9" s="39"/>
       <c r="AX9" s="39"/>
-      <c r="AY9" s="44"/>
-      <c r="AZ9" s="44"/>
-      <c r="BA9" s="42">
+      <c r="AY9" s="40"/>
+      <c r="AZ9" s="40"/>
+      <c r="BA9" s="38">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -2189,20 +2152,20 @@
       <c r="BC9" s="39"/>
       <c r="BD9" s="39"/>
       <c r="BE9" s="39"/>
-      <c r="BF9" s="42">
+      <c r="BF9" s="38">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BG9" s="39"/>
-      <c r="BH9" s="45">
+      <c r="BH9" s="41">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI9" s="46">
+      <c r="BI9" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ9" s="36"/>
+      <c r="BJ9" s="43"/>
     </row>
     <row r="10" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="23">
@@ -2215,7 +2178,7 @@
       <c r="C10" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="D10" s="42">
+      <c r="D10" s="38">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -2223,14 +2186,14 @@
       <c r="F10" s="39"/>
       <c r="G10" s="39"/>
       <c r="H10" s="39"/>
-      <c r="I10" s="52"/>
+      <c r="I10" s="39"/>
       <c r="J10" s="39"/>
-      <c r="K10" s="42">
+      <c r="K10" s="38">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L10" s="39"/>
-      <c r="M10" s="42">
+      <c r="M10" s="38">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2238,16 +2201,16 @@
       <c r="O10" s="39"/>
       <c r="P10" s="39"/>
       <c r="Q10" s="39"/>
-      <c r="R10" s="42">
+      <c r="R10" s="38">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S10" s="39"/>
-      <c r="T10" s="42">
+      <c r="T10" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U10" s="47"/>
+      <c r="U10" s="39"/>
       <c r="V10" s="39"/>
       <c r="W10" s="39"/>
       <c r="X10" s="39"/>
@@ -2263,7 +2226,7 @@
       <c r="AH10" s="39"/>
       <c r="AI10" s="39"/>
       <c r="AJ10" s="39"/>
-      <c r="AK10" s="42">
+      <c r="AK10" s="38">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -2272,23 +2235,23 @@
       <c r="AN10" s="39"/>
       <c r="AO10" s="39"/>
       <c r="AP10" s="39"/>
-      <c r="AQ10" s="42">
+      <c r="AQ10" s="38">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AR10" s="39"/>
       <c r="AS10" s="39"/>
       <c r="AT10" s="39"/>
-      <c r="AU10" s="42">
+      <c r="AU10" s="38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV10" s="39"/>
       <c r="AW10" s="39"/>
       <c r="AX10" s="39"/>
-      <c r="AY10" s="44"/>
+      <c r="AY10" s="40"/>
       <c r="AZ10" s="39"/>
-      <c r="BA10" s="42">
+      <c r="BA10" s="38">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -2296,20 +2259,20 @@
       <c r="BC10" s="39"/>
       <c r="BD10" s="39"/>
       <c r="BE10" s="39"/>
-      <c r="BF10" s="42">
+      <c r="BF10" s="38">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BG10" s="39"/>
-      <c r="BH10" s="45">
+      <c r="BH10" s="41">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI10" s="46">
+      <c r="BI10" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ10" s="36"/>
+      <c r="BJ10" s="43"/>
     </row>
     <row r="11" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="23">
@@ -2322,7 +2285,7 @@
       <c r="C11" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="D11" s="42">
+      <c r="D11" s="38">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -2332,12 +2295,12 @@
       <c r="H11" s="39"/>
       <c r="I11" s="39"/>
       <c r="J11" s="39"/>
-      <c r="K11" s="42">
+      <c r="K11" s="38">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L11" s="39"/>
-      <c r="M11" s="42">
+      <c r="M11" s="38">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2345,16 +2308,16 @@
       <c r="O11" s="39"/>
       <c r="P11" s="39"/>
       <c r="Q11" s="39"/>
-      <c r="R11" s="42">
+      <c r="R11" s="38">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S11" s="39"/>
-      <c r="T11" s="42">
+      <c r="T11" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U11" s="47"/>
+      <c r="U11" s="39"/>
       <c r="V11" s="39"/>
       <c r="W11" s="39"/>
       <c r="X11" s="39"/>
@@ -2370,7 +2333,7 @@
       <c r="AH11" s="39"/>
       <c r="AI11" s="39"/>
       <c r="AJ11" s="39"/>
-      <c r="AK11" s="42">
+      <c r="AK11" s="38">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -2378,24 +2341,24 @@
       <c r="AM11" s="39"/>
       <c r="AN11" s="39"/>
       <c r="AO11" s="39"/>
-      <c r="AP11" s="44"/>
-      <c r="AQ11" s="42">
+      <c r="AP11" s="40"/>
+      <c r="AQ11" s="38">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AR11" s="39"/>
       <c r="AS11" s="39"/>
       <c r="AT11" s="39"/>
-      <c r="AU11" s="42">
+      <c r="AU11" s="38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV11" s="39"/>
       <c r="AW11" s="39"/>
       <c r="AX11" s="39"/>
-      <c r="AY11" s="44"/>
+      <c r="AY11" s="40"/>
       <c r="AZ11" s="39"/>
-      <c r="BA11" s="42">
+      <c r="BA11" s="38">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -2403,20 +2366,20 @@
       <c r="BC11" s="39"/>
       <c r="BD11" s="39"/>
       <c r="BE11" s="39"/>
-      <c r="BF11" s="42">
+      <c r="BF11" s="38">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BG11" s="39"/>
-      <c r="BH11" s="45">
+      <c r="BH11" s="41">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI11" s="46">
+      <c r="BI11" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ11" s="36"/>
+      <c r="BJ11" s="43"/>
     </row>
     <row r="12" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="23">
@@ -2429,7 +2392,7 @@
       <c r="C12" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="42">
+      <c r="D12" s="38">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -2439,12 +2402,12 @@
       <c r="H12" s="39"/>
       <c r="I12" s="39"/>
       <c r="J12" s="39"/>
-      <c r="K12" s="42">
+      <c r="K12" s="38">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L12" s="39"/>
-      <c r="M12" s="42">
+      <c r="M12" s="38">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2452,16 +2415,16 @@
       <c r="O12" s="39"/>
       <c r="P12" s="39"/>
       <c r="Q12" s="39"/>
-      <c r="R12" s="42">
+      <c r="R12" s="38">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S12" s="39"/>
-      <c r="T12" s="42">
+      <c r="T12" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U12" s="47"/>
+      <c r="U12" s="39"/>
       <c r="V12" s="39"/>
       <c r="W12" s="39"/>
       <c r="X12" s="39"/>
@@ -2477,7 +2440,7 @@
       <c r="AH12" s="39"/>
       <c r="AI12" s="39"/>
       <c r="AJ12" s="39"/>
-      <c r="AK12" s="42">
+      <c r="AK12" s="38">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -2486,23 +2449,23 @@
       <c r="AN12" s="39"/>
       <c r="AO12" s="39"/>
       <c r="AP12" s="39"/>
-      <c r="AQ12" s="42">
+      <c r="AQ12" s="38">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AR12" s="39"/>
       <c r="AS12" s="39"/>
       <c r="AT12" s="39"/>
-      <c r="AU12" s="42">
+      <c r="AU12" s="38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV12" s="39"/>
       <c r="AW12" s="39"/>
       <c r="AX12" s="39"/>
-      <c r="AY12" s="44"/>
+      <c r="AY12" s="40"/>
       <c r="AZ12" s="39"/>
-      <c r="BA12" s="42">
+      <c r="BA12" s="38">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -2510,20 +2473,20 @@
       <c r="BC12" s="39"/>
       <c r="BD12" s="39"/>
       <c r="BE12" s="39"/>
-      <c r="BF12" s="42">
+      <c r="BF12" s="38">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BG12" s="39"/>
-      <c r="BH12" s="45">
+      <c r="BH12" s="41">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI12" s="46">
+      <c r="BI12" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ12" s="36"/>
+      <c r="BJ12" s="43"/>
     </row>
     <row r="13" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="23">
@@ -2536,7 +2499,7 @@
       <c r="C13" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="D13" s="42">
+      <c r="D13" s="38">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -2546,12 +2509,12 @@
       <c r="H13" s="39"/>
       <c r="I13" s="39"/>
       <c r="J13" s="39"/>
-      <c r="K13" s="42">
+      <c r="K13" s="38">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L13" s="39"/>
-      <c r="M13" s="42">
+      <c r="M13" s="38">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2559,16 +2522,16 @@
       <c r="O13" s="39"/>
       <c r="P13" s="39"/>
       <c r="Q13" s="39"/>
-      <c r="R13" s="42">
+      <c r="R13" s="38">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S13" s="39"/>
-      <c r="T13" s="42">
+      <c r="T13" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U13" s="47"/>
+      <c r="U13" s="39"/>
       <c r="V13" s="39"/>
       <c r="W13" s="39"/>
       <c r="X13" s="39"/>
@@ -2584,7 +2547,7 @@
       <c r="AH13" s="39"/>
       <c r="AI13" s="39"/>
       <c r="AJ13" s="39"/>
-      <c r="AK13" s="42">
+      <c r="AK13" s="38">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -2593,23 +2556,23 @@
       <c r="AN13" s="39"/>
       <c r="AO13" s="39"/>
       <c r="AP13" s="39"/>
-      <c r="AQ13" s="42">
+      <c r="AQ13" s="38">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AR13" s="39"/>
       <c r="AS13" s="39"/>
       <c r="AT13" s="39"/>
-      <c r="AU13" s="42">
+      <c r="AU13" s="38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV13" s="39"/>
       <c r="AW13" s="39"/>
       <c r="AX13" s="39"/>
-      <c r="AY13" s="44"/>
+      <c r="AY13" s="40"/>
       <c r="AZ13" s="39"/>
-      <c r="BA13" s="42">
+      <c r="BA13" s="38">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -2617,20 +2580,20 @@
       <c r="BC13" s="39"/>
       <c r="BD13" s="39"/>
       <c r="BE13" s="39"/>
-      <c r="BF13" s="42">
+      <c r="BF13" s="38">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BG13" s="39"/>
-      <c r="BH13" s="45">
+      <c r="BH13" s="41">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI13" s="46">
+      <c r="BI13" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ13" s="36"/>
+      <c r="BJ13" s="43"/>
     </row>
     <row r="14" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="23">
@@ -2643,7 +2606,7 @@
       <c r="C14" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="42">
+      <c r="D14" s="38">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -2653,12 +2616,12 @@
       <c r="H14" s="39"/>
       <c r="I14" s="39"/>
       <c r="J14" s="39"/>
-      <c r="K14" s="42">
+      <c r="K14" s="38">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L14" s="39"/>
-      <c r="M14" s="42">
+      <c r="M14" s="38">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2666,16 +2629,16 @@
       <c r="O14" s="39"/>
       <c r="P14" s="39"/>
       <c r="Q14" s="39"/>
-      <c r="R14" s="42">
+      <c r="R14" s="38">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S14" s="39"/>
-      <c r="T14" s="42">
+      <c r="T14" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U14" s="47"/>
+      <c r="U14" s="39"/>
       <c r="V14" s="39"/>
       <c r="W14" s="39"/>
       <c r="X14" s="39"/>
@@ -2691,7 +2654,7 @@
       <c r="AH14" s="39"/>
       <c r="AI14" s="39"/>
       <c r="AJ14" s="39"/>
-      <c r="AK14" s="42">
+      <c r="AK14" s="38">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -2700,23 +2663,23 @@
       <c r="AN14" s="39"/>
       <c r="AO14" s="39"/>
       <c r="AP14" s="39"/>
-      <c r="AQ14" s="42">
+      <c r="AQ14" s="38">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AR14" s="39"/>
       <c r="AS14" s="39"/>
       <c r="AT14" s="39"/>
-      <c r="AU14" s="42">
+      <c r="AU14" s="38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV14" s="39"/>
       <c r="AW14" s="39"/>
       <c r="AX14" s="39"/>
-      <c r="AY14" s="44"/>
+      <c r="AY14" s="40"/>
       <c r="AZ14" s="39"/>
-      <c r="BA14" s="42">
+      <c r="BA14" s="38">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -2724,20 +2687,20 @@
       <c r="BC14" s="39"/>
       <c r="BD14" s="39"/>
       <c r="BE14" s="39"/>
-      <c r="BF14" s="42">
+      <c r="BF14" s="38">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BG14" s="39"/>
-      <c r="BH14" s="45">
+      <c r="BH14" s="41">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI14" s="46">
+      <c r="BI14" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ14" s="36"/>
+      <c r="BJ14" s="43"/>
     </row>
     <row r="15" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="23">
@@ -2750,7 +2713,7 @@
       <c r="C15" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="D15" s="42">
+      <c r="D15" s="38">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -2760,12 +2723,12 @@
       <c r="H15" s="39"/>
       <c r="I15" s="39"/>
       <c r="J15" s="39"/>
-      <c r="K15" s="42">
+      <c r="K15" s="38">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L15" s="39"/>
-      <c r="M15" s="42">
+      <c r="M15" s="38">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2773,16 +2736,16 @@
       <c r="O15" s="39"/>
       <c r="P15" s="39"/>
       <c r="Q15" s="39"/>
-      <c r="R15" s="42">
+      <c r="R15" s="38">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S15" s="39"/>
-      <c r="T15" s="42">
+      <c r="T15" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U15" s="47"/>
+      <c r="U15" s="39"/>
       <c r="V15" s="39"/>
       <c r="W15" s="39"/>
       <c r="X15" s="39"/>
@@ -2798,7 +2761,7 @@
       <c r="AH15" s="39"/>
       <c r="AI15" s="39"/>
       <c r="AJ15" s="39"/>
-      <c r="AK15" s="42">
+      <c r="AK15" s="38">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -2807,23 +2770,23 @@
       <c r="AN15" s="39"/>
       <c r="AO15" s="39"/>
       <c r="AP15" s="39"/>
-      <c r="AQ15" s="42">
+      <c r="AQ15" s="38">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AR15" s="39"/>
       <c r="AS15" s="39"/>
       <c r="AT15" s="39"/>
-      <c r="AU15" s="42">
+      <c r="AU15" s="38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV15" s="39"/>
       <c r="AW15" s="39"/>
       <c r="AX15" s="39"/>
-      <c r="AY15" s="44"/>
+      <c r="AY15" s="40"/>
       <c r="AZ15" s="39"/>
-      <c r="BA15" s="42">
+      <c r="BA15" s="38">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -2831,20 +2794,20 @@
       <c r="BC15" s="39"/>
       <c r="BD15" s="39"/>
       <c r="BE15" s="39"/>
-      <c r="BF15" s="42">
+      <c r="BF15" s="38">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BG15" s="39"/>
-      <c r="BH15" s="45">
+      <c r="BH15" s="41">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI15" s="46">
+      <c r="BI15" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ15" s="36"/>
+      <c r="BJ15" s="43"/>
     </row>
     <row r="16" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="23">
@@ -2857,7 +2820,7 @@
       <c r="C16" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="42">
+      <c r="D16" s="38">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -2867,12 +2830,12 @@
       <c r="H16" s="39"/>
       <c r="I16" s="39"/>
       <c r="J16" s="39"/>
-      <c r="K16" s="42">
+      <c r="K16" s="38">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L16" s="39"/>
-      <c r="M16" s="42">
+      <c r="M16" s="38">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2880,16 +2843,16 @@
       <c r="O16" s="39"/>
       <c r="P16" s="39"/>
       <c r="Q16" s="39"/>
-      <c r="R16" s="42">
+      <c r="R16" s="38">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S16" s="39"/>
-      <c r="T16" s="42">
+      <c r="T16" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U16" s="47"/>
+      <c r="U16" s="39"/>
       <c r="V16" s="39"/>
       <c r="W16" s="39"/>
       <c r="X16" s="39"/>
@@ -2905,7 +2868,7 @@
       <c r="AH16" s="39"/>
       <c r="AI16" s="39"/>
       <c r="AJ16" s="39"/>
-      <c r="AK16" s="42">
+      <c r="AK16" s="38">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -2914,23 +2877,23 @@
       <c r="AN16" s="39"/>
       <c r="AO16" s="39"/>
       <c r="AP16" s="39"/>
-      <c r="AQ16" s="42">
+      <c r="AQ16" s="38">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AR16" s="39"/>
       <c r="AS16" s="39"/>
       <c r="AT16" s="39"/>
-      <c r="AU16" s="42">
+      <c r="AU16" s="38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV16" s="39"/>
       <c r="AW16" s="39"/>
       <c r="AX16" s="39"/>
-      <c r="AY16" s="44"/>
+      <c r="AY16" s="40"/>
       <c r="AZ16" s="39"/>
-      <c r="BA16" s="42">
+      <c r="BA16" s="38">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -2938,20 +2901,20 @@
       <c r="BC16" s="39"/>
       <c r="BD16" s="39"/>
       <c r="BE16" s="39"/>
-      <c r="BF16" s="42">
+      <c r="BF16" s="38">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BG16" s="39"/>
-      <c r="BH16" s="45">
+      <c r="BH16" s="41">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI16" s="46">
+      <c r="BI16" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ16" s="36"/>
+      <c r="BJ16" s="43"/>
     </row>
     <row r="17" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="23">
@@ -2964,7 +2927,7 @@
       <c r="C17" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="D17" s="42">
+      <c r="D17" s="38">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -2974,12 +2937,12 @@
       <c r="H17" s="39"/>
       <c r="I17" s="39"/>
       <c r="J17" s="39"/>
-      <c r="K17" s="42">
+      <c r="K17" s="38">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L17" s="39"/>
-      <c r="M17" s="42">
+      <c r="M17" s="38">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2987,16 +2950,16 @@
       <c r="O17" s="39"/>
       <c r="P17" s="39"/>
       <c r="Q17" s="39"/>
-      <c r="R17" s="42">
+      <c r="R17" s="38">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S17" s="39"/>
-      <c r="T17" s="42">
+      <c r="T17" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U17" s="47"/>
+      <c r="U17" s="39"/>
       <c r="V17" s="39"/>
       <c r="W17" s="39"/>
       <c r="X17" s="39"/>
@@ -3012,7 +2975,7 @@
       <c r="AH17" s="39"/>
       <c r="AI17" s="39"/>
       <c r="AJ17" s="39"/>
-      <c r="AK17" s="42">
+      <c r="AK17" s="38">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -3021,44 +2984,44 @@
       <c r="AN17" s="39"/>
       <c r="AO17" s="39"/>
       <c r="AP17" s="39"/>
-      <c r="AQ17" s="42">
+      <c r="AQ17" s="38">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AR17" s="39"/>
       <c r="AS17" s="39"/>
       <c r="AT17" s="39"/>
-      <c r="AU17" s="42">
+      <c r="AU17" s="38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV17" s="39"/>
       <c r="AW17" s="39"/>
       <c r="AX17" s="39"/>
-      <c r="AY17" s="44"/>
+      <c r="AY17" s="40"/>
       <c r="AZ17" s="39"/>
-      <c r="BA17" s="42">
+      <c r="BA17" s="38">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB17" s="47"/>
-      <c r="BC17" s="47"/>
-      <c r="BD17" s="47"/>
-      <c r="BE17" s="47"/>
-      <c r="BF17" s="42">
+      <c r="BB17" s="39"/>
+      <c r="BC17" s="39"/>
+      <c r="BD17" s="39"/>
+      <c r="BE17" s="39"/>
+      <c r="BF17" s="38">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BG17" s="47"/>
-      <c r="BH17" s="45">
+      <c r="BG17" s="39"/>
+      <c r="BH17" s="41">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI17" s="46">
+      <c r="BI17" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ17" s="36"/>
+      <c r="BJ17" s="43"/>
     </row>
     <row r="18" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="23">
@@ -3071,7 +3034,7 @@
       <c r="C18" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="D18" s="42">
+      <c r="D18" s="38">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -3081,29 +3044,29 @@
       <c r="H18" s="39"/>
       <c r="I18" s="39"/>
       <c r="J18" s="39"/>
-      <c r="K18" s="42">
+      <c r="K18" s="38">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L18" s="39"/>
-      <c r="M18" s="42">
+      <c r="M18" s="38">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N18" s="48"/>
-      <c r="O18" s="48"/>
+      <c r="N18" s="39"/>
+      <c r="O18" s="39"/>
       <c r="P18" s="39"/>
       <c r="Q18" s="39"/>
-      <c r="R18" s="42">
+      <c r="R18" s="38">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S18" s="39"/>
-      <c r="T18" s="42">
+      <c r="T18" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U18" s="47"/>
+      <c r="U18" s="39"/>
       <c r="V18" s="39"/>
       <c r="W18" s="39"/>
       <c r="X18" s="39"/>
@@ -3119,53 +3082,53 @@
       <c r="AH18" s="39"/>
       <c r="AI18" s="39"/>
       <c r="AJ18" s="39"/>
-      <c r="AK18" s="42">
+      <c r="AK18" s="38">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AL18" s="39"/>
-      <c r="AM18" s="44"/>
+      <c r="AM18" s="40"/>
       <c r="AN18" s="39"/>
       <c r="AO18" s="39"/>
       <c r="AP18" s="39"/>
-      <c r="AQ18" s="42">
+      <c r="AQ18" s="38">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AR18" s="39"/>
       <c r="AS18" s="39"/>
       <c r="AT18" s="39"/>
-      <c r="AU18" s="42">
+      <c r="AU18" s="38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV18" s="39"/>
       <c r="AW18" s="39"/>
       <c r="AX18" s="39"/>
-      <c r="AY18" s="44"/>
+      <c r="AY18" s="40"/>
       <c r="AZ18" s="39"/>
-      <c r="BA18" s="42">
+      <c r="BA18" s="38">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB18" s="47"/>
-      <c r="BC18" s="47"/>
-      <c r="BD18" s="47"/>
-      <c r="BE18" s="47"/>
-      <c r="BF18" s="42">
+      <c r="BB18" s="39"/>
+      <c r="BC18" s="39"/>
+      <c r="BD18" s="39"/>
+      <c r="BE18" s="39"/>
+      <c r="BF18" s="38">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BG18" s="47"/>
-      <c r="BH18" s="45">
+      <c r="BG18" s="39"/>
+      <c r="BH18" s="41">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI18" s="46">
+      <c r="BI18" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ18" s="36"/>
+      <c r="BJ18" s="43"/>
     </row>
     <row r="19" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="23">
@@ -3178,7 +3141,7 @@
       <c r="C19" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="42">
+      <c r="D19" s="38">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -3188,12 +3151,12 @@
       <c r="H19" s="39"/>
       <c r="I19" s="39"/>
       <c r="J19" s="39"/>
-      <c r="K19" s="42">
+      <c r="K19" s="38">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L19" s="39"/>
-      <c r="M19" s="42">
+      <c r="M19" s="38">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3201,16 +3164,16 @@
       <c r="O19" s="39"/>
       <c r="P19" s="39"/>
       <c r="Q19" s="39"/>
-      <c r="R19" s="42">
+      <c r="R19" s="38">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S19" s="39"/>
-      <c r="T19" s="42">
+      <c r="T19" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U19" s="47"/>
+      <c r="U19" s="39"/>
       <c r="V19" s="39"/>
       <c r="W19" s="39"/>
       <c r="X19" s="39"/>
@@ -3226,7 +3189,7 @@
       <c r="AH19" s="39"/>
       <c r="AI19" s="39"/>
       <c r="AJ19" s="39"/>
-      <c r="AK19" s="42">
+      <c r="AK19" s="38">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -3235,14 +3198,14 @@
       <c r="AN19" s="39"/>
       <c r="AO19" s="39"/>
       <c r="AP19" s="39"/>
-      <c r="AQ19" s="42">
+      <c r="AQ19" s="38">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AR19" s="39"/>
       <c r="AS19" s="39"/>
       <c r="AT19" s="39"/>
-      <c r="AU19" s="42">
+      <c r="AU19" s="38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -3251,28 +3214,28 @@
       <c r="AX19" s="39"/>
       <c r="AY19" s="39"/>
       <c r="AZ19" s="39"/>
-      <c r="BA19" s="42">
+      <c r="BA19" s="38">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB19" s="47"/>
-      <c r="BC19" s="47"/>
-      <c r="BD19" s="47"/>
-      <c r="BE19" s="47"/>
-      <c r="BF19" s="42">
+      <c r="BB19" s="39"/>
+      <c r="BC19" s="39"/>
+      <c r="BD19" s="39"/>
+      <c r="BE19" s="39"/>
+      <c r="BF19" s="38">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BG19" s="47"/>
-      <c r="BH19" s="45">
+      <c r="BG19" s="39"/>
+      <c r="BH19" s="41">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI19" s="46">
+      <c r="BI19" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ19" s="36"/>
+      <c r="BJ19" s="43"/>
     </row>
     <row r="20" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="23">
@@ -3285,7 +3248,7 @@
       <c r="C20" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="42">
+      <c r="D20" s="38">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -3295,12 +3258,12 @@
       <c r="H20" s="39"/>
       <c r="I20" s="39"/>
       <c r="J20" s="39"/>
-      <c r="K20" s="42">
+      <c r="K20" s="38">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L20" s="39"/>
-      <c r="M20" s="42">
+      <c r="M20" s="38">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3308,16 +3271,16 @@
       <c r="O20" s="39"/>
       <c r="P20" s="39"/>
       <c r="Q20" s="39"/>
-      <c r="R20" s="42">
+      <c r="R20" s="38">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S20" s="39"/>
-      <c r="T20" s="42">
+      <c r="T20" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U20" s="47"/>
+      <c r="U20" s="39"/>
       <c r="V20" s="39"/>
       <c r="W20" s="39"/>
       <c r="X20" s="39"/>
@@ -3333,7 +3296,7 @@
       <c r="AH20" s="39"/>
       <c r="AI20" s="39"/>
       <c r="AJ20" s="39"/>
-      <c r="AK20" s="42">
+      <c r="AK20" s="38">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -3341,15 +3304,15 @@
       <c r="AM20" s="39"/>
       <c r="AN20" s="39"/>
       <c r="AO20" s="39"/>
-      <c r="AP20" s="44"/>
-      <c r="AQ20" s="42">
+      <c r="AP20" s="40"/>
+      <c r="AQ20" s="38">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AR20" s="39"/>
       <c r="AS20" s="39"/>
       <c r="AT20" s="39"/>
-      <c r="AU20" s="42">
+      <c r="AU20" s="38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -3358,28 +3321,28 @@
       <c r="AX20" s="39"/>
       <c r="AY20" s="39"/>
       <c r="AZ20" s="39"/>
-      <c r="BA20" s="42">
+      <c r="BA20" s="38">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB20" s="47"/>
-      <c r="BC20" s="47"/>
-      <c r="BD20" s="47"/>
-      <c r="BE20" s="47"/>
-      <c r="BF20" s="42">
+      <c r="BB20" s="39"/>
+      <c r="BC20" s="39"/>
+      <c r="BD20" s="39"/>
+      <c r="BE20" s="39"/>
+      <c r="BF20" s="38">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BG20" s="47"/>
-      <c r="BH20" s="45">
+      <c r="BG20" s="39"/>
+      <c r="BH20" s="41">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI20" s="46">
+      <c r="BI20" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ20" s="36"/>
+      <c r="BJ20" s="43"/>
     </row>
     <row r="21" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="23">
@@ -3392,7 +3355,7 @@
       <c r="C21" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="D21" s="42">
+      <c r="D21" s="38">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -3402,12 +3365,12 @@
       <c r="H21" s="39"/>
       <c r="I21" s="39"/>
       <c r="J21" s="39"/>
-      <c r="K21" s="42">
+      <c r="K21" s="38">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L21" s="39"/>
-      <c r="M21" s="42">
+      <c r="M21" s="38">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3415,16 +3378,16 @@
       <c r="O21" s="39"/>
       <c r="P21" s="39"/>
       <c r="Q21" s="39"/>
-      <c r="R21" s="42">
+      <c r="R21" s="38">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S21" s="39"/>
-      <c r="T21" s="42">
+      <c r="T21" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U21" s="47"/>
+      <c r="U21" s="39"/>
       <c r="V21" s="39"/>
       <c r="W21" s="39"/>
       <c r="X21" s="39"/>
@@ -3440,53 +3403,53 @@
       <c r="AH21" s="39"/>
       <c r="AI21" s="39"/>
       <c r="AJ21" s="39"/>
-      <c r="AK21" s="42">
+      <c r="AK21" s="38">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AL21" s="39"/>
-      <c r="AM21" s="44"/>
+      <c r="AM21" s="40"/>
       <c r="AN21" s="39"/>
       <c r="AO21" s="39"/>
-      <c r="AP21" s="44"/>
-      <c r="AQ21" s="42">
+      <c r="AP21" s="40"/>
+      <c r="AQ21" s="38">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AR21" s="39"/>
       <c r="AS21" s="39"/>
       <c r="AT21" s="39"/>
-      <c r="AU21" s="42">
+      <c r="AU21" s="38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV21" s="39"/>
       <c r="AW21" s="39"/>
       <c r="AX21" s="39"/>
-      <c r="AY21" s="44"/>
+      <c r="AY21" s="40"/>
       <c r="AZ21" s="39"/>
-      <c r="BA21" s="42">
+      <c r="BA21" s="38">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB21" s="47"/>
-      <c r="BC21" s="47"/>
-      <c r="BD21" s="47"/>
-      <c r="BE21" s="47"/>
-      <c r="BF21" s="42">
+      <c r="BB21" s="39"/>
+      <c r="BC21" s="39"/>
+      <c r="BD21" s="39"/>
+      <c r="BE21" s="39"/>
+      <c r="BF21" s="38">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BG21" s="47"/>
-      <c r="BH21" s="45">
+      <c r="BG21" s="39"/>
+      <c r="BH21" s="41">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI21" s="46">
+      <c r="BI21" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ21" s="36"/>
+      <c r="BJ21" s="43"/>
     </row>
     <row r="22" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="23">
@@ -3499,7 +3462,7 @@
       <c r="C22" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="D22" s="42">
+      <c r="D22" s="38">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -3509,12 +3472,12 @@
       <c r="H22" s="39"/>
       <c r="I22" s="39"/>
       <c r="J22" s="39"/>
-      <c r="K22" s="42">
+      <c r="K22" s="38">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L22" s="39"/>
-      <c r="M22" s="42">
+      <c r="M22" s="38">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3522,16 +3485,16 @@
       <c r="O22" s="39"/>
       <c r="P22" s="39"/>
       <c r="Q22" s="39"/>
-      <c r="R22" s="42">
+      <c r="R22" s="38">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S22" s="39"/>
-      <c r="T22" s="42">
+      <c r="T22" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U22" s="47"/>
+      <c r="U22" s="39"/>
       <c r="V22" s="39"/>
       <c r="W22" s="39"/>
       <c r="X22" s="39"/>
@@ -3547,53 +3510,53 @@
       <c r="AH22" s="39"/>
       <c r="AI22" s="39"/>
       <c r="AJ22" s="39"/>
-      <c r="AK22" s="42">
+      <c r="AK22" s="38">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AL22" s="39"/>
       <c r="AM22" s="39"/>
-      <c r="AN22" s="44"/>
+      <c r="AN22" s="40"/>
       <c r="AO22" s="39"/>
-      <c r="AP22" s="44"/>
-      <c r="AQ22" s="42">
+      <c r="AP22" s="40"/>
+      <c r="AQ22" s="38">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AR22" s="39"/>
       <c r="AS22" s="39"/>
       <c r="AT22" s="39"/>
-      <c r="AU22" s="42">
+      <c r="AU22" s="38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV22" s="39"/>
       <c r="AW22" s="39"/>
       <c r="AX22" s="39"/>
-      <c r="AY22" s="44"/>
-      <c r="AZ22" s="49"/>
-      <c r="BA22" s="42">
+      <c r="AY22" s="40"/>
+      <c r="AZ22" s="40"/>
+      <c r="BA22" s="38">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB22" s="44"/>
-      <c r="BC22" s="44"/>
-      <c r="BD22" s="44"/>
-      <c r="BE22" s="44"/>
-      <c r="BF22" s="42">
+      <c r="BB22" s="40"/>
+      <c r="BC22" s="40"/>
+      <c r="BD22" s="40"/>
+      <c r="BE22" s="40"/>
+      <c r="BF22" s="38">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BG22" s="44"/>
-      <c r="BH22" s="45">
+      <c r="BG22" s="40"/>
+      <c r="BH22" s="41">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI22" s="46">
+      <c r="BI22" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ22" s="40"/>
+      <c r="BJ22" s="46"/>
     </row>
     <row r="23" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="23">
@@ -3606,7 +3569,7 @@
       <c r="C23" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="D23" s="42">
+      <c r="D23" s="38">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -3616,12 +3579,12 @@
       <c r="H23" s="39"/>
       <c r="I23" s="39"/>
       <c r="J23" s="39"/>
-      <c r="K23" s="42">
+      <c r="K23" s="38">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L23" s="39"/>
-      <c r="M23" s="42">
+      <c r="M23" s="38">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3629,16 +3592,16 @@
       <c r="O23" s="39"/>
       <c r="P23" s="39"/>
       <c r="Q23" s="39"/>
-      <c r="R23" s="42">
+      <c r="R23" s="38">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S23" s="39"/>
-      <c r="T23" s="42">
+      <c r="T23" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U23" s="47"/>
+      <c r="U23" s="39"/>
       <c r="V23" s="39"/>
       <c r="W23" s="39"/>
       <c r="X23" s="39"/>
@@ -3654,32 +3617,32 @@
       <c r="AH23" s="39"/>
       <c r="AI23" s="39"/>
       <c r="AJ23" s="39"/>
-      <c r="AK23" s="42">
+      <c r="AK23" s="38">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AL23" s="39"/>
       <c r="AM23" s="39"/>
       <c r="AN23" s="39"/>
-      <c r="AO23" s="44"/>
+      <c r="AO23" s="40"/>
       <c r="AP23" s="39"/>
-      <c r="AQ23" s="42">
+      <c r="AQ23" s="38">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AR23" s="39"/>
       <c r="AS23" s="39"/>
       <c r="AT23" s="39"/>
-      <c r="AU23" s="42">
+      <c r="AU23" s="38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV23" s="39"/>
       <c r="AW23" s="39"/>
       <c r="AX23" s="39"/>
-      <c r="AY23" s="44"/>
-      <c r="AZ23" s="44"/>
-      <c r="BA23" s="42">
+      <c r="AY23" s="40"/>
+      <c r="AZ23" s="40"/>
+      <c r="BA23" s="38">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -3687,20 +3650,20 @@
       <c r="BC23" s="39"/>
       <c r="BD23" s="39"/>
       <c r="BE23" s="39"/>
-      <c r="BF23" s="42">
+      <c r="BF23" s="38">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BG23" s="39"/>
-      <c r="BH23" s="45">
+      <c r="BH23" s="41">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI23" s="46">
+      <c r="BI23" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ23" s="41"/>
+      <c r="BJ23" s="44"/>
     </row>
     <row r="24" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="23">
@@ -3713,7 +3676,7 @@
       <c r="C24" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="D24" s="42">
+      <c r="D24" s="38">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -3723,12 +3686,12 @@
       <c r="H24" s="39"/>
       <c r="I24" s="39"/>
       <c r="J24" s="39"/>
-      <c r="K24" s="42">
+      <c r="K24" s="38">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L24" s="39"/>
-      <c r="M24" s="42">
+      <c r="M24" s="38">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3736,16 +3699,16 @@
       <c r="O24" s="39"/>
       <c r="P24" s="39"/>
       <c r="Q24" s="39"/>
-      <c r="R24" s="42">
+      <c r="R24" s="38">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S24" s="39"/>
-      <c r="T24" s="42">
+      <c r="T24" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U24" s="47"/>
+      <c r="U24" s="39"/>
       <c r="V24" s="39"/>
       <c r="W24" s="39"/>
       <c r="X24" s="39"/>
@@ -3761,7 +3724,7 @@
       <c r="AH24" s="39"/>
       <c r="AI24" s="39"/>
       <c r="AJ24" s="39"/>
-      <c r="AK24" s="42">
+      <c r="AK24" s="38">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -3769,24 +3732,24 @@
       <c r="AM24" s="39"/>
       <c r="AN24" s="39"/>
       <c r="AO24" s="39"/>
-      <c r="AP24" s="44"/>
-      <c r="AQ24" s="42">
+      <c r="AP24" s="40"/>
+      <c r="AQ24" s="38">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AR24" s="39"/>
       <c r="AS24" s="39"/>
       <c r="AT24" s="39"/>
-      <c r="AU24" s="42">
+      <c r="AU24" s="38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV24" s="39"/>
       <c r="AW24" s="39"/>
       <c r="AX24" s="39"/>
-      <c r="AY24" s="44"/>
+      <c r="AY24" s="40"/>
       <c r="AZ24" s="39"/>
-      <c r="BA24" s="42">
+      <c r="BA24" s="38">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -3794,20 +3757,20 @@
       <c r="BC24" s="39"/>
       <c r="BD24" s="39"/>
       <c r="BE24" s="39"/>
-      <c r="BF24" s="42">
+      <c r="BF24" s="38">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BG24" s="39"/>
-      <c r="BH24" s="45">
+      <c r="BH24" s="41">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI24" s="46">
+      <c r="BI24" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ24" s="41"/>
+      <c r="BJ24" s="44"/>
     </row>
     <row r="25" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="23">
@@ -3820,7 +3783,7 @@
       <c r="C25" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="D25" s="42">
+      <c r="D25" s="38">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -3830,12 +3793,12 @@
       <c r="H25" s="39"/>
       <c r="I25" s="39"/>
       <c r="J25" s="39"/>
-      <c r="K25" s="42">
+      <c r="K25" s="38">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L25" s="39"/>
-      <c r="M25" s="42">
+      <c r="M25" s="38">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3843,16 +3806,16 @@
       <c r="O25" s="39"/>
       <c r="P25" s="39"/>
       <c r="Q25" s="39"/>
-      <c r="R25" s="42">
+      <c r="R25" s="38">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S25" s="39"/>
-      <c r="T25" s="42">
+      <c r="T25" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U25" s="47"/>
+      <c r="U25" s="39"/>
       <c r="V25" s="39"/>
       <c r="W25" s="39"/>
       <c r="X25" s="39"/>
@@ -3868,7 +3831,7 @@
       <c r="AH25" s="39"/>
       <c r="AI25" s="39"/>
       <c r="AJ25" s="39"/>
-      <c r="AK25" s="42">
+      <c r="AK25" s="38">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -3877,23 +3840,23 @@
       <c r="AN25" s="39"/>
       <c r="AO25" s="39"/>
       <c r="AP25" s="39"/>
-      <c r="AQ25" s="42">
+      <c r="AQ25" s="38">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AR25" s="39"/>
       <c r="AS25" s="39"/>
       <c r="AT25" s="39"/>
-      <c r="AU25" s="42">
+      <c r="AU25" s="38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV25" s="39"/>
       <c r="AW25" s="39"/>
       <c r="AX25" s="39"/>
-      <c r="AY25" s="44"/>
+      <c r="AY25" s="40"/>
       <c r="AZ25" s="39"/>
-      <c r="BA25" s="42">
+      <c r="BA25" s="38">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -3901,20 +3864,20 @@
       <c r="BC25" s="39"/>
       <c r="BD25" s="39"/>
       <c r="BE25" s="39"/>
-      <c r="BF25" s="42">
+      <c r="BF25" s="38">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BG25" s="39"/>
-      <c r="BH25" s="45">
+      <c r="BH25" s="41">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI25" s="46">
+      <c r="BI25" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ25" s="41"/>
+      <c r="BJ25" s="44"/>
     </row>
     <row r="26" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="23">
@@ -3927,7 +3890,7 @@
       <c r="C26" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="D26" s="42">
+      <c r="D26" s="38">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -3937,12 +3900,12 @@
       <c r="H26" s="39"/>
       <c r="I26" s="39"/>
       <c r="J26" s="39"/>
-      <c r="K26" s="42">
+      <c r="K26" s="38">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L26" s="39"/>
-      <c r="M26" s="42">
+      <c r="M26" s="38">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3950,16 +3913,16 @@
       <c r="O26" s="39"/>
       <c r="P26" s="39"/>
       <c r="Q26" s="39"/>
-      <c r="R26" s="42">
+      <c r="R26" s="38">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S26" s="39"/>
-      <c r="T26" s="42">
+      <c r="T26" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U26" s="47"/>
+      <c r="U26" s="39"/>
       <c r="V26" s="39"/>
       <c r="W26" s="39"/>
       <c r="X26" s="39"/>
@@ -3975,7 +3938,7 @@
       <c r="AH26" s="39"/>
       <c r="AI26" s="39"/>
       <c r="AJ26" s="39"/>
-      <c r="AK26" s="42">
+      <c r="AK26" s="38">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -3984,44 +3947,44 @@
       <c r="AN26" s="39"/>
       <c r="AO26" s="39"/>
       <c r="AP26" s="39"/>
-      <c r="AQ26" s="42">
+      <c r="AQ26" s="38">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AR26" s="39"/>
       <c r="AS26" s="39"/>
       <c r="AT26" s="39"/>
-      <c r="AU26" s="42">
+      <c r="AU26" s="38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV26" s="39"/>
       <c r="AW26" s="39"/>
       <c r="AX26" s="39"/>
-      <c r="AY26" s="44"/>
+      <c r="AY26" s="40"/>
       <c r="AZ26" s="39"/>
-      <c r="BA26" s="42">
+      <c r="BA26" s="38">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB26" s="47"/>
-      <c r="BC26" s="47"/>
-      <c r="BD26" s="47"/>
-      <c r="BE26" s="47"/>
-      <c r="BF26" s="42">
+      <c r="BB26" s="39"/>
+      <c r="BC26" s="39"/>
+      <c r="BD26" s="39"/>
+      <c r="BE26" s="39"/>
+      <c r="BF26" s="38">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BG26" s="47"/>
-      <c r="BH26" s="45">
+      <c r="BG26" s="39"/>
+      <c r="BH26" s="41">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI26" s="46">
+      <c r="BI26" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ26" s="41"/>
+      <c r="BJ26" s="44"/>
     </row>
     <row r="27" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="23">
@@ -4034,7 +3997,7 @@
       <c r="C27" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="D27" s="42">
+      <c r="D27" s="38">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -4044,12 +4007,12 @@
       <c r="H27" s="39"/>
       <c r="I27" s="39"/>
       <c r="J27" s="39"/>
-      <c r="K27" s="42">
+      <c r="K27" s="38">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L27" s="39"/>
-      <c r="M27" s="42">
+      <c r="M27" s="38">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4057,16 +4020,16 @@
       <c r="O27" s="39"/>
       <c r="P27" s="39"/>
       <c r="Q27" s="39"/>
-      <c r="R27" s="42">
+      <c r="R27" s="38">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S27" s="39"/>
-      <c r="T27" s="42">
+      <c r="T27" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U27" s="47"/>
+      <c r="U27" s="39"/>
       <c r="V27" s="39"/>
       <c r="W27" s="39"/>
       <c r="X27" s="39"/>
@@ -4082,7 +4045,7 @@
       <c r="AH27" s="39"/>
       <c r="AI27" s="39"/>
       <c r="AJ27" s="39"/>
-      <c r="AK27" s="42">
+      <c r="AK27" s="38">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -4090,24 +4053,24 @@
       <c r="AM27" s="39"/>
       <c r="AN27" s="39"/>
       <c r="AO27" s="39"/>
-      <c r="AP27" s="44"/>
-      <c r="AQ27" s="42">
+      <c r="AP27" s="40"/>
+      <c r="AQ27" s="38">
         <f t="shared" ref="AQ27:AQ35" si="13">AM27-AN27-AO27-AP27</f>
         <v>0</v>
       </c>
       <c r="AR27" s="39"/>
       <c r="AS27" s="39"/>
       <c r="AT27" s="39"/>
-      <c r="AU27" s="42">
+      <c r="AU27" s="38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV27" s="39"/>
       <c r="AW27" s="39"/>
       <c r="AX27" s="39"/>
-      <c r="AY27" s="44"/>
+      <c r="AY27" s="40"/>
       <c r="AZ27" s="39"/>
-      <c r="BA27" s="42">
+      <c r="BA27" s="38">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -4115,20 +4078,20 @@
       <c r="BC27" s="39"/>
       <c r="BD27" s="39"/>
       <c r="BE27" s="39"/>
-      <c r="BF27" s="42">
+      <c r="BF27" s="38">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BG27" s="39"/>
-      <c r="BH27" s="45">
+      <c r="BH27" s="41">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI27" s="46">
+      <c r="BI27" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ27" s="41"/>
+      <c r="BJ27" s="44"/>
     </row>
     <row r="28" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="23">
@@ -4141,7 +4104,7 @@
       <c r="C28" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="D28" s="42">
+      <c r="D28" s="38">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -4151,12 +4114,12 @@
       <c r="H28" s="39"/>
       <c r="I28" s="39"/>
       <c r="J28" s="39"/>
-      <c r="K28" s="42">
+      <c r="K28" s="38">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L28" s="39"/>
-      <c r="M28" s="42">
+      <c r="M28" s="38">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4164,16 +4127,16 @@
       <c r="O28" s="39"/>
       <c r="P28" s="39"/>
       <c r="Q28" s="39"/>
-      <c r="R28" s="42">
+      <c r="R28" s="38">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S28" s="39"/>
-      <c r="T28" s="42">
+      <c r="T28" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U28" s="47"/>
+      <c r="U28" s="39"/>
       <c r="V28" s="39"/>
       <c r="W28" s="39"/>
       <c r="X28" s="39"/>
@@ -4189,53 +4152,53 @@
       <c r="AH28" s="39"/>
       <c r="AI28" s="39"/>
       <c r="AJ28" s="39"/>
-      <c r="AK28" s="42">
+      <c r="AK28" s="38">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AL28" s="39"/>
-      <c r="AM28" s="44"/>
+      <c r="AM28" s="40"/>
       <c r="AN28" s="39"/>
       <c r="AO28" s="39"/>
-      <c r="AP28" s="44"/>
-      <c r="AQ28" s="42">
+      <c r="AP28" s="40"/>
+      <c r="AQ28" s="38">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AR28" s="39"/>
       <c r="AS28" s="39"/>
       <c r="AT28" s="39"/>
-      <c r="AU28" s="42">
+      <c r="AU28" s="38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV28" s="39"/>
       <c r="AW28" s="39"/>
       <c r="AX28" s="39"/>
-      <c r="AY28" s="44"/>
-      <c r="AZ28" s="44"/>
-      <c r="BA28" s="42">
+      <c r="AY28" s="40"/>
+      <c r="AZ28" s="40"/>
+      <c r="BA28" s="38">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BB28" s="47"/>
-      <c r="BC28" s="47"/>
-      <c r="BD28" s="47"/>
-      <c r="BE28" s="47"/>
-      <c r="BF28" s="42">
+      <c r="BB28" s="39"/>
+      <c r="BC28" s="39"/>
+      <c r="BD28" s="39"/>
+      <c r="BE28" s="39"/>
+      <c r="BF28" s="38">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BG28" s="47"/>
-      <c r="BH28" s="45">
+      <c r="BG28" s="39"/>
+      <c r="BH28" s="41">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI28" s="46">
+      <c r="BI28" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ28" s="41"/>
+      <c r="BJ28" s="44"/>
     </row>
     <row r="29" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="23">
@@ -4248,7 +4211,7 @@
       <c r="C29" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="D29" s="42">
+      <c r="D29" s="38">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -4258,12 +4221,12 @@
       <c r="H29" s="39"/>
       <c r="I29" s="39"/>
       <c r="J29" s="39"/>
-      <c r="K29" s="42">
+      <c r="K29" s="38">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L29" s="39"/>
-      <c r="M29" s="42">
+      <c r="M29" s="38">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4271,16 +4234,16 @@
       <c r="O29" s="39"/>
       <c r="P29" s="39"/>
       <c r="Q29" s="39"/>
-      <c r="R29" s="42">
+      <c r="R29" s="38">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S29" s="39"/>
-      <c r="T29" s="42">
+      <c r="T29" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U29" s="47"/>
+      <c r="U29" s="39"/>
       <c r="V29" s="39"/>
       <c r="W29" s="39"/>
       <c r="X29" s="39"/>
@@ -4296,32 +4259,32 @@
       <c r="AH29" s="39"/>
       <c r="AI29" s="39"/>
       <c r="AJ29" s="39"/>
-      <c r="AK29" s="42">
+      <c r="AK29" s="38">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AL29" s="39"/>
-      <c r="AM29" s="44"/>
-      <c r="AN29" s="44"/>
+      <c r="AM29" s="40"/>
+      <c r="AN29" s="40"/>
       <c r="AO29" s="39"/>
       <c r="AP29" s="39"/>
-      <c r="AQ29" s="42">
+      <c r="AQ29" s="38">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AR29" s="39"/>
       <c r="AS29" s="39"/>
       <c r="AT29" s="39"/>
-      <c r="AU29" s="42">
+      <c r="AU29" s="38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV29" s="39"/>
       <c r="AW29" s="39"/>
       <c r="AX29" s="39"/>
-      <c r="AY29" s="44"/>
+      <c r="AY29" s="40"/>
       <c r="AZ29" s="39"/>
-      <c r="BA29" s="42">
+      <c r="BA29" s="38">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -4329,20 +4292,20 @@
       <c r="BC29" s="39"/>
       <c r="BD29" s="39"/>
       <c r="BE29" s="39"/>
-      <c r="BF29" s="42">
+      <c r="BF29" s="38">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BG29" s="39"/>
-      <c r="BH29" s="45">
+      <c r="BH29" s="41">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI29" s="46">
+      <c r="BI29" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ29" s="41"/>
+      <c r="BJ29" s="44"/>
     </row>
     <row r="30" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="23">
@@ -4355,7 +4318,7 @@
       <c r="C30" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="D30" s="42">
+      <c r="D30" s="38">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -4365,12 +4328,12 @@
       <c r="H30" s="39"/>
       <c r="I30" s="39"/>
       <c r="J30" s="39"/>
-      <c r="K30" s="42">
+      <c r="K30" s="38">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L30" s="39"/>
-      <c r="M30" s="42">
+      <c r="M30" s="38">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4378,16 +4341,16 @@
       <c r="O30" s="39"/>
       <c r="P30" s="39"/>
       <c r="Q30" s="39"/>
-      <c r="R30" s="42">
+      <c r="R30" s="38">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S30" s="39"/>
-      <c r="T30" s="42">
+      <c r="T30" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U30" s="47"/>
+      <c r="U30" s="39"/>
       <c r="V30" s="39"/>
       <c r="W30" s="39"/>
       <c r="X30" s="39"/>
@@ -4403,7 +4366,7 @@
       <c r="AH30" s="39"/>
       <c r="AI30" s="39"/>
       <c r="AJ30" s="39"/>
-      <c r="AK30" s="42">
+      <c r="AK30" s="38">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -4412,23 +4375,23 @@
       <c r="AN30" s="39"/>
       <c r="AO30" s="39"/>
       <c r="AP30" s="39"/>
-      <c r="AQ30" s="42">
+      <c r="AQ30" s="38">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AR30" s="39"/>
       <c r="AS30" s="39"/>
       <c r="AT30" s="39"/>
-      <c r="AU30" s="42">
+      <c r="AU30" s="38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV30" s="39"/>
       <c r="AW30" s="39"/>
       <c r="AX30" s="39"/>
-      <c r="AY30" s="44"/>
+      <c r="AY30" s="40"/>
       <c r="AZ30" s="39"/>
-      <c r="BA30" s="42">
+      <c r="BA30" s="38">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -4436,20 +4399,20 @@
       <c r="BC30" s="39"/>
       <c r="BD30" s="39"/>
       <c r="BE30" s="39"/>
-      <c r="BF30" s="42">
+      <c r="BF30" s="38">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BG30" s="39"/>
-      <c r="BH30" s="45">
+      <c r="BH30" s="41">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI30" s="46">
+      <c r="BI30" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ30" s="41"/>
+      <c r="BJ30" s="44"/>
     </row>
     <row r="31" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="23">
@@ -4462,7 +4425,7 @@
       <c r="C31" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="D31" s="42">
+      <c r="D31" s="38">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -4472,12 +4435,12 @@
       <c r="H31" s="39"/>
       <c r="I31" s="39"/>
       <c r="J31" s="39"/>
-      <c r="K31" s="42">
+      <c r="K31" s="38">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L31" s="39"/>
-      <c r="M31" s="42">
+      <c r="M31" s="38">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4485,16 +4448,16 @@
       <c r="O31" s="39"/>
       <c r="P31" s="39"/>
       <c r="Q31" s="39"/>
-      <c r="R31" s="42">
+      <c r="R31" s="38">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S31" s="39"/>
-      <c r="T31" s="42">
+      <c r="T31" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U31" s="47"/>
+      <c r="U31" s="39"/>
       <c r="V31" s="39"/>
       <c r="W31" s="39"/>
       <c r="X31" s="39"/>
@@ -4510,32 +4473,32 @@
       <c r="AH31" s="39"/>
       <c r="AI31" s="39"/>
       <c r="AJ31" s="39"/>
-      <c r="AK31" s="42">
+      <c r="AK31" s="38">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AL31" s="47"/>
+      <c r="AL31" s="39"/>
       <c r="AM31" s="39"/>
       <c r="AN31" s="39"/>
       <c r="AO31" s="39"/>
       <c r="AP31" s="39"/>
-      <c r="AQ31" s="42">
+      <c r="AQ31" s="38">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AR31" s="39"/>
       <c r="AS31" s="39"/>
       <c r="AT31" s="39"/>
-      <c r="AU31" s="42">
+      <c r="AU31" s="38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV31" s="39"/>
       <c r="AW31" s="39"/>
       <c r="AX31" s="39"/>
-      <c r="AY31" s="44"/>
-      <c r="AZ31" s="44"/>
-      <c r="BA31" s="42">
+      <c r="AY31" s="40"/>
+      <c r="AZ31" s="40"/>
+      <c r="BA31" s="38">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -4543,20 +4506,20 @@
       <c r="BC31" s="39"/>
       <c r="BD31" s="39"/>
       <c r="BE31" s="39"/>
-      <c r="BF31" s="42">
+      <c r="BF31" s="38">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BG31" s="39"/>
-      <c r="BH31" s="45">
+      <c r="BH31" s="41">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI31" s="46">
+      <c r="BI31" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ31" s="41"/>
+      <c r="BJ31" s="44"/>
     </row>
     <row r="32" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="23">
@@ -4569,7 +4532,7 @@
       <c r="C32" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="D32" s="42">
+      <c r="D32" s="38">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -4579,12 +4542,12 @@
       <c r="H32" s="39"/>
       <c r="I32" s="39"/>
       <c r="J32" s="39"/>
-      <c r="K32" s="42">
+      <c r="K32" s="38">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L32" s="39"/>
-      <c r="M32" s="42">
+      <c r="M32" s="38">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4592,16 +4555,16 @@
       <c r="O32" s="39"/>
       <c r="P32" s="39"/>
       <c r="Q32" s="39"/>
-      <c r="R32" s="42">
+      <c r="R32" s="38">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S32" s="39"/>
-      <c r="T32" s="42">
+      <c r="T32" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U32" s="47"/>
+      <c r="U32" s="39"/>
       <c r="V32" s="39"/>
       <c r="W32" s="39"/>
       <c r="X32" s="39"/>
@@ -4617,32 +4580,32 @@
       <c r="AH32" s="39"/>
       <c r="AI32" s="39"/>
       <c r="AJ32" s="39"/>
-      <c r="AK32" s="42">
+      <c r="AK32" s="38">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AL32" s="47"/>
-      <c r="AM32" s="44"/>
+      <c r="AL32" s="39"/>
+      <c r="AM32" s="40"/>
       <c r="AN32" s="39"/>
       <c r="AO32" s="39"/>
       <c r="AP32" s="39"/>
-      <c r="AQ32" s="42">
+      <c r="AQ32" s="38">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AR32" s="39"/>
       <c r="AS32" s="39"/>
       <c r="AT32" s="39"/>
-      <c r="AU32" s="42">
+      <c r="AU32" s="38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV32" s="39"/>
       <c r="AW32" s="39"/>
       <c r="AX32" s="39"/>
-      <c r="AY32" s="44"/>
+      <c r="AY32" s="40"/>
       <c r="AZ32" s="39"/>
-      <c r="BA32" s="42">
+      <c r="BA32" s="38">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -4650,20 +4613,20 @@
       <c r="BC32" s="39"/>
       <c r="BD32" s="39"/>
       <c r="BE32" s="39"/>
-      <c r="BF32" s="42">
+      <c r="BF32" s="38">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BG32" s="39"/>
-      <c r="BH32" s="45">
+      <c r="BH32" s="41">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI32" s="46">
+      <c r="BI32" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ32" s="36"/>
+      <c r="BJ32" s="43"/>
     </row>
     <row r="33" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="23">
@@ -4676,7 +4639,7 @@
       <c r="C33" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="42">
+      <c r="D33" s="38">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -4686,12 +4649,12 @@
       <c r="H33" s="39"/>
       <c r="I33" s="39"/>
       <c r="J33" s="39"/>
-      <c r="K33" s="42">
+      <c r="K33" s="38">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L33" s="39"/>
-      <c r="M33" s="42">
+      <c r="M33" s="38">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4699,16 +4662,16 @@
       <c r="O33" s="39"/>
       <c r="P33" s="39"/>
       <c r="Q33" s="39"/>
-      <c r="R33" s="42">
+      <c r="R33" s="38">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S33" s="39"/>
-      <c r="T33" s="42">
+      <c r="T33" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U33" s="47"/>
+      <c r="U33" s="39"/>
       <c r="V33" s="39"/>
       <c r="W33" s="39"/>
       <c r="X33" s="39"/>
@@ -4724,32 +4687,32 @@
       <c r="AH33" s="39"/>
       <c r="AI33" s="39"/>
       <c r="AJ33" s="39"/>
-      <c r="AK33" s="42">
+      <c r="AK33" s="38">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AL33" s="47"/>
-      <c r="AM33" s="44"/>
+      <c r="AL33" s="39"/>
+      <c r="AM33" s="40"/>
       <c r="AN33" s="39"/>
       <c r="AO33" s="39"/>
       <c r="AP33" s="39"/>
-      <c r="AQ33" s="42">
+      <c r="AQ33" s="38">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AR33" s="39"/>
       <c r="AS33" s="39"/>
       <c r="AT33" s="39"/>
-      <c r="AU33" s="42">
+      <c r="AU33" s="38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV33" s="39"/>
       <c r="AW33" s="39"/>
       <c r="AX33" s="39"/>
-      <c r="AY33" s="44"/>
+      <c r="AY33" s="40"/>
       <c r="AZ33" s="39"/>
-      <c r="BA33" s="42">
+      <c r="BA33" s="38">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -4757,20 +4720,20 @@
       <c r="BC33" s="39"/>
       <c r="BD33" s="39"/>
       <c r="BE33" s="39"/>
-      <c r="BF33" s="42">
+      <c r="BF33" s="38">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BG33" s="39"/>
-      <c r="BH33" s="45">
+      <c r="BH33" s="41">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI33" s="46">
+      <c r="BI33" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ33" s="36"/>
+      <c r="BJ33" s="43"/>
     </row>
     <row r="34" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="23">
@@ -4783,7 +4746,7 @@
       <c r="C34" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="D34" s="42">
+      <c r="D34" s="38">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -4793,12 +4756,12 @@
       <c r="H34" s="39"/>
       <c r="I34" s="39"/>
       <c r="J34" s="39"/>
-      <c r="K34" s="42">
+      <c r="K34" s="38">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L34" s="39"/>
-      <c r="M34" s="42">
+      <c r="M34" s="38">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4806,16 +4769,16 @@
       <c r="O34" s="39"/>
       <c r="P34" s="39"/>
       <c r="Q34" s="39"/>
-      <c r="R34" s="42">
+      <c r="R34" s="38">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S34" s="39"/>
-      <c r="T34" s="42">
+      <c r="T34" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U34" s="47"/>
+      <c r="U34" s="39"/>
       <c r="V34" s="39"/>
       <c r="W34" s="39"/>
       <c r="X34" s="39"/>
@@ -4831,32 +4794,32 @@
       <c r="AH34" s="39"/>
       <c r="AI34" s="39"/>
       <c r="AJ34" s="39"/>
-      <c r="AK34" s="42">
+      <c r="AK34" s="38">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AL34" s="47"/>
-      <c r="AM34" s="44"/>
+      <c r="AL34" s="39"/>
+      <c r="AM34" s="40"/>
       <c r="AN34" s="39"/>
       <c r="AO34" s="39"/>
       <c r="AP34" s="39"/>
-      <c r="AQ34" s="42">
+      <c r="AQ34" s="38">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AR34" s="39"/>
       <c r="AS34" s="39"/>
       <c r="AT34" s="39"/>
-      <c r="AU34" s="42">
+      <c r="AU34" s="38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV34" s="39"/>
       <c r="AW34" s="39"/>
       <c r="AX34" s="39"/>
-      <c r="AY34" s="44"/>
+      <c r="AY34" s="40"/>
       <c r="AZ34" s="39"/>
-      <c r="BA34" s="42">
+      <c r="BA34" s="38">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -4864,20 +4827,20 @@
       <c r="BC34" s="39"/>
       <c r="BD34" s="39"/>
       <c r="BE34" s="39"/>
-      <c r="BF34" s="42">
+      <c r="BF34" s="38">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BG34" s="39"/>
-      <c r="BH34" s="45">
+      <c r="BH34" s="41">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI34" s="46">
+      <c r="BI34" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ34" s="36"/>
+      <c r="BJ34" s="43"/>
     </row>
     <row r="35" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="23">
@@ -4886,7 +4849,7 @@
       </c>
       <c r="B35" s="19"/>
       <c r="C35" s="19"/>
-      <c r="D35" s="42">
+      <c r="D35" s="38">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -4896,12 +4859,12 @@
       <c r="H35" s="39"/>
       <c r="I35" s="39"/>
       <c r="J35" s="39"/>
-      <c r="K35" s="42">
+      <c r="K35" s="38">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L35" s="39"/>
-      <c r="M35" s="42">
+      <c r="M35" s="38">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4909,16 +4872,16 @@
       <c r="O35" s="39"/>
       <c r="P35" s="39"/>
       <c r="Q35" s="39"/>
-      <c r="R35" s="42">
+      <c r="R35" s="38">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S35" s="39"/>
-      <c r="T35" s="42">
+      <c r="T35" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U35" s="47"/>
+      <c r="U35" s="39"/>
       <c r="V35" s="39"/>
       <c r="W35" s="39"/>
       <c r="X35" s="39"/>
@@ -4934,32 +4897,32 @@
       <c r="AH35" s="39"/>
       <c r="AI35" s="39"/>
       <c r="AJ35" s="39"/>
-      <c r="AK35" s="42">
+      <c r="AK35" s="38">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AL35" s="47"/>
-      <c r="AM35" s="44"/>
+      <c r="AL35" s="39"/>
+      <c r="AM35" s="40"/>
       <c r="AN35" s="39"/>
       <c r="AO35" s="39"/>
       <c r="AP35" s="39"/>
-      <c r="AQ35" s="42">
+      <c r="AQ35" s="38">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AR35" s="39"/>
       <c r="AS35" s="39"/>
       <c r="AT35" s="39"/>
-      <c r="AU35" s="42">
+      <c r="AU35" s="38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV35" s="39"/>
       <c r="AW35" s="39"/>
       <c r="AX35" s="39"/>
-      <c r="AY35" s="44"/>
+      <c r="AY35" s="40"/>
       <c r="AZ35" s="39"/>
-      <c r="BA35" s="42">
+      <c r="BA35" s="38">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -4967,20 +4930,20 @@
       <c r="BC35" s="39"/>
       <c r="BD35" s="39"/>
       <c r="BE35" s="39"/>
-      <c r="BF35" s="42">
+      <c r="BF35" s="38">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BG35" s="39"/>
-      <c r="BH35" s="45">
+      <c r="BH35" s="41">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BI35" s="46">
+      <c r="BI35" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BJ35" s="36"/>
+      <c r="BJ35" s="43"/>
     </row>
     <row r="36" spans="1:62" s="18" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="23">
@@ -4991,239 +4954,239 @@
         <v>79</v>
       </c>
       <c r="C36" s="36"/>
-      <c r="D36" s="50">
+      <c r="D36" s="47">
         <f t="shared" ref="D36:BI36" si="14">SUM(D5:D35)</f>
         <v>0</v>
       </c>
-      <c r="E36" s="50">
+      <c r="E36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="F36" s="50">
+      <c r="F36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G36" s="50">
+      <c r="G36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="H36" s="50">
+      <c r="H36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="I36" s="50">
+      <c r="I36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="J36" s="50">
+      <c r="J36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="K36" s="50">
+      <c r="K36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="L36" s="50">
+      <c r="L36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="M36" s="50">
+      <c r="M36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="N36" s="50">
+      <c r="N36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="O36" s="50">
+      <c r="O36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="P36" s="50">
+      <c r="P36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="Q36" s="50">
+      <c r="Q36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="R36" s="50">
+      <c r="R36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="S36" s="50">
+      <c r="S36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="T36" s="50">
+      <c r="T36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="U36" s="50">
+      <c r="U36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="V36" s="50">
+      <c r="V36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="W36" s="50">
+      <c r="W36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="X36" s="50">
+      <c r="X36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="Y36" s="50">
+      <c r="Y36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="Z36" s="50">
+      <c r="Z36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AA36" s="50">
+      <c r="AA36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AB36" s="50">
+      <c r="AB36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AC36" s="50">
+      <c r="AC36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AD36" s="50">
+      <c r="AD36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AE36" s="50">
+      <c r="AE36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AF36" s="50">
+      <c r="AF36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AG36" s="50">
+      <c r="AG36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AH36" s="50">
+      <c r="AH36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AI36" s="50">
+      <c r="AI36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AJ36" s="50">
+      <c r="AJ36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AK36" s="50">
+      <c r="AK36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AL36" s="50">
+      <c r="AL36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AM36" s="50">
+      <c r="AM36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AN36" s="50">
+      <c r="AN36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AO36" s="50">
+      <c r="AO36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AP36" s="50">
+      <c r="AP36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AQ36" s="50">
+      <c r="AQ36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AR36" s="50">
+      <c r="AR36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AS36" s="50">
+      <c r="AS36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AT36" s="50">
+      <c r="AT36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AU36" s="50">
+      <c r="AU36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AV36" s="50">
+      <c r="AV36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AW36" s="50">
+      <c r="AW36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AX36" s="50">
+      <c r="AX36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AY36" s="50">
+      <c r="AY36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AZ36" s="50">
+      <c r="AZ36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BA36" s="50">
+      <c r="BA36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BB36" s="50">
+      <c r="BB36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BC36" s="50">
+      <c r="BC36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BD36" s="50">
+      <c r="BD36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BE36" s="50">
+      <c r="BE36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BF36" s="50">
+      <c r="BF36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BG36" s="50">
+      <c r="BG36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BH36" s="50">
+      <c r="BH36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BI36" s="50">
+      <c r="BI36" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BJ36" s="36"/>
+      <c r="BJ36" s="43"/>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A37" s="20"/>
@@ -15683,7 +15646,7 @@
     <mergeCell ref="V3:V4"/>
     <mergeCell ref="AC3:AC4"/>
   </mergeCells>
-  <phoneticPr fontId="23" type="noConversion"/>
+  <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -15708,23 +15671,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="69"/>
-      <c r="I1" s="69"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
     </row>
     <row r="2" spans="1:9" s="2" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="70" t="s">
+      <c r="A2" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="70"/>
+      <c r="B2" s="65"/>
       <c r="C2" s="3" t="s">
         <v>81</v>
       </c>
@@ -16415,10 +16378,10 @@
       <c r="I33" s="11"/>
     </row>
     <row r="34" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="71" t="s">
+      <c r="A34" s="66" t="s">
         <v>85</v>
       </c>
-      <c r="B34" s="71"/>
+      <c r="B34" s="66"/>
       <c r="C34" s="9"/>
       <c r="D34" s="9">
         <f>SUM(D3:D33)</f>
@@ -16448,7 +16411,7 @@
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A34:B34"/>
   </mergeCells>
-  <phoneticPr fontId="23" type="noConversion"/>
+  <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
